--- a/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
+++ b/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="4" activeTab="8"/>
+    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="4" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="修订记录" sheetId="1" r:id="rId1"/>
@@ -1024,7 +1024,7 @@
     <t>客户资产负债表</t>
   </si>
   <si>
-    <t>CUST_ASSE_LIAB</t>
+    <t>DWS_CUST_ASSE_LIAB</t>
   </si>
   <si>
     <t>归属机构</t>
@@ -1099,7 +1099,7 @@
     <t>客户等级信息表</t>
   </si>
   <si>
-    <t>CUST_LVL_INFO</t>
+    <t>DWS_CUST_LVL_INFO</t>
   </si>
   <si>
     <t>DATA_DT</t>
@@ -3070,7 +3070,7 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="176" fontId="52" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3169,9 +3169,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4414,273 +4411,273 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="19.1018518518519" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="5.44444444444444" style="113" customWidth="1"/>
-    <col min="2" max="2" width="10.6666666666667" style="113" customWidth="1"/>
-    <col min="3" max="3" width="8.23148148148148" style="113" customWidth="1"/>
-    <col min="4" max="4" width="6.88888888888889" style="113" customWidth="1"/>
-    <col min="5" max="5" width="8.36111111111111" style="113" customWidth="1"/>
-    <col min="6" max="6" width="54.3611111111111" style="113" customWidth="1"/>
-    <col min="7" max="7" width="6.88888888888889" style="113" customWidth="1"/>
-    <col min="8" max="8" width="6.76851851851852" style="113" customWidth="1"/>
-    <col min="9" max="9" width="8.76851851851852" style="113" customWidth="1"/>
-    <col min="10" max="26" width="19.1018518518519" style="113"/>
+    <col min="1" max="1" width="5.44444444444444" style="112" customWidth="1"/>
+    <col min="2" max="2" width="10.6666666666667" style="112" customWidth="1"/>
+    <col min="3" max="3" width="8.23148148148148" style="112" customWidth="1"/>
+    <col min="4" max="4" width="6.88888888888889" style="112" customWidth="1"/>
+    <col min="5" max="5" width="8.36111111111111" style="112" customWidth="1"/>
+    <col min="6" max="6" width="54.3611111111111" style="112" customWidth="1"/>
+    <col min="7" max="7" width="6.88888888888889" style="112" customWidth="1"/>
+    <col min="8" max="8" width="6.76851851851852" style="112" customWidth="1"/>
+    <col min="9" max="9" width="8.76851851851852" style="112" customWidth="1"/>
+    <col min="10" max="26" width="19.1018518518519" style="112"/>
   </cols>
   <sheetData>
-    <row r="1" s="110" customFormat="1" ht="29.25" customHeight="1" spans="1:9">
-      <c r="A1" s="114"/>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-    </row>
-    <row r="2" s="110" customFormat="1" ht="18.15" spans="1:9">
-      <c r="A2" s="115" t="s">
+    <row r="1" s="109" customFormat="1" ht="29.25" customHeight="1" spans="1:9">
+      <c r="A1" s="113"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+    </row>
+    <row r="2" s="109" customFormat="1" ht="18.15" spans="1:9">
+      <c r="A2" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-    </row>
-    <row r="3" s="110" customFormat="1" ht="12.75" spans="1:9">
-      <c r="A3" s="116"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-    </row>
-    <row r="4" s="110" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A4" s="118" t="s">
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+    </row>
+    <row r="3" s="109" customFormat="1" ht="12.75" spans="1:9">
+      <c r="A3" s="115"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+    </row>
+    <row r="4" s="109" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A4" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="120" t="s">
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="121"/>
-    </row>
-    <row r="5" s="110" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A5" s="122"/>
-      <c r="B5" s="123"/>
-      <c r="C5" s="123"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="124" t="s">
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="120"/>
+    </row>
+    <row r="5" s="109" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A5" s="121"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="125"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="126"/>
-    </row>
-    <row r="6" s="110" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A6" s="122"/>
-      <c r="B6" s="123"/>
-      <c r="C6" s="123"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="125" t="s">
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="125"/>
+    </row>
+    <row r="6" s="109" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A6" s="121"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="125"/>
-      <c r="G6" s="125"/>
-      <c r="H6" s="125"/>
-      <c r="I6" s="126"/>
-    </row>
-    <row r="7" s="110" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A7" s="127"/>
-      <c r="B7" s="128"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="129" t="s">
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="125"/>
+    </row>
+    <row r="7" s="109" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A7" s="126"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="130"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="131"/>
-    </row>
-    <row r="8" s="110" customFormat="1" ht="21" customHeight="1" spans="1:9">
-      <c r="A8" s="132" t="s">
+      <c r="F7" s="129"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="130"/>
+    </row>
+    <row r="8" s="109" customFormat="1" ht="21" customHeight="1" spans="1:9">
+      <c r="A8" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="132" t="s">
+      <c r="B8" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="132" t="s">
+      <c r="C8" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="132" t="s">
+      <c r="D8" s="131" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="132" t="s">
+      <c r="E8" s="131" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132" t="s">
+      <c r="F8" s="131"/>
+      <c r="G8" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="132" t="s">
+      <c r="H8" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="132" t="s">
+      <c r="I8" s="131" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" s="111" customFormat="1" ht="16.95" customHeight="1" spans="1:9">
-      <c r="A9" s="133"/>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="137"/>
-      <c r="F9" s="137"/>
-      <c r="G9" s="135"/>
-      <c r="H9" s="135"/>
-      <c r="I9" s="135"/>
-    </row>
-    <row r="10" s="111" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A10" s="133"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="135"/>
-      <c r="D10" s="136"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="137"/>
-      <c r="G10" s="135"/>
-      <c r="H10" s="135"/>
-      <c r="I10" s="135"/>
-    </row>
-    <row r="11" s="111" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A11" s="133"/>
-      <c r="B11" s="134"/>
-      <c r="C11" s="135"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="135"/>
-      <c r="H11" s="135"/>
-      <c r="I11" s="135"/>
-    </row>
-    <row r="12" s="111" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A12" s="133"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="135"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="137"/>
-      <c r="F12" s="137"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="135"/>
-      <c r="I12" s="135"/>
-    </row>
-    <row r="13" s="111" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A13" s="133"/>
-      <c r="B13" s="134"/>
-      <c r="C13" s="135"/>
-      <c r="D13" s="136"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="135"/>
-    </row>
-    <row r="14" s="111" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A14" s="133"/>
-      <c r="B14" s="134"/>
-      <c r="C14" s="135"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="137"/>
-      <c r="G14" s="135"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="135"/>
-    </row>
-    <row r="15" s="111" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A15" s="133"/>
-      <c r="B15" s="134"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="135"/>
-    </row>
-    <row r="16" s="111" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A16" s="133"/>
-      <c r="B16" s="134"/>
-      <c r="C16" s="135"/>
-      <c r="D16" s="136"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="137"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="135"/>
-    </row>
-    <row r="17" s="111" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A17" s="133"/>
-      <c r="B17" s="134"/>
-      <c r="C17" s="135"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="135"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="135"/>
-    </row>
-    <row r="18" s="111" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A18" s="133"/>
-      <c r="B18" s="134"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="136"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="137"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="135"/>
-    </row>
-    <row r="19" s="111" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A19" s="133"/>
-      <c r="B19" s="134"/>
-      <c r="C19" s="135"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="137"/>
-      <c r="F19" s="137"/>
-      <c r="G19" s="135"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="135"/>
-    </row>
-    <row r="20" s="111" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A20" s="133"/>
-      <c r="B20" s="134"/>
-      <c r="C20" s="135"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="137"/>
-      <c r="G20" s="135"/>
-      <c r="H20" s="135"/>
-      <c r="I20" s="135"/>
-    </row>
-    <row r="21" s="112" customFormat="1" ht="12" spans="1:9">
-      <c r="A21" s="138"/>
-    </row>
-    <row r="22" s="112" customFormat="1" ht="12" spans="1:9">
-      <c r="A22" s="138"/>
-    </row>
-    <row r="23" s="112" customFormat="1" ht="12"/>
+    <row r="9" s="110" customFormat="1" ht="16.95" customHeight="1" spans="1:9">
+      <c r="A9" s="132"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="134"/>
+      <c r="D9" s="135"/>
+      <c r="E9" s="136"/>
+      <c r="F9" s="136"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="134"/>
+      <c r="I9" s="134"/>
+    </row>
+    <row r="10" s="110" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A10" s="132"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="134"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="136"/>
+      <c r="F10" s="136"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="134"/>
+    </row>
+    <row r="11" s="110" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A11" s="132"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="136"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="134"/>
+      <c r="H11" s="134"/>
+      <c r="I11" s="134"/>
+    </row>
+    <row r="12" s="110" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A12" s="132"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="134"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="134"/>
+      <c r="H12" s="134"/>
+      <c r="I12" s="134"/>
+    </row>
+    <row r="13" s="110" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A13" s="132"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="136"/>
+      <c r="F13" s="136"/>
+      <c r="G13" s="134"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="134"/>
+    </row>
+    <row r="14" s="110" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A14" s="132"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="134"/>
+      <c r="D14" s="135"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="134"/>
+      <c r="I14" s="134"/>
+    </row>
+    <row r="15" s="110" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A15" s="132"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="136"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="134"/>
+    </row>
+    <row r="16" s="110" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A16" s="132"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="134"/>
+      <c r="D16" s="135"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="136"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="134"/>
+    </row>
+    <row r="17" s="110" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A17" s="132"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="134"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+    </row>
+    <row r="18" s="110" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A18" s="132"/>
+      <c r="B18" s="133"/>
+      <c r="C18" s="134"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="136"/>
+      <c r="F18" s="136"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="134"/>
+    </row>
+    <row r="19" s="110" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A19" s="132"/>
+      <c r="B19" s="133"/>
+      <c r="C19" s="134"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="136"/>
+      <c r="F19" s="136"/>
+      <c r="G19" s="134"/>
+      <c r="H19" s="134"/>
+      <c r="I19" s="134"/>
+    </row>
+    <row r="20" s="110" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A20" s="132"/>
+      <c r="B20" s="133"/>
+      <c r="C20" s="134"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="134"/>
+      <c r="H20" s="134"/>
+      <c r="I20" s="134"/>
+    </row>
+    <row r="21" s="111" customFormat="1" ht="12" spans="1:9">
+      <c r="A21" s="137"/>
+    </row>
+    <row r="22" s="111" customFormat="1" ht="12" spans="1:9">
+      <c r="A22" s="137"/>
+    </row>
+    <row r="23" s="111" customFormat="1" ht="12"/>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="20">
@@ -4845,14 +4842,14 @@
     </row>
     <row r="6" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A6" s="23"/>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="35" t="s">
+      <c r="C6" s="64"/>
+      <c r="D6" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="24" t="s">
         <v>138</v>
       </c>
       <c r="F6" s="26"/>
@@ -4869,14 +4866,14 @@
     </row>
     <row r="7" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="23"/>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="35" t="s">
+      <c r="C7" s="64"/>
+      <c r="D7" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="24" t="s">
         <v>210</v>
       </c>
       <c r="F7" s="26"/>
@@ -4893,14 +4890,14 @@
     </row>
     <row r="8" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="23"/>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="C8" s="65"/>
-      <c r="D8" s="35" t="s">
+      <c r="C8" s="64"/>
+      <c r="D8" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="24" t="s">
         <v>146</v>
       </c>
       <c r="F8" s="26"/>
@@ -4917,14 +4914,14 @@
     </row>
     <row r="9" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="23"/>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="35" t="s">
+      <c r="C9" s="64"/>
+      <c r="D9" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="24" t="s">
         <v>213</v>
       </c>
       <c r="F9" s="26"/>
@@ -4941,14 +4938,14 @@
     </row>
     <row r="10" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="23"/>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="35" t="s">
+      <c r="C10" s="64"/>
+      <c r="D10" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="24" t="s">
         <v>215</v>
       </c>
       <c r="F10" s="26"/>
@@ -4965,13 +4962,13 @@
     </row>
     <row r="11" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="23"/>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="24" t="s">
         <v>218</v>
       </c>
       <c r="F11" s="26"/>
@@ -4988,14 +4985,14 @@
     </row>
     <row r="12" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="23"/>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="35" t="s">
+      <c r="C12" s="64"/>
+      <c r="D12" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="24" t="s">
         <v>220</v>
       </c>
       <c r="F12" s="26"/>
@@ -5012,14 +5009,14 @@
     </row>
     <row r="13" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="23"/>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="35" t="s">
+      <c r="C13" s="64"/>
+      <c r="D13" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="24" t="s">
         <v>222</v>
       </c>
       <c r="F13" s="26"/>
@@ -5036,14 +5033,14 @@
     </row>
     <row r="14" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="23"/>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="65"/>
-      <c r="D14" s="35" t="s">
+      <c r="C14" s="64"/>
+      <c r="D14" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="24" t="s">
         <v>224</v>
       </c>
       <c r="F14" s="26"/>
@@ -5060,14 +5057,14 @@
     </row>
     <row r="15" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="23"/>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="C15" s="65"/>
-      <c r="D15" s="35" t="s">
+      <c r="C15" s="64"/>
+      <c r="D15" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="24" t="s">
         <v>226</v>
       </c>
       <c r="F15" s="26"/>
@@ -5084,14 +5081,14 @@
     </row>
     <row r="16" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="23"/>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="C16" s="65"/>
-      <c r="D16" s="35" t="s">
+      <c r="C16" s="64"/>
+      <c r="D16" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="24" t="s">
         <v>228</v>
       </c>
       <c r="F16" s="26"/>
@@ -5108,14 +5105,14 @@
     </row>
     <row r="17" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="23"/>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="C17" s="65"/>
-      <c r="D17" s="35" t="s">
+      <c r="C17" s="64"/>
+      <c r="D17" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="24" t="s">
         <v>230</v>
       </c>
       <c r="F17" s="26"/>
@@ -5132,14 +5129,14 @@
     </row>
     <row r="18" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="23"/>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="C18" s="66"/>
-      <c r="D18" s="35" t="s">
+      <c r="C18" s="65"/>
+      <c r="D18" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="24" t="s">
         <v>232</v>
       </c>
       <c r="F18" s="26"/>
@@ -5155,12 +5152,12 @@
       <c r="Q18" s="32"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B19" s="67"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
       <c r="H19" s="27"/>
       <c r="I19" s="28"/>
       <c r="J19" s="29"/>
@@ -5168,25 +5165,25 @@
       <c r="M19" s="31"/>
       <c r="N19" s="30"/>
       <c r="O19" s="30"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="39"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="38"/>
     </row>
     <row r="20" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B20" s="40"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
       <c r="H20" s="27"/>
       <c r="I20" s="28"/>
       <c r="J20" s="29"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="39"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="38"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
       <c r="B21" s="7" t="s">
@@ -5200,7 +5197,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
-      <c r="L21" s="45" t="s">
+      <c r="L21" s="44" t="s">
         <v>99</v>
       </c>
       <c r="M21" s="17"/>
@@ -5210,25 +5207,25 @@
       <c r="Q21" s="17"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="L22" s="47" t="s">
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="L22" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="M22" s="48" t="s">
+      <c r="M22" s="47" t="s">
         <v>102</v>
       </c>
       <c r="N22" s="21" t="s">
@@ -5237,14 +5234,14 @@
       <c r="O22" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P22" s="49" t="s">
+      <c r="P22" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="Q22" s="50"/>
+      <c r="Q22" s="49"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
-      <c r="B23" s="51"/>
-      <c r="C23" s="52"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="29"/>
       <c r="E23" s="29"/>
       <c r="F23" s="29"/>
@@ -5252,28 +5249,28 @@
       <c r="H23" s="29"/>
       <c r="I23" s="29"/>
       <c r="J23" s="29"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="56"/>
-      <c r="Q23" s="50"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="55"/>
+      <c r="Q23" s="49"/>
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L24" s="53"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="55"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="50"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="55"/>
+      <c r="Q24" s="49"/>
     </row>
     <row r="25" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L25" s="53"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="50"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="49"/>
     </row>
     <row r="26" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A26" s="5"/>
@@ -5287,12 +5284,12 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="57"/>
-      <c r="Q26" s="50"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="56"/>
+      <c r="Q26" s="49"/>
     </row>
     <row r="27" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A27" s="5"/>
@@ -5306,12 +5303,12 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="57"/>
-      <c r="Q27" s="50"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="56"/>
+      <c r="Q27" s="49"/>
     </row>
     <row r="28" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A28" s="5"/>
@@ -5325,12 +5322,12 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="57"/>
-      <c r="Q28" s="50"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="56"/>
+      <c r="Q28" s="49"/>
     </row>
     <row r="29" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A29" s="5"/>
@@ -5344,12 +5341,12 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="57"/>
-      <c r="Q29" s="50"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="56"/>
+      <c r="Q29" s="49"/>
     </row>
     <row r="30" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A30" s="5"/>
@@ -5363,12 +5360,12 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="57"/>
-      <c r="Q30" s="50"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="49"/>
     </row>
     <row r="31" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A31" s="5"/>
@@ -5382,12 +5379,12 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="57"/>
-      <c r="Q31" s="50"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="56"/>
+      <c r="Q31" s="49"/>
     </row>
     <row r="32" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A32" s="5"/>
@@ -5401,12 +5398,12 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
-      <c r="L32" s="59"/>
-      <c r="M32" s="60"/>
-      <c r="N32" s="61"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="62"/>
-      <c r="Q32" s="50"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="59"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="49"/>
     </row>
     <row r="33" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A33" s="5"/>
@@ -5420,7 +5417,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="63" t="s">
+      <c r="L33" s="62" t="s">
         <v>118</v>
       </c>
       <c r="M33" s="17"/>
@@ -5441,7 +5438,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
-      <c r="L34" s="64"/>
+      <c r="L34" s="63"/>
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
       <c r="O34" s="17"/>
@@ -5665,14 +5662,14 @@
     </row>
     <row r="6" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A6" s="23"/>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="24" t="s">
         <v>136</v>
       </c>
       <c r="C6" s="25"/>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="24" t="s">
         <v>138</v>
       </c>
       <c r="F6" s="26"/>
@@ -5689,14 +5686,14 @@
     </row>
     <row r="7" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="23"/>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="24" t="s">
         <v>61</v>
       </c>
       <c r="C7" s="25"/>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="24" t="s">
         <v>210</v>
       </c>
       <c r="F7" s="26"/>
@@ -5713,14 +5710,14 @@
     </row>
     <row r="8" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="23"/>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="24" t="s">
         <v>76</v>
       </c>
       <c r="C8" s="25"/>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="24" t="s">
         <v>235</v>
       </c>
       <c r="F8" s="26"/>
@@ -5737,14 +5734,14 @@
     </row>
     <row r="9" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="23"/>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="24" t="s">
         <v>236</v>
       </c>
       <c r="C9" s="25"/>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="24" t="s">
         <v>237</v>
       </c>
       <c r="F9" s="26"/>
@@ -5761,14 +5758,14 @@
     </row>
     <row r="10" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="23"/>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="24" t="s">
         <v>238</v>
       </c>
       <c r="C10" s="25"/>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="24" t="s">
         <v>239</v>
       </c>
       <c r="F10" s="26"/>
@@ -5785,14 +5782,14 @@
     </row>
     <row r="11" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="23"/>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="24" t="s">
         <v>240</v>
       </c>
       <c r="C11" s="25"/>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="24" t="s">
         <v>241</v>
       </c>
       <c r="F11" s="26"/>
@@ -5809,14 +5806,14 @@
     </row>
     <row r="12" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="23"/>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="24" t="s">
         <v>242</v>
       </c>
       <c r="C12" s="25"/>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="24" t="s">
         <v>243</v>
       </c>
       <c r="F12" s="26"/>
@@ -5833,14 +5830,14 @@
     </row>
     <row r="13" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="23"/>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="24" t="s">
         <v>244</v>
       </c>
       <c r="C13" s="25"/>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="24" t="s">
         <v>245</v>
       </c>
       <c r="F13" s="26"/>
@@ -5857,14 +5854,14 @@
     </row>
     <row r="14" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="23"/>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="24" t="s">
         <v>246</v>
       </c>
       <c r="C14" s="25"/>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="24" t="s">
         <v>247</v>
       </c>
       <c r="F14" s="26"/>
@@ -5881,14 +5878,14 @@
     </row>
     <row r="15" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="23"/>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="24" t="s">
         <v>248</v>
       </c>
       <c r="C15" s="25"/>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="24" t="s">
         <v>249</v>
       </c>
       <c r="F15" s="26"/>
@@ -5905,14 +5902,14 @@
     </row>
     <row r="16" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="23"/>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="24" t="s">
         <v>250</v>
       </c>
       <c r="C16" s="25"/>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="24" t="s">
         <v>251</v>
       </c>
       <c r="F16" s="26"/>
@@ -5929,14 +5926,14 @@
     </row>
     <row r="17" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="23"/>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="24" t="s">
         <v>252</v>
       </c>
       <c r="C17" s="25"/>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="24" t="s">
         <v>253</v>
       </c>
       <c r="F17" s="26"/>
@@ -5953,14 +5950,14 @@
     </row>
     <row r="18" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="23"/>
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="35" t="s">
         <v>254</v>
       </c>
       <c r="C18" s="25"/>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="24" t="s">
         <v>255</v>
       </c>
       <c r="F18" s="26"/>
@@ -5976,18 +5973,18 @@
       <c r="Q18" s="32"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="35" t="s">
         <v>256</v>
       </c>
       <c r="C19" s="25"/>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="E19" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
       <c r="H19" s="27"/>
       <c r="I19" s="28"/>
       <c r="J19" s="29"/>
@@ -5995,25 +5992,25 @@
       <c r="M19" s="31"/>
       <c r="N19" s="30"/>
       <c r="O19" s="30"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="39"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="38"/>
     </row>
     <row r="20" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B20" s="40"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
       <c r="H20" s="27"/>
       <c r="I20" s="28"/>
       <c r="J20" s="29"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="39"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="38"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
       <c r="B21" s="7" t="s">
@@ -6027,7 +6024,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
-      <c r="L21" s="45" t="s">
+      <c r="L21" s="44" t="s">
         <v>99</v>
       </c>
       <c r="M21" s="17"/>
@@ -6037,25 +6034,25 @@
       <c r="Q21" s="17"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="L22" s="47" t="s">
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="L22" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="M22" s="48" t="s">
+      <c r="M22" s="47" t="s">
         <v>102</v>
       </c>
       <c r="N22" s="21" t="s">
@@ -6064,14 +6061,14 @@
       <c r="O22" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P22" s="49" t="s">
+      <c r="P22" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="Q22" s="50"/>
+      <c r="Q22" s="49"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
-      <c r="B23" s="51"/>
-      <c r="C23" s="52"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="29"/>
       <c r="E23" s="29"/>
       <c r="F23" s="29"/>
@@ -6079,28 +6076,28 @@
       <c r="H23" s="29"/>
       <c r="I23" s="29"/>
       <c r="J23" s="29"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="56"/>
-      <c r="Q23" s="50"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="55"/>
+      <c r="Q23" s="49"/>
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L24" s="53"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="55"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="50"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="55"/>
+      <c r="Q24" s="49"/>
     </row>
     <row r="25" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L25" s="53"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="50"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="49"/>
     </row>
     <row r="26" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A26" s="5"/>
@@ -6114,12 +6111,12 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="57"/>
-      <c r="Q26" s="50"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="56"/>
+      <c r="Q26" s="49"/>
     </row>
     <row r="27" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A27" s="5"/>
@@ -6133,12 +6130,12 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="57"/>
-      <c r="Q27" s="50"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="56"/>
+      <c r="Q27" s="49"/>
     </row>
     <row r="28" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A28" s="5"/>
@@ -6152,12 +6149,12 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="57"/>
-      <c r="Q28" s="50"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="56"/>
+      <c r="Q28" s="49"/>
     </row>
     <row r="29" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A29" s="5"/>
@@ -6171,12 +6168,12 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="57"/>
-      <c r="Q29" s="50"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="56"/>
+      <c r="Q29" s="49"/>
     </row>
     <row r="30" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A30" s="5"/>
@@ -6190,12 +6187,12 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="57"/>
-      <c r="Q30" s="50"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="49"/>
     </row>
     <row r="31" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A31" s="5"/>
@@ -6209,12 +6206,12 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="57"/>
-      <c r="Q31" s="50"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="56"/>
+      <c r="Q31" s="49"/>
     </row>
     <row r="32" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A32" s="5"/>
@@ -6228,12 +6225,12 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
-      <c r="L32" s="59"/>
-      <c r="M32" s="60"/>
-      <c r="N32" s="61"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="62"/>
-      <c r="Q32" s="50"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="59"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="49"/>
     </row>
     <row r="33" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A33" s="5"/>
@@ -6247,7 +6244,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="63" t="s">
+      <c r="L33" s="62" t="s">
         <v>118</v>
       </c>
       <c r="M33" s="17"/>
@@ -6268,7 +6265,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
-      <c r="L34" s="64"/>
+      <c r="L34" s="63"/>
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
       <c r="O34" s="17"/>
@@ -6564,10 +6561,10 @@
     </row>
     <row r="9" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="23"/>
-      <c r="B9" s="35"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="25"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
       <c r="H9" s="27"/>
@@ -6582,10 +6579,10 @@
     </row>
     <row r="10" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="23"/>
-      <c r="B10" s="35"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="25"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
       <c r="H10" s="27"/>
@@ -6600,10 +6597,10 @@
     </row>
     <row r="11" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="23"/>
-      <c r="B11" s="35"/>
+      <c r="B11" s="24"/>
       <c r="C11" s="25"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
       <c r="H11" s="27"/>
@@ -6618,10 +6615,10 @@
     </row>
     <row r="12" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="23"/>
-      <c r="B12" s="35"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="25"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
       <c r="H12" s="27"/>
@@ -6636,10 +6633,10 @@
     </row>
     <row r="13" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="23"/>
-      <c r="B13" s="35"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="25"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
       <c r="H13" s="27"/>
@@ -6654,10 +6651,10 @@
     </row>
     <row r="14" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="23"/>
-      <c r="B14" s="35"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="25"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
       <c r="H14" s="27"/>
@@ -6672,10 +6669,10 @@
     </row>
     <row r="15" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="23"/>
-      <c r="B15" s="35"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="25"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
       <c r="H15" s="27"/>
@@ -6690,10 +6687,10 @@
     </row>
     <row r="16" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="23"/>
-      <c r="B16" s="35"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
       <c r="H16" s="27"/>
@@ -6708,10 +6705,10 @@
     </row>
     <row r="17" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="23"/>
-      <c r="B17" s="35"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="25"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
       <c r="H17" s="27"/>
@@ -6726,10 +6723,10 @@
     </row>
     <row r="18" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="23"/>
-      <c r="B18" s="36"/>
+      <c r="B18" s="35"/>
       <c r="C18" s="25"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="26"/>
       <c r="G18" s="26"/>
       <c r="H18" s="27"/>
@@ -6743,12 +6740,12 @@
       <c r="Q18" s="32"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B19" s="36"/>
+      <c r="B19" s="35"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
       <c r="H19" s="27"/>
       <c r="I19" s="28"/>
       <c r="J19" s="29"/>
@@ -6756,25 +6753,25 @@
       <c r="M19" s="31"/>
       <c r="N19" s="30"/>
       <c r="O19" s="30"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="39"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="38"/>
     </row>
     <row r="20" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B20" s="40"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
       <c r="H20" s="27"/>
       <c r="I20" s="28"/>
       <c r="J20" s="29"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="39"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="38"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
       <c r="B21" s="7" t="s">
@@ -6788,7 +6785,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
-      <c r="L21" s="45" t="s">
+      <c r="L21" s="44" t="s">
         <v>99</v>
       </c>
       <c r="M21" s="17"/>
@@ -6798,25 +6795,25 @@
       <c r="Q21" s="17"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="L22" s="47" t="s">
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="L22" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="M22" s="48" t="s">
+      <c r="M22" s="47" t="s">
         <v>102</v>
       </c>
       <c r="N22" s="21" t="s">
@@ -6825,14 +6822,14 @@
       <c r="O22" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P22" s="49" t="s">
+      <c r="P22" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="Q22" s="50"/>
+      <c r="Q22" s="49"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
-      <c r="B23" s="51"/>
-      <c r="C23" s="52"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="29"/>
       <c r="E23" s="29"/>
       <c r="F23" s="29"/>
@@ -6840,28 +6837,28 @@
       <c r="H23" s="29"/>
       <c r="I23" s="29"/>
       <c r="J23" s="29"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="56"/>
-      <c r="Q23" s="50"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="55"/>
+      <c r="Q23" s="49"/>
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L24" s="53"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="55"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="50"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="55"/>
+      <c r="Q24" s="49"/>
     </row>
     <row r="25" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L25" s="53"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="50"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="49"/>
     </row>
     <row r="26" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A26" s="5"/>
@@ -6875,12 +6872,12 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="57"/>
-      <c r="Q26" s="50"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="56"/>
+      <c r="Q26" s="49"/>
     </row>
     <row r="27" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A27" s="5"/>
@@ -6894,12 +6891,12 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="57"/>
-      <c r="Q27" s="50"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="56"/>
+      <c r="Q27" s="49"/>
     </row>
     <row r="28" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A28" s="5"/>
@@ -6913,12 +6910,12 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="57"/>
-      <c r="Q28" s="50"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="56"/>
+      <c r="Q28" s="49"/>
     </row>
     <row r="29" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A29" s="5"/>
@@ -6932,12 +6929,12 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="57"/>
-      <c r="Q29" s="50"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="56"/>
+      <c r="Q29" s="49"/>
     </row>
     <row r="30" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A30" s="5"/>
@@ -6951,12 +6948,12 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="57"/>
-      <c r="Q30" s="50"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="49"/>
     </row>
     <row r="31" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A31" s="5"/>
@@ -6970,12 +6967,12 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="57"/>
-      <c r="Q31" s="50"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="56"/>
+      <c r="Q31" s="49"/>
     </row>
     <row r="32" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A32" s="5"/>
@@ -6989,12 +6986,12 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
-      <c r="L32" s="59"/>
-      <c r="M32" s="60"/>
-      <c r="N32" s="61"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="62"/>
-      <c r="Q32" s="50"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="59"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="49"/>
     </row>
     <row r="33" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A33" s="5"/>
@@ -7008,7 +7005,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="63" t="s">
+      <c r="L33" s="62" t="s">
         <v>118</v>
       </c>
       <c r="M33" s="17"/>
@@ -7029,7 +7026,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
-      <c r="L34" s="64"/>
+      <c r="L34" s="63"/>
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
       <c r="O34" s="17"/>
@@ -7281,111 +7278,111 @@
   <sheetFormatPr defaultColWidth="6.66666666666667" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="2.66666666666667" style="5" customWidth="1"/>
-    <col min="2" max="2" width="4.33333333333333" style="93" customWidth="1"/>
-    <col min="3" max="3" width="6.44444444444444" style="94" customWidth="1"/>
-    <col min="4" max="4" width="12.1018518518519" style="94" customWidth="1"/>
-    <col min="5" max="5" width="19.4444444444444" style="95" customWidth="1"/>
-    <col min="6" max="6" width="29.4444444444444" style="96" customWidth="1"/>
-    <col min="7" max="7" width="52.6666666666667" style="95" customWidth="1"/>
+    <col min="2" max="2" width="4.33333333333333" style="92" customWidth="1"/>
+    <col min="3" max="3" width="6.44444444444444" style="93" customWidth="1"/>
+    <col min="4" max="4" width="12.1018518518519" style="93" customWidth="1"/>
+    <col min="5" max="5" width="19.4444444444444" style="94" customWidth="1"/>
+    <col min="6" max="6" width="29.4444444444444" style="95" customWidth="1"/>
+    <col min="7" max="7" width="52.6666666666667" style="94" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="92" customFormat="1" ht="21.6" spans="1:7">
-      <c r="A1" s="97"/>
-      <c r="B1" s="98" t="s">
+    <row r="1" s="91" customFormat="1" ht="21.6" spans="1:7">
+      <c r="A1" s="96"/>
+      <c r="B1" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="99" t="s">
+      <c r="C1" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="99" t="s">
+      <c r="D1" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="100" t="s">
+      <c r="E1" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="101" t="s">
+      <c r="F1" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="100" t="s">
+      <c r="G1" s="99" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="B2" s="102">
+      <c r="B2" s="101">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="103" t="s">
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="105" t="s">
+      <c r="F2" s="103"/>
+      <c r="G2" s="104" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="108" t="s">
+      <c r="B3" s="105"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="109"/>
-      <c r="G3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="107"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="B4" s="106"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="108" t="s">
+      <c r="B4" s="105"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="109"/>
-      <c r="G4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="107"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="B5" s="106"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="108" t="s">
+      <c r="B5" s="105"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="109"/>
-      <c r="G5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="107"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="B6" s="106"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="103" t="s">
+      <c r="B6" s="105"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="109"/>
-      <c r="G6" s="108" t="s">
+      <c r="F6" s="108"/>
+      <c r="G6" s="107" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="B7" s="106"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="108" t="s">
+      <c r="B7" s="105"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="109"/>
-      <c r="G7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="107"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="B8" s="106"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="108" t="s">
+      <c r="B8" s="105"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="109"/>
-      <c r="G8" s="108"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="107"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -7544,648 +7541,648 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="71"/>
-      <c r="B6" s="68" t="s">
+    <row r="6" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="70"/>
+      <c r="B6" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68" t="s">
+      <c r="C6" s="67"/>
+      <c r="D6" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-    </row>
-    <row r="7" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="71"/>
-      <c r="B7" s="68" t="s">
+      <c r="O6" s="73"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+    </row>
+    <row r="7" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="70"/>
+      <c r="B7" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68" t="s">
+      <c r="C7" s="67"/>
+      <c r="D7" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="80" t="s">
+      <c r="E7" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
       <c r="N7" s="30"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-    </row>
-    <row r="8" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="71"/>
-      <c r="B8" s="68" t="s">
+      <c r="O7" s="73"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+    </row>
+    <row r="8" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="70"/>
+      <c r="B8" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68" t="s">
+      <c r="C8" s="67"/>
+      <c r="D8" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="80" t="s">
+      <c r="E8" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
     </row>
     <row r="9" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="71"/>
-      <c r="B9" s="68" t="s">
+      <c r="A9" s="70"/>
+      <c r="B9" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68" t="s">
+      <c r="C9" s="67"/>
+      <c r="D9" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="80" t="s">
+      <c r="E9" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="68"/>
-      <c r="G9" s="35"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="29"/>
       <c r="I9" s="29"/>
-      <c r="J9" s="75"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
+      <c r="J9" s="74"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="30"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
     </row>
     <row r="10" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="71"/>
-      <c r="B10" s="68" t="s">
+      <c r="A10" s="70"/>
+      <c r="B10" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68" t="s">
+      <c r="C10" s="67"/>
+      <c r="D10" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="80" t="s">
+      <c r="E10" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="68"/>
-      <c r="G10" s="35"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="29"/>
       <c r="I10" s="29"/>
-      <c r="J10" s="75"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
+      <c r="J10" s="74"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="30"/>
-      <c r="O10" s="74"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-    </row>
-    <row r="11" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="71"/>
-      <c r="B11" s="68" t="s">
+      <c r="O10" s="73"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+    </row>
+    <row r="11" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="70"/>
+      <c r="B11" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68" t="s">
+      <c r="C11" s="67"/>
+      <c r="D11" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="80" t="s">
+      <c r="E11" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="68"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="73"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="30"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="71"/>
-      <c r="B12" s="68" t="s">
+      <c r="A12" s="70"/>
+      <c r="B12" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68" t="s">
+      <c r="C12" s="67"/>
+      <c r="D12" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="80" t="s">
+      <c r="E12" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="68"/>
-      <c r="G12" s="35"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="27"/>
       <c r="I12" s="28"/>
       <c r="J12" s="29"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="30"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
     </row>
     <row r="13" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="71"/>
-      <c r="B13" s="68" t="s">
+      <c r="A13" s="70"/>
+      <c r="B13" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68" t="s">
+      <c r="C13" s="67"/>
+      <c r="D13" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="80" t="s">
+      <c r="E13" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="68"/>
-      <c r="G13" s="35"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="27"/>
       <c r="I13" s="28"/>
       <c r="J13" s="29"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="30"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
     </row>
     <row r="14" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="71"/>
-      <c r="B14" s="68" t="s">
+      <c r="A14" s="70"/>
+      <c r="B14" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68" t="s">
+      <c r="C14" s="67"/>
+      <c r="D14" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="80" t="s">
+      <c r="E14" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="68"/>
-      <c r="G14" s="35"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="27"/>
       <c r="I14" s="29"/>
-      <c r="J14" s="75"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
+      <c r="J14" s="74"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="30"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
     </row>
     <row r="15" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="71"/>
-      <c r="B15" s="68" t="s">
+      <c r="A15" s="70"/>
+      <c r="B15" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68" t="s">
+      <c r="C15" s="67"/>
+      <c r="D15" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="80" t="s">
+      <c r="E15" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="35"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="27"/>
       <c r="I15" s="29"/>
-      <c r="J15" s="75"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
+      <c r="J15" s="74"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="30"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
     </row>
     <row r="16" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="71"/>
-      <c r="B16" s="68" t="s">
+      <c r="A16" s="70"/>
+      <c r="B16" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68" t="s">
+      <c r="C16" s="67"/>
+      <c r="D16" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="80" t="s">
+      <c r="E16" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="35"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="27"/>
       <c r="I16" s="29"/>
-      <c r="J16" s="75"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
+      <c r="J16" s="74"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
       <c r="N16" s="30"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35" t="s">
+      <c r="O16" s="73"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="71"/>
-      <c r="B17" s="68" t="s">
+      <c r="A17" s="70"/>
+      <c r="B17" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68" t="s">
+      <c r="C17" s="67"/>
+      <c r="D17" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="80" t="s">
+      <c r="E17" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="35"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="27"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
       <c r="N17" s="30"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="71"/>
-      <c r="B18" s="68" t="s">
+      <c r="A18" s="70"/>
+      <c r="B18" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68" t="s">
+      <c r="C18" s="67"/>
+      <c r="D18" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="80" t="s">
+      <c r="E18" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="68"/>
-      <c r="G18" s="35"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="27"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="30"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="71"/>
-      <c r="B19" s="68" t="s">
+      <c r="A19" s="70"/>
+      <c r="B19" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68" t="s">
+      <c r="C19" s="67"/>
+      <c r="D19" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="80" t="s">
+      <c r="E19" s="79" t="s">
         <v>82</v>
       </c>
-      <c r="F19" s="68"/>
-      <c r="G19" s="35"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="27"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="30"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
+      <c r="O19" s="73"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
     </row>
     <row r="20" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="71"/>
-      <c r="B20" s="68" t="s">
+      <c r="A20" s="70"/>
+      <c r="B20" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="79"/>
-      <c r="D20" s="68" t="s">
+      <c r="C20" s="78"/>
+      <c r="D20" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="80" t="s">
+      <c r="E20" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="79"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="30"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
     </row>
     <row r="21" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="71"/>
-      <c r="B21" s="68" t="s">
+      <c r="A21" s="70"/>
+      <c r="B21" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68" t="s">
+      <c r="C21" s="67"/>
+      <c r="D21" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="80" t="s">
+      <c r="E21" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="68"/>
-      <c r="G21" s="35"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="27"/>
       <c r="I21" s="29"/>
       <c r="J21" s="29"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="30"/>
-      <c r="O21" s="74"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
+      <c r="O21" s="73"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
     </row>
     <row r="22" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="71"/>
-      <c r="B22" s="68" t="s">
+      <c r="A22" s="70"/>
+      <c r="B22" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68" t="s">
+      <c r="C22" s="67"/>
+      <c r="D22" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="80" t="s">
+      <c r="E22" s="79" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="68"/>
-      <c r="G22" s="35"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="27"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="30"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
     </row>
     <row r="23" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68" t="s">
+      <c r="A23" s="84"/>
+      <c r="B23" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68" t="s">
+      <c r="C23" s="67"/>
+      <c r="D23" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="80" t="s">
+      <c r="E23" s="79" t="s">
         <v>92</v>
       </c>
       <c r="F23" s="26"/>
       <c r="G23" s="26"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="87"/>
-      <c r="J23" s="87"/>
-      <c r="L23" s="88"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="L23" s="87"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="90"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="89"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
     <row r="24" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68" t="s">
+      <c r="A24" s="84"/>
+      <c r="B24" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68" t="s">
+      <c r="C24" s="67"/>
+      <c r="D24" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="80" t="s">
+      <c r="E24" s="79" t="s">
         <v>95</v>
       </c>
       <c r="F24" s="26"/>
       <c r="G24" s="26"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
-      <c r="L24" s="88"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="L24" s="87"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="90"/>
+      <c r="N24" s="88"/>
+      <c r="O24" s="89"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
     <row r="25" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68" t="s">
+      <c r="A25" s="84"/>
+      <c r="B25" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68" t="s">
+      <c r="C25" s="67"/>
+      <c r="D25" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="E25" s="80" t="s">
+      <c r="E25" s="79" t="s">
         <v>97</v>
       </c>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="L25" s="88"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="L25" s="87"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="90"/>
+      <c r="N25" s="88"/>
+      <c r="O25" s="89"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
     <row r="26" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="91"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="90"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="L26" s="88"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="L26" s="87"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="90"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="89"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
     <row r="27" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="91"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="90"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="L27" s="88"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="86"/>
+      <c r="L27" s="87"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="90"/>
+      <c r="N27" s="88"/>
+      <c r="O27" s="89"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
     <row r="28" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="91"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="90"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="L28" s="88"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="L28" s="87"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="89"/>
-      <c r="O28" s="90"/>
+      <c r="N28" s="88"/>
+      <c r="O28" s="89"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
     <row r="29" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="91"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="90"/>
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="L29" s="88"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="86"/>
+      <c r="L29" s="87"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="90"/>
+      <c r="N29" s="88"/>
+      <c r="O29" s="89"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
     <row r="30" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="91"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="90"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="L30" s="88"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="L30" s="87"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="90"/>
+      <c r="N30" s="88"/>
+      <c r="O30" s="89"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
     <row r="31" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="91"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="90"/>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="L31" s="88"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="86"/>
+      <c r="L31" s="87"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="89"/>
-      <c r="O31" s="90"/>
+      <c r="N31" s="88"/>
+      <c r="O31" s="89"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
     <row r="32" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="91"/>
+      <c r="A32" s="84"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="90"/>
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="L32" s="88"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="L32" s="87"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="90"/>
+      <c r="N32" s="88"/>
+      <c r="O32" s="89"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
     <row r="33" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28"/>
       <c r="J33" s="29"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="44"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="39"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="38"/>
     </row>
     <row r="34" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B34" s="40"/>
+      <c r="B34" s="39"/>
       <c r="C34" s="25"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="27"/>
       <c r="I34" s="28"/>
       <c r="J34" s="29"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="39"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="38"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
       <c r="B35" s="7" t="s">
@@ -8199,7 +8196,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
-      <c r="L35" s="45" t="s">
+      <c r="L35" s="44" t="s">
         <v>99</v>
       </c>
       <c r="M35" s="17"/>
@@ -8209,25 +8206,25 @@
       <c r="Q35" s="17"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="46" t="s">
+      <c r="C36" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="46" t="s">
+      <c r="D36" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="L36" s="47" t="s">
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="L36" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="M36" s="48" t="s">
+      <c r="M36" s="47" t="s">
         <v>102</v>
       </c>
       <c r="N36" s="21" t="s">
@@ -8236,14 +8233,14 @@
       <c r="O36" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P36" s="49" t="s">
+      <c r="P36" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="Q36" s="50"/>
+      <c r="Q36" s="49"/>
     </row>
     <row r="37" s="3" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
-      <c r="B37" s="51"/>
-      <c r="C37" s="52"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
       <c r="D37" s="29"/>
       <c r="E37" s="29"/>
       <c r="F37" s="29"/>
@@ -8251,50 +8248,50 @@
       <c r="H37" s="29"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
-      <c r="L37" s="35" t="s">
+      <c r="L37" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="M37" s="35" t="s">
+      <c r="M37" s="24" t="s">
         <v>107</v>
       </c>
       <c r="N37" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="O37" s="74"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="50"/>
+      <c r="O37" s="73"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="49"/>
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L38" s="35" t="s">
+      <c r="L38" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="M38" s="35" t="s">
+      <c r="M38" s="24" t="s">
         <v>110</v>
       </c>
       <c r="N38" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="O38" s="74"/>
-      <c r="P38" s="56" t="s">
+      <c r="O38" s="73"/>
+      <c r="P38" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="Q38" s="50"/>
+      <c r="Q38" s="49"/>
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L39" s="35" t="s">
+      <c r="L39" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="M39" s="35" t="s">
+      <c r="M39" s="24" t="s">
         <v>114</v>
       </c>
       <c r="N39" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="O39" s="74"/>
-      <c r="P39" s="56" t="s">
+      <c r="O39" s="73"/>
+      <c r="P39" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="Q39" s="50"/>
+      <c r="Q39" s="49"/>
     </row>
     <row r="40" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A40" s="5"/>
@@ -8308,14 +8305,14 @@
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
       <c r="N40" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="O40" s="74"/>
-      <c r="P40" s="57"/>
-      <c r="Q40" s="50"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="49"/>
     </row>
     <row r="41" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A41" s="5"/>
@@ -8329,12 +8326,12 @@
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="57"/>
-      <c r="Q41" s="50"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="56"/>
+      <c r="Q41" s="49"/>
     </row>
     <row r="42" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A42" s="5"/>
@@ -8348,12 +8345,12 @@
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
-      <c r="L42" s="58"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="50"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="38"/>
+      <c r="P42" s="56"/>
+      <c r="Q42" s="49"/>
     </row>
     <row r="43" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A43" s="5"/>
@@ -8367,12 +8364,12 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="58"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="57"/>
-      <c r="Q43" s="50"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="56"/>
+      <c r="Q43" s="49"/>
     </row>
     <row r="44" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A44" s="5"/>
@@ -8386,12 +8383,12 @@
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
-      <c r="L44" s="58"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="50"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="56"/>
+      <c r="Q44" s="49"/>
     </row>
     <row r="45" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A45" s="5"/>
@@ -8405,12 +8402,12 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="39"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="39"/>
-      <c r="P45" s="57"/>
-      <c r="Q45" s="50"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="38"/>
+      <c r="P45" s="56"/>
+      <c r="Q45" s="49"/>
     </row>
     <row r="46" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A46" s="5"/>
@@ -8424,12 +8421,12 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
-      <c r="L46" s="59"/>
-      <c r="M46" s="60"/>
-      <c r="N46" s="61"/>
-      <c r="O46" s="39"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="50"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="59"/>
+      <c r="N46" s="60"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="49"/>
     </row>
     <row r="47" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A47" s="5"/>
@@ -8443,7 +8440,7 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
-      <c r="L47" s="63" t="s">
+      <c r="L47" s="62" t="s">
         <v>118</v>
       </c>
       <c r="M47" s="17"/>
@@ -8464,7 +8461,7 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
-      <c r="L48" s="64" t="s">
+      <c r="L48" s="63" t="s">
         <v>119</v>
       </c>
       <c r="M48" s="17"/>
@@ -8698,630 +8695,630 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="71"/>
-      <c r="B6" s="68" t="s">
+    <row r="6" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="70"/>
+      <c r="B6" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68" t="s">
+      <c r="C6" s="67"/>
+      <c r="D6" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-    </row>
-    <row r="7" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="71"/>
-      <c r="B7" s="68" t="s">
+      <c r="O6" s="73"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+    </row>
+    <row r="7" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="70"/>
+      <c r="B7" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68" t="s">
+      <c r="C7" s="67"/>
+      <c r="D7" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="80" t="s">
+      <c r="E7" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
       <c r="N7" s="30"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-    </row>
-    <row r="8" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="71"/>
-      <c r="B8" s="68" t="s">
+      <c r="O7" s="73"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+    </row>
+    <row r="8" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="70"/>
+      <c r="B8" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68" t="s">
+      <c r="C8" s="67"/>
+      <c r="D8" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="80" t="s">
+      <c r="E8" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
     </row>
     <row r="9" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="71"/>
-      <c r="B9" s="68" t="s">
+      <c r="A9" s="70"/>
+      <c r="B9" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68" t="s">
+      <c r="C9" s="67"/>
+      <c r="D9" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="80" t="s">
+      <c r="E9" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="68"/>
-      <c r="G9" s="35"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="29"/>
       <c r="I9" s="29"/>
-      <c r="J9" s="75"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
+      <c r="J9" s="74"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="30"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
     </row>
     <row r="10" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="71"/>
-      <c r="B10" s="68" t="s">
+      <c r="A10" s="70"/>
+      <c r="B10" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68" t="s">
+      <c r="C10" s="67"/>
+      <c r="D10" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="80" t="s">
+      <c r="E10" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="68"/>
-      <c r="G10" s="35"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="29"/>
       <c r="I10" s="29"/>
-      <c r="J10" s="75"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
+      <c r="J10" s="74"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="30"/>
-      <c r="O10" s="74"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-    </row>
-    <row r="11" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="71"/>
-      <c r="B11" s="68" t="s">
+      <c r="O10" s="73"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+    </row>
+    <row r="11" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="70"/>
+      <c r="B11" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68" t="s">
+      <c r="C11" s="67"/>
+      <c r="D11" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="80" t="s">
+      <c r="E11" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="68"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="73"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="30"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="71"/>
-      <c r="B12" s="68" t="s">
+      <c r="A12" s="70"/>
+      <c r="B12" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68" t="s">
+      <c r="C12" s="67"/>
+      <c r="D12" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="80" t="s">
+      <c r="E12" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="68"/>
-      <c r="G12" s="35"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="27"/>
       <c r="I12" s="28"/>
       <c r="J12" s="29"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="30"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
     </row>
     <row r="13" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="71"/>
-      <c r="B13" s="68" t="s">
+      <c r="A13" s="70"/>
+      <c r="B13" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68" t="s">
+      <c r="C13" s="67"/>
+      <c r="D13" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="80" t="s">
+      <c r="E13" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="68"/>
-      <c r="G13" s="35"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="27"/>
       <c r="I13" s="28"/>
       <c r="J13" s="29"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="30"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
     </row>
     <row r="14" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="71"/>
-      <c r="B14" s="68" t="s">
+      <c r="A14" s="70"/>
+      <c r="B14" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68" t="s">
+      <c r="C14" s="67"/>
+      <c r="D14" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="80" t="s">
+      <c r="E14" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="F14" s="68"/>
-      <c r="G14" s="35"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="27"/>
       <c r="I14" s="29"/>
-      <c r="J14" s="75"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
+      <c r="J14" s="74"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="30"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
     </row>
     <row r="15" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="71"/>
-      <c r="B15" s="68" t="s">
+      <c r="A15" s="70"/>
+      <c r="B15" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68" t="s">
+      <c r="C15" s="67"/>
+      <c r="D15" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="80" t="s">
+      <c r="E15" s="79" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="35"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="27"/>
       <c r="I15" s="29"/>
-      <c r="J15" s="75"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
+      <c r="J15" s="74"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="30"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
     </row>
     <row r="16" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="71"/>
-      <c r="B16" s="68" t="s">
+      <c r="A16" s="70"/>
+      <c r="B16" s="67" t="s">
         <v>129</v>
       </c>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68" t="s">
+      <c r="C16" s="67"/>
+      <c r="D16" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="80" t="s">
+      <c r="E16" s="79" t="s">
         <v>130</v>
       </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="35"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="27"/>
       <c r="I16" s="29"/>
-      <c r="J16" s="75"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
+      <c r="J16" s="74"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
       <c r="N16" s="30"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35" t="s">
+      <c r="O16" s="73"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="71"/>
-      <c r="B17" s="68" t="s">
+      <c r="A17" s="70"/>
+      <c r="B17" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68" t="s">
+      <c r="C17" s="67"/>
+      <c r="D17" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="80" t="s">
+      <c r="E17" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="35"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="27"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
       <c r="N17" s="30"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="71"/>
-      <c r="B18" s="68" t="s">
+      <c r="A18" s="70"/>
+      <c r="B18" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68" t="s">
+      <c r="C18" s="67"/>
+      <c r="D18" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="80" t="s">
+      <c r="E18" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="68"/>
-      <c r="G18" s="35"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="27"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="30"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="71"/>
-      <c r="B19" s="68" t="s">
+      <c r="A19" s="70"/>
+      <c r="B19" s="67" t="s">
         <v>131</v>
       </c>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68" t="s">
+      <c r="C19" s="67"/>
+      <c r="D19" s="67" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="80" t="s">
+      <c r="E19" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="F19" s="68"/>
-      <c r="G19" s="35"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="27"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="30"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
+      <c r="O19" s="73"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
     </row>
     <row r="20" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="71"/>
-      <c r="B20" s="68" t="s">
+      <c r="A20" s="70"/>
+      <c r="B20" s="67" t="s">
         <v>134</v>
       </c>
-      <c r="C20" s="79"/>
-      <c r="D20" s="68" t="s">
+      <c r="C20" s="78"/>
+      <c r="D20" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="80" t="s">
+      <c r="E20" s="79" t="s">
         <v>135</v>
       </c>
-      <c r="F20" s="79"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="30"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
     </row>
     <row r="21" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="71"/>
-      <c r="B21" s="68" t="s">
+      <c r="A21" s="70"/>
+      <c r="B21" s="67" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68" t="s">
+      <c r="C21" s="67"/>
+      <c r="D21" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="E21" s="80" t="s">
+      <c r="E21" s="79" t="s">
         <v>138</v>
       </c>
-      <c r="F21" s="68"/>
-      <c r="G21" s="35"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="27"/>
       <c r="I21" s="29"/>
       <c r="J21" s="29"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="30"/>
-      <c r="O21" s="74"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
+      <c r="O21" s="73"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
     </row>
     <row r="22" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="71"/>
-      <c r="B22" s="68" t="s">
+      <c r="A22" s="70"/>
+      <c r="B22" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68" t="s">
+      <c r="C22" s="67"/>
+      <c r="D22" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="80" t="s">
+      <c r="E22" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="F22" s="68"/>
-      <c r="G22" s="35"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="27"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="30"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
     </row>
     <row r="23" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="80"/>
+      <c r="A23" s="84"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="79"/>
       <c r="F23" s="26"/>
       <c r="G23" s="26"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="87"/>
-      <c r="J23" s="87"/>
-      <c r="L23" s="88"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="L23" s="87"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="90"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="89"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
     <row r="24" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="80"/>
+      <c r="A24" s="84"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="79"/>
       <c r="F24" s="26"/>
       <c r="G24" s="26"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
-      <c r="L24" s="88"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="L24" s="87"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="90"/>
+      <c r="N24" s="88"/>
+      <c r="O24" s="89"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
     <row r="25" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="80"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="79"/>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="L25" s="88"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="L25" s="87"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="90"/>
+      <c r="N25" s="88"/>
+      <c r="O25" s="89"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
     <row r="26" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="91"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="90"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="L26" s="88"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="L26" s="87"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="90"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="89"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
     <row r="27" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="91"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="90"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="L27" s="88"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="86"/>
+      <c r="L27" s="87"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="90"/>
+      <c r="N27" s="88"/>
+      <c r="O27" s="89"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
     <row r="28" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="91"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="90"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="L28" s="88"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="L28" s="87"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="89"/>
-      <c r="O28" s="90"/>
+      <c r="N28" s="88"/>
+      <c r="O28" s="89"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
     <row r="29" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="91"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="90"/>
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="L29" s="88"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="86"/>
+      <c r="L29" s="87"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="90"/>
+      <c r="N29" s="88"/>
+      <c r="O29" s="89"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
     <row r="30" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="91"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="90"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="L30" s="88"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="L30" s="87"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="90"/>
+      <c r="N30" s="88"/>
+      <c r="O30" s="89"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
     <row r="31" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="91"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="90"/>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="L31" s="88"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="86"/>
+      <c r="L31" s="87"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="89"/>
-      <c r="O31" s="90"/>
+      <c r="N31" s="88"/>
+      <c r="O31" s="89"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
     <row r="32" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="91"/>
+      <c r="A32" s="84"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="90"/>
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="L32" s="88"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="L32" s="87"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="90"/>
+      <c r="N32" s="88"/>
+      <c r="O32" s="89"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
     <row r="33" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28"/>
       <c r="J33" s="29"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="44"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="39"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="38"/>
     </row>
     <row r="34" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B34" s="40"/>
+      <c r="B34" s="39"/>
       <c r="C34" s="25"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="27"/>
       <c r="I34" s="28"/>
       <c r="J34" s="29"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="39"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="38"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
       <c r="B35" s="7" t="s">
@@ -9335,7 +9332,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
-      <c r="L35" s="45" t="s">
+      <c r="L35" s="44" t="s">
         <v>99</v>
       </c>
       <c r="M35" s="17"/>
@@ -9345,25 +9342,25 @@
       <c r="Q35" s="17"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="46" t="s">
+      <c r="C36" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="46" t="s">
+      <c r="D36" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="L36" s="47" t="s">
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="L36" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="M36" s="48" t="s">
+      <c r="M36" s="47" t="s">
         <v>102</v>
       </c>
       <c r="N36" s="21" t="s">
@@ -9372,14 +9369,14 @@
       <c r="O36" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P36" s="49" t="s">
+      <c r="P36" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="Q36" s="50"/>
+      <c r="Q36" s="49"/>
     </row>
     <row r="37" s="3" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
-      <c r="B37" s="51"/>
-      <c r="C37" s="52"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
       <c r="D37" s="29"/>
       <c r="E37" s="29"/>
       <c r="F37" s="29"/>
@@ -9387,50 +9384,50 @@
       <c r="H37" s="29"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
-      <c r="L37" s="35" t="s">
+      <c r="L37" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="M37" s="35" t="s">
+      <c r="M37" s="24" t="s">
         <v>107</v>
       </c>
       <c r="N37" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="O37" s="74"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="50"/>
+      <c r="O37" s="73"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="49"/>
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L38" s="35" t="s">
+      <c r="L38" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="M38" s="35" t="s">
+      <c r="M38" s="24" t="s">
         <v>110</v>
       </c>
       <c r="N38" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="O38" s="74"/>
-      <c r="P38" s="56" t="s">
+      <c r="O38" s="73"/>
+      <c r="P38" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="Q38" s="50"/>
+      <c r="Q38" s="49"/>
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L39" s="35" t="s">
+      <c r="L39" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="M39" s="35" t="s">
+      <c r="M39" s="24" t="s">
         <v>114</v>
       </c>
       <c r="N39" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="O39" s="74"/>
-      <c r="P39" s="56" t="s">
+      <c r="O39" s="73"/>
+      <c r="P39" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="Q39" s="50"/>
+      <c r="Q39" s="49"/>
     </row>
     <row r="40" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A40" s="5"/>
@@ -9444,14 +9441,14 @@
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
       <c r="N40" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="O40" s="74"/>
-      <c r="P40" s="57"/>
-      <c r="Q40" s="50"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="49"/>
     </row>
     <row r="41" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A41" s="5"/>
@@ -9465,12 +9462,12 @@
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="57"/>
-      <c r="Q41" s="50"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="56"/>
+      <c r="Q41" s="49"/>
     </row>
     <row r="42" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A42" s="5"/>
@@ -9484,12 +9481,12 @@
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
-      <c r="L42" s="58"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="50"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="38"/>
+      <c r="P42" s="56"/>
+      <c r="Q42" s="49"/>
     </row>
     <row r="43" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A43" s="5"/>
@@ -9503,12 +9500,12 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="58"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="57"/>
-      <c r="Q43" s="50"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="56"/>
+      <c r="Q43" s="49"/>
     </row>
     <row r="44" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A44" s="5"/>
@@ -9522,12 +9519,12 @@
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
-      <c r="L44" s="58"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="50"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="56"/>
+      <c r="Q44" s="49"/>
     </row>
     <row r="45" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A45" s="5"/>
@@ -9541,12 +9538,12 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="39"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="39"/>
-      <c r="P45" s="57"/>
-      <c r="Q45" s="50"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="38"/>
+      <c r="P45" s="56"/>
+      <c r="Q45" s="49"/>
     </row>
     <row r="46" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A46" s="5"/>
@@ -9560,12 +9557,12 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
-      <c r="L46" s="59"/>
-      <c r="M46" s="60"/>
-      <c r="N46" s="61"/>
-      <c r="O46" s="39"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="50"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="59"/>
+      <c r="N46" s="60"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="49"/>
     </row>
     <row r="47" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A47" s="5"/>
@@ -9579,7 +9576,7 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
-      <c r="L47" s="63" t="s">
+      <c r="L47" s="62" t="s">
         <v>118</v>
       </c>
       <c r="M47" s="17"/>
@@ -9600,7 +9597,7 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
-      <c r="L48" s="64" t="s">
+      <c r="L48" s="63" t="s">
         <v>119</v>
       </c>
       <c r="M48" s="17"/>
@@ -9834,654 +9831,654 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="71"/>
-      <c r="B6" s="68" t="s">
+    <row r="6" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="70"/>
+      <c r="B6" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68" t="s">
+      <c r="C6" s="67"/>
+      <c r="D6" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-    </row>
-    <row r="7" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="71"/>
-      <c r="B7" s="68" t="s">
+      <c r="O6" s="73"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+    </row>
+    <row r="7" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="70"/>
+      <c r="B7" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68" t="s">
+      <c r="C7" s="67"/>
+      <c r="D7" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="80" t="s">
+      <c r="E7" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
       <c r="N7" s="30"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-    </row>
-    <row r="8" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="71"/>
-      <c r="B8" s="68" t="s">
+      <c r="O7" s="73"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+    </row>
+    <row r="8" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="70"/>
+      <c r="B8" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68" t="s">
+      <c r="C8" s="67"/>
+      <c r="D8" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="80" t="s">
+      <c r="E8" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
     </row>
     <row r="9" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="71"/>
-      <c r="B9" s="68" t="s">
+      <c r="A9" s="70"/>
+      <c r="B9" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68" t="s">
+      <c r="C9" s="67"/>
+      <c r="D9" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="80" t="s">
+      <c r="E9" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="F9" s="68"/>
-      <c r="G9" s="35"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="29"/>
       <c r="I9" s="29"/>
-      <c r="J9" s="75"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
+      <c r="J9" s="74"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="30"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
     </row>
     <row r="10" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="71"/>
-      <c r="B10" s="68" t="s">
+      <c r="A10" s="70"/>
+      <c r="B10" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68" t="s">
+      <c r="C10" s="67"/>
+      <c r="D10" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="80" t="s">
+      <c r="E10" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="68"/>
-      <c r="G10" s="35"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="29"/>
       <c r="I10" s="29"/>
-      <c r="J10" s="75"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
+      <c r="J10" s="74"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="30"/>
-      <c r="O10" s="74"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-    </row>
-    <row r="11" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="71"/>
-      <c r="B11" s="68" t="s">
+      <c r="O10" s="73"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+    </row>
+    <row r="11" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="70"/>
+      <c r="B11" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68" t="s">
+      <c r="C11" s="67"/>
+      <c r="D11" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="80" t="s">
+      <c r="E11" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="68"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="73"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="30"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="71"/>
-      <c r="B12" s="68" t="s">
+      <c r="A12" s="70"/>
+      <c r="B12" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68" t="s">
+      <c r="C12" s="67"/>
+      <c r="D12" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="80" t="s">
+      <c r="E12" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="F12" s="68"/>
-      <c r="G12" s="35"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="27"/>
       <c r="I12" s="28"/>
       <c r="J12" s="29"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="30"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
     </row>
     <row r="13" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="71"/>
-      <c r="B13" s="68" t="s">
+      <c r="A13" s="70"/>
+      <c r="B13" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68" t="s">
+      <c r="C13" s="67"/>
+      <c r="D13" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="80" t="s">
+      <c r="E13" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="F13" s="68"/>
-      <c r="G13" s="35"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="27"/>
       <c r="I13" s="28"/>
       <c r="J13" s="29"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="30"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
     </row>
     <row r="14" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="71"/>
-      <c r="B14" s="68" t="s">
+      <c r="A14" s="70"/>
+      <c r="B14" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68" t="s">
+      <c r="C14" s="67"/>
+      <c r="D14" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="80" t="s">
+      <c r="E14" s="79" t="s">
         <v>149</v>
       </c>
-      <c r="F14" s="68"/>
-      <c r="G14" s="35"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="27"/>
       <c r="I14" s="29"/>
-      <c r="J14" s="75"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
+      <c r="J14" s="74"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="30"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
     </row>
     <row r="15" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="71"/>
-      <c r="B15" s="68" t="s">
+      <c r="A15" s="70"/>
+      <c r="B15" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68" t="s">
+      <c r="C15" s="67"/>
+      <c r="D15" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="80" t="s">
+      <c r="E15" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="35"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="27"/>
       <c r="I15" s="29"/>
-      <c r="J15" s="75"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
+      <c r="J15" s="74"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="30"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
     </row>
     <row r="16" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="71"/>
-      <c r="B16" s="68" t="s">
+      <c r="A16" s="70"/>
+      <c r="B16" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68" t="s">
+      <c r="C16" s="67"/>
+      <c r="D16" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="80" t="s">
+      <c r="E16" s="79" t="s">
         <v>150</v>
       </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="35"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="27"/>
       <c r="I16" s="29"/>
-      <c r="J16" s="75"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
+      <c r="J16" s="74"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
       <c r="N16" s="30"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35" t="s">
+      <c r="O16" s="73"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="71"/>
-      <c r="B17" s="68" t="s">
+      <c r="A17" s="70"/>
+      <c r="B17" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68" t="s">
+      <c r="C17" s="67"/>
+      <c r="D17" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="80" t="s">
+      <c r="E17" s="79" t="s">
         <v>152</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="35"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="27"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
       <c r="N17" s="30"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="71"/>
-      <c r="B18" s="68" t="s">
+      <c r="A18" s="70"/>
+      <c r="B18" s="67" t="s">
         <v>153</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68" t="s">
+      <c r="C18" s="67"/>
+      <c r="D18" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="80" t="s">
+      <c r="E18" s="79" t="s">
         <v>154</v>
       </c>
-      <c r="F18" s="68"/>
-      <c r="G18" s="35"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="27"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="30"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="71"/>
-      <c r="B19" s="68" t="s">
+      <c r="A19" s="70"/>
+      <c r="B19" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68" t="s">
+      <c r="C19" s="67"/>
+      <c r="D19" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="80" t="s">
+      <c r="E19" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="68"/>
-      <c r="G19" s="35"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="27"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="30"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
+      <c r="O19" s="73"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
     </row>
     <row r="20" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="71"/>
-      <c r="B20" s="68" t="s">
+      <c r="A20" s="70"/>
+      <c r="B20" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="79"/>
-      <c r="D20" s="68" t="s">
+      <c r="C20" s="78"/>
+      <c r="D20" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="80" t="s">
+      <c r="E20" s="79" t="s">
         <v>158</v>
       </c>
-      <c r="F20" s="79"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="30"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
     </row>
     <row r="21" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="71"/>
-      <c r="B21" s="68" t="s">
+      <c r="A21" s="70"/>
+      <c r="B21" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68" t="s">
+      <c r="C21" s="67"/>
+      <c r="D21" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="80" t="s">
+      <c r="E21" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="F21" s="68"/>
-      <c r="G21" s="35"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="27"/>
       <c r="I21" s="29"/>
       <c r="J21" s="29"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="30"/>
-      <c r="O21" s="74"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
+      <c r="O21" s="73"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
     </row>
     <row r="22" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="71"/>
-      <c r="B22" s="68" t="s">
+      <c r="A22" s="70"/>
+      <c r="B22" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68" t="s">
+      <c r="C22" s="67"/>
+      <c r="D22" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="80" t="s">
+      <c r="E22" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="68"/>
-      <c r="G22" s="35"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="27"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="30"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
     </row>
     <row r="23" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68" t="s">
+      <c r="A23" s="84"/>
+      <c r="B23" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68" t="s">
+      <c r="C23" s="67"/>
+      <c r="D23" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="80" t="s">
+      <c r="E23" s="79" t="s">
         <v>87</v>
       </c>
       <c r="F23" s="26"/>
       <c r="G23" s="26"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="87"/>
-      <c r="J23" s="87"/>
-      <c r="L23" s="88"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="L23" s="87"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="90"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="89"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
     <row r="24" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68" t="s">
+      <c r="A24" s="84"/>
+      <c r="B24" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68" t="s">
+      <c r="C24" s="67"/>
+      <c r="D24" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="80" t="s">
+      <c r="E24" s="79" t="s">
         <v>45</v>
       </c>
       <c r="F24" s="26"/>
       <c r="G24" s="26"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
-      <c r="L24" s="88"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="L24" s="87"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="90"/>
+      <c r="N24" s="88"/>
+      <c r="O24" s="89"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
     <row r="25" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68" t="s">
+      <c r="A25" s="84"/>
+      <c r="B25" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68" t="s">
+      <c r="C25" s="67"/>
+      <c r="D25" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="E25" s="80" t="s">
+      <c r="E25" s="79" t="s">
         <v>97</v>
       </c>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="L25" s="88"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="L25" s="87"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="90"/>
+      <c r="N25" s="88"/>
+      <c r="O25" s="89"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
     <row r="26" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68" t="s">
+      <c r="A26" s="84"/>
+      <c r="B26" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68" t="s">
+      <c r="C26" s="67"/>
+      <c r="D26" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="E26" s="80" t="s">
+      <c r="E26" s="79" t="s">
         <v>95</v>
       </c>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="L26" s="88"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="L26" s="87"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="90"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="89"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
     <row r="27" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="91"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="90"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="L27" s="88"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="86"/>
+      <c r="L27" s="87"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="90"/>
+      <c r="N27" s="88"/>
+      <c r="O27" s="89"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
     <row r="28" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="91"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="90"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="L28" s="88"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="L28" s="87"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="89"/>
-      <c r="O28" s="90"/>
+      <c r="N28" s="88"/>
+      <c r="O28" s="89"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
     <row r="29" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="91"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="90"/>
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="L29" s="88"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="86"/>
+      <c r="L29" s="87"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="90"/>
+      <c r="N29" s="88"/>
+      <c r="O29" s="89"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
     <row r="30" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="91"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="90"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="L30" s="88"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="L30" s="87"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="90"/>
+      <c r="N30" s="88"/>
+      <c r="O30" s="89"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
     <row r="31" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="91"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="90"/>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="L31" s="88"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="86"/>
+      <c r="L31" s="87"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="89"/>
-      <c r="O31" s="90"/>
+      <c r="N31" s="88"/>
+      <c r="O31" s="89"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
     <row r="32" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="91"/>
+      <c r="A32" s="84"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="90"/>
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="L32" s="88"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="L32" s="87"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="90"/>
+      <c r="N32" s="88"/>
+      <c r="O32" s="89"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
     <row r="33" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28"/>
       <c r="J33" s="29"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="44"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="39"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="38"/>
     </row>
     <row r="34" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B34" s="40"/>
+      <c r="B34" s="39"/>
       <c r="C34" s="25"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="27"/>
       <c r="I34" s="28"/>
       <c r="J34" s="29"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="39"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="38"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
       <c r="B35" s="7" t="s">
@@ -10495,7 +10492,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
-      <c r="L35" s="45" t="s">
+      <c r="L35" s="44" t="s">
         <v>99</v>
       </c>
       <c r="M35" s="17"/>
@@ -10505,25 +10502,25 @@
       <c r="Q35" s="17"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="46" t="s">
+      <c r="C36" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="46" t="s">
+      <c r="D36" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="L36" s="47" t="s">
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="L36" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="M36" s="48" t="s">
+      <c r="M36" s="47" t="s">
         <v>102</v>
       </c>
       <c r="N36" s="21" t="s">
@@ -10532,14 +10529,14 @@
       <c r="O36" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P36" s="49" t="s">
+      <c r="P36" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="Q36" s="50"/>
+      <c r="Q36" s="49"/>
     </row>
     <row r="37" s="3" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
-      <c r="B37" s="51"/>
-      <c r="C37" s="52"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
       <c r="D37" s="29"/>
       <c r="E37" s="29"/>
       <c r="F37" s="29"/>
@@ -10547,50 +10544,50 @@
       <c r="H37" s="29"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
-      <c r="L37" s="35" t="s">
+      <c r="L37" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="M37" s="35" t="s">
+      <c r="M37" s="24" t="s">
         <v>107</v>
       </c>
       <c r="N37" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="O37" s="74"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="50"/>
+      <c r="O37" s="73"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="49"/>
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L38" s="35" t="s">
+      <c r="L38" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="M38" s="35" t="s">
+      <c r="M38" s="24" t="s">
         <v>110</v>
       </c>
       <c r="N38" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="O38" s="74"/>
-      <c r="P38" s="56" t="s">
+      <c r="O38" s="73"/>
+      <c r="P38" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="Q38" s="50"/>
+      <c r="Q38" s="49"/>
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L39" s="35" t="s">
+      <c r="L39" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="M39" s="35" t="s">
+      <c r="M39" s="24" t="s">
         <v>114</v>
       </c>
       <c r="N39" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="O39" s="74"/>
-      <c r="P39" s="56" t="s">
+      <c r="O39" s="73"/>
+      <c r="P39" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="Q39" s="50"/>
+      <c r="Q39" s="49"/>
     </row>
     <row r="40" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A40" s="5"/>
@@ -10604,14 +10601,14 @@
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
       <c r="N40" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="O40" s="74"/>
-      <c r="P40" s="57"/>
-      <c r="Q40" s="50"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="49"/>
     </row>
     <row r="41" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A41" s="5"/>
@@ -10625,12 +10622,12 @@
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="57"/>
-      <c r="Q41" s="50"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="56"/>
+      <c r="Q41" s="49"/>
     </row>
     <row r="42" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A42" s="5"/>
@@ -10644,12 +10641,12 @@
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
-      <c r="L42" s="58"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="50"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="38"/>
+      <c r="P42" s="56"/>
+      <c r="Q42" s="49"/>
     </row>
     <row r="43" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A43" s="5"/>
@@ -10663,12 +10660,12 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="58"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="57"/>
-      <c r="Q43" s="50"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="56"/>
+      <c r="Q43" s="49"/>
     </row>
     <row r="44" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A44" s="5"/>
@@ -10682,12 +10679,12 @@
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
-      <c r="L44" s="58"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="50"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="56"/>
+      <c r="Q44" s="49"/>
     </row>
     <row r="45" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A45" s="5"/>
@@ -10701,12 +10698,12 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="39"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="39"/>
-      <c r="P45" s="57"/>
-      <c r="Q45" s="50"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="38"/>
+      <c r="P45" s="56"/>
+      <c r="Q45" s="49"/>
     </row>
     <row r="46" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A46" s="5"/>
@@ -10720,12 +10717,12 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
-      <c r="L46" s="59"/>
-      <c r="M46" s="60"/>
-      <c r="N46" s="61"/>
-      <c r="O46" s="39"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="50"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="59"/>
+      <c r="N46" s="60"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="49"/>
     </row>
     <row r="47" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A47" s="5"/>
@@ -10739,7 +10736,7 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
-      <c r="L47" s="63" t="s">
+      <c r="L47" s="62" t="s">
         <v>118</v>
       </c>
       <c r="M47" s="17"/>
@@ -10760,7 +10757,7 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
-      <c r="L48" s="64" t="s">
+      <c r="L48" s="63" t="s">
         <v>119</v>
       </c>
       <c r="M48" s="17"/>
@@ -10954,526 +10951,526 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="22"/>
     </row>
-    <row r="6" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="71"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
+    <row r="6" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="70"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-    </row>
-    <row r="7" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="71"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+    </row>
+    <row r="7" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="70"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
       <c r="N7" s="30"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-    </row>
-    <row r="8" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="71"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+    </row>
+    <row r="8" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="70"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
     </row>
     <row r="9" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="71"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="35"/>
+      <c r="A9" s="70"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="29"/>
       <c r="I9" s="29"/>
-      <c r="J9" s="75"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
+      <c r="J9" s="74"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="30"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
     </row>
     <row r="10" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="71"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="35"/>
+      <c r="A10" s="70"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="29"/>
       <c r="I10" s="29"/>
-      <c r="J10" s="75"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
+      <c r="J10" s="74"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="30"/>
-      <c r="O10" s="74"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-    </row>
-    <row r="11" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="71"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="73"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+    </row>
+    <row r="11" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="70"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="30"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="71"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="35"/>
+      <c r="A12" s="70"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="27"/>
       <c r="I12" s="28"/>
       <c r="J12" s="29"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="30"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
     </row>
     <row r="13" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="71"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="35"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="27"/>
       <c r="I13" s="28"/>
       <c r="J13" s="29"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="30"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
     </row>
     <row r="14" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="71"/>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="35"/>
+      <c r="A14" s="70"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="27"/>
       <c r="I14" s="29"/>
-      <c r="J14" s="75"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
+      <c r="J14" s="74"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="30"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
     </row>
     <row r="15" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="71"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="35"/>
+      <c r="A15" s="70"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="27"/>
       <c r="I15" s="29"/>
-      <c r="J15" s="75"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
+      <c r="J15" s="74"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="30"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
     </row>
     <row r="16" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="71"/>
-      <c r="B16" s="68"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="35"/>
+      <c r="A16" s="70"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="27"/>
       <c r="I16" s="29"/>
-      <c r="J16" s="75"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
+      <c r="J16" s="74"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
       <c r="N16" s="30"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
+      <c r="O16" s="73"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
     </row>
     <row r="17" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="71"/>
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="35"/>
+      <c r="A17" s="70"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="27"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
       <c r="N17" s="30"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="71"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="35"/>
+      <c r="A18" s="70"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="27"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="30"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="71"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="35"/>
+      <c r="A19" s="70"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="27"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="30"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
+      <c r="O19" s="73"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
     </row>
     <row r="20" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="71"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
+      <c r="A20" s="70"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="30"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
     </row>
     <row r="21" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="71"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="35"/>
+      <c r="A21" s="70"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="27"/>
       <c r="I21" s="29"/>
       <c r="J21" s="29"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="30"/>
-      <c r="O21" s="74"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
+      <c r="O21" s="73"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
     </row>
     <row r="22" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="71"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="35"/>
+      <c r="A22" s="70"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="27"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="30"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
     </row>
     <row r="23" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="80"/>
+      <c r="A23" s="84"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="79"/>
       <c r="F23" s="26"/>
       <c r="G23" s="26"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="87"/>
-      <c r="J23" s="87"/>
-      <c r="L23" s="88"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="L23" s="87"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="90"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="89"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
     <row r="24" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="80"/>
+      <c r="A24" s="84"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="79"/>
       <c r="F24" s="26"/>
       <c r="G24" s="26"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
-      <c r="L24" s="88"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="L24" s="87"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="90"/>
+      <c r="N24" s="88"/>
+      <c r="O24" s="89"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
     <row r="25" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="80"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="79"/>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="L25" s="88"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="L25" s="87"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="90"/>
+      <c r="N25" s="88"/>
+      <c r="O25" s="89"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
     <row r="26" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="80"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="79"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="L26" s="88"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="L26" s="87"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="90"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="89"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
     <row r="27" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="91"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="90"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="L27" s="88"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="86"/>
+      <c r="L27" s="87"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="90"/>
+      <c r="N27" s="88"/>
+      <c r="O27" s="89"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
     <row r="28" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="91"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="90"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="L28" s="88"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="L28" s="87"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="89"/>
-      <c r="O28" s="90"/>
+      <c r="N28" s="88"/>
+      <c r="O28" s="89"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
     <row r="29" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="91"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="90"/>
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="L29" s="88"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="86"/>
+      <c r="L29" s="87"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="90"/>
+      <c r="N29" s="88"/>
+      <c r="O29" s="89"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
     <row r="30" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="91"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="90"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="L30" s="88"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="L30" s="87"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="90"/>
+      <c r="N30" s="88"/>
+      <c r="O30" s="89"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
     <row r="31" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="91"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="90"/>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="L31" s="88"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="86"/>
+      <c r="L31" s="87"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="89"/>
-      <c r="O31" s="90"/>
+      <c r="N31" s="88"/>
+      <c r="O31" s="89"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
     <row r="32" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="91"/>
+      <c r="A32" s="84"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="90"/>
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="L32" s="88"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="L32" s="87"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="90"/>
+      <c r="N32" s="88"/>
+      <c r="O32" s="89"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
     <row r="33" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28"/>
       <c r="J33" s="29"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="44"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="39"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="38"/>
     </row>
     <row r="34" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B34" s="40"/>
+      <c r="B34" s="39"/>
       <c r="C34" s="25"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="27"/>
       <c r="I34" s="28"/>
       <c r="J34" s="29"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="39"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="38"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
       <c r="B35" s="7"/>
@@ -11485,7 +11482,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
-      <c r="L35" s="45"/>
+      <c r="L35" s="44"/>
       <c r="M35" s="17"/>
       <c r="N35" s="17"/>
       <c r="O35" s="17"/>
@@ -11493,25 +11490,25 @@
       <c r="Q35" s="17"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="L36" s="47"/>
-      <c r="M36" s="48"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="47"/>
       <c r="N36" s="21"/>
       <c r="O36" s="21"/>
-      <c r="P36" s="49"/>
-      <c r="Q36" s="50"/>
+      <c r="P36" s="48"/>
+      <c r="Q36" s="49"/>
     </row>
     <row r="37" s="3" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
-      <c r="B37" s="51"/>
-      <c r="C37" s="52"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
       <c r="D37" s="29"/>
       <c r="E37" s="29"/>
       <c r="F37" s="29"/>
@@ -11519,28 +11516,28 @@
       <c r="H37" s="29"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="35"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24"/>
       <c r="N37" s="30"/>
-      <c r="O37" s="74"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="50"/>
+      <c r="O37" s="73"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="49"/>
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L38" s="35"/>
-      <c r="M38" s="35"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24"/>
       <c r="N38" s="30"/>
-      <c r="O38" s="74"/>
-      <c r="P38" s="56"/>
-      <c r="Q38" s="50"/>
+      <c r="O38" s="73"/>
+      <c r="P38" s="55"/>
+      <c r="Q38" s="49"/>
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L39" s="35"/>
-      <c r="M39" s="35"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="24"/>
       <c r="N39" s="30"/>
-      <c r="O39" s="74"/>
-      <c r="P39" s="56"/>
-      <c r="Q39" s="50"/>
+      <c r="O39" s="73"/>
+      <c r="P39" s="55"/>
+      <c r="Q39" s="49"/>
     </row>
     <row r="40" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A40" s="5"/>
@@ -11554,12 +11551,12 @@
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
       <c r="N40" s="30"/>
-      <c r="O40" s="74"/>
-      <c r="P40" s="57"/>
-      <c r="Q40" s="50"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="49"/>
     </row>
     <row r="41" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A41" s="5"/>
@@ -11573,12 +11570,12 @@
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="57"/>
-      <c r="Q41" s="50"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="56"/>
+      <c r="Q41" s="49"/>
     </row>
     <row r="42" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A42" s="5"/>
@@ -11592,12 +11589,12 @@
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
-      <c r="L42" s="58"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="50"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="38"/>
+      <c r="P42" s="56"/>
+      <c r="Q42" s="49"/>
     </row>
     <row r="43" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A43" s="5"/>
@@ -11611,12 +11608,12 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="58"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="57"/>
-      <c r="Q43" s="50"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="56"/>
+      <c r="Q43" s="49"/>
     </row>
     <row r="44" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A44" s="5"/>
@@ -11630,12 +11627,12 @@
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
-      <c r="L44" s="58"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="50"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="56"/>
+      <c r="Q44" s="49"/>
     </row>
     <row r="45" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A45" s="5"/>
@@ -11649,12 +11646,12 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="39"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="39"/>
-      <c r="P45" s="57"/>
-      <c r="Q45" s="50"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="38"/>
+      <c r="P45" s="56"/>
+      <c r="Q45" s="49"/>
     </row>
     <row r="46" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A46" s="5"/>
@@ -11668,12 +11665,12 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
-      <c r="L46" s="59"/>
-      <c r="M46" s="60"/>
-      <c r="N46" s="61"/>
-      <c r="O46" s="39"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="50"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="59"/>
+      <c r="N46" s="60"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="49"/>
     </row>
     <row r="47" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A47" s="5"/>
@@ -11687,7 +11684,7 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
-      <c r="L47" s="63"/>
+      <c r="L47" s="62"/>
       <c r="M47" s="17"/>
       <c r="N47" s="17"/>
       <c r="O47" s="17"/>
@@ -11706,7 +11703,7 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
-      <c r="L48" s="64"/>
+      <c r="L48" s="63"/>
       <c r="M48" s="17"/>
       <c r="N48" s="17"/>
       <c r="O48" s="17"/>
@@ -11938,612 +11935,612 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="71"/>
-      <c r="B6" s="68" t="s">
+    <row r="6" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="70"/>
+      <c r="B6" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68" t="s">
+      <c r="C6" s="67"/>
+      <c r="D6" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-    </row>
-    <row r="7" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="71"/>
-      <c r="B7" s="68" t="s">
+      <c r="O6" s="73"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+    </row>
+    <row r="7" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="70"/>
+      <c r="B7" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68" t="s">
+      <c r="C7" s="67"/>
+      <c r="D7" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="68" t="s">
+      <c r="E7" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
       <c r="N7" s="30"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-    </row>
-    <row r="8" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="71"/>
-      <c r="B8" s="68" t="s">
+      <c r="O7" s="73"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+    </row>
+    <row r="8" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="70"/>
+      <c r="B8" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68" t="s">
+      <c r="C8" s="67"/>
+      <c r="D8" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="68" t="s">
+      <c r="E8" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
     </row>
     <row r="9" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="71"/>
-      <c r="B9" s="68" t="s">
+      <c r="A9" s="70"/>
+      <c r="B9" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68" t="s">
+      <c r="C9" s="67"/>
+      <c r="D9" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="68" t="s">
+      <c r="E9" s="67" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="68"/>
-      <c r="G9" s="35"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="29"/>
       <c r="I9" s="29"/>
-      <c r="J9" s="75"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
+      <c r="J9" s="74"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="30"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
     </row>
     <row r="10" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="71"/>
-      <c r="B10" s="68" t="s">
+      <c r="A10" s="70"/>
+      <c r="B10" s="67" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68" t="s">
+      <c r="C10" s="67"/>
+      <c r="D10" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="68" t="s">
+      <c r="E10" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="F10" s="68"/>
-      <c r="G10" s="35"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="29"/>
       <c r="I10" s="29"/>
-      <c r="J10" s="75"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
+      <c r="J10" s="74"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="30"/>
-      <c r="O10" s="74"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-    </row>
-    <row r="11" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="71"/>
-      <c r="B11" s="68" t="s">
+      <c r="O10" s="73"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+    </row>
+    <row r="11" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="70"/>
+      <c r="B11" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68" t="s">
+      <c r="C11" s="67"/>
+      <c r="D11" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="68" t="s">
+      <c r="E11" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="F11" s="68"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="73"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="30"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="71"/>
-      <c r="B12" s="68" t="s">
+      <c r="A12" s="70"/>
+      <c r="B12" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68" t="s">
+      <c r="C12" s="67"/>
+      <c r="D12" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="F12" s="68"/>
-      <c r="G12" s="35"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="27"/>
       <c r="I12" s="28"/>
       <c r="J12" s="29"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="30"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
     </row>
     <row r="13" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="71"/>
-      <c r="B13" s="68" t="s">
+      <c r="A13" s="70"/>
+      <c r="B13" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68" t="s">
+      <c r="C13" s="67"/>
+      <c r="D13" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="68" t="s">
+      <c r="E13" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="F13" s="68"/>
-      <c r="G13" s="35"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="27"/>
       <c r="I13" s="28"/>
       <c r="J13" s="29"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="30"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
     </row>
     <row r="14" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="71"/>
-      <c r="B14" s="68" t="s">
+      <c r="A14" s="70"/>
+      <c r="B14" s="67" t="s">
         <v>177</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68" t="s">
+      <c r="C14" s="67"/>
+      <c r="D14" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="E14" s="68" t="s">
+      <c r="E14" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="F14" s="68"/>
-      <c r="G14" s="35"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="27"/>
       <c r="I14" s="29"/>
-      <c r="J14" s="75"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
+      <c r="J14" s="74"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="30"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
     </row>
     <row r="15" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="71"/>
-      <c r="B15" s="68" t="s">
+      <c r="A15" s="70"/>
+      <c r="B15" s="67" t="s">
         <v>179</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68" t="s">
+      <c r="C15" s="67"/>
+      <c r="D15" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="E15" s="68" t="s">
+      <c r="E15" s="67" t="s">
         <v>180</v>
       </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="35"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="27"/>
       <c r="I15" s="29"/>
-      <c r="J15" s="75"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
+      <c r="J15" s="74"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="30"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
     </row>
     <row r="16" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="71"/>
-      <c r="B16" s="68" t="s">
+      <c r="A16" s="70"/>
+      <c r="B16" s="67" t="s">
         <v>181</v>
       </c>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68" t="s">
+      <c r="C16" s="67"/>
+      <c r="D16" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="68" t="s">
+      <c r="E16" s="67" t="s">
         <v>182</v>
       </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="35"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="27"/>
       <c r="I16" s="29"/>
-      <c r="J16" s="75"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
+      <c r="J16" s="74"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
       <c r="N16" s="30"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35" t="s">
+      <c r="O16" s="73"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="71"/>
-      <c r="B17" s="76" t="s">
+      <c r="A17" s="70"/>
+      <c r="B17" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68" t="s">
+      <c r="C17" s="67"/>
+      <c r="D17" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="E17" s="68" t="s">
+      <c r="E17" s="67" t="s">
         <v>185</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="35"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="27"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
       <c r="N17" s="30"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="71"/>
-      <c r="B18" s="77" t="s">
+      <c r="A18" s="70"/>
+      <c r="B18" s="76" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="78" t="s">
+      <c r="C18" s="67"/>
+      <c r="D18" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="77" t="s">
+      <c r="E18" s="76" t="s">
         <v>187</v>
       </c>
-      <c r="F18" s="68"/>
-      <c r="G18" s="35"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="27"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="30"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="71"/>
-      <c r="B19" s="68" t="s">
+      <c r="A19" s="70"/>
+      <c r="B19" s="67" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="68"/>
-      <c r="D19" s="78" t="s">
+      <c r="C19" s="67"/>
+      <c r="D19" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="68" t="s">
+      <c r="E19" s="67" t="s">
         <v>189</v>
       </c>
-      <c r="F19" s="68"/>
-      <c r="G19" s="35"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="27"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="30"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
+      <c r="O19" s="73"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
     </row>
     <row r="20" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="71"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
+      <c r="A20" s="70"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="30"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
     </row>
     <row r="21" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="71"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="35"/>
+      <c r="A21" s="70"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="27"/>
       <c r="I21" s="29"/>
       <c r="J21" s="29"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="30"/>
-      <c r="O21" s="74"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
+      <c r="O21" s="73"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
     </row>
     <row r="22" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="71"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="35"/>
+      <c r="A22" s="70"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="27"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="30"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
     </row>
     <row r="23" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="80"/>
+      <c r="A23" s="84"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="79"/>
       <c r="F23" s="26"/>
       <c r="G23" s="26"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="87"/>
-      <c r="J23" s="87"/>
-      <c r="L23" s="88"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="L23" s="87"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="90"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="89"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
     <row r="24" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="80"/>
+      <c r="A24" s="84"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="79"/>
       <c r="F24" s="26"/>
       <c r="G24" s="26"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
-      <c r="L24" s="88"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="L24" s="87"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="90"/>
+      <c r="N24" s="88"/>
+      <c r="O24" s="89"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
     <row r="25" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="80"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="79"/>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="L25" s="88"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="L25" s="87"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="90"/>
+      <c r="N25" s="88"/>
+      <c r="O25" s="89"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
     <row r="26" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="80"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="79"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="L26" s="88"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="L26" s="87"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="90"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="89"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
     <row r="27" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="91"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="90"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="L27" s="88"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="86"/>
+      <c r="L27" s="87"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="90"/>
+      <c r="N27" s="88"/>
+      <c r="O27" s="89"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
     <row r="28" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="91"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="90"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="L28" s="88"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="L28" s="87"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="89"/>
-      <c r="O28" s="90"/>
+      <c r="N28" s="88"/>
+      <c r="O28" s="89"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
     <row r="29" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="91"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="90"/>
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="L29" s="88"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="86"/>
+      <c r="L29" s="87"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="90"/>
+      <c r="N29" s="88"/>
+      <c r="O29" s="89"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
     <row r="30" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="91"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="90"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="L30" s="88"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="L30" s="87"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="90"/>
+      <c r="N30" s="88"/>
+      <c r="O30" s="89"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
     <row r="31" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="91"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="90"/>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="L31" s="88"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="86"/>
+      <c r="L31" s="87"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="89"/>
-      <c r="O31" s="90"/>
+      <c r="N31" s="88"/>
+      <c r="O31" s="89"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
     <row r="32" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="91"/>
+      <c r="A32" s="84"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="90"/>
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="L32" s="88"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="L32" s="87"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="90"/>
+      <c r="N32" s="88"/>
+      <c r="O32" s="89"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
     <row r="33" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28"/>
       <c r="J33" s="29"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="44"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="39"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="38"/>
     </row>
     <row r="34" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B34" s="40"/>
+      <c r="B34" s="39"/>
       <c r="C34" s="25"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="27"/>
       <c r="I34" s="28"/>
       <c r="J34" s="29"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="39"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="38"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
       <c r="B35" s="7" t="s">
@@ -12557,7 +12554,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
-      <c r="L35" s="45" t="s">
+      <c r="L35" s="44" t="s">
         <v>99</v>
       </c>
       <c r="M35" s="17"/>
@@ -12567,25 +12564,25 @@
       <c r="Q35" s="17"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="46" t="s">
+      <c r="C36" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="46" t="s">
+      <c r="D36" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="L36" s="47" t="s">
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="L36" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="M36" s="48" t="s">
+      <c r="M36" s="47" t="s">
         <v>102</v>
       </c>
       <c r="N36" s="21" t="s">
@@ -12594,14 +12591,14 @@
       <c r="O36" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P36" s="49" t="s">
+      <c r="P36" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="Q36" s="50"/>
+      <c r="Q36" s="49"/>
     </row>
     <row r="37" s="3" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
-      <c r="B37" s="51"/>
-      <c r="C37" s="52"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
       <c r="D37" s="29"/>
       <c r="E37" s="29"/>
       <c r="F37" s="29"/>
@@ -12609,50 +12606,50 @@
       <c r="H37" s="29"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
-      <c r="L37" s="35" t="s">
+      <c r="L37" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="M37" s="35" t="s">
+      <c r="M37" s="24" t="s">
         <v>107</v>
       </c>
       <c r="N37" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="O37" s="74"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="50"/>
+      <c r="O37" s="73"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="49"/>
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L38" s="35" t="s">
+      <c r="L38" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="M38" s="35" t="s">
+      <c r="M38" s="24" t="s">
         <v>110</v>
       </c>
       <c r="N38" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="O38" s="74"/>
-      <c r="P38" s="56" t="s">
+      <c r="O38" s="73"/>
+      <c r="P38" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="Q38" s="50"/>
+      <c r="Q38" s="49"/>
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L39" s="35" t="s">
+      <c r="L39" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="M39" s="35" t="s">
+      <c r="M39" s="24" t="s">
         <v>114</v>
       </c>
       <c r="N39" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="O39" s="74"/>
-      <c r="P39" s="56" t="s">
+      <c r="O39" s="73"/>
+      <c r="P39" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="Q39" s="50"/>
+      <c r="Q39" s="49"/>
     </row>
     <row r="40" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A40" s="5"/>
@@ -12666,14 +12663,14 @@
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
       <c r="N40" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="O40" s="74"/>
-      <c r="P40" s="57"/>
-      <c r="Q40" s="50"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="49"/>
     </row>
     <row r="41" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A41" s="5"/>
@@ -12687,12 +12684,12 @@
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="57"/>
-      <c r="Q41" s="50"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="56"/>
+      <c r="Q41" s="49"/>
     </row>
     <row r="42" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A42" s="5"/>
@@ -12706,12 +12703,12 @@
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
-      <c r="L42" s="58"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="50"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="38"/>
+      <c r="P42" s="56"/>
+      <c r="Q42" s="49"/>
     </row>
     <row r="43" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A43" s="5"/>
@@ -12725,12 +12722,12 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="58"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="57"/>
-      <c r="Q43" s="50"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="56"/>
+      <c r="Q43" s="49"/>
     </row>
     <row r="44" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A44" s="5"/>
@@ -12744,12 +12741,12 @@
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
-      <c r="L44" s="58"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="50"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="56"/>
+      <c r="Q44" s="49"/>
     </row>
     <row r="45" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A45" s="5"/>
@@ -12763,12 +12760,12 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="39"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="39"/>
-      <c r="P45" s="57"/>
-      <c r="Q45" s="50"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="38"/>
+      <c r="P45" s="56"/>
+      <c r="Q45" s="49"/>
     </row>
     <row r="46" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A46" s="5"/>
@@ -12782,12 +12779,12 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
-      <c r="L46" s="59"/>
-      <c r="M46" s="60"/>
-      <c r="N46" s="61"/>
-      <c r="O46" s="39"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="50"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="59"/>
+      <c r="N46" s="60"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="49"/>
     </row>
     <row r="47" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A47" s="5"/>
@@ -12801,7 +12798,7 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
-      <c r="L47" s="63" t="s">
+      <c r="L47" s="62" t="s">
         <v>118</v>
       </c>
       <c r="M47" s="17"/>
@@ -12822,7 +12819,7 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
-      <c r="L48" s="64" t="s">
+      <c r="L48" s="63" t="s">
         <v>119</v>
       </c>
       <c r="M48" s="17"/>
@@ -13056,588 +13053,588 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="71"/>
-      <c r="B6" s="68" t="s">
+    <row r="6" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="70"/>
+      <c r="B6" s="67" t="s">
         <v>192</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68" t="s">
+      <c r="C6" s="67"/>
+      <c r="D6" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
       <c r="N6" s="30"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-    </row>
-    <row r="7" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="71"/>
-      <c r="B7" s="68" t="s">
+      <c r="O6" s="73"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+    </row>
+    <row r="7" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="70"/>
+      <c r="B7" s="67" t="s">
         <v>193</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68" t="s">
+      <c r="C7" s="67"/>
+      <c r="D7" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="68" t="s">
+      <c r="E7" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
       <c r="N7" s="30"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-    </row>
-    <row r="8" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="71"/>
-      <c r="B8" s="68" t="s">
+      <c r="O7" s="73"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+    </row>
+    <row r="8" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="70"/>
+      <c r="B8" s="67" t="s">
         <v>194</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68" t="s">
+      <c r="C8" s="67"/>
+      <c r="D8" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="68" t="s">
+      <c r="E8" s="67" t="s">
         <v>195</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="30"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
     </row>
     <row r="9" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="71"/>
-      <c r="B9" s="68" t="s">
+      <c r="A9" s="70"/>
+      <c r="B9" s="67" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68" t="s">
+      <c r="C9" s="67"/>
+      <c r="D9" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="68" t="s">
+      <c r="E9" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="F9" s="68"/>
-      <c r="G9" s="35"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="29"/>
       <c r="I9" s="29"/>
-      <c r="J9" s="75"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
+      <c r="J9" s="74"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="30"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
     </row>
     <row r="10" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="71"/>
-      <c r="B10" s="68" t="s">
+      <c r="A10" s="70"/>
+      <c r="B10" s="67" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68" t="s">
+      <c r="C10" s="67"/>
+      <c r="D10" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="68" t="s">
+      <c r="E10" s="67" t="s">
         <v>199</v>
       </c>
-      <c r="F10" s="68"/>
-      <c r="G10" s="35"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="29"/>
       <c r="I10" s="29"/>
-      <c r="J10" s="75"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
+      <c r="J10" s="74"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="30"/>
-      <c r="O10" s="74"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-    </row>
-    <row r="11" s="70" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="71"/>
-      <c r="B11" s="68" t="s">
+      <c r="O10" s="73"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+    </row>
+    <row r="11" s="69" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="70"/>
+      <c r="B11" s="67" t="s">
         <v>200</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68" t="s">
+      <c r="C11" s="67"/>
+      <c r="D11" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="68" t="s">
+      <c r="E11" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="F11" s="68"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="73"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="30"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="71"/>
-      <c r="B12" s="68" t="s">
+      <c r="A12" s="70"/>
+      <c r="B12" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68" t="s">
+      <c r="C12" s="67"/>
+      <c r="D12" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="67" t="s">
         <v>203</v>
       </c>
-      <c r="F12" s="68"/>
-      <c r="G12" s="35"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="27"/>
       <c r="I12" s="28"/>
       <c r="J12" s="29"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="30"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
     </row>
     <row r="13" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="71"/>
-      <c r="B13" s="68" t="s">
+      <c r="A13" s="70"/>
+      <c r="B13" s="67" t="s">
         <v>204</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68" t="s">
+      <c r="C13" s="67"/>
+      <c r="D13" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="E13" s="68" t="s">
+      <c r="E13" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="68"/>
-      <c r="G13" s="35"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="27"/>
       <c r="I13" s="28"/>
       <c r="J13" s="29"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="30"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
     </row>
     <row r="14" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="71"/>
-      <c r="B14" s="68" t="s">
+      <c r="A14" s="70"/>
+      <c r="B14" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68" t="s">
+      <c r="C14" s="67"/>
+      <c r="D14" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="68" t="s">
+      <c r="E14" s="67" t="s">
         <v>206</v>
       </c>
-      <c r="F14" s="68"/>
-      <c r="G14" s="35"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="27"/>
       <c r="I14" s="29"/>
-      <c r="J14" s="75"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
+      <c r="J14" s="74"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="30"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
     </row>
     <row r="15" s="4" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="71"/>
-      <c r="B15" s="68" t="s">
+      <c r="A15" s="70"/>
+      <c r="B15" s="67" t="s">
         <v>207</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68" t="s">
+      <c r="C15" s="67"/>
+      <c r="D15" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="68" t="s">
+      <c r="E15" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="35"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="27"/>
       <c r="I15" s="29"/>
-      <c r="J15" s="75"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
+      <c r="J15" s="74"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="30"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
     </row>
     <row r="16" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="71"/>
-      <c r="B16" s="68"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="35"/>
+      <c r="A16" s="70"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="27"/>
       <c r="I16" s="29"/>
-      <c r="J16" s="75"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
+      <c r="J16" s="74"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
       <c r="N16" s="30"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35" t="s">
+      <c r="O16" s="73"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="71"/>
-      <c r="B17" s="76"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="35"/>
+      <c r="A17" s="70"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="27"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
       <c r="N17" s="30"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
     </row>
     <row r="18" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="71"/>
-      <c r="B18" s="77"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="35"/>
+      <c r="A18" s="70"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="27"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="30"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
     </row>
     <row r="19" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="71"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="35"/>
+      <c r="A19" s="70"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="27"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="30"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
+      <c r="O19" s="73"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
     </row>
     <row r="20" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="71"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
+      <c r="A20" s="70"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="30"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
     </row>
     <row r="21" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="71"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="35"/>
+      <c r="A21" s="70"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="27"/>
       <c r="I21" s="29"/>
       <c r="J21" s="29"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="30"/>
-      <c r="O21" s="74"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
+      <c r="O21" s="73"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
     </row>
     <row r="22" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="71"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="35"/>
+      <c r="A22" s="70"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="27"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="30"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
     </row>
     <row r="23" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="80"/>
+      <c r="A23" s="84"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="79"/>
       <c r="F23" s="26"/>
       <c r="G23" s="26"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="87"/>
-      <c r="J23" s="87"/>
-      <c r="L23" s="88"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="L23" s="87"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="90"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="89"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
     <row r="24" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="80"/>
+      <c r="A24" s="84"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="79"/>
       <c r="F24" s="26"/>
       <c r="G24" s="26"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
-      <c r="L24" s="88"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="L24" s="87"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="90"/>
+      <c r="N24" s="88"/>
+      <c r="O24" s="89"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
     <row r="25" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="80"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="79"/>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="L25" s="88"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="L25" s="87"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="90"/>
+      <c r="N25" s="88"/>
+      <c r="O25" s="89"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
     <row r="26" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="80"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="79"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="L26" s="88"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="L26" s="87"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="90"/>
+      <c r="N26" s="88"/>
+      <c r="O26" s="89"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
     <row r="27" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="91"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="90"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="L27" s="88"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="86"/>
+      <c r="L27" s="87"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="90"/>
+      <c r="N27" s="88"/>
+      <c r="O27" s="89"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
     <row r="28" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="91"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="90"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="L28" s="88"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="L28" s="87"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="89"/>
-      <c r="O28" s="90"/>
+      <c r="N28" s="88"/>
+      <c r="O28" s="89"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
     <row r="29" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="91"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="90"/>
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="L29" s="88"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="86"/>
+      <c r="L29" s="87"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="90"/>
+      <c r="N29" s="88"/>
+      <c r="O29" s="89"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
     <row r="30" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="91"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="90"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="L30" s="88"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="L30" s="87"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="90"/>
+      <c r="N30" s="88"/>
+      <c r="O30" s="89"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
     <row r="31" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="91"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="90"/>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="L31" s="88"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="86"/>
+      <c r="L31" s="87"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="89"/>
-      <c r="O31" s="90"/>
+      <c r="N31" s="88"/>
+      <c r="O31" s="89"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
     <row r="32" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="91"/>
+      <c r="A32" s="84"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="90"/>
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="L32" s="88"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="L32" s="87"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="90"/>
+      <c r="N32" s="88"/>
+      <c r="O32" s="89"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
     <row r="33" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="27"/>
       <c r="I33" s="28"/>
       <c r="J33" s="29"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="44"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="39"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="38"/>
     </row>
     <row r="34" s="4" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B34" s="40"/>
+      <c r="B34" s="39"/>
       <c r="C34" s="25"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="27"/>
       <c r="I34" s="28"/>
       <c r="J34" s="29"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="39"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="38"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
       <c r="B35" s="7" t="s">
@@ -13651,7 +13648,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
-      <c r="L35" s="45" t="s">
+      <c r="L35" s="44" t="s">
         <v>99</v>
       </c>
       <c r="M35" s="17"/>
@@ -13661,25 +13658,25 @@
       <c r="Q35" s="17"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="46" t="s">
+      <c r="C36" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="46" t="s">
+      <c r="D36" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="L36" s="47" t="s">
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="L36" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="M36" s="48" t="s">
+      <c r="M36" s="47" t="s">
         <v>102</v>
       </c>
       <c r="N36" s="21" t="s">
@@ -13688,14 +13685,14 @@
       <c r="O36" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P36" s="49" t="s">
+      <c r="P36" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="Q36" s="50"/>
+      <c r="Q36" s="49"/>
     </row>
     <row r="37" s="3" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
-      <c r="B37" s="51"/>
-      <c r="C37" s="52"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="51"/>
       <c r="D37" s="29"/>
       <c r="E37" s="29"/>
       <c r="F37" s="29"/>
@@ -13703,50 +13700,50 @@
       <c r="H37" s="29"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
-      <c r="L37" s="35" t="s">
+      <c r="L37" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="M37" s="35" t="s">
+      <c r="M37" s="24" t="s">
         <v>107</v>
       </c>
       <c r="N37" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="O37" s="74"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="50"/>
+      <c r="O37" s="73"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="49"/>
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L38" s="35" t="s">
+      <c r="L38" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="M38" s="35" t="s">
+      <c r="M38" s="24" t="s">
         <v>110</v>
       </c>
       <c r="N38" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="O38" s="74"/>
-      <c r="P38" s="56" t="s">
+      <c r="O38" s="73"/>
+      <c r="P38" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="Q38" s="50"/>
+      <c r="Q38" s="49"/>
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="1:17">
-      <c r="L39" s="35" t="s">
+      <c r="L39" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="M39" s="35" t="s">
+      <c r="M39" s="24" t="s">
         <v>114</v>
       </c>
       <c r="N39" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="O39" s="74"/>
-      <c r="P39" s="56" t="s">
+      <c r="O39" s="73"/>
+      <c r="P39" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="Q39" s="50"/>
+      <c r="Q39" s="49"/>
     </row>
     <row r="40" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A40" s="5"/>
@@ -13760,14 +13757,14 @@
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
       <c r="N40" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="O40" s="74"/>
-      <c r="P40" s="57"/>
-      <c r="Q40" s="50"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="49"/>
     </row>
     <row r="41" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A41" s="5"/>
@@ -13781,12 +13778,12 @@
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="57"/>
-      <c r="Q41" s="50"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="56"/>
+      <c r="Q41" s="49"/>
     </row>
     <row r="42" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A42" s="5"/>
@@ -13800,12 +13797,12 @@
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
-      <c r="L42" s="58"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="50"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="38"/>
+      <c r="P42" s="56"/>
+      <c r="Q42" s="49"/>
     </row>
     <row r="43" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A43" s="5"/>
@@ -13819,12 +13816,12 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="58"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="57"/>
-      <c r="Q43" s="50"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="56"/>
+      <c r="Q43" s="49"/>
     </row>
     <row r="44" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A44" s="5"/>
@@ -13838,12 +13835,12 @@
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
-      <c r="L44" s="58"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="50"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="56"/>
+      <c r="Q44" s="49"/>
     </row>
     <row r="45" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A45" s="5"/>
@@ -13857,12 +13854,12 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="39"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="39"/>
-      <c r="P45" s="57"/>
-      <c r="Q45" s="50"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="38"/>
+      <c r="P45" s="56"/>
+      <c r="Q45" s="49"/>
     </row>
     <row r="46" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A46" s="5"/>
@@ -13876,12 +13873,12 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
-      <c r="L46" s="59"/>
-      <c r="M46" s="60"/>
-      <c r="N46" s="61"/>
-      <c r="O46" s="39"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="50"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="59"/>
+      <c r="N46" s="60"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="49"/>
     </row>
     <row r="47" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A47" s="5"/>
@@ -13895,7 +13892,7 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
-      <c r="L47" s="63" t="s">
+      <c r="L47" s="62" t="s">
         <v>118</v>
       </c>
       <c r="M47" s="17"/>
@@ -13916,7 +13913,7 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
-      <c r="L48" s="64" t="s">
+      <c r="L48" s="63" t="s">
         <v>119</v>
       </c>
       <c r="M48" s="17"/>

--- a/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
+++ b/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="4" activeTab="9"/>
+    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="4" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="修订记录" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="289">
   <si>
     <t>文档修订记录</t>
   </si>
@@ -2896,7 +2896,7 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="51" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3067,9 +3067,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3112,9 +3109,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4185,261 +4179,261 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="19.1018518518519" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="5.44444444444444" style="105" customWidth="1"/>
-    <col min="2" max="2" width="10.6666666666667" style="105" customWidth="1"/>
-    <col min="3" max="3" width="8.23148148148148" style="105" customWidth="1"/>
-    <col min="4" max="4" width="6.88888888888889" style="105" customWidth="1"/>
-    <col min="5" max="5" width="8.36111111111111" style="105" customWidth="1"/>
-    <col min="6" max="6" width="54.3611111111111" style="105" customWidth="1"/>
-    <col min="7" max="7" width="6.88888888888889" style="105" customWidth="1"/>
-    <col min="8" max="8" width="6.76851851851852" style="105" customWidth="1"/>
-    <col min="9" max="9" width="8.76851851851852" style="105" customWidth="1"/>
-    <col min="10" max="26" width="19.1018518518519" style="105" customWidth="1"/>
+    <col min="1" max="1" width="5.44444444444444" style="103" customWidth="1"/>
+    <col min="2" max="2" width="10.6666666666667" style="103" customWidth="1"/>
+    <col min="3" max="3" width="8.23148148148148" style="103" customWidth="1"/>
+    <col min="4" max="4" width="6.88888888888889" style="103" customWidth="1"/>
+    <col min="5" max="5" width="8.36111111111111" style="103" customWidth="1"/>
+    <col min="6" max="6" width="54.3611111111111" style="103" customWidth="1"/>
+    <col min="7" max="7" width="6.88888888888889" style="103" customWidth="1"/>
+    <col min="8" max="8" width="6.76851851851852" style="103" customWidth="1"/>
+    <col min="9" max="9" width="8.76851851851852" style="103" customWidth="1"/>
+    <col min="10" max="26" width="19.1018518518519" style="103" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="102" customFormat="1" ht="29.25" customHeight="1" spans="1:9">
-      <c r="A1" s="106"/>
-    </row>
-    <row r="2" s="102" customFormat="1" ht="18.15" customHeight="1" spans="1:9">
-      <c r="A2" s="107" t="s">
+    <row r="1" s="100" customFormat="1" ht="29.25" customHeight="1" spans="1:9">
+      <c r="A1" s="104"/>
+    </row>
+    <row r="2" s="100" customFormat="1" ht="18.15" customHeight="1" spans="1:9">
+      <c r="A2" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="109"/>
-    </row>
-    <row r="3" s="102" customFormat="1" ht="12.75" customHeight="1" spans="1:9">
-      <c r="A3" s="110"/>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-    </row>
-    <row r="4" s="102" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A4" s="112" t="s">
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="107"/>
+    </row>
+    <row r="3" s="100" customFormat="1" ht="12.75" customHeight="1" spans="1:9">
+      <c r="A3" s="108"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+    </row>
+    <row r="4" s="100" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A4" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="115" t="s">
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="115"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="117"/>
-    </row>
-    <row r="5" s="102" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A5" s="118"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="119" t="s">
+      <c r="F4" s="113"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="115"/>
+    </row>
+    <row r="5" s="100" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A5" s="116"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="119"/>
+      <c r="F5" s="117"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="13"/>
     </row>
-    <row r="6" s="102" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A6" s="118"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="119" t="s">
+    <row r="6" s="100" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A6" s="116"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="119"/>
+      <c r="F6" s="117"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="13"/>
     </row>
-    <row r="7" s="102" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A7" s="120"/>
+    <row r="7" s="100" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A7" s="118"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="122" t="s">
+      <c r="D7" s="119"/>
+      <c r="E7" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="123"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="125"/>
-    </row>
-    <row r="8" s="102" customFormat="1" ht="21" customHeight="1" spans="1:9">
-      <c r="A8" s="126" t="s">
+      <c r="F7" s="121"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="123"/>
+    </row>
+    <row r="8" s="100" customFormat="1" ht="21" customHeight="1" spans="1:9">
+      <c r="A8" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="126" t="s">
+      <c r="B8" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="126" t="s">
+      <c r="C8" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="126" t="s">
+      <c r="D8" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="126" t="s">
+      <c r="E8" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="121"/>
-      <c r="G8" s="126" t="s">
+      <c r="F8" s="119"/>
+      <c r="G8" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="126" t="s">
+      <c r="H8" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="126" t="s">
+      <c r="I8" s="124" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" s="103" customFormat="1" ht="16.95" customHeight="1" spans="1:9">
-      <c r="A9" s="127"/>
-      <c r="B9" s="128"/>
-      <c r="C9" s="129"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="131"/>
+    <row r="9" s="101" customFormat="1" ht="16.95" customHeight="1" spans="1:9">
+      <c r="A9" s="125"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="129"/>
       <c r="F9" s="13"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="129"/>
-      <c r="I9" s="129"/>
-    </row>
-    <row r="10" s="103" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A10" s="127"/>
-      <c r="B10" s="128"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="130"/>
-      <c r="E10" s="131"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+    </row>
+    <row r="10" s="101" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A10" s="125"/>
+      <c r="B10" s="126"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="129"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="129"/>
-      <c r="I10" s="129"/>
-    </row>
-    <row r="11" s="103" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A11" s="127"/>
-      <c r="B11" s="128"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="131"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+    </row>
+    <row r="11" s="101" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A11" s="125"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="129"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129"/>
-    </row>
-    <row r="12" s="103" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A12" s="127"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="130"/>
-      <c r="E12" s="131"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+    </row>
+    <row r="12" s="101" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A12" s="125"/>
+      <c r="B12" s="126"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="128"/>
+      <c r="E12" s="129"/>
       <c r="F12" s="13"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="129"/>
-    </row>
-    <row r="13" s="103" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A13" s="127"/>
-      <c r="B13" s="128"/>
-      <c r="C13" s="129"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="131"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+    </row>
+    <row r="13" s="101" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A13" s="125"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="129"/>
       <c r="F13" s="13"/>
-      <c r="G13" s="129"/>
-      <c r="H13" s="129"/>
-      <c r="I13" s="129"/>
-    </row>
-    <row r="14" s="103" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A14" s="127"/>
-      <c r="B14" s="128"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="130"/>
-      <c r="E14" s="131"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+    </row>
+    <row r="14" s="101" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A14" s="125"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="129"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="129"/>
-      <c r="H14" s="129"/>
-      <c r="I14" s="129"/>
-    </row>
-    <row r="15" s="103" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A15" s="127"/>
-      <c r="B15" s="128"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="130"/>
-      <c r="E15" s="131"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+    </row>
+    <row r="15" s="101" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A15" s="125"/>
+      <c r="B15" s="126"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="129"/>
       <c r="F15" s="13"/>
-      <c r="G15" s="129"/>
-      <c r="H15" s="129"/>
-      <c r="I15" s="129"/>
-    </row>
-    <row r="16" s="103" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A16" s="127"/>
-      <c r="B16" s="128"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="130"/>
-      <c r="E16" s="131"/>
+      <c r="G15" s="127"/>
+      <c r="H15" s="127"/>
+      <c r="I15" s="127"/>
+    </row>
+    <row r="16" s="101" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A16" s="125"/>
+      <c r="B16" s="126"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="129"/>
       <c r="F16" s="13"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="129"/>
-    </row>
-    <row r="17" s="103" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A17" s="127"/>
-      <c r="B17" s="128"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="130"/>
-      <c r="E17" s="131"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="127"/>
+      <c r="I16" s="127"/>
+    </row>
+    <row r="17" s="101" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A17" s="125"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="128"/>
+      <c r="E17" s="129"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="129"/>
-    </row>
-    <row r="18" s="103" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A18" s="127"/>
-      <c r="B18" s="128"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="130"/>
-      <c r="E18" s="131"/>
+      <c r="G17" s="127"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="127"/>
+    </row>
+    <row r="18" s="101" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A18" s="125"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="128"/>
+      <c r="E18" s="129"/>
       <c r="F18" s="13"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="129"/>
-    </row>
-    <row r="19" s="103" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A19" s="127"/>
-      <c r="B19" s="128"/>
-      <c r="C19" s="129"/>
-      <c r="D19" s="130"/>
-      <c r="E19" s="131"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="127"/>
+    </row>
+    <row r="19" s="101" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A19" s="125"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="129"/>
       <c r="F19" s="13"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="129"/>
-      <c r="I19" s="129"/>
-    </row>
-    <row r="20" s="103" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A20" s="127"/>
-      <c r="B20" s="128"/>
-      <c r="C20" s="129"/>
-      <c r="D20" s="130"/>
-      <c r="E20" s="131"/>
+      <c r="G19" s="127"/>
+      <c r="H19" s="127"/>
+      <c r="I19" s="127"/>
+    </row>
+    <row r="20" s="101" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A20" s="125"/>
+      <c r="B20" s="126"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="128"/>
+      <c r="E20" s="129"/>
       <c r="F20" s="13"/>
-      <c r="G20" s="129"/>
-      <c r="H20" s="129"/>
-      <c r="I20" s="129"/>
-    </row>
-    <row r="21" s="104" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A21" s="132"/>
-    </row>
-    <row r="22" s="104" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A22" s="132"/>
-    </row>
-    <row r="23" s="104" customFormat="1" ht="12" customHeight="1"/>
+      <c r="G20" s="127"/>
+      <c r="H20" s="127"/>
+      <c r="I20" s="127"/>
+    </row>
+    <row r="21" s="102" customFormat="1" ht="12" customHeight="1" spans="1:9">
+      <c r="A21" s="130"/>
+    </row>
+    <row r="22" s="102" customFormat="1" ht="12" customHeight="1" spans="1:9">
+      <c r="A22" s="130"/>
+    </row>
+    <row r="23" s="102" customFormat="1" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="A1:I1"/>
@@ -4627,14 +4621,14 @@
     </row>
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="24"/>
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62" t="s">
+      <c r="C7" s="25"/>
+      <c r="D7" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="25" t="s">
         <v>86</v>
       </c>
       <c r="F7" s="27"/>
@@ -4651,14 +4645,14 @@
     </row>
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="24"/>
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62" t="s">
+      <c r="C8" s="25"/>
+      <c r="D8" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="63" t="s">
+      <c r="E8" s="62" t="s">
         <v>212</v>
       </c>
       <c r="F8" s="27"/>
@@ -4941,7 +4935,7 @@
       <c r="B20" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="C20" s="64"/>
+      <c r="C20" s="63"/>
       <c r="D20" s="25" t="s">
         <v>70</v>
       </c>
@@ -4961,10 +4955,10 @@
       <c r="Q20" s="32"/>
     </row>
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B21" s="65"/>
+      <c r="B21" s="64"/>
       <c r="C21" s="25"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="66"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="65"/>
       <c r="F21" s="14"/>
       <c r="G21" s="13"/>
       <c r="H21" s="28"/>
@@ -5234,7 +5228,7 @@
     <mergeCell ref="L36:Q36"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7 C8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C8">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -5711,10 +5705,16 @@
       <c r="Q19" s="37"/>
     </row>
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B20" s="38"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
+      <c r="B20" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>86</v>
+      </c>
       <c r="F20" s="14"/>
       <c r="G20" s="13"/>
       <c r="H20" s="28"/>
@@ -5966,6 +5966,11 @@
     <mergeCell ref="L33:Q33"/>
     <mergeCell ref="L34:Q34"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C20">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -6177,10 +6182,16 @@
     </row>
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
+      <c r="B9" s="25" t="s">
+        <v>84</v>
+      </c>
       <c r="C9" s="26"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="D9" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>86</v>
+      </c>
       <c r="F9" s="27"/>
       <c r="G9" s="27"/>
       <c r="H9" s="28"/>
@@ -6628,6 +6639,11 @@
     <mergeCell ref="L33:Q33"/>
     <mergeCell ref="L34:Q34"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -6794,111 +6810,111 @@
   <sheetFormatPr defaultColWidth="6.66666666666667" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="2.66666666666667" style="6" customWidth="1"/>
-    <col min="2" max="2" width="4.33333333333333" style="87" customWidth="1"/>
-    <col min="3" max="3" width="6.44444444444444" style="88" customWidth="1"/>
-    <col min="4" max="4" width="12.1018518518519" style="88" customWidth="1"/>
-    <col min="5" max="5" width="19.4444444444444" style="89" customWidth="1"/>
-    <col min="6" max="6" width="29.4444444444444" style="90" customWidth="1"/>
-    <col min="7" max="7" width="52.6666666666667" style="89" customWidth="1"/>
+    <col min="2" max="2" width="4.33333333333333" style="85" customWidth="1"/>
+    <col min="3" max="3" width="6.44444444444444" style="86" customWidth="1"/>
+    <col min="4" max="4" width="12.1018518518519" style="86" customWidth="1"/>
+    <col min="5" max="5" width="19.4444444444444" style="87" customWidth="1"/>
+    <col min="6" max="6" width="29.4444444444444" style="88" customWidth="1"/>
+    <col min="7" max="7" width="52.6666666666667" style="87" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="86" customFormat="1" ht="21.6" customHeight="1" spans="1:7">
-      <c r="A1" s="91"/>
-      <c r="B1" s="92" t="s">
+    <row r="1" s="84" customFormat="1" ht="21.6" customHeight="1" spans="1:7">
+      <c r="A1" s="89"/>
+      <c r="B1" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="93" t="s">
+      <c r="C1" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="93" t="s">
+      <c r="D1" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="94" t="s">
+      <c r="E1" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="95" t="s">
+      <c r="F1" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="94" t="s">
+      <c r="G1" s="92" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="B2" s="96">
+      <c r="B2" s="94">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="97" t="s">
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="98"/>
-      <c r="G2" s="99" t="s">
+      <c r="F2" s="96"/>
+      <c r="G2" s="97" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="B3" s="100"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="101" t="s">
+      <c r="B3" s="98"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="98"/>
-      <c r="G3" s="101"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="99"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="B4" s="100"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="101" t="s">
+      <c r="B4" s="98"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="98"/>
-      <c r="G4" s="101"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="99"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="B5" s="100"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="101" t="s">
+      <c r="B5" s="98"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="98"/>
-      <c r="G5" s="101"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="99"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="B6" s="100"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="97" t="s">
+      <c r="B6" s="98"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="98"/>
-      <c r="G6" s="101" t="s">
+      <c r="F6" s="96"/>
+      <c r="G6" s="99" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="B7" s="100"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="101" t="s">
+      <c r="B7" s="98"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="98"/>
-      <c r="G7" s="101"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="99"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="B8" s="100"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="101" t="s">
+      <c r="B8" s="98"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
+      <c r="E8" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="98"/>
-      <c r="G8" s="101"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="99"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:G8" etc:filterBottomFollowUsedRange="0">
@@ -7056,8 +7072,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="68"/>
+    <row r="6" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="67"/>
       <c r="B6" s="25" t="s">
         <v>46</v>
       </c>
@@ -7065,23 +7081,23 @@
       <c r="D6" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="78" t="s">
+      <c r="E6" s="62" t="s">
         <v>48</v>
       </c>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
       <c r="L6" s="25"/>
       <c r="M6" s="25"/>
       <c r="N6" s="31"/>
-      <c r="O6" s="71"/>
+      <c r="O6" s="70"/>
       <c r="P6" s="25"/>
       <c r="Q6" s="25"/>
     </row>
-    <row r="7" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="72"/>
+    <row r="7" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="71"/>
       <c r="B7" s="25" t="s">
         <v>49</v>
       </c>
@@ -7089,23 +7105,23 @@
       <c r="D7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="78" t="s">
+      <c r="E7" s="62" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
       <c r="L7" s="25"/>
       <c r="M7" s="25"/>
       <c r="N7" s="31"/>
-      <c r="O7" s="71"/>
+      <c r="O7" s="70"/>
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
     </row>
-    <row r="8" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="72"/>
+    <row r="8" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="71"/>
       <c r="B8" s="25" t="s">
         <v>52</v>
       </c>
@@ -7113,23 +7129,23 @@
       <c r="D8" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="78" t="s">
+      <c r="E8" s="62" t="s">
         <v>54</v>
       </c>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
       <c r="N8" s="31"/>
-      <c r="O8" s="71"/>
+      <c r="O8" s="70"/>
       <c r="P8" s="25"/>
       <c r="Q8" s="25"/>
     </row>
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="68"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="25" t="s">
         <v>55</v>
       </c>
@@ -7137,23 +7153,23 @@
       <c r="D9" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="78" t="s">
+      <c r="E9" s="62" t="s">
         <v>57</v>
       </c>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
-      <c r="J9" s="73"/>
+      <c r="J9" s="72"/>
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
       <c r="N9" s="31"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="70"/>
       <c r="P9" s="25"/>
       <c r="Q9" s="25"/>
     </row>
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="72"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="25" t="s">
         <v>58</v>
       </c>
@@ -7161,23 +7177,23 @@
       <c r="D10" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="78" t="s">
+      <c r="E10" s="62" t="s">
         <v>60</v>
       </c>
       <c r="F10" s="25"/>
       <c r="G10" s="25"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
-      <c r="J10" s="73"/>
+      <c r="J10" s="72"/>
       <c r="L10" s="25"/>
       <c r="M10" s="25"/>
       <c r="N10" s="31"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="70"/>
       <c r="P10" s="25"/>
       <c r="Q10" s="25"/>
     </row>
-    <row r="11" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="72"/>
+    <row r="11" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="71"/>
       <c r="B11" s="25" t="s">
         <v>61</v>
       </c>
@@ -7185,23 +7201,23 @@
       <c r="D11" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="62" t="s">
         <v>62</v>
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
       <c r="L11" s="25"/>
       <c r="M11" s="25"/>
       <c r="N11" s="31"/>
-      <c r="O11" s="71"/>
+      <c r="O11" s="70"/>
       <c r="P11" s="25"/>
       <c r="Q11" s="25"/>
     </row>
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="72"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="25" t="s">
         <v>63</v>
       </c>
@@ -7209,7 +7225,7 @@
       <c r="D12" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="78" t="s">
+      <c r="E12" s="62" t="s">
         <v>64</v>
       </c>
       <c r="F12" s="25"/>
@@ -7220,12 +7236,12 @@
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
       <c r="N12" s="31"/>
-      <c r="O12" s="71"/>
+      <c r="O12" s="70"/>
       <c r="P12" s="25"/>
       <c r="Q12" s="25"/>
     </row>
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="68"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="25" t="s">
         <v>65</v>
       </c>
@@ -7233,7 +7249,7 @@
       <c r="D13" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="78" t="s">
+      <c r="E13" s="62" t="s">
         <v>66</v>
       </c>
       <c r="F13" s="25"/>
@@ -7244,12 +7260,12 @@
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="31"/>
-      <c r="O13" s="71"/>
+      <c r="O13" s="70"/>
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
     </row>
     <row r="14" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="68"/>
+      <c r="A14" s="67"/>
       <c r="B14" s="25" t="s">
         <v>67</v>
       </c>
@@ -7257,23 +7273,23 @@
       <c r="D14" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="78" t="s">
+      <c r="E14" s="62" t="s">
         <v>68</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
       <c r="H14" s="28"/>
       <c r="I14" s="30"/>
-      <c r="J14" s="73"/>
+      <c r="J14" s="72"/>
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
       <c r="N14" s="31"/>
-      <c r="O14" s="71"/>
+      <c r="O14" s="70"/>
       <c r="P14" s="25"/>
       <c r="Q14" s="25"/>
     </row>
     <row r="15" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="72"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="25" t="s">
         <v>69</v>
       </c>
@@ -7281,23 +7297,23 @@
       <c r="D15" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="78" t="s">
+      <c r="E15" s="62" t="s">
         <v>71</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="28"/>
       <c r="I15" s="30"/>
-      <c r="J15" s="73"/>
+      <c r="J15" s="72"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="31"/>
-      <c r="O15" s="71"/>
+      <c r="O15" s="70"/>
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
     </row>
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="72"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="25" t="s">
         <v>72</v>
       </c>
@@ -7305,25 +7321,25 @@
       <c r="D16" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="78" t="s">
+      <c r="E16" s="62" t="s">
         <v>74</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="28"/>
       <c r="I16" s="30"/>
-      <c r="J16" s="73"/>
+      <c r="J16" s="72"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="31"/>
-      <c r="O16" s="71"/>
+      <c r="O16" s="70"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="25" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="72"/>
+      <c r="A17" s="71"/>
       <c r="B17" s="25" t="s">
         <v>76</v>
       </c>
@@ -7331,7 +7347,7 @@
       <c r="D17" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="78" t="s">
+      <c r="E17" s="62" t="s">
         <v>78</v>
       </c>
       <c r="F17" s="25"/>
@@ -7342,12 +7358,12 @@
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
       <c r="N17" s="31"/>
-      <c r="O17" s="71"/>
+      <c r="O17" s="70"/>
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
     </row>
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="72"/>
+      <c r="A18" s="71"/>
       <c r="B18" s="25" t="s">
         <v>79</v>
       </c>
@@ -7355,7 +7371,7 @@
       <c r="D18" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="78" t="s">
+      <c r="E18" s="62" t="s">
         <v>81</v>
       </c>
       <c r="F18" s="25"/>
@@ -7366,12 +7382,12 @@
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
       <c r="N18" s="31"/>
-      <c r="O18" s="71"/>
+      <c r="O18" s="70"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
     </row>
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="72"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="25" t="s">
         <v>82</v>
       </c>
@@ -7379,7 +7395,7 @@
       <c r="D19" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="78" t="s">
+      <c r="E19" s="62" t="s">
         <v>83</v>
       </c>
       <c r="F19" s="25"/>
@@ -7390,37 +7406,37 @@
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
       <c r="N19" s="31"/>
-      <c r="O19" s="71"/>
+      <c r="O19" s="70"/>
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
     </row>
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="72"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="77"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="78" t="s">
+      <c r="E20" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="81"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="79"/>
       <c r="L20" s="25"/>
       <c r="M20" s="25"/>
       <c r="N20" s="31"/>
-      <c r="O20" s="71"/>
+      <c r="O20" s="70"/>
       <c r="P20" s="25"/>
       <c r="Q20" s="25"/>
     </row>
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="72"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="25" t="s">
         <v>87</v>
       </c>
@@ -7428,7 +7444,7 @@
       <c r="D21" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="78" t="s">
+      <c r="E21" s="62" t="s">
         <v>88</v>
       </c>
       <c r="F21" s="25"/>
@@ -7439,12 +7455,12 @@
       <c r="L21" s="25"/>
       <c r="M21" s="25"/>
       <c r="N21" s="31"/>
-      <c r="O21" s="71"/>
+      <c r="O21" s="70"/>
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
     </row>
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="68"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="25" t="s">
         <v>89</v>
       </c>
@@ -7452,7 +7468,7 @@
       <c r="D22" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="78" t="s">
+      <c r="E22" s="62" t="s">
         <v>91</v>
       </c>
       <c r="F22" s="25"/>
@@ -7463,7 +7479,7 @@
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
       <c r="N22" s="31"/>
-      <c r="O22" s="71"/>
+      <c r="O22" s="70"/>
       <c r="P22" s="25"/>
       <c r="Q22" s="25"/>
     </row>
@@ -7476,7 +7492,7 @@
       <c r="D23" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="78" t="s">
+      <c r="E23" s="62" t="s">
         <v>93</v>
       </c>
       <c r="F23" s="27"/>
@@ -7484,10 +7500,10 @@
       <c r="H23" s="28"/>
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
-      <c r="L23" s="82"/>
+      <c r="L23" s="80"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="84"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="82"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
@@ -7500,7 +7516,7 @@
       <c r="D24" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="78" t="s">
+      <c r="E24" s="62" t="s">
         <v>96</v>
       </c>
       <c r="F24" s="27"/>
@@ -7508,10 +7524,10 @@
       <c r="H24" s="28"/>
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
-      <c r="L24" s="82"/>
+      <c r="L24" s="80"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="84"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="82"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
@@ -7524,7 +7540,7 @@
       <c r="D25" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="78" t="s">
+      <c r="E25" s="62" t="s">
         <v>98</v>
       </c>
       <c r="F25" s="27"/>
@@ -7532,10 +7548,10 @@
       <c r="H25" s="28"/>
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
-      <c r="L25" s="82"/>
+      <c r="L25" s="80"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="84"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="82"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
@@ -7544,16 +7560,16 @@
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="85"/>
+      <c r="E26" s="83"/>
       <c r="F26" s="27"/>
       <c r="G26" s="27"/>
       <c r="H26" s="28"/>
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
-      <c r="L26" s="82"/>
+      <c r="L26" s="80"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="84"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="82"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
@@ -7562,16 +7578,16 @@
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="85"/>
+      <c r="E27" s="83"/>
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
       <c r="H27" s="28"/>
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
-      <c r="L27" s="82"/>
+      <c r="L27" s="80"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="84"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="82"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
@@ -7580,16 +7596,16 @@
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="85"/>
+      <c r="E28" s="83"/>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
       <c r="H28" s="28"/>
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
-      <c r="L28" s="82"/>
+      <c r="L28" s="80"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="84"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="82"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
@@ -7598,16 +7614,16 @@
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
-      <c r="E29" s="85"/>
+      <c r="E29" s="83"/>
       <c r="F29" s="27"/>
       <c r="G29" s="27"/>
       <c r="H29" s="28"/>
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
-      <c r="L29" s="82"/>
+      <c r="L29" s="80"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="84"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="82"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
@@ -7616,16 +7632,16 @@
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="85"/>
+      <c r="E30" s="83"/>
       <c r="F30" s="27"/>
       <c r="G30" s="27"/>
       <c r="H30" s="28"/>
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
-      <c r="L30" s="82"/>
+      <c r="L30" s="80"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="84"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="82"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
@@ -7634,16 +7650,16 @@
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
-      <c r="E31" s="85"/>
+      <c r="E31" s="83"/>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
       <c r="H31" s="28"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
-      <c r="L31" s="82"/>
+      <c r="L31" s="80"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="84"/>
+      <c r="N31" s="81"/>
+      <c r="O31" s="82"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
@@ -7652,16 +7668,16 @@
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
-      <c r="E32" s="85"/>
+      <c r="E32" s="83"/>
       <c r="F32" s="27"/>
       <c r="G32" s="27"/>
       <c r="H32" s="28"/>
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
-      <c r="L32" s="82"/>
+      <c r="L32" s="80"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="84"/>
+      <c r="N32" s="81"/>
+      <c r="O32" s="82"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
@@ -7772,7 +7788,7 @@
       <c r="N37" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="O37" s="71"/>
+      <c r="O37" s="70"/>
       <c r="P37" s="52"/>
       <c r="Q37" s="18"/>
     </row>
@@ -7786,7 +7802,7 @@
       <c r="N38" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="O38" s="71"/>
+      <c r="O38" s="70"/>
       <c r="P38" s="52" t="s">
         <v>113</v>
       </c>
@@ -7802,7 +7818,7 @@
       <c r="N39" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="O39" s="71"/>
+      <c r="O39" s="70"/>
       <c r="P39" s="52" t="s">
         <v>117</v>
       </c>
@@ -7814,7 +7830,7 @@
       <c r="N40" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="O40" s="71"/>
+      <c r="O40" s="70"/>
       <c r="P40" s="53"/>
       <c r="Q40" s="18"/>
     </row>
@@ -8111,8 +8127,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="68"/>
+    <row r="6" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="67"/>
       <c r="B6" s="25" t="s">
         <v>123</v>
       </c>
@@ -8120,23 +8136,23 @@
       <c r="D6" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="78" t="s">
+      <c r="E6" s="62" t="s">
         <v>124</v>
       </c>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
       <c r="L6" s="25"/>
       <c r="M6" s="25"/>
       <c r="N6" s="31"/>
-      <c r="O6" s="71"/>
+      <c r="O6" s="70"/>
       <c r="P6" s="25"/>
       <c r="Q6" s="25"/>
     </row>
-    <row r="7" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="72"/>
+    <row r="7" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="71"/>
       <c r="B7" s="25" t="s">
         <v>125</v>
       </c>
@@ -8144,23 +8160,23 @@
       <c r="D7" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="78" t="s">
+      <c r="E7" s="62" t="s">
         <v>126</v>
       </c>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
       <c r="L7" s="25"/>
       <c r="M7" s="25"/>
       <c r="N7" s="31"/>
-      <c r="O7" s="71"/>
+      <c r="O7" s="70"/>
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
     </row>
-    <row r="8" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="72"/>
+    <row r="8" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="71"/>
       <c r="B8" s="25" t="s">
         <v>55</v>
       </c>
@@ -8168,23 +8184,23 @@
       <c r="D8" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="78" t="s">
+      <c r="E8" s="62" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
       <c r="N8" s="31"/>
-      <c r="O8" s="71"/>
+      <c r="O8" s="70"/>
       <c r="P8" s="25"/>
       <c r="Q8" s="25"/>
     </row>
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="68"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="25" t="s">
         <v>58</v>
       </c>
@@ -8192,23 +8208,23 @@
       <c r="D9" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="78" t="s">
+      <c r="E9" s="62" t="s">
         <v>60</v>
       </c>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
-      <c r="J9" s="73"/>
+      <c r="J9" s="72"/>
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
       <c r="N9" s="31"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="70"/>
       <c r="P9" s="25"/>
       <c r="Q9" s="25"/>
     </row>
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="72"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="25" t="s">
         <v>61</v>
       </c>
@@ -8216,23 +8232,23 @@
       <c r="D10" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="78" t="s">
+      <c r="E10" s="62" t="s">
         <v>62</v>
       </c>
       <c r="F10" s="25"/>
       <c r="G10" s="25"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
-      <c r="J10" s="73"/>
+      <c r="J10" s="72"/>
       <c r="L10" s="25"/>
       <c r="M10" s="25"/>
       <c r="N10" s="31"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="70"/>
       <c r="P10" s="25"/>
       <c r="Q10" s="25"/>
     </row>
-    <row r="11" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="72"/>
+    <row r="11" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="71"/>
       <c r="B11" s="25" t="s">
         <v>65</v>
       </c>
@@ -8240,23 +8256,23 @@
       <c r="D11" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="62" t="s">
         <v>66</v>
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
       <c r="L11" s="25"/>
       <c r="M11" s="25"/>
       <c r="N11" s="31"/>
-      <c r="O11" s="71"/>
+      <c r="O11" s="70"/>
       <c r="P11" s="25"/>
       <c r="Q11" s="25"/>
     </row>
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="72"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="25" t="s">
         <v>92</v>
       </c>
@@ -8264,7 +8280,7 @@
       <c r="D12" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="78" t="s">
+      <c r="E12" s="62" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="25"/>
@@ -8275,12 +8291,12 @@
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
       <c r="N12" s="31"/>
-      <c r="O12" s="71"/>
+      <c r="O12" s="70"/>
       <c r="P12" s="25"/>
       <c r="Q12" s="25"/>
     </row>
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="68"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="25" t="s">
         <v>63</v>
       </c>
@@ -8288,7 +8304,7 @@
       <c r="D13" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="78" t="s">
+      <c r="E13" s="62" t="s">
         <v>64</v>
       </c>
       <c r="F13" s="25"/>
@@ -8299,12 +8315,12 @@
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="31"/>
-      <c r="O13" s="71"/>
+      <c r="O13" s="70"/>
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
     </row>
     <row r="14" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="68"/>
+      <c r="A14" s="67"/>
       <c r="B14" s="25" t="s">
         <v>76</v>
       </c>
@@ -8312,23 +8328,23 @@
       <c r="D14" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="78" t="s">
+      <c r="E14" s="62" t="s">
         <v>128</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
       <c r="H14" s="28"/>
       <c r="I14" s="30"/>
-      <c r="J14" s="73"/>
+      <c r="J14" s="72"/>
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
       <c r="N14" s="31"/>
-      <c r="O14" s="71"/>
+      <c r="O14" s="70"/>
       <c r="P14" s="25"/>
       <c r="Q14" s="25"/>
     </row>
     <row r="15" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="72"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="25" t="s">
         <v>79</v>
       </c>
@@ -8336,23 +8352,23 @@
       <c r="D15" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="78" t="s">
+      <c r="E15" s="62" t="s">
         <v>129</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="28"/>
       <c r="I15" s="30"/>
-      <c r="J15" s="73"/>
+      <c r="J15" s="72"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="31"/>
-      <c r="O15" s="71"/>
+      <c r="O15" s="70"/>
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
     </row>
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="72"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="25" t="s">
         <v>130</v>
       </c>
@@ -8360,33 +8376,33 @@
       <c r="D16" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="78" t="s">
+      <c r="E16" s="62" t="s">
         <v>131</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="28"/>
       <c r="I16" s="30"/>
-      <c r="J16" s="73"/>
+      <c r="J16" s="72"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="31"/>
-      <c r="O16" s="71"/>
+      <c r="O16" s="70"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="25" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="72"/>
+      <c r="A17" s="71"/>
       <c r="B17" s="25" t="s">
         <v>84</v>
       </c>
       <c r="C17" s="25"/>
       <c r="D17" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="62" t="s">
         <v>86</v>
       </c>
       <c r="F17" s="25"/>
@@ -8397,12 +8413,12 @@
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
       <c r="N17" s="31"/>
-      <c r="O17" s="71"/>
+      <c r="O17" s="70"/>
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
     </row>
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="72"/>
+      <c r="A18" s="71"/>
       <c r="B18" s="25" t="s">
         <v>87</v>
       </c>
@@ -8410,7 +8426,7 @@
       <c r="D18" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="78" t="s">
+      <c r="E18" s="62" t="s">
         <v>88</v>
       </c>
       <c r="F18" s="25"/>
@@ -8421,12 +8437,12 @@
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
       <c r="N18" s="31"/>
-      <c r="O18" s="71"/>
+      <c r="O18" s="70"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
     </row>
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="72"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="25" t="s">
         <v>132</v>
       </c>
@@ -8434,7 +8450,7 @@
       <c r="D19" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="78" t="s">
+      <c r="E19" s="62" t="s">
         <v>134</v>
       </c>
       <c r="F19" s="25"/>
@@ -8445,37 +8461,37 @@
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
       <c r="N19" s="31"/>
-      <c r="O19" s="71"/>
+      <c r="O19" s="70"/>
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
     </row>
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="72"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="77"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="78" t="s">
+      <c r="E20" s="62" t="s">
         <v>136</v>
       </c>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="81"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="79"/>
       <c r="L20" s="25"/>
       <c r="M20" s="25"/>
       <c r="N20" s="31"/>
-      <c r="O20" s="71"/>
+      <c r="O20" s="70"/>
       <c r="P20" s="25"/>
       <c r="Q20" s="25"/>
     </row>
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="72"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="25" t="s">
         <v>137</v>
       </c>
@@ -8483,7 +8499,7 @@
       <c r="D21" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="E21" s="78" t="s">
+      <c r="E21" s="62" t="s">
         <v>139</v>
       </c>
       <c r="F21" s="25"/>
@@ -8494,12 +8510,12 @@
       <c r="L21" s="25"/>
       <c r="M21" s="25"/>
       <c r="N21" s="31"/>
-      <c r="O21" s="71"/>
+      <c r="O21" s="70"/>
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
     </row>
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="68"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="25" t="s">
         <v>140</v>
       </c>
@@ -8507,7 +8523,7 @@
       <c r="D22" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="78" t="s">
+      <c r="E22" s="62" t="s">
         <v>141</v>
       </c>
       <c r="F22" s="25"/>
@@ -8518,7 +8534,7 @@
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
       <c r="N22" s="31"/>
-      <c r="O22" s="71"/>
+      <c r="O22" s="70"/>
       <c r="P22" s="25"/>
       <c r="Q22" s="25"/>
     </row>
@@ -8527,16 +8543,16 @@
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="78"/>
+      <c r="E23" s="62"/>
       <c r="F23" s="27"/>
       <c r="G23" s="27"/>
       <c r="H23" s="28"/>
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
-      <c r="L23" s="82"/>
+      <c r="L23" s="80"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="84"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="82"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
@@ -8545,16 +8561,16 @@
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
-      <c r="E24" s="78"/>
+      <c r="E24" s="62"/>
       <c r="F24" s="27"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28"/>
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
-      <c r="L24" s="82"/>
+      <c r="L24" s="80"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="84"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="82"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
@@ -8563,16 +8579,16 @@
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="E25" s="78"/>
+      <c r="E25" s="62"/>
       <c r="F25" s="27"/>
       <c r="G25" s="27"/>
       <c r="H25" s="28"/>
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
-      <c r="L25" s="82"/>
+      <c r="L25" s="80"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="84"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="82"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
@@ -8581,16 +8597,16 @@
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="85"/>
+      <c r="E26" s="83"/>
       <c r="F26" s="27"/>
       <c r="G26" s="27"/>
       <c r="H26" s="28"/>
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
-      <c r="L26" s="82"/>
+      <c r="L26" s="80"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="84"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="82"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
@@ -8599,16 +8615,16 @@
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="85"/>
+      <c r="E27" s="83"/>
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
       <c r="H27" s="28"/>
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
-      <c r="L27" s="82"/>
+      <c r="L27" s="80"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="84"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="82"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
@@ -8617,16 +8633,16 @@
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="85"/>
+      <c r="E28" s="83"/>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
       <c r="H28" s="28"/>
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
-      <c r="L28" s="82"/>
+      <c r="L28" s="80"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="84"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="82"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
@@ -8635,16 +8651,16 @@
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
-      <c r="E29" s="85"/>
+      <c r="E29" s="83"/>
       <c r="F29" s="27"/>
       <c r="G29" s="27"/>
       <c r="H29" s="28"/>
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
-      <c r="L29" s="82"/>
+      <c r="L29" s="80"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="84"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="82"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
@@ -8653,16 +8669,16 @@
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="85"/>
+      <c r="E30" s="83"/>
       <c r="F30" s="27"/>
       <c r="G30" s="27"/>
       <c r="H30" s="28"/>
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
-      <c r="L30" s="82"/>
+      <c r="L30" s="80"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="84"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="82"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
@@ -8671,16 +8687,16 @@
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
-      <c r="E31" s="85"/>
+      <c r="E31" s="83"/>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
       <c r="H31" s="28"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
-      <c r="L31" s="82"/>
+      <c r="L31" s="80"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="84"/>
+      <c r="N31" s="81"/>
+      <c r="O31" s="82"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
@@ -8689,16 +8705,16 @@
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
-      <c r="E32" s="85"/>
+      <c r="E32" s="83"/>
       <c r="F32" s="27"/>
       <c r="G32" s="27"/>
       <c r="H32" s="28"/>
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
-      <c r="L32" s="82"/>
+      <c r="L32" s="80"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="84"/>
+      <c r="N32" s="81"/>
+      <c r="O32" s="82"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
@@ -8809,7 +8825,7 @@
       <c r="N37" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="O37" s="71"/>
+      <c r="O37" s="70"/>
       <c r="P37" s="52"/>
       <c r="Q37" s="18"/>
     </row>
@@ -8823,7 +8839,7 @@
       <c r="N38" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="O38" s="71"/>
+      <c r="O38" s="70"/>
       <c r="P38" s="52" t="s">
         <v>113</v>
       </c>
@@ -8839,7 +8855,7 @@
       <c r="N39" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="O39" s="71"/>
+      <c r="O39" s="70"/>
       <c r="P39" s="52" t="s">
         <v>117</v>
       </c>
@@ -8851,7 +8867,7 @@
       <c r="N40" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="O40" s="71"/>
+      <c r="O40" s="70"/>
       <c r="P40" s="53"/>
       <c r="Q40" s="18"/>
     </row>
@@ -9148,8 +9164,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="68"/>
+    <row r="6" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="67"/>
       <c r="B6" s="25" t="s">
         <v>46</v>
       </c>
@@ -9157,23 +9173,23 @@
       <c r="D6" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="78" t="s">
+      <c r="E6" s="62" t="s">
         <v>144</v>
       </c>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
       <c r="L6" s="25"/>
       <c r="M6" s="25"/>
       <c r="N6" s="31"/>
-      <c r="O6" s="71"/>
+      <c r="O6" s="70"/>
       <c r="P6" s="25"/>
       <c r="Q6" s="25"/>
     </row>
-    <row r="7" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="72"/>
+    <row r="7" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="71"/>
       <c r="B7" s="25" t="s">
         <v>55</v>
       </c>
@@ -9181,23 +9197,23 @@
       <c r="D7" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="78" t="s">
+      <c r="E7" s="62" t="s">
         <v>57</v>
       </c>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
       <c r="L7" s="25"/>
       <c r="M7" s="25"/>
       <c r="N7" s="31"/>
-      <c r="O7" s="71"/>
+      <c r="O7" s="70"/>
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
     </row>
-    <row r="8" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="72"/>
+    <row r="8" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="71"/>
       <c r="B8" s="25" t="s">
         <v>58</v>
       </c>
@@ -9205,23 +9221,23 @@
       <c r="D8" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="78" t="s">
+      <c r="E8" s="62" t="s">
         <v>60</v>
       </c>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
       <c r="N8" s="31"/>
-      <c r="O8" s="71"/>
+      <c r="O8" s="70"/>
       <c r="P8" s="25"/>
       <c r="Q8" s="25"/>
     </row>
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="68"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="25" t="s">
         <v>61</v>
       </c>
@@ -9229,23 +9245,23 @@
       <c r="D9" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="78" t="s">
+      <c r="E9" s="62" t="s">
         <v>145</v>
       </c>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
-      <c r="J9" s="73"/>
+      <c r="J9" s="72"/>
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
       <c r="N9" s="31"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="70"/>
       <c r="P9" s="25"/>
       <c r="Q9" s="25"/>
     </row>
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="72"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="25" t="s">
         <v>63</v>
       </c>
@@ -9253,23 +9269,23 @@
       <c r="D10" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="78" t="s">
+      <c r="E10" s="62" t="s">
         <v>64</v>
       </c>
       <c r="F10" s="25"/>
       <c r="G10" s="25"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
-      <c r="J10" s="73"/>
+      <c r="J10" s="72"/>
       <c r="L10" s="25"/>
       <c r="M10" s="25"/>
       <c r="N10" s="31"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="70"/>
       <c r="P10" s="25"/>
       <c r="Q10" s="25"/>
     </row>
-    <row r="11" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="72"/>
+    <row r="11" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="71"/>
       <c r="B11" s="25" t="s">
         <v>65</v>
       </c>
@@ -9277,23 +9293,23 @@
       <c r="D11" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="62" t="s">
         <v>66</v>
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
       <c r="L11" s="25"/>
       <c r="M11" s="25"/>
       <c r="N11" s="31"/>
-      <c r="O11" s="71"/>
+      <c r="O11" s="70"/>
       <c r="P11" s="25"/>
       <c r="Q11" s="25"/>
     </row>
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="72"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="25" t="s">
         <v>146</v>
       </c>
@@ -9301,7 +9317,7 @@
       <c r="D12" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="78" t="s">
+      <c r="E12" s="62" t="s">
         <v>147</v>
       </c>
       <c r="F12" s="25"/>
@@ -9312,12 +9328,12 @@
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
       <c r="N12" s="31"/>
-      <c r="O12" s="71"/>
+      <c r="O12" s="70"/>
       <c r="P12" s="25"/>
       <c r="Q12" s="25"/>
     </row>
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="68"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="25" t="s">
         <v>148</v>
       </c>
@@ -9325,7 +9341,7 @@
       <c r="D13" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="78" t="s">
+      <c r="E13" s="62" t="s">
         <v>149</v>
       </c>
       <c r="F13" s="25"/>
@@ -9336,12 +9352,12 @@
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="31"/>
-      <c r="O13" s="71"/>
+      <c r="O13" s="70"/>
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
     </row>
     <row r="14" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="68"/>
+      <c r="A14" s="67"/>
       <c r="B14" s="25" t="s">
         <v>76</v>
       </c>
@@ -9349,23 +9365,23 @@
       <c r="D14" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="78" t="s">
+      <c r="E14" s="62" t="s">
         <v>150</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
       <c r="H14" s="28"/>
       <c r="I14" s="30"/>
-      <c r="J14" s="73"/>
+      <c r="J14" s="72"/>
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
       <c r="N14" s="31"/>
-      <c r="O14" s="71"/>
+      <c r="O14" s="70"/>
       <c r="P14" s="25"/>
       <c r="Q14" s="25"/>
     </row>
     <row r="15" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="72"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="25" t="s">
         <v>92</v>
       </c>
@@ -9373,23 +9389,23 @@
       <c r="D15" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="E15" s="78" t="s">
+      <c r="E15" s="62" t="s">
         <v>93</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="28"/>
       <c r="I15" s="30"/>
-      <c r="J15" s="73"/>
+      <c r="J15" s="72"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="31"/>
-      <c r="O15" s="71"/>
+      <c r="O15" s="70"/>
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
     </row>
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="72"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="25" t="s">
         <v>79</v>
       </c>
@@ -9397,25 +9413,25 @@
       <c r="D16" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="78" t="s">
+      <c r="E16" s="62" t="s">
         <v>151</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="28"/>
       <c r="I16" s="30"/>
-      <c r="J16" s="73"/>
+      <c r="J16" s="72"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="31"/>
-      <c r="O16" s="71"/>
+      <c r="O16" s="70"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="25" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="72"/>
+      <c r="A17" s="71"/>
       <c r="B17" s="25" t="s">
         <v>152</v>
       </c>
@@ -9423,7 +9439,7 @@
       <c r="D17" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="78" t="s">
+      <c r="E17" s="62" t="s">
         <v>153</v>
       </c>
       <c r="F17" s="25"/>
@@ -9434,12 +9450,12 @@
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
       <c r="N17" s="31"/>
-      <c r="O17" s="71"/>
+      <c r="O17" s="70"/>
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
     </row>
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="72"/>
+      <c r="A18" s="71"/>
       <c r="B18" s="25" t="s">
         <v>154</v>
       </c>
@@ -9447,7 +9463,7 @@
       <c r="D18" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="78" t="s">
+      <c r="E18" s="62" t="s">
         <v>155</v>
       </c>
       <c r="F18" s="25"/>
@@ -9458,12 +9474,12 @@
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
       <c r="N18" s="31"/>
-      <c r="O18" s="71"/>
+      <c r="O18" s="70"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
     </row>
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="72"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="25" t="s">
         <v>156</v>
       </c>
@@ -9471,7 +9487,7 @@
       <c r="D19" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="78" t="s">
+      <c r="E19" s="62" t="s">
         <v>157</v>
       </c>
       <c r="F19" s="25"/>
@@ -9482,37 +9498,37 @@
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
       <c r="N19" s="31"/>
-      <c r="O19" s="71"/>
+      <c r="O19" s="70"/>
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
     </row>
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="72"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="77"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E20" s="78" t="s">
+      <c r="E20" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="81"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="79"/>
       <c r="L20" s="25"/>
       <c r="M20" s="25"/>
       <c r="N20" s="31"/>
-      <c r="O20" s="71"/>
+      <c r="O20" s="70"/>
       <c r="P20" s="25"/>
       <c r="Q20" s="25"/>
     </row>
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="72"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="25" t="s">
         <v>160</v>
       </c>
@@ -9520,7 +9536,7 @@
       <c r="D21" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="78" t="s">
+      <c r="E21" s="62" t="s">
         <v>161</v>
       </c>
       <c r="F21" s="25"/>
@@ -9531,20 +9547,20 @@
       <c r="L21" s="25"/>
       <c r="M21" s="25"/>
       <c r="N21" s="31"/>
-      <c r="O21" s="71"/>
+      <c r="O21" s="70"/>
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
     </row>
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="68"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="25" t="s">
         <v>84</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="62" t="s">
         <v>86</v>
       </c>
       <c r="F22" s="25"/>
@@ -9555,7 +9571,7 @@
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
       <c r="N22" s="31"/>
-      <c r="O22" s="71"/>
+      <c r="O22" s="70"/>
       <c r="P22" s="25"/>
       <c r="Q22" s="25"/>
     </row>
@@ -9568,7 +9584,7 @@
       <c r="D23" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="78" t="s">
+      <c r="E23" s="62" t="s">
         <v>88</v>
       </c>
       <c r="F23" s="27"/>
@@ -9576,10 +9592,10 @@
       <c r="H23" s="28"/>
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
-      <c r="L23" s="82"/>
+      <c r="L23" s="80"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="84"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="82"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
@@ -9592,7 +9608,7 @@
       <c r="D24" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="78" t="s">
+      <c r="E24" s="62" t="s">
         <v>45</v>
       </c>
       <c r="F24" s="27"/>
@@ -9600,10 +9616,10 @@
       <c r="H24" s="28"/>
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
-      <c r="L24" s="82"/>
+      <c r="L24" s="80"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="84"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="82"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
@@ -9616,7 +9632,7 @@
       <c r="D25" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="78" t="s">
+      <c r="E25" s="62" t="s">
         <v>98</v>
       </c>
       <c r="F25" s="27"/>
@@ -9624,10 +9640,10 @@
       <c r="H25" s="28"/>
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
-      <c r="L25" s="82"/>
+      <c r="L25" s="80"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="84"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="82"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
@@ -9640,7 +9656,7 @@
       <c r="D26" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="E26" s="78" t="s">
+      <c r="E26" s="62" t="s">
         <v>96</v>
       </c>
       <c r="F26" s="27"/>
@@ -9648,10 +9664,10 @@
       <c r="H26" s="28"/>
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
-      <c r="L26" s="82"/>
+      <c r="L26" s="80"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="84"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="82"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
@@ -9660,16 +9676,16 @@
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="85"/>
+      <c r="E27" s="83"/>
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
       <c r="H27" s="28"/>
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
-      <c r="L27" s="82"/>
+      <c r="L27" s="80"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="84"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="82"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
@@ -9678,16 +9694,16 @@
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="85"/>
+      <c r="E28" s="83"/>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
       <c r="H28" s="28"/>
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
-      <c r="L28" s="82"/>
+      <c r="L28" s="80"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="84"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="82"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
@@ -9696,16 +9712,16 @@
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
-      <c r="E29" s="85"/>
+      <c r="E29" s="83"/>
       <c r="F29" s="27"/>
       <c r="G29" s="27"/>
       <c r="H29" s="28"/>
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
-      <c r="L29" s="82"/>
+      <c r="L29" s="80"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="84"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="82"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
@@ -9714,16 +9730,16 @@
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="85"/>
+      <c r="E30" s="83"/>
       <c r="F30" s="27"/>
       <c r="G30" s="27"/>
       <c r="H30" s="28"/>
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
-      <c r="L30" s="82"/>
+      <c r="L30" s="80"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="84"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="82"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
@@ -9732,16 +9748,16 @@
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
-      <c r="E31" s="85"/>
+      <c r="E31" s="83"/>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
       <c r="H31" s="28"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
-      <c r="L31" s="82"/>
+      <c r="L31" s="80"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="84"/>
+      <c r="N31" s="81"/>
+      <c r="O31" s="82"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
@@ -9750,16 +9766,16 @@
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
-      <c r="E32" s="85"/>
+      <c r="E32" s="83"/>
       <c r="F32" s="27"/>
       <c r="G32" s="27"/>
       <c r="H32" s="28"/>
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
-      <c r="L32" s="82"/>
+      <c r="L32" s="80"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="84"/>
+      <c r="N32" s="81"/>
+      <c r="O32" s="82"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
@@ -9870,7 +9886,7 @@
       <c r="N37" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="O37" s="71"/>
+      <c r="O37" s="70"/>
       <c r="P37" s="52"/>
       <c r="Q37" s="18"/>
     </row>
@@ -9884,7 +9900,7 @@
       <c r="N38" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="O38" s="71"/>
+      <c r="O38" s="70"/>
       <c r="P38" s="52" t="s">
         <v>113</v>
       </c>
@@ -9900,7 +9916,7 @@
       <c r="N39" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="O39" s="71"/>
+      <c r="O39" s="70"/>
       <c r="P39" s="52" t="s">
         <v>117</v>
       </c>
@@ -9912,7 +9928,7 @@
       <c r="N40" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="O40" s="71"/>
+      <c r="O40" s="70"/>
       <c r="P40" s="53"/>
       <c r="Q40" s="18"/>
     </row>
@@ -10066,7 +10082,7 @@
     <mergeCell ref="A14:A21"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C32">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 C9:C21 C23:C32">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -10169,120 +10185,120 @@
       <c r="P5" s="22"/>
       <c r="Q5" s="23"/>
     </row>
-    <row r="6" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="68"/>
+    <row r="6" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="67"/>
       <c r="B6" s="25"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
-      <c r="E6" s="78"/>
+      <c r="E6" s="62"/>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
       <c r="L6" s="25"/>
       <c r="M6" s="25"/>
       <c r="N6" s="31"/>
-      <c r="O6" s="71"/>
+      <c r="O6" s="70"/>
       <c r="P6" s="25"/>
       <c r="Q6" s="25"/>
     </row>
-    <row r="7" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="72"/>
+    <row r="7" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="71"/>
       <c r="B7" s="25"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
-      <c r="E7" s="78"/>
+      <c r="E7" s="62"/>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
       <c r="L7" s="25"/>
       <c r="M7" s="25"/>
       <c r="N7" s="31"/>
-      <c r="O7" s="71"/>
+      <c r="O7" s="70"/>
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
     </row>
-    <row r="8" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="72"/>
+    <row r="8" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="71"/>
       <c r="B8" s="25"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
-      <c r="E8" s="78"/>
+      <c r="E8" s="62"/>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
       <c r="N8" s="31"/>
-      <c r="O8" s="71"/>
+      <c r="O8" s="70"/>
       <c r="P8" s="25"/>
       <c r="Q8" s="25"/>
     </row>
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="68"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
-      <c r="E9" s="78"/>
+      <c r="E9" s="62"/>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
-      <c r="J9" s="73"/>
+      <c r="J9" s="72"/>
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
       <c r="N9" s="31"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="70"/>
       <c r="P9" s="25"/>
       <c r="Q9" s="25"/>
     </row>
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="72"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="25"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
-      <c r="E10" s="78"/>
+      <c r="E10" s="62"/>
       <c r="F10" s="25"/>
       <c r="G10" s="25"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
-      <c r="J10" s="73"/>
+      <c r="J10" s="72"/>
       <c r="L10" s="25"/>
       <c r="M10" s="25"/>
       <c r="N10" s="31"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="70"/>
       <c r="P10" s="25"/>
       <c r="Q10" s="25"/>
     </row>
-    <row r="11" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="72"/>
+    <row r="11" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="71"/>
       <c r="B11" s="25"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
-      <c r="E11" s="78"/>
+      <c r="E11" s="62"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
       <c r="L11" s="25"/>
       <c r="M11" s="25"/>
       <c r="N11" s="31"/>
-      <c r="O11" s="71"/>
+      <c r="O11" s="70"/>
       <c r="P11" s="25"/>
       <c r="Q11" s="25"/>
     </row>
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="72"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="25"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
-      <c r="E12" s="78"/>
+      <c r="E12" s="62"/>
       <c r="F12" s="25"/>
       <c r="G12" s="25"/>
       <c r="H12" s="28"/>
@@ -10291,16 +10307,16 @@
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
       <c r="N12" s="31"/>
-      <c r="O12" s="71"/>
+      <c r="O12" s="70"/>
       <c r="P12" s="25"/>
       <c r="Q12" s="25"/>
     </row>
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="68"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
-      <c r="E13" s="78"/>
+      <c r="E13" s="62"/>
       <c r="F13" s="25"/>
       <c r="G13" s="25"/>
       <c r="H13" s="28"/>
@@ -10309,70 +10325,70 @@
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="31"/>
-      <c r="O13" s="71"/>
+      <c r="O13" s="70"/>
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
     </row>
     <row r="14" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="68"/>
+      <c r="A14" s="67"/>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
-      <c r="E14" s="78"/>
+      <c r="E14" s="62"/>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
       <c r="H14" s="28"/>
       <c r="I14" s="30"/>
-      <c r="J14" s="73"/>
+      <c r="J14" s="72"/>
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
       <c r="N14" s="31"/>
-      <c r="O14" s="71"/>
+      <c r="O14" s="70"/>
       <c r="P14" s="25"/>
       <c r="Q14" s="25"/>
     </row>
     <row r="15" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="72"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
-      <c r="E15" s="78"/>
+      <c r="E15" s="62"/>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="28"/>
       <c r="I15" s="30"/>
-      <c r="J15" s="73"/>
+      <c r="J15" s="72"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="31"/>
-      <c r="O15" s="71"/>
+      <c r="O15" s="70"/>
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
     </row>
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="72"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="25"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
-      <c r="E16" s="78"/>
+      <c r="E16" s="62"/>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
       <c r="H16" s="28"/>
       <c r="I16" s="30"/>
-      <c r="J16" s="73"/>
+      <c r="J16" s="72"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="31"/>
-      <c r="O16" s="71"/>
+      <c r="O16" s="70"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="25"/>
     </row>
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="72"/>
+      <c r="A17" s="71"/>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
-      <c r="E17" s="78"/>
+      <c r="E17" s="62"/>
       <c r="F17" s="25"/>
       <c r="G17" s="25"/>
       <c r="H17" s="28"/>
@@ -10381,16 +10397,16 @@
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
       <c r="N17" s="31"/>
-      <c r="O17" s="71"/>
+      <c r="O17" s="70"/>
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
     </row>
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="72"/>
+      <c r="A18" s="71"/>
       <c r="B18" s="25"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
-      <c r="E18" s="78"/>
+      <c r="E18" s="62"/>
       <c r="F18" s="25"/>
       <c r="G18" s="25"/>
       <c r="H18" s="28"/>
@@ -10399,16 +10415,16 @@
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
       <c r="N18" s="31"/>
-      <c r="O18" s="71"/>
+      <c r="O18" s="70"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
     </row>
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="72"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
-      <c r="E19" s="78"/>
+      <c r="E19" s="62"/>
       <c r="F19" s="25"/>
       <c r="G19" s="25"/>
       <c r="H19" s="28"/>
@@ -10417,35 +10433,35 @@
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
       <c r="N19" s="31"/>
-      <c r="O19" s="71"/>
+      <c r="O19" s="70"/>
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
     </row>
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="72"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="25"/>
-      <c r="C20" s="77"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="25"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="81"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="79"/>
       <c r="L20" s="25"/>
       <c r="M20" s="25"/>
       <c r="N20" s="31"/>
-      <c r="O20" s="71"/>
+      <c r="O20" s="70"/>
       <c r="P20" s="25"/>
       <c r="Q20" s="25"/>
     </row>
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="72"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
-      <c r="E21" s="78"/>
+      <c r="E21" s="62"/>
       <c r="F21" s="25"/>
       <c r="G21" s="25"/>
       <c r="H21" s="28"/>
@@ -10454,16 +10470,16 @@
       <c r="L21" s="25"/>
       <c r="M21" s="25"/>
       <c r="N21" s="31"/>
-      <c r="O21" s="71"/>
+      <c r="O21" s="70"/>
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
     </row>
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="68"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
-      <c r="E22" s="78"/>
+      <c r="E22" s="62"/>
       <c r="F22" s="25"/>
       <c r="G22" s="25"/>
       <c r="H22" s="28"/>
@@ -10472,7 +10488,7 @@
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
       <c r="N22" s="31"/>
-      <c r="O22" s="71"/>
+      <c r="O22" s="70"/>
       <c r="P22" s="25"/>
       <c r="Q22" s="25"/>
     </row>
@@ -10481,16 +10497,16 @@
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="78"/>
+      <c r="E23" s="62"/>
       <c r="F23" s="27"/>
       <c r="G23" s="27"/>
       <c r="H23" s="28"/>
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
-      <c r="L23" s="82"/>
+      <c r="L23" s="80"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="84"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="82"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
@@ -10499,16 +10515,16 @@
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
-      <c r="E24" s="78"/>
+      <c r="E24" s="62"/>
       <c r="F24" s="27"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28"/>
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
-      <c r="L24" s="82"/>
+      <c r="L24" s="80"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="84"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="82"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
@@ -10517,16 +10533,16 @@
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="E25" s="78"/>
+      <c r="E25" s="62"/>
       <c r="F25" s="27"/>
       <c r="G25" s="27"/>
       <c r="H25" s="28"/>
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
-      <c r="L25" s="82"/>
+      <c r="L25" s="80"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="84"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="82"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
@@ -10535,16 +10551,16 @@
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="78"/>
+      <c r="E26" s="62"/>
       <c r="F26" s="27"/>
       <c r="G26" s="27"/>
       <c r="H26" s="28"/>
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
-      <c r="L26" s="82"/>
+      <c r="L26" s="80"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="84"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="82"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
@@ -10553,16 +10569,16 @@
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="85"/>
+      <c r="E27" s="83"/>
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
       <c r="H27" s="28"/>
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
-      <c r="L27" s="82"/>
+      <c r="L27" s="80"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="84"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="82"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
@@ -10571,16 +10587,16 @@
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="85"/>
+      <c r="E28" s="83"/>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
       <c r="H28" s="28"/>
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
-      <c r="L28" s="82"/>
+      <c r="L28" s="80"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="84"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="82"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
@@ -10589,16 +10605,16 @@
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
-      <c r="E29" s="85"/>
+      <c r="E29" s="83"/>
       <c r="F29" s="27"/>
       <c r="G29" s="27"/>
       <c r="H29" s="28"/>
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
-      <c r="L29" s="82"/>
+      <c r="L29" s="80"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="84"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="82"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
@@ -10607,16 +10623,16 @@
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="85"/>
+      <c r="E30" s="83"/>
       <c r="F30" s="27"/>
       <c r="G30" s="27"/>
       <c r="H30" s="28"/>
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
-      <c r="L30" s="82"/>
+      <c r="L30" s="80"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="84"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="82"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
@@ -10625,16 +10641,16 @@
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
-      <c r="E31" s="85"/>
+      <c r="E31" s="83"/>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
       <c r="H31" s="28"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
-      <c r="L31" s="82"/>
+      <c r="L31" s="80"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="84"/>
+      <c r="N31" s="81"/>
+      <c r="O31" s="82"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
@@ -10643,16 +10659,16 @@
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
-      <c r="E32" s="85"/>
+      <c r="E32" s="83"/>
       <c r="F32" s="27"/>
       <c r="G32" s="27"/>
       <c r="H32" s="28"/>
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
-      <c r="L32" s="82"/>
+      <c r="L32" s="80"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="84"/>
+      <c r="N32" s="81"/>
+      <c r="O32" s="82"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
@@ -10737,7 +10753,7 @@
       <c r="L37" s="25"/>
       <c r="M37" s="25"/>
       <c r="N37" s="31"/>
-      <c r="O37" s="71"/>
+      <c r="O37" s="70"/>
       <c r="P37" s="52"/>
       <c r="Q37" s="18"/>
     </row>
@@ -10745,7 +10761,7 @@
       <c r="L38" s="25"/>
       <c r="M38" s="25"/>
       <c r="N38" s="31"/>
-      <c r="O38" s="71"/>
+      <c r="O38" s="70"/>
       <c r="P38" s="52"/>
       <c r="Q38" s="18"/>
     </row>
@@ -10753,7 +10769,7 @@
       <c r="L39" s="25"/>
       <c r="M39" s="25"/>
       <c r="N39" s="31"/>
-      <c r="O39" s="71"/>
+      <c r="O39" s="70"/>
       <c r="P39" s="52"/>
       <c r="Q39" s="18"/>
     </row>
@@ -10761,7 +10777,7 @@
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
       <c r="N40" s="31"/>
-      <c r="O40" s="71"/>
+      <c r="O40" s="70"/>
       <c r="P40" s="53"/>
       <c r="Q40" s="18"/>
     </row>
@@ -11054,8 +11070,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="68"/>
+    <row r="6" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="67"/>
       <c r="B6" s="25" t="s">
         <v>165</v>
       </c>
@@ -11068,18 +11084,18 @@
       </c>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
       <c r="L6" s="25"/>
       <c r="M6" s="25"/>
       <c r="N6" s="31"/>
-      <c r="O6" s="71"/>
+      <c r="O6" s="70"/>
       <c r="P6" s="25"/>
       <c r="Q6" s="25"/>
     </row>
-    <row r="7" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="72"/>
+    <row r="7" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="71"/>
       <c r="B7" s="25" t="s">
         <v>61</v>
       </c>
@@ -11092,18 +11108,18 @@
       </c>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
       <c r="L7" s="25"/>
       <c r="M7" s="25"/>
       <c r="N7" s="31"/>
-      <c r="O7" s="71"/>
+      <c r="O7" s="70"/>
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
     </row>
-    <row r="8" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="72"/>
+    <row r="8" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="71"/>
       <c r="B8" s="25" t="s">
         <v>65</v>
       </c>
@@ -11116,18 +11132,18 @@
       </c>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
       <c r="N8" s="31"/>
-      <c r="O8" s="71"/>
+      <c r="O8" s="70"/>
       <c r="P8" s="25"/>
       <c r="Q8" s="25"/>
     </row>
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="68"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="25" t="s">
         <v>63</v>
       </c>
@@ -11142,16 +11158,16 @@
       <c r="G9" s="25"/>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
-      <c r="J9" s="73"/>
+      <c r="J9" s="72"/>
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
       <c r="N9" s="31"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="70"/>
       <c r="P9" s="25"/>
       <c r="Q9" s="25"/>
     </row>
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="72"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="25" t="s">
         <v>170</v>
       </c>
@@ -11166,16 +11182,16 @@
       <c r="G10" s="25"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
-      <c r="J10" s="73"/>
+      <c r="J10" s="72"/>
       <c r="L10" s="25"/>
       <c r="M10" s="25"/>
       <c r="N10" s="31"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="70"/>
       <c r="P10" s="25"/>
       <c r="Q10" s="25"/>
     </row>
-    <row r="11" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="72"/>
+    <row r="11" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="71"/>
       <c r="B11" s="25" t="s">
         <v>172</v>
       </c>
@@ -11188,18 +11204,18 @@
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
       <c r="L11" s="25"/>
       <c r="M11" s="25"/>
       <c r="N11" s="31"/>
-      <c r="O11" s="71"/>
+      <c r="O11" s="70"/>
       <c r="P11" s="25"/>
       <c r="Q11" s="25"/>
     </row>
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="72"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="25" t="s">
         <v>174</v>
       </c>
@@ -11218,12 +11234,12 @@
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
       <c r="N12" s="31"/>
-      <c r="O12" s="71"/>
+      <c r="O12" s="70"/>
       <c r="P12" s="25"/>
       <c r="Q12" s="25"/>
     </row>
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="68"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="25" t="s">
         <v>176</v>
       </c>
@@ -11242,12 +11258,12 @@
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="31"/>
-      <c r="O13" s="71"/>
+      <c r="O13" s="70"/>
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
     </row>
     <row r="14" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="68"/>
+      <c r="A14" s="67"/>
       <c r="B14" s="25" t="s">
         <v>178</v>
       </c>
@@ -11262,16 +11278,16 @@
       <c r="G14" s="25"/>
       <c r="H14" s="28"/>
       <c r="I14" s="30"/>
-      <c r="J14" s="73"/>
+      <c r="J14" s="72"/>
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
       <c r="N14" s="31"/>
-      <c r="O14" s="71"/>
+      <c r="O14" s="70"/>
       <c r="P14" s="25"/>
       <c r="Q14" s="25"/>
     </row>
     <row r="15" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="72"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="25" t="s">
         <v>180</v>
       </c>
@@ -11286,16 +11302,16 @@
       <c r="G15" s="25"/>
       <c r="H15" s="28"/>
       <c r="I15" s="30"/>
-      <c r="J15" s="73"/>
+      <c r="J15" s="72"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="31"/>
-      <c r="O15" s="71"/>
+      <c r="O15" s="70"/>
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
     </row>
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="72"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="25" t="s">
         <v>182</v>
       </c>
@@ -11310,19 +11326,19 @@
       <c r="G16" s="25"/>
       <c r="H16" s="28"/>
       <c r="I16" s="30"/>
-      <c r="J16" s="73"/>
+      <c r="J16" s="72"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="31"/>
-      <c r="O16" s="71"/>
+      <c r="O16" s="70"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="25" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="72"/>
-      <c r="B17" s="74" t="s">
+      <c r="A17" s="71"/>
+      <c r="B17" s="73" t="s">
         <v>184</v>
       </c>
       <c r="C17" s="25"/>
@@ -11340,20 +11356,20 @@
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
       <c r="N17" s="31"/>
-      <c r="O17" s="71"/>
+      <c r="O17" s="70"/>
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
     </row>
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="72"/>
-      <c r="B18" s="75" t="s">
+      <c r="A18" s="71"/>
+      <c r="B18" s="74" t="s">
         <v>187</v>
       </c>
       <c r="C18" s="25"/>
-      <c r="D18" s="76" t="s">
+      <c r="D18" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="75" t="s">
+      <c r="E18" s="74" t="s">
         <v>188</v>
       </c>
       <c r="F18" s="25"/>
@@ -11364,17 +11380,17 @@
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
       <c r="N18" s="31"/>
-      <c r="O18" s="71"/>
+      <c r="O18" s="70"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
     </row>
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="72"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="25" t="s">
         <v>189</v>
       </c>
       <c r="C19" s="25"/>
-      <c r="D19" s="76" t="s">
+      <c r="D19" s="75" t="s">
         <v>70</v>
       </c>
       <c r="E19" s="25" t="s">
@@ -11388,35 +11404,35 @@
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
       <c r="N19" s="31"/>
-      <c r="O19" s="71"/>
+      <c r="O19" s="70"/>
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
     </row>
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="72"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="25"/>
-      <c r="C20" s="77"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="25"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="81"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="79"/>
       <c r="L20" s="25"/>
       <c r="M20" s="25"/>
       <c r="N20" s="31"/>
-      <c r="O20" s="71"/>
+      <c r="O20" s="70"/>
       <c r="P20" s="25"/>
       <c r="Q20" s="25"/>
     </row>
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="72"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
-      <c r="E21" s="78"/>
+      <c r="E21" s="62"/>
       <c r="F21" s="25"/>
       <c r="G21" s="25"/>
       <c r="H21" s="28"/>
@@ -11425,16 +11441,16 @@
       <c r="L21" s="25"/>
       <c r="M21" s="25"/>
       <c r="N21" s="31"/>
-      <c r="O21" s="71"/>
+      <c r="O21" s="70"/>
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
     </row>
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="68"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
-      <c r="E22" s="78"/>
+      <c r="E22" s="62"/>
       <c r="F22" s="25"/>
       <c r="G22" s="25"/>
       <c r="H22" s="28"/>
@@ -11443,7 +11459,7 @@
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
       <c r="N22" s="31"/>
-      <c r="O22" s="71"/>
+      <c r="O22" s="70"/>
       <c r="P22" s="25"/>
       <c r="Q22" s="25"/>
     </row>
@@ -11452,16 +11468,16 @@
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="78"/>
+      <c r="E23" s="62"/>
       <c r="F23" s="27"/>
       <c r="G23" s="27"/>
       <c r="H23" s="28"/>
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
-      <c r="L23" s="82"/>
+      <c r="L23" s="80"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="84"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="82"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
@@ -11470,16 +11486,16 @@
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
-      <c r="E24" s="78"/>
+      <c r="E24" s="62"/>
       <c r="F24" s="27"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28"/>
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
-      <c r="L24" s="82"/>
+      <c r="L24" s="80"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="84"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="82"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
@@ -11488,16 +11504,16 @@
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="E25" s="78"/>
+      <c r="E25" s="62"/>
       <c r="F25" s="27"/>
       <c r="G25" s="27"/>
       <c r="H25" s="28"/>
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
-      <c r="L25" s="82"/>
+      <c r="L25" s="80"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="84"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="82"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
@@ -11506,16 +11522,16 @@
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="78"/>
+      <c r="E26" s="62"/>
       <c r="F26" s="27"/>
       <c r="G26" s="27"/>
       <c r="H26" s="28"/>
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
-      <c r="L26" s="82"/>
+      <c r="L26" s="80"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="84"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="82"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
@@ -11524,16 +11540,16 @@
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="85"/>
+      <c r="E27" s="83"/>
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
       <c r="H27" s="28"/>
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
-      <c r="L27" s="82"/>
+      <c r="L27" s="80"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="84"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="82"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
@@ -11542,16 +11558,16 @@
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="85"/>
+      <c r="E28" s="83"/>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
       <c r="H28" s="28"/>
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
-      <c r="L28" s="82"/>
+      <c r="L28" s="80"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="84"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="82"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
@@ -11560,16 +11576,16 @@
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
-      <c r="E29" s="85"/>
+      <c r="E29" s="83"/>
       <c r="F29" s="27"/>
       <c r="G29" s="27"/>
       <c r="H29" s="28"/>
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
-      <c r="L29" s="82"/>
+      <c r="L29" s="80"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="84"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="82"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
@@ -11578,16 +11594,16 @@
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="85"/>
+      <c r="E30" s="83"/>
       <c r="F30" s="27"/>
       <c r="G30" s="27"/>
       <c r="H30" s="28"/>
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
-      <c r="L30" s="82"/>
+      <c r="L30" s="80"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="84"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="82"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
@@ -11596,16 +11612,16 @@
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
-      <c r="E31" s="85"/>
+      <c r="E31" s="83"/>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
       <c r="H31" s="28"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
-      <c r="L31" s="82"/>
+      <c r="L31" s="80"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="84"/>
+      <c r="N31" s="81"/>
+      <c r="O31" s="82"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
@@ -11614,16 +11630,16 @@
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
-      <c r="E32" s="85"/>
+      <c r="E32" s="83"/>
       <c r="F32" s="27"/>
       <c r="G32" s="27"/>
       <c r="H32" s="28"/>
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
-      <c r="L32" s="82"/>
+      <c r="L32" s="80"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="84"/>
+      <c r="N32" s="81"/>
+      <c r="O32" s="82"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
@@ -11734,7 +11750,7 @@
       <c r="N37" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="O37" s="71"/>
+      <c r="O37" s="70"/>
       <c r="P37" s="52"/>
       <c r="Q37" s="18"/>
     </row>
@@ -11748,7 +11764,7 @@
       <c r="N38" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="O38" s="71"/>
+      <c r="O38" s="70"/>
       <c r="P38" s="52" t="s">
         <v>113</v>
       </c>
@@ -11764,7 +11780,7 @@
       <c r="N39" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="O39" s="71"/>
+      <c r="O39" s="70"/>
       <c r="P39" s="52" t="s">
         <v>117</v>
       </c>
@@ -11776,7 +11792,7 @@
       <c r="N40" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="O40" s="71"/>
+      <c r="O40" s="70"/>
       <c r="P40" s="53"/>
       <c r="Q40" s="18"/>
     </row>
@@ -12073,8 +12089,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="68"/>
+    <row r="6" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="67"/>
       <c r="B6" s="25" t="s">
         <v>193</v>
       </c>
@@ -12087,18 +12103,18 @@
       </c>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
       <c r="L6" s="25"/>
       <c r="M6" s="25"/>
       <c r="N6" s="31"/>
-      <c r="O6" s="71"/>
+      <c r="O6" s="70"/>
       <c r="P6" s="25"/>
       <c r="Q6" s="25"/>
     </row>
-    <row r="7" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="72"/>
+    <row r="7" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="71"/>
       <c r="B7" s="25" t="s">
         <v>194</v>
       </c>
@@ -12111,18 +12127,18 @@
       </c>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
       <c r="L7" s="25"/>
       <c r="M7" s="25"/>
       <c r="N7" s="31"/>
-      <c r="O7" s="71"/>
+      <c r="O7" s="70"/>
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
     </row>
-    <row r="8" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="72"/>
+    <row r="8" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="71"/>
       <c r="B8" s="25" t="s">
         <v>195</v>
       </c>
@@ -12135,18 +12151,18 @@
       </c>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
       <c r="N8" s="31"/>
-      <c r="O8" s="71"/>
+      <c r="O8" s="70"/>
       <c r="P8" s="25"/>
       <c r="Q8" s="25"/>
     </row>
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="68"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="25" t="s">
         <v>197</v>
       </c>
@@ -12161,16 +12177,16 @@
       <c r="G9" s="25"/>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
-      <c r="J9" s="73"/>
+      <c r="J9" s="72"/>
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
       <c r="N9" s="31"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="70"/>
       <c r="P9" s="25"/>
       <c r="Q9" s="25"/>
     </row>
     <row r="10" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="72"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="25" t="s">
         <v>199</v>
       </c>
@@ -12185,16 +12201,16 @@
       <c r="G10" s="25"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
-      <c r="J10" s="73"/>
+      <c r="J10" s="72"/>
       <c r="L10" s="25"/>
       <c r="M10" s="25"/>
       <c r="N10" s="31"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="70"/>
       <c r="P10" s="25"/>
       <c r="Q10" s="25"/>
     </row>
-    <row r="11" s="67" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="72"/>
+    <row r="11" s="66" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="71"/>
       <c r="B11" s="25" t="s">
         <v>201</v>
       </c>
@@ -12207,18 +12223,18 @@
       </c>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
       <c r="L11" s="25"/>
       <c r="M11" s="25"/>
       <c r="N11" s="31"/>
-      <c r="O11" s="71"/>
+      <c r="O11" s="70"/>
       <c r="P11" s="25"/>
       <c r="Q11" s="25"/>
     </row>
     <row r="12" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="72"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="25" t="s">
         <v>203</v>
       </c>
@@ -12237,12 +12253,12 @@
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
       <c r="N12" s="31"/>
-      <c r="O12" s="71"/>
+      <c r="O12" s="70"/>
       <c r="P12" s="25"/>
       <c r="Q12" s="25"/>
     </row>
     <row r="13" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="68"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="25" t="s">
         <v>205</v>
       </c>
@@ -12261,12 +12277,12 @@
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="31"/>
-      <c r="O13" s="71"/>
+      <c r="O13" s="70"/>
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
     </row>
     <row r="14" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="68"/>
+      <c r="A14" s="67"/>
       <c r="B14" s="25" t="s">
         <v>206</v>
       </c>
@@ -12281,16 +12297,16 @@
       <c r="G14" s="25"/>
       <c r="H14" s="28"/>
       <c r="I14" s="30"/>
-      <c r="J14" s="73"/>
+      <c r="J14" s="72"/>
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
       <c r="N14" s="31"/>
-      <c r="O14" s="71"/>
+      <c r="O14" s="70"/>
       <c r="P14" s="25"/>
       <c r="Q14" s="25"/>
     </row>
     <row r="15" s="5" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="72"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="25" t="s">
         <v>208</v>
       </c>
@@ -12305,16 +12321,16 @@
       <c r="G15" s="25"/>
       <c r="H15" s="28"/>
       <c r="I15" s="30"/>
-      <c r="J15" s="73"/>
+      <c r="J15" s="72"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="31"/>
-      <c r="O15" s="71"/>
+      <c r="O15" s="70"/>
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
     </row>
     <row r="16" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="72"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="25"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -12323,19 +12339,19 @@
       <c r="G16" s="25"/>
       <c r="H16" s="28"/>
       <c r="I16" s="30"/>
-      <c r="J16" s="73"/>
+      <c r="J16" s="72"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="31"/>
-      <c r="O16" s="71"/>
+      <c r="O16" s="70"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="25" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="72"/>
-      <c r="B17" s="74"/>
+      <c r="A17" s="71"/>
+      <c r="B17" s="73"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
@@ -12347,16 +12363,16 @@
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
       <c r="N17" s="31"/>
-      <c r="O17" s="71"/>
+      <c r="O17" s="70"/>
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
     </row>
     <row r="18" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="72"/>
-      <c r="B18" s="75"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="74"/>
       <c r="C18" s="25"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="74"/>
       <c r="F18" s="25"/>
       <c r="G18" s="25"/>
       <c r="H18" s="28"/>
@@ -12365,15 +12381,15 @@
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
       <c r="N18" s="31"/>
-      <c r="O18" s="71"/>
+      <c r="O18" s="70"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
     </row>
     <row r="19" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="72"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="76"/>
+      <c r="D19" s="75"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
       <c r="G19" s="25"/>
@@ -12383,35 +12399,35 @@
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
       <c r="N19" s="31"/>
-      <c r="O19" s="71"/>
+      <c r="O19" s="70"/>
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
     </row>
     <row r="20" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="72"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="25"/>
-      <c r="C20" s="77"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="25"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="81"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="79"/>
       <c r="L20" s="25"/>
       <c r="M20" s="25"/>
       <c r="N20" s="31"/>
-      <c r="O20" s="71"/>
+      <c r="O20" s="70"/>
       <c r="P20" s="25"/>
       <c r="Q20" s="25"/>
     </row>
     <row r="21" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="72"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
-      <c r="E21" s="78"/>
+      <c r="E21" s="62"/>
       <c r="F21" s="25"/>
       <c r="G21" s="25"/>
       <c r="H21" s="28"/>
@@ -12420,16 +12436,16 @@
       <c r="L21" s="25"/>
       <c r="M21" s="25"/>
       <c r="N21" s="31"/>
-      <c r="O21" s="71"/>
+      <c r="O21" s="70"/>
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
     </row>
     <row r="22" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="68"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
-      <c r="E22" s="78"/>
+      <c r="E22" s="62"/>
       <c r="F22" s="25"/>
       <c r="G22" s="25"/>
       <c r="H22" s="28"/>
@@ -12438,7 +12454,7 @@
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
       <c r="N22" s="31"/>
-      <c r="O22" s="71"/>
+      <c r="O22" s="70"/>
       <c r="P22" s="25"/>
       <c r="Q22" s="25"/>
     </row>
@@ -12447,16 +12463,16 @@
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="78"/>
+      <c r="E23" s="62"/>
       <c r="F23" s="27"/>
       <c r="G23" s="27"/>
       <c r="H23" s="28"/>
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
-      <c r="L23" s="82"/>
+      <c r="L23" s="80"/>
       <c r="M23" s="32"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="84"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="82"/>
       <c r="P23" s="32"/>
       <c r="Q23" s="32"/>
     </row>
@@ -12465,16 +12481,16 @@
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
-      <c r="E24" s="78"/>
+      <c r="E24" s="62"/>
       <c r="F24" s="27"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28"/>
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
-      <c r="L24" s="82"/>
+      <c r="L24" s="80"/>
       <c r="M24" s="32"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="84"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="82"/>
       <c r="P24" s="32"/>
       <c r="Q24" s="32"/>
     </row>
@@ -12483,16 +12499,16 @@
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="E25" s="78"/>
+      <c r="E25" s="62"/>
       <c r="F25" s="27"/>
       <c r="G25" s="27"/>
       <c r="H25" s="28"/>
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
-      <c r="L25" s="82"/>
+      <c r="L25" s="80"/>
       <c r="M25" s="32"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="84"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="82"/>
       <c r="P25" s="32"/>
       <c r="Q25" s="32"/>
     </row>
@@ -12501,16 +12517,16 @@
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="78"/>
+      <c r="E26" s="62"/>
       <c r="F26" s="27"/>
       <c r="G26" s="27"/>
       <c r="H26" s="28"/>
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
-      <c r="L26" s="82"/>
+      <c r="L26" s="80"/>
       <c r="M26" s="32"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="84"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="82"/>
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
     </row>
@@ -12519,16 +12535,16 @@
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="85"/>
+      <c r="E27" s="83"/>
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
       <c r="H27" s="28"/>
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
-      <c r="L27" s="82"/>
+      <c r="L27" s="80"/>
       <c r="M27" s="32"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="84"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="82"/>
       <c r="P27" s="32"/>
       <c r="Q27" s="32"/>
     </row>
@@ -12537,16 +12553,16 @@
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
-      <c r="E28" s="85"/>
+      <c r="E28" s="83"/>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
       <c r="H28" s="28"/>
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
-      <c r="L28" s="82"/>
+      <c r="L28" s="80"/>
       <c r="M28" s="32"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="84"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="82"/>
       <c r="P28" s="32"/>
       <c r="Q28" s="32"/>
     </row>
@@ -12555,16 +12571,16 @@
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
-      <c r="E29" s="85"/>
+      <c r="E29" s="83"/>
       <c r="F29" s="27"/>
       <c r="G29" s="27"/>
       <c r="H29" s="28"/>
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
-      <c r="L29" s="82"/>
+      <c r="L29" s="80"/>
       <c r="M29" s="32"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="84"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="82"/>
       <c r="P29" s="32"/>
       <c r="Q29" s="32"/>
     </row>
@@ -12573,16 +12589,16 @@
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="85"/>
+      <c r="E30" s="83"/>
       <c r="F30" s="27"/>
       <c r="G30" s="27"/>
       <c r="H30" s="28"/>
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
-      <c r="L30" s="82"/>
+      <c r="L30" s="80"/>
       <c r="M30" s="32"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="84"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="82"/>
       <c r="P30" s="32"/>
       <c r="Q30" s="32"/>
     </row>
@@ -12591,16 +12607,16 @@
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
-      <c r="E31" s="85"/>
+      <c r="E31" s="83"/>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
       <c r="H31" s="28"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
-      <c r="L31" s="82"/>
+      <c r="L31" s="80"/>
       <c r="M31" s="32"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="84"/>
+      <c r="N31" s="81"/>
+      <c r="O31" s="82"/>
       <c r="P31" s="32"/>
       <c r="Q31" s="32"/>
     </row>
@@ -12609,16 +12625,16 @@
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
-      <c r="E32" s="85"/>
+      <c r="E32" s="83"/>
       <c r="F32" s="27"/>
       <c r="G32" s="27"/>
       <c r="H32" s="28"/>
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
-      <c r="L32" s="82"/>
+      <c r="L32" s="80"/>
       <c r="M32" s="32"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="84"/>
+      <c r="N32" s="81"/>
+      <c r="O32" s="82"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
     </row>
@@ -12729,7 +12745,7 @@
       <c r="N37" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="O37" s="71"/>
+      <c r="O37" s="70"/>
       <c r="P37" s="52"/>
       <c r="Q37" s="18"/>
     </row>
@@ -12743,7 +12759,7 @@
       <c r="N38" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="O38" s="71"/>
+      <c r="O38" s="70"/>
       <c r="P38" s="52" t="s">
         <v>113</v>
       </c>
@@ -12759,7 +12775,7 @@
       <c r="N39" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="O39" s="71"/>
+      <c r="O39" s="70"/>
       <c r="P39" s="52" t="s">
         <v>117</v>
       </c>
@@ -12771,7 +12787,7 @@
       <c r="N40" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="O40" s="71"/>
+      <c r="O40" s="70"/>
       <c r="P40" s="53"/>
       <c r="Q40" s="18"/>
     </row>

--- a/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
+++ b/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="4" activeTab="11"/>
+    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="5" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="修订记录" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,12 @@
     <sheet name="客户资产负债基数表" sheetId="10" r:id="rId10"/>
     <sheet name="客户资产负债表" sheetId="11" r:id="rId11"/>
     <sheet name="客户等级信息表" sheetId="12" r:id="rId12"/>
-    <sheet name="Sheet1" sheetId="13" r:id="rId13"/>
-    <sheet name="逻辑模型维度描述" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet name="逻辑模型维度描述" sheetId="14" state="hidden" r:id="rId13"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId14"/>
     <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
-    <externalReference r:id="rId17"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">实体清单!$B$1:$G$8</definedName>
@@ -92,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="288">
   <si>
     <t>文档修订记录</t>
   </si>
@@ -885,9 +884,6 @@
   </si>
   <si>
     <t>DWS_CUST_LVL_INFO</t>
-  </si>
-  <si>
-    <t>DATA_DT</t>
   </si>
   <si>
     <t>客户等级</t>
@@ -6111,7 +6107,7 @@
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A6" s="24"/>
       <c r="B6" s="25" t="s">
-        <v>262</v>
+        <v>137</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="25" t="s">
@@ -6166,7 +6162,7 @@
         <v>80</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F8" s="27"/>
       <c r="G8" s="27"/>
@@ -6651,17 +6647,6 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet690"/>
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
@@ -6674,102 +6659,102 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -6777,7 +6762,7 @@
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -6785,7 +6770,7 @@
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -10082,7 +10067,7 @@
     <mergeCell ref="A14:A21"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 C9:C21 C23:C32">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C32">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
+++ b/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="5" activeTab="12"/>
+    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="5" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="修订记录" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,6 @@
     <externalReference r:id="rId17"/>
     <externalReference r:id="rId18"/>
     <externalReference r:id="rId19"/>
-    <externalReference r:id="rId20"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">实体清单!$B$1:$G$8</definedName>
@@ -108,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="430">
   <si>
     <t>文档修订记录</t>
   </si>
@@ -904,6 +903,12 @@
   </si>
   <si>
     <t>客户等级</t>
+  </si>
+  <si>
+    <t>CUST_HRAKY</t>
+  </si>
+  <si>
+    <t>客户权益等级</t>
   </si>
   <si>
     <t>实体中文名称</t>
@@ -4653,31 +4658,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="实体清单"/>
-      <sheetName val="目标表定义"/>
-      <sheetName val="客户渠道使用表"/>
-      <sheetName val="客户渠道使用表-全渠道-废弃"/>
-      <sheetName val="零售潜在客户信息表"/>
-      <sheetName val="客户生命周期表"/>
-      <sheetName val="逻辑模型维度描述"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -6770,7 +6750,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultColWidth="8.23148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="75" customWidth="1"/>
@@ -6902,14 +6882,14 @@
     <row r="6" s="74" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A6" s="90"/>
       <c r="B6" s="91" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="C6" s="92"/>
       <c r="D6" s="91" t="s">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="E6" s="91" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="F6" s="93"/>
       <c r="G6" s="93"/>
@@ -6926,14 +6906,14 @@
     <row r="7" s="74" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A7" s="90"/>
       <c r="B7" s="91" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="C7" s="92"/>
       <c r="D7" s="91" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="E7" s="91" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F7" s="93"/>
       <c r="G7" s="93"/>
@@ -6949,15 +6929,15 @@
     </row>
     <row r="8" s="74" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A8" s="90"/>
-      <c r="B8" s="99" t="s">
-        <v>97</v>
+      <c r="B8" s="91" t="s">
+        <v>61</v>
       </c>
       <c r="C8" s="92"/>
       <c r="D8" s="91" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E8" s="91" t="s">
-        <v>262</v>
+        <v>145</v>
       </c>
       <c r="F8" s="93"/>
       <c r="G8" s="93"/>
@@ -6967,21 +6947,21 @@
       <c r="L8" s="97"/>
       <c r="M8" s="91"/>
       <c r="N8" s="97"/>
-      <c r="O8" s="100"/>
+      <c r="O8" s="97"/>
       <c r="P8" s="98"/>
       <c r="Q8" s="98"/>
     </row>
     <row r="9" s="74" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="90"/>
-      <c r="B9" s="91" t="s">
-        <v>84</v>
+      <c r="B9" s="99" t="s">
+        <v>97</v>
       </c>
       <c r="C9" s="92"/>
       <c r="D9" s="91" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E9" s="91" t="s">
-        <v>86</v>
+        <v>262</v>
       </c>
       <c r="F9" s="93"/>
       <c r="G9" s="93"/>
@@ -6991,16 +6971,22 @@
       <c r="L9" s="97"/>
       <c r="M9" s="91"/>
       <c r="N9" s="97"/>
-      <c r="O9" s="97"/>
+      <c r="O9" s="100"/>
       <c r="P9" s="98"/>
       <c r="Q9" s="98"/>
     </row>
     <row r="10" s="74" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="90"/>
-      <c r="B10" s="91"/>
+      <c r="B10" s="91" t="s">
+        <v>76</v>
+      </c>
       <c r="C10" s="92"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
+      <c r="D10" s="91" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10" s="74" t="s">
+        <v>212</v>
+      </c>
       <c r="F10" s="93"/>
       <c r="G10" s="93"/>
       <c r="H10" s="94"/>
@@ -7015,10 +7001,16 @@
     </row>
     <row r="11" s="74" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="90"/>
-      <c r="B11" s="91"/>
+      <c r="B11" s="99" t="s">
+        <v>263</v>
+      </c>
       <c r="C11" s="92"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
+      <c r="D11" s="91" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="91" t="s">
+        <v>264</v>
+      </c>
       <c r="F11" s="93"/>
       <c r="G11" s="93"/>
       <c r="H11" s="94"/>
@@ -7045,7 +7037,7 @@
       <c r="L12" s="97"/>
       <c r="M12" s="91"/>
       <c r="N12" s="97"/>
-      <c r="O12" s="100"/>
+      <c r="O12" s="97"/>
       <c r="P12" s="98"/>
       <c r="Q12" s="98"/>
     </row>
@@ -7099,7 +7091,7 @@
       <c r="L15" s="97"/>
       <c r="M15" s="91"/>
       <c r="N15" s="97"/>
-      <c r="O15" s="97"/>
+      <c r="O15" s="100"/>
       <c r="P15" s="98"/>
       <c r="Q15" s="98"/>
     </row>
@@ -7117,7 +7109,7 @@
       <c r="L16" s="97"/>
       <c r="M16" s="91"/>
       <c r="N16" s="97"/>
-      <c r="O16" s="100"/>
+      <c r="O16" s="97"/>
       <c r="P16" s="98"/>
       <c r="Q16" s="98"/>
     </row>
@@ -7135,13 +7127,13 @@
       <c r="L17" s="97"/>
       <c r="M17" s="91"/>
       <c r="N17" s="97"/>
-      <c r="O17" s="97"/>
+      <c r="O17" s="100"/>
       <c r="P17" s="98"/>
       <c r="Q17" s="98"/>
     </row>
     <row r="18" s="74" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="90"/>
-      <c r="B18" s="101"/>
+      <c r="B18" s="91"/>
       <c r="C18" s="92"/>
       <c r="D18" s="91"/>
       <c r="E18" s="91"/>
@@ -7153,116 +7145,126 @@
       <c r="L18" s="97"/>
       <c r="M18" s="91"/>
       <c r="N18" s="97"/>
-      <c r="O18" s="100"/>
+      <c r="O18" s="97"/>
       <c r="P18" s="98"/>
       <c r="Q18" s="98"/>
     </row>
     <row r="19" s="74" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A19" s="90"/>
       <c r="B19" s="101"/>
       <c r="C19" s="92"/>
       <c r="D19" s="91"/>
       <c r="E19" s="91"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="82"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
       <c r="H19" s="94"/>
       <c r="I19" s="95"/>
       <c r="J19" s="96"/>
       <c r="L19" s="97"/>
       <c r="M19" s="91"/>
       <c r="N19" s="97"/>
-      <c r="O19" s="97"/>
-      <c r="P19" s="102"/>
-      <c r="Q19" s="103"/>
+      <c r="O19" s="100"/>
+      <c r="P19" s="98"/>
+      <c r="Q19" s="98"/>
     </row>
     <row r="20" s="74" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B20" s="104"/>
+      <c r="B20" s="101"/>
       <c r="C20" s="92"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="91"/>
       <c r="F20" s="83"/>
       <c r="G20" s="82"/>
       <c r="H20" s="94"/>
       <c r="I20" s="95"/>
       <c r="J20" s="96"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="107"/>
-      <c r="N20" s="107"/>
-      <c r="O20" s="107"/>
+      <c r="L20" s="97"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="97"/>
+      <c r="O20" s="97"/>
       <c r="P20" s="102"/>
       <c r="Q20" s="103"/>
     </row>
-    <row r="21" s="72" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B21" s="78" t="s">
+    <row r="21" s="74" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="B21" s="104"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="107"/>
+      <c r="N21" s="107"/>
+      <c r="O21" s="107"/>
+      <c r="P21" s="102"/>
+      <c r="Q21" s="103"/>
+    </row>
+    <row r="22" s="72" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
+      <c r="B22" s="78" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="82"/>
-      <c r="L21" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="M21" s="86"/>
-      <c r="N21" s="86"/>
-      <c r="O21" s="86"/>
-      <c r="P21" s="86"/>
-      <c r="Q21" s="87"/>
-    </row>
-    <row r="22" s="72" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B22" s="108" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="108" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="108" t="s">
-        <v>45</v>
-      </c>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
       <c r="E22" s="80"/>
       <c r="F22" s="80"/>
       <c r="G22" s="80"/>
       <c r="H22" s="80"/>
       <c r="I22" s="80"/>
       <c r="J22" s="82"/>
-      <c r="L22" s="109" t="s">
-        <v>102</v>
-      </c>
-      <c r="M22" s="110" t="s">
-        <v>103</v>
-      </c>
-      <c r="N22" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O22" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="P22" s="42" t="s">
-        <v>106</v>
-      </c>
+      <c r="L22" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="M22" s="86"/>
+      <c r="N22" s="86"/>
+      <c r="O22" s="86"/>
+      <c r="P22" s="86"/>
       <c r="Q22" s="87"/>
     </row>
-    <row r="23" s="73" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
-      <c r="B23" s="111"/>
-      <c r="C23" s="112"/>
-      <c r="D23" s="96"/>
+    <row r="23" s="72" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
+      <c r="B23" s="108" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="108" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="108" t="s">
+        <v>45</v>
+      </c>
       <c r="E23" s="80"/>
       <c r="F23" s="80"/>
       <c r="G23" s="80"/>
       <c r="H23" s="80"/>
       <c r="I23" s="80"/>
       <c r="J23" s="82"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="46"/>
+      <c r="L23" s="109" t="s">
+        <v>102</v>
+      </c>
+      <c r="M23" s="110" t="s">
+        <v>103</v>
+      </c>
+      <c r="N23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O23" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="P23" s="42" t="s">
+        <v>106</v>
+      </c>
       <c r="Q23" s="87"/>
     </row>
-    <row r="24" s="73" customFormat="1" ht="10.8" spans="1:17">
+    <row r="24" s="73" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
+      <c r="B24" s="111"/>
+      <c r="C24" s="112"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="82"/>
       <c r="L24" s="35"/>
       <c r="M24" s="36"/>
       <c r="N24" s="47"/>
@@ -7278,12 +7280,12 @@
       <c r="P25" s="46"/>
       <c r="Q25" s="87"/>
     </row>
-    <row r="26" ht="13.95" customHeight="1" spans="1:17">
+    <row r="26" s="73" customFormat="1" ht="10.8" spans="1:17">
       <c r="L26" s="35"/>
       <c r="M26" s="36"/>
       <c r="N26" s="47"/>
       <c r="O26" s="47"/>
-      <c r="P26" s="113"/>
+      <c r="P26" s="46"/>
       <c r="Q26" s="87"/>
     </row>
     <row r="27" ht="13.95" customHeight="1" spans="1:17">
@@ -7295,10 +7297,10 @@
       <c r="Q27" s="87"/>
     </row>
     <row r="28" ht="13.95" customHeight="1" spans="1:17">
-      <c r="L28" s="114"/>
-      <c r="M28" s="103"/>
-      <c r="N28" s="103"/>
-      <c r="O28" s="103"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="47"/>
+      <c r="O28" s="47"/>
       <c r="P28" s="113"/>
       <c r="Q28" s="87"/>
     </row>
@@ -7327,32 +7329,39 @@
       <c r="Q31" s="87"/>
     </row>
     <row r="32" ht="13.95" customHeight="1" spans="1:17">
-      <c r="L32" s="68"/>
-      <c r="M32" s="69"/>
-      <c r="N32" s="70"/>
+      <c r="L32" s="114"/>
+      <c r="M32" s="103"/>
+      <c r="N32" s="103"/>
       <c r="O32" s="103"/>
-      <c r="P32" s="71"/>
+      <c r="P32" s="113"/>
       <c r="Q32" s="87"/>
     </row>
     <row r="33" ht="13.95" customHeight="1" spans="12:17">
-      <c r="L33" s="115" t="s">
+      <c r="L33" s="68"/>
+      <c r="M33" s="69"/>
+      <c r="N33" s="70"/>
+      <c r="O33" s="103"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="87"/>
+    </row>
+    <row r="34" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L34" s="115" t="s">
         <v>119</v>
       </c>
-      <c r="M33" s="86"/>
-      <c r="N33" s="86"/>
-      <c r="O33" s="86"/>
-      <c r="P33" s="86"/>
-      <c r="Q33" s="87"/>
-    </row>
-    <row r="34" ht="56" customHeight="1" spans="12:17">
-      <c r="L34" s="116"/>
       <c r="M34" s="86"/>
       <c r="N34" s="86"/>
       <c r="O34" s="86"/>
       <c r="P34" s="86"/>
       <c r="Q34" s="87"/>
     </row>
-    <row r="35" ht="13.95" customHeight="1"/>
+    <row r="35" ht="56" customHeight="1" spans="12:17">
+      <c r="L35" s="116"/>
+      <c r="M35" s="86"/>
+      <c r="N35" s="86"/>
+      <c r="O35" s="86"/>
+      <c r="P35" s="86"/>
+      <c r="Q35" s="87"/>
+    </row>
     <row r="36" ht="13.95" customHeight="1"/>
     <row r="37" ht="13.95" customHeight="1"/>
     <row r="38" ht="13.95" customHeight="1"/>
@@ -7401,6 +7410,7 @@
     <row r="81" ht="13.95" customHeight="1"/>
     <row r="82" ht="13.95" customHeight="1"/>
     <row r="83" ht="13.95" customHeight="1"/>
+    <row r="84" ht="13.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
     <mergeCell ref="B1:J1"/>
@@ -7410,14 +7420,13 @@
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="L4:Q4"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F19:G19"/>
     <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B21:J21"/>
-    <mergeCell ref="L21:Q21"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="L22:Q22"/>
     <mergeCell ref="D23:J23"/>
     <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="D24:J24"/>
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="P25:Q25"/>
     <mergeCell ref="P26:Q26"/>
@@ -7427,11 +7436,12 @@
     <mergeCell ref="P30:Q30"/>
     <mergeCell ref="P31:Q31"/>
     <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="L33:Q33"/>
+    <mergeCell ref="P33:Q33"/>
     <mergeCell ref="L34:Q34"/>
+    <mergeCell ref="L35:Q35"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -7467,22 +7477,22 @@
   <sheetData>
     <row r="1" customFormat="1" ht="35" customHeight="1" spans="1:25">
       <c r="A1" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="10"/>
     </row>
     <row r="2" customFormat="1" ht="56" customHeight="1" spans="1:25">
       <c r="A2" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -7491,7 +7501,7 @@
     </row>
     <row r="3" customFormat="1" ht="23" customHeight="1" spans="1:25">
       <c r="A3" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B3" s="14">
         <v>1</v>
@@ -7522,66 +7532,66 @@
     </row>
     <row r="4" s="3" customFormat="1" ht="34" customHeight="1" spans="1:25">
       <c r="A4" s="17" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H4" s="19"/>
       <c r="I4" s="19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K4" s="19"/>
       <c r="L4" s="18"/>
       <c r="M4" s="19" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N4" s="19" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O4" s="19"/>
       <c r="P4" s="19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R4" s="19"/>
       <c r="S4" s="18"/>
       <c r="T4" s="19" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="U4" s="19" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="V4" s="19"/>
       <c r="W4" s="19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="X4" s="19" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Y4" s="19"/>
     </row>
     <row r="5" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:25">
       <c r="A5" s="20" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>186</v>
@@ -7591,7 +7601,7 @@
         <v>40</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>42</v>
@@ -7610,7 +7620,7 @@
         <v>40</v>
       </c>
       <c r="N5" s="23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O5" s="23" t="s">
         <v>42</v>
@@ -7629,7 +7639,7 @@
         <v>40</v>
       </c>
       <c r="U5" s="23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="V5" s="23" t="s">
         <v>42</v>
@@ -7646,7 +7656,7 @@
     </row>
     <row r="6" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:25">
       <c r="A6" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>84</v>
@@ -7657,7 +7667,7 @@
       <c r="D6" s="27"/>
       <c r="E6" s="21"/>
       <c r="F6" s="28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>109</v>
@@ -7672,7 +7682,7 @@
       <c r="K6" s="28"/>
       <c r="L6" s="21"/>
       <c r="M6" s="28" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N6" s="28" t="s">
         <v>109</v>
@@ -7687,7 +7697,7 @@
       <c r="R6" s="28"/>
       <c r="S6" s="21"/>
       <c r="T6" s="28" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="U6" s="28" t="s">
         <v>109</v>
@@ -7703,7 +7713,7 @@
     </row>
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A7" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>61</v>
@@ -7714,7 +7724,7 @@
       <c r="D7" s="27"/>
       <c r="E7" s="31"/>
       <c r="F7" s="28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>109</v>
@@ -7729,7 +7739,7 @@
       <c r="K7" s="28"/>
       <c r="L7" s="31"/>
       <c r="M7" s="28" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N7" s="28" t="s">
         <v>109</v>
@@ -7744,7 +7754,7 @@
       <c r="R7" s="28"/>
       <c r="S7" s="31"/>
       <c r="T7" s="28" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="U7" s="28" t="s">
         <v>109</v>
@@ -7760,7 +7770,7 @@
     </row>
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A8" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>65</v>
@@ -7771,7 +7781,7 @@
       <c r="D8" s="27"/>
       <c r="E8" s="31"/>
       <c r="F8" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>112</v>
@@ -7786,7 +7796,7 @@
       <c r="K8" s="28"/>
       <c r="L8" s="31"/>
       <c r="M8" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N8" s="28" t="s">
         <v>112</v>
@@ -7801,7 +7811,7 @@
       <c r="R8" s="28"/>
       <c r="S8" s="31"/>
       <c r="T8" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="U8" s="28" t="s">
         <v>112</v>
@@ -7817,18 +7827,18 @@
     </row>
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A9" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>172</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="31"/>
       <c r="F9" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>112</v>
@@ -7837,13 +7847,13 @@
         <v>172</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J9" s="32"/>
       <c r="K9" s="28"/>
       <c r="L9" s="31"/>
       <c r="M9" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N9" s="28" t="s">
         <v>112</v>
@@ -7852,13 +7862,13 @@
         <v>172</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q9" s="32"/>
       <c r="R9" s="28"/>
       <c r="S9" s="31"/>
       <c r="T9" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="U9" s="28" t="s">
         <v>112</v>
@@ -7867,25 +7877,25 @@
         <v>172</v>
       </c>
       <c r="W9" s="30" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="X9" s="32"/>
       <c r="Y9" s="28"/>
     </row>
     <row r="10" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A10" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>92</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="33"/>
       <c r="F10" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>112</v>
@@ -7894,13 +7904,13 @@
         <v>92</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J10" s="32"/>
       <c r="K10" s="28"/>
       <c r="L10" s="33"/>
       <c r="M10" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N10" s="28" t="s">
         <v>112</v>
@@ -7909,13 +7919,13 @@
         <v>92</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q10" s="32"/>
       <c r="R10" s="28"/>
       <c r="S10" s="33"/>
       <c r="T10" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="U10" s="28" t="s">
         <v>112</v>
@@ -7924,25 +7934,25 @@
         <v>92</v>
       </c>
       <c r="W10" s="30" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="X10" s="32"/>
       <c r="Y10" s="28"/>
     </row>
     <row r="11" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A11" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D11" s="34"/>
       <c r="E11" s="33"/>
       <c r="F11" s="28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>109</v>
@@ -7957,7 +7967,7 @@
       <c r="K11" s="32"/>
       <c r="L11" s="33"/>
       <c r="M11" s="28" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N11" s="28" t="s">
         <v>109</v>
@@ -7966,55 +7976,55 @@
         <v>215</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q11" s="32"/>
       <c r="R11" s="32"/>
       <c r="S11" s="33"/>
       <c r="T11" s="28" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="U11" s="28" t="s">
         <v>109</v>
       </c>
       <c r="V11" s="29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="W11" s="30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="X11" s="32"/>
       <c r="Y11" s="32"/>
     </row>
     <row r="12" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A12" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="33"/>
       <c r="F12" s="28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I12" s="36" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J12" s="28"/>
       <c r="K12" s="28"/>
       <c r="L12" s="33"/>
       <c r="M12" s="28" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N12" s="28" t="s">
         <v>109</v>
@@ -8023,79 +8033,79 @@
         <v>211</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q12" s="28"/>
       <c r="R12" s="28"/>
       <c r="S12" s="33"/>
       <c r="T12" s="28" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="U12" s="28" t="s">
         <v>109</v>
       </c>
       <c r="V12" s="29" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="W12" s="30" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="X12" s="28"/>
       <c r="Y12" s="28"/>
     </row>
     <row r="13" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A13" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="33"/>
       <c r="F13" s="28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G13" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I13" s="36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J13" s="28"/>
       <c r="K13" s="28"/>
       <c r="L13" s="33"/>
       <c r="M13" s="28" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N13" s="28" t="s">
         <v>109</v>
       </c>
       <c r="O13" s="29" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q13" s="28"/>
       <c r="R13" s="28"/>
       <c r="S13" s="33"/>
       <c r="T13" s="28" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="U13" s="28" t="s">
         <v>109</v>
       </c>
       <c r="V13" s="29" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="W13" s="30" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="X13" s="28"/>
       <c r="Y13" s="28"/>
@@ -8230,10 +8240,10 @@
       <c r="D17" s="45"/>
       <c r="E17" s="21"/>
       <c r="F17" s="28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>109</v>
@@ -8243,10 +8253,10 @@
       <c r="K17" s="43"/>
       <c r="L17" s="21"/>
       <c r="M17" s="28" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N17" s="28" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O17" s="29" t="s">
         <v>109</v>
@@ -8256,10 +8266,10 @@
       <c r="R17" s="43"/>
       <c r="S17" s="21"/>
       <c r="T17" s="28" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="U17" s="28" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="V17" s="29" t="s">
         <v>109</v>
@@ -8275,53 +8285,53 @@
       <c r="D18" s="21"/>
       <c r="E18" s="21"/>
       <c r="F18" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H18" s="29" t="s">
         <v>112</v>
       </c>
       <c r="I18" s="30" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J18" s="46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K18" s="43"/>
       <c r="L18" s="21"/>
       <c r="M18" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O18" s="29" t="s">
         <v>112</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q18" s="46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="R18" s="43"/>
       <c r="S18" s="21"/>
       <c r="T18" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="U18" s="28" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="V18" s="29" t="s">
         <v>112</v>
       </c>
       <c r="W18" s="30" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="X18" s="46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y18" s="43"/>
     </row>
@@ -8392,7 +8402,7 @@
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="48" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G21" s="40"/>
       <c r="H21" s="40"/>
@@ -8401,7 +8411,7 @@
       <c r="K21" s="40"/>
       <c r="L21" s="16"/>
       <c r="M21" s="48" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N21" s="40"/>
       <c r="O21" s="40"/>
@@ -8410,7 +8420,7 @@
       <c r="R21" s="40"/>
       <c r="S21" s="16"/>
       <c r="T21" s="48" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="U21" s="40"/>
       <c r="V21" s="40"/>
@@ -8421,7 +8431,7 @@
     <row r="22" ht="13.95" customHeight="1"/>
     <row r="23" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A23" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B23" s="14">
         <v>2</v>
@@ -8438,24 +8448,24 @@
     </row>
     <row r="24" customFormat="1" ht="36" customHeight="1" spans="1:25">
       <c r="A24" s="17" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
       <c r="E24" s="18"/>
       <c r="F24" s="19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H24" s="19"/>
       <c r="I24" s="19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K24" s="19"/>
       <c r="M24" s="49"/>
@@ -8467,13 +8477,13 @@
     </row>
     <row r="25" customFormat="1" ht="29" customHeight="1" spans="1:25">
       <c r="A25" s="20" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>186</v>
@@ -8483,7 +8493,7 @@
         <v>40</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H25" s="23" t="s">
         <v>42</v>
@@ -8506,7 +8516,7 @@
     </row>
     <row r="26" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A26" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B26" s="53" t="s">
         <v>84</v>
@@ -8521,7 +8531,7 @@
       <c r="H26" s="29"/>
       <c r="I26" s="30"/>
       <c r="J26" s="187" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K26" s="28"/>
       <c r="M26" s="54"/>
@@ -8533,13 +8543,13 @@
     </row>
     <row r="27" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A27" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B27" s="53" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="21"/>
@@ -8547,10 +8557,10 @@
       <c r="G27" s="28"/>
       <c r="H27" s="29"/>
       <c r="I27" s="30" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K27" s="28"/>
       <c r="M27" s="54"/>
@@ -8562,27 +8572,27 @@
     </row>
     <row r="28" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A28" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="31"/>
       <c r="F28" s="28" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G28" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I28" s="30" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J28" s="28"/>
       <c r="K28" s="28"/>
@@ -8595,16 +8605,16 @@
     </row>
     <row r="29" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A29" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B29" s="53" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E29" s="31"/>
       <c r="F29" s="28"/>
@@ -8612,7 +8622,7 @@
       <c r="H29" s="29"/>
       <c r="I29" s="30"/>
       <c r="J29" s="187" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K29" s="28"/>
       <c r="M29" s="54"/>
@@ -8624,27 +8634,27 @@
     </row>
     <row r="30" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A30" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B30" s="53" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D30" s="34"/>
       <c r="E30" s="33"/>
       <c r="F30" s="28" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G30" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I30" s="30" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J30" s="32"/>
       <c r="K30" s="28"/>
@@ -8657,27 +8667,27 @@
     </row>
     <row r="31" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A31" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B31" s="53" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D31" s="34"/>
       <c r="E31" s="33"/>
       <c r="F31" s="28" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G31" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I31" s="30" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J31" s="28"/>
       <c r="K31" s="28"/>
@@ -8690,18 +8700,18 @@
     </row>
     <row r="32" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A32" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B32" s="53" t="s">
         <v>172</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D32" s="34"/>
       <c r="E32" s="33"/>
       <c r="F32" s="28" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G32" s="28" t="s">
         <v>109</v>
@@ -8710,7 +8720,7 @@
         <v>172</v>
       </c>
       <c r="I32" s="30" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
@@ -8723,18 +8733,18 @@
     </row>
     <row r="33" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A33" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B33" s="53" t="s">
         <v>170</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D33" s="34"/>
       <c r="E33" s="33"/>
       <c r="F33" s="28" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G33" s="28" t="s">
         <v>109</v>
@@ -8743,7 +8753,7 @@
         <v>170</v>
       </c>
       <c r="I33" s="30" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J33" s="28"/>
       <c r="K33" s="28"/>
@@ -8756,18 +8766,18 @@
     </row>
     <row r="34" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A34" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B34" s="53" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D34" s="34"/>
       <c r="E34" s="33"/>
       <c r="F34" s="28" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G34" s="28" t="s">
         <v>109</v>
@@ -8789,13 +8799,13 @@
     </row>
     <row r="35" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A35" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B35" s="53" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D35" s="34"/>
       <c r="E35" s="33"/>
@@ -8804,10 +8814,10 @@
       <c r="H35" s="29"/>
       <c r="I35" s="30"/>
       <c r="J35" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K35" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M35" s="54"/>
       <c r="N35" s="54"/>
@@ -8818,13 +8828,13 @@
     </row>
     <row r="36" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A36" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D36" s="34"/>
       <c r="E36" s="33"/>
@@ -8833,10 +8843,10 @@
       <c r="H36" s="29"/>
       <c r="I36" s="30"/>
       <c r="J36" s="187" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K36" s="28" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M36" s="54"/>
       <c r="N36" s="54"/>
@@ -8847,13 +8857,13 @@
     </row>
     <row r="37" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A37" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B37" s="53" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D37" s="34"/>
       <c r="E37" s="33"/>
@@ -8862,10 +8872,10 @@
       <c r="H37" s="29"/>
       <c r="I37" s="30"/>
       <c r="J37" s="28" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K37" s="28" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M37" s="54"/>
       <c r="N37" s="54"/>
@@ -8876,16 +8886,16 @@
     </row>
     <row r="38" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A38" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E38" s="33"/>
       <c r="F38" s="28"/>
@@ -8893,7 +8903,7 @@
       <c r="H38" s="29"/>
       <c r="I38" s="30"/>
       <c r="J38" s="28" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K38" s="28"/>
       <c r="M38" s="54"/>
@@ -8905,16 +8915,16 @@
     </row>
     <row r="39" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A39" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B39" s="53" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E39" s="33"/>
       <c r="F39" s="28"/>
@@ -8922,7 +8932,7 @@
       <c r="H39" s="29"/>
       <c r="I39" s="30"/>
       <c r="J39" s="28" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K39" s="28"/>
       <c r="M39" s="54"/>
@@ -8934,13 +8944,13 @@
     </row>
     <row r="40" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A40" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B40" s="53" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D40" s="34"/>
       <c r="E40" s="33"/>
@@ -8949,10 +8959,10 @@
       <c r="H40" s="29"/>
       <c r="I40" s="30"/>
       <c r="J40" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K40" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M40" s="54"/>
       <c r="N40" s="54"/>
@@ -8963,10 +8973,10 @@
     </row>
     <row r="41" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A41" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B41" s="53" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C41" s="27" t="s">
         <v>212</v>
@@ -8978,10 +8988,10 @@
       <c r="H41" s="29"/>
       <c r="I41" s="30"/>
       <c r="J41" s="187" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K41" s="28" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M41" s="54"/>
       <c r="N41" s="54"/>
@@ -8992,13 +9002,13 @@
     </row>
     <row r="42" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A42" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B42" s="53" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D42" s="27"/>
       <c r="E42" s="33"/>
@@ -9007,10 +9017,10 @@
       <c r="H42" s="29"/>
       <c r="I42" s="30"/>
       <c r="J42" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K42" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M42" s="54"/>
       <c r="N42" s="54"/>
@@ -9021,13 +9031,13 @@
     </row>
     <row r="43" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A43" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B43" s="53" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="33"/>
@@ -9036,10 +9046,10 @@
       <c r="H43" s="29"/>
       <c r="I43" s="30"/>
       <c r="J43" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K43" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M43" s="54"/>
       <c r="N43" s="54"/>
@@ -9050,13 +9060,13 @@
     </row>
     <row r="44" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A44" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B44" s="53" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D44" s="27"/>
       <c r="E44" s="33"/>
@@ -9065,10 +9075,10 @@
       <c r="H44" s="29"/>
       <c r="I44" s="30"/>
       <c r="J44" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K44" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M44" s="54"/>
       <c r="N44" s="54"/>
@@ -9079,13 +9089,13 @@
     </row>
     <row r="45" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A45" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B45" s="53" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D45" s="27"/>
       <c r="E45" s="33"/>
@@ -9094,10 +9104,10 @@
       <c r="H45" s="29"/>
       <c r="I45" s="30"/>
       <c r="J45" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K45" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M45" s="54"/>
       <c r="N45" s="54"/>
@@ -9108,10 +9118,10 @@
     </row>
     <row r="46" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A46" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B46" s="53" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C46" s="27" t="s">
         <v>45</v>
@@ -9123,10 +9133,10 @@
       <c r="H46" s="29"/>
       <c r="I46" s="30"/>
       <c r="J46" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K46" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M46" s="54"/>
       <c r="N46" s="54"/>
@@ -9137,13 +9147,13 @@
     </row>
     <row r="47" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A47" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B47" s="53" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D47" s="27"/>
       <c r="E47" s="33"/>
@@ -9152,10 +9162,10 @@
       <c r="H47" s="29"/>
       <c r="I47" s="30"/>
       <c r="J47" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K47" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M47" s="54"/>
       <c r="N47" s="54"/>
@@ -9166,13 +9176,13 @@
     </row>
     <row r="48" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A48" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B48" s="53" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D48" s="27"/>
       <c r="E48" s="33"/>
@@ -9181,10 +9191,10 @@
       <c r="H48" s="29"/>
       <c r="I48" s="30"/>
       <c r="J48" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K48" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M48" s="54"/>
       <c r="N48" s="54"/>
@@ -9195,13 +9205,13 @@
     </row>
     <row r="49" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A49" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B49" s="53" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D49" s="27"/>
       <c r="E49" s="33"/>
@@ -9210,10 +9220,10 @@
       <c r="H49" s="29"/>
       <c r="I49" s="30"/>
       <c r="J49" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K49" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M49" s="54"/>
       <c r="N49" s="54"/>
@@ -9224,13 +9234,13 @@
     </row>
     <row r="50" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A50" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B50" s="53" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D50" s="27"/>
       <c r="E50" s="33"/>
@@ -9239,10 +9249,10 @@
       <c r="H50" s="29"/>
       <c r="I50" s="30"/>
       <c r="J50" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K50" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M50" s="54"/>
       <c r="N50" s="54"/>
@@ -9253,13 +9263,13 @@
     </row>
     <row r="51" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A51" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B51" s="53" t="s">
         <v>61</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D51" s="27"/>
       <c r="E51" s="33"/>
@@ -9268,10 +9278,10 @@
       <c r="H51" s="29"/>
       <c r="I51" s="30"/>
       <c r="J51" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K51" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M51" s="54"/>
       <c r="N51" s="54"/>
@@ -9282,13 +9292,13 @@
     </row>
     <row r="52" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A52" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B52" s="53" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D52" s="34"/>
       <c r="E52" s="33"/>
@@ -9297,10 +9307,10 @@
       <c r="H52" s="29"/>
       <c r="I52" s="30"/>
       <c r="J52" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K52" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M52" s="54"/>
       <c r="N52" s="54"/>
@@ -9311,13 +9321,13 @@
     </row>
     <row r="53" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A53" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B53" s="53" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D53" s="27"/>
       <c r="E53" s="33"/>
@@ -9326,10 +9336,10 @@
       <c r="H53" s="29"/>
       <c r="I53" s="30"/>
       <c r="J53" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K53" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M53" s="54"/>
       <c r="N53" s="54"/>
@@ -9340,13 +9350,13 @@
     </row>
     <row r="54" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A54" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B54" s="53" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D54" s="27"/>
       <c r="E54" s="33"/>
@@ -9355,10 +9365,10 @@
       <c r="H54" s="29"/>
       <c r="I54" s="30"/>
       <c r="J54" s="187" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K54" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M54" s="54"/>
       <c r="N54" s="54"/>
@@ -9369,13 +9379,13 @@
     </row>
     <row r="55" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A55" s="57" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C55" s="59" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D55" s="59"/>
       <c r="E55" s="60"/>
@@ -9384,10 +9394,10 @@
       <c r="H55" s="62"/>
       <c r="I55" s="63"/>
       <c r="J55" s="188" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K55" s="61" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M55" s="54"/>
       <c r="N55" s="54"/>
@@ -9398,13 +9408,13 @@
     </row>
     <row r="56" customFormat="1" ht="13.95" customHeight="1" spans="1:18">
       <c r="A56" s="57" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B56" s="58" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C56" s="59" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D56" s="59"/>
       <c r="E56" s="60"/>
@@ -9416,7 +9426,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="61" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M56" s="54"/>
       <c r="N56" s="54"/>
@@ -9488,10 +9498,10 @@
       <c r="D59" s="45"/>
       <c r="E59" s="21"/>
       <c r="F59" s="28" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H59" s="29" t="s">
         <v>109</v>
@@ -9553,7 +9563,7 @@
       <c r="D62" s="15"/>
       <c r="E62" s="15"/>
       <c r="F62" s="48" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G62" s="40"/>
       <c r="H62" s="40"/>
@@ -9570,7 +9580,7 @@
     <row r="63" ht="13.95" customHeight="1"/>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:18">
       <c r="A64" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B64" s="14">
         <v>3</v>
@@ -9587,36 +9597,36 @@
     </row>
     <row r="65" customFormat="1" ht="20" customHeight="1" spans="1:11">
       <c r="A65" s="17" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
       <c r="D65" s="17"/>
       <c r="E65" s="18"/>
       <c r="F65" s="19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H65" s="19"/>
       <c r="I65" s="19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J65" s="19" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K65" s="19"/>
     </row>
     <row r="66" customFormat="1" ht="37" customHeight="1" spans="1:11">
       <c r="A66" s="20" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D66" s="20" t="s">
         <v>186</v>
@@ -9626,7 +9636,7 @@
         <v>40</v>
       </c>
       <c r="G66" s="23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H66" s="23" t="s">
         <v>42</v>
@@ -9643,7 +9653,7 @@
     </row>
     <row r="67" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A67" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B67" s="53" t="s">
         <v>84</v>
@@ -9654,7 +9664,7 @@
       <c r="D67" s="34"/>
       <c r="E67" s="33"/>
       <c r="F67" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G67" s="28" t="s">
         <v>109</v>
@@ -9670,13 +9680,13 @@
     </row>
     <row r="68" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A68" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B68" s="53" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C68" s="27" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D68" s="27"/>
       <c r="E68" s="21"/>
@@ -9684,137 +9694,137 @@
       <c r="G68" s="28"/>
       <c r="H68" s="29"/>
       <c r="I68" s="30" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J68" s="28" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K68" s="28"/>
     </row>
     <row r="69" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A69" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B69" s="53" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D69" s="27"/>
       <c r="E69" s="31"/>
       <c r="F69" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G69" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H69" s="53" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I69" s="27" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J69" s="28"/>
       <c r="K69" s="28"/>
     </row>
     <row r="70" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A70" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B70" s="53" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D70" s="34" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E70" s="31"/>
       <c r="F70" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G70" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H70" s="53" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I70" s="34" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J70" s="28"/>
       <c r="K70" s="28"/>
     </row>
     <row r="71" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A71" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B71" s="53" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D71" s="34"/>
       <c r="E71" s="33"/>
       <c r="F71" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G71" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H71" s="53" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I71" s="34" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J71" s="32"/>
       <c r="K71" s="28"/>
     </row>
     <row r="72" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A72" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B72" s="53" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D72" s="34"/>
       <c r="E72" s="33"/>
       <c r="F72" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G72" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H72" s="53" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I72" s="34" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J72" s="28"/>
       <c r="K72" s="28"/>
     </row>
     <row r="73" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A73" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B73" s="53" t="s">
         <v>172</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D73" s="34"/>
       <c r="E73" s="33"/>
       <c r="F73" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G73" s="28" t="s">
         <v>109</v>
@@ -9823,25 +9833,25 @@
         <v>172</v>
       </c>
       <c r="I73" s="34" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J73" s="28"/>
       <c r="K73" s="28"/>
     </row>
     <row r="74" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A74" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B74" s="53" t="s">
         <v>170</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D74" s="34"/>
       <c r="E74" s="33"/>
       <c r="F74" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G74" s="28" t="s">
         <v>109</v>
@@ -9850,214 +9860,214 @@
         <v>170</v>
       </c>
       <c r="I74" s="34" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J74" s="28"/>
       <c r="K74" s="28"/>
     </row>
     <row r="75" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A75" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B75" s="53" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D75" s="34"/>
       <c r="E75" s="33"/>
       <c r="F75" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G75" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H75" s="53" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I75" s="34" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J75" s="28"/>
       <c r="K75" s="28"/>
     </row>
     <row r="76" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A76" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B76" s="53" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D76" s="34"/>
       <c r="E76" s="33"/>
       <c r="F76" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G76" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H76" s="53" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I76" s="34" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J76" s="28"/>
       <c r="K76" s="28"/>
     </row>
     <row r="77" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A77" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B77" s="53" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D77" s="34"/>
       <c r="E77" s="33"/>
       <c r="F77" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G77" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H77" s="53" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I77" s="34" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J77" s="28"/>
       <c r="K77" s="28"/>
     </row>
     <row r="78" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A78" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B78" s="53" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D78" s="34"/>
       <c r="E78" s="33"/>
       <c r="F78" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G78" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H78" s="53" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I78" s="34" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J78" s="28"/>
       <c r="K78" s="28"/>
     </row>
     <row r="79" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A79" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B79" s="53" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D79" s="34" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E79" s="33"/>
       <c r="F79" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G79" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H79" s="53" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I79" s="34" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J79" s="28"/>
       <c r="K79" s="28"/>
     </row>
     <row r="80" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A80" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B80" s="53" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C80" s="34" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D80" s="34" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E80" s="33"/>
       <c r="F80" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G80" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H80" s="53" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I80" s="34" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J80" s="28" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K80" s="28" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="81" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A81" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B81" s="53" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D81" s="34"/>
       <c r="E81" s="33"/>
       <c r="F81" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G81" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H81" s="53" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I81" s="34" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J81" s="28"/>
       <c r="K81" s="28"/>
     </row>
     <row r="82" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A82" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B82" s="53" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C82" s="27" t="s">
         <v>212</v>
@@ -10065,13 +10075,13 @@
       <c r="D82" s="27"/>
       <c r="E82" s="33"/>
       <c r="F82" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G82" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H82" s="53" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I82" s="27" t="s">
         <v>212</v>
@@ -10081,118 +10091,118 @@
     </row>
     <row r="83" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A83" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B83" s="53" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C83" s="27" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="33"/>
       <c r="F83" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G83" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H83" s="53" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I83" s="27" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J83" s="28"/>
       <c r="K83" s="28"/>
     </row>
     <row r="84" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A84" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B84" s="53" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C84" s="27" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="33"/>
       <c r="F84" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G84" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H84" s="53" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I84" s="27" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J84" s="28"/>
       <c r="K84" s="28"/>
     </row>
     <row r="85" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A85" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B85" s="53" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C85" s="27" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D85" s="27"/>
       <c r="E85" s="33"/>
       <c r="F85" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G85" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H85" s="53" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I85" s="27" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J85" s="28"/>
       <c r="K85" s="28"/>
     </row>
     <row r="86" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A86" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B86" s="53" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C86" s="27" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D86" s="27"/>
       <c r="E86" s="33"/>
       <c r="F86" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G86" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H86" s="53" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I86" s="27" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J86" s="28"/>
       <c r="K86" s="28"/>
     </row>
     <row r="87" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A87" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B87" s="53" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C87" s="27" t="s">
         <v>45</v>
@@ -10200,13 +10210,13 @@
       <c r="D87" s="27"/>
       <c r="E87" s="33"/>
       <c r="F87" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G87" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H87" s="53" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I87" s="27" t="s">
         <v>45</v>
@@ -10216,126 +10226,126 @@
     </row>
     <row r="88" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A88" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B88" s="53" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C88" s="27" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D88" s="27"/>
       <c r="E88" s="33"/>
       <c r="F88" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G88" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H88" s="53" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I88" s="27" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J88" s="28"/>
       <c r="K88" s="28"/>
     </row>
     <row r="89" customFormat="1" ht="13.95" customHeight="1" spans="1:11">
       <c r="A89" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B89" s="53" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C89" s="27" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D89" s="27"/>
       <c r="E89" s="33"/>
       <c r="F89" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G89" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H89" s="53" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I89" s="27" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J89" s="28"/>
       <c r="K89" s="28"/>
     </row>
     <row r="90" customFormat="1" spans="1:11">
       <c r="A90" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B90" s="53" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C90" s="27" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D90" s="27"/>
       <c r="E90" s="33"/>
       <c r="F90" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G90" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H90" s="53" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I90" s="27" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J90" s="28"/>
       <c r="K90" s="28"/>
     </row>
     <row r="91" customFormat="1" spans="1:11">
       <c r="A91" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B91" s="53" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C91" s="27" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D91" s="27"/>
       <c r="E91" s="33"/>
       <c r="F91" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G91" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H91" s="53" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I91" s="27" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J91" s="28"/>
       <c r="K91" s="28"/>
     </row>
     <row r="92" customFormat="1" spans="1:11">
       <c r="A92" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B92" s="53" t="s">
         <v>61</v>
       </c>
       <c r="C92" s="27" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D92" s="27"/>
       <c r="E92" s="33"/>
       <c r="F92" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G92" s="28" t="s">
         <v>109</v>
@@ -10344,148 +10354,148 @@
         <v>61</v>
       </c>
       <c r="I92" s="27" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J92" s="28"/>
       <c r="K92" s="28"/>
     </row>
     <row r="93" customFormat="1" spans="1:11">
       <c r="A93" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B93" s="53" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D93" s="34"/>
       <c r="E93" s="33"/>
       <c r="F93" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G93" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H93" s="53" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I93" s="34" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J93" s="28"/>
       <c r="K93" s="28"/>
     </row>
     <row r="94" customFormat="1" spans="1:11">
       <c r="A94" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B94" s="53" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C94" s="27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D94" s="27"/>
       <c r="E94" s="33"/>
       <c r="F94" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G94" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H94" s="53" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I94" s="27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J94" s="28"/>
       <c r="K94" s="28"/>
     </row>
     <row r="95" customFormat="1" spans="1:11">
       <c r="A95" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B95" s="53" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C95" s="27" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D95" s="27"/>
       <c r="E95" s="33"/>
       <c r="F95" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G95" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H95" s="53" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I95" s="27" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J95" s="28"/>
       <c r="K95" s="28"/>
     </row>
     <row r="96" customFormat="1" spans="1:11">
       <c r="A96" s="57" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B96" s="58" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C96" s="59" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D96" s="59"/>
       <c r="E96" s="60"/>
       <c r="F96" s="61" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G96" s="61" t="s">
         <v>109</v>
       </c>
       <c r="H96" s="58" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I96" s="59" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J96" s="61"/>
       <c r="K96" s="61" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:11">
       <c r="A97" s="57" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B97" s="58" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C97" s="59" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D97" s="59"/>
       <c r="E97" s="60"/>
       <c r="F97" s="61" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G97" s="61" t="s">
         <v>109</v>
       </c>
       <c r="H97" s="58" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I97" s="59" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J97" s="61"/>
       <c r="K97" s="61" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:11">
@@ -10539,10 +10549,10 @@
       <c r="D100" s="45"/>
       <c r="E100" s="21"/>
       <c r="F100" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G100" s="28" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H100" s="29" t="s">
         <v>109</v>
@@ -10586,7 +10596,7 @@
       <c r="D103" s="15"/>
       <c r="E103" s="15"/>
       <c r="F103" s="48" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G103" s="40"/>
       <c r="H103" s="40"/>
@@ -10596,7 +10606,7 @@
     </row>
     <row r="105" customFormat="1" ht="22" customHeight="1" spans="1:11">
       <c r="A105" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B105" s="14">
         <v>4</v>
@@ -10613,36 +10623,36 @@
     </row>
     <row r="106" customFormat="1" ht="27" customHeight="1" spans="1:11">
       <c r="A106" s="17" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
       <c r="D106" s="17"/>
       <c r="E106" s="18"/>
       <c r="F106" s="19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H106" s="19"/>
       <c r="I106" s="19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J106" s="19" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K106" s="19"/>
     </row>
     <row r="107" customFormat="1" ht="25" customHeight="1" spans="1:11">
       <c r="A107" s="20" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>186</v>
@@ -10652,7 +10662,7 @@
         <v>40</v>
       </c>
       <c r="G107" s="23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H107" s="23" t="s">
         <v>42</v>
@@ -10669,16 +10679,16 @@
     </row>
     <row r="108" customFormat="1" spans="1:11">
       <c r="A108" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B108" s="26" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E108" s="33"/>
       <c r="F108" s="28"/>
@@ -10686,51 +10696,51 @@
       <c r="H108" s="53"/>
       <c r="I108" s="34"/>
       <c r="J108" s="187" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K108" s="28"/>
     </row>
     <row r="109" customFormat="1" spans="1:11">
       <c r="A109" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B109" s="26" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C109" s="27" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D109" s="27"/>
       <c r="E109" s="33"/>
       <c r="F109" s="28" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G109" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H109" s="53" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I109" s="27" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J109" s="28"/>
       <c r="K109" s="28"/>
     </row>
     <row r="110" customFormat="1" spans="1:11">
       <c r="A110" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B110" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C110" s="27" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D110" s="27"/>
       <c r="E110" s="33"/>
       <c r="F110" s="28" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G110" s="28" t="s">
         <v>112</v>
@@ -10746,54 +10756,54 @@
     </row>
     <row r="111" customFormat="1" spans="1:11">
       <c r="A111" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B111" s="26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D111" s="34"/>
       <c r="E111" s="33"/>
       <c r="F111" s="28" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G111" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H111" s="53" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I111" s="34" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J111" s="28"/>
       <c r="K111" s="28"/>
     </row>
     <row r="112" customFormat="1" spans="1:11">
       <c r="A112" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C112" s="27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D112" s="27"/>
       <c r="E112" s="33"/>
       <c r="F112" s="28" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G112" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H112" s="53" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I112" s="27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J112" s="28"/>
       <c r="K112" s="28"/>
@@ -10849,10 +10859,10 @@
       <c r="D115" s="45"/>
       <c r="E115" s="21"/>
       <c r="F115" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="G115" s="28" t="s">
         <v>266</v>
-      </c>
-      <c r="G115" s="28" t="s">
-        <v>264</v>
       </c>
       <c r="H115" s="29" t="s">
         <v>109</v>
@@ -10868,17 +10878,17 @@
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="28" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G116" s="28" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H116" s="29" t="s">
         <v>112</v>
       </c>
       <c r="I116" s="30"/>
       <c r="J116" s="46" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K116" s="43"/>
     </row>
@@ -10930,7 +10940,7 @@
       <c r="D120" s="15"/>
       <c r="E120" s="15"/>
       <c r="F120" s="48" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G120" s="40"/>
       <c r="H120" s="40"/>
@@ -11042,102 +11052,102 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -11145,7 +11155,7 @@
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -11153,7 +11163,7 @@
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>

--- a/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
+++ b/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="5" activeTab="10"/>
+    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="5" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="修订记录" sheetId="1" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="442">
   <si>
     <t>文档修订记录</t>
   </si>
@@ -822,6 +822,24 @@
     <t>年天数</t>
   </si>
   <si>
+    <t>CHNL_NO</t>
+  </si>
+  <si>
+    <t>办理渠道</t>
+  </si>
+  <si>
+    <t>ISSU_DATE</t>
+  </si>
+  <si>
+    <t>办理日期</t>
+  </si>
+  <si>
+    <t>IOU_NO</t>
+  </si>
+  <si>
+    <t>投保单号或者借据号</t>
+  </si>
+  <si>
     <t>客户资产负债表</t>
   </si>
   <si>
@@ -1054,12 +1072,6 @@
   </si>
   <si>
     <t>开户日期</t>
-  </si>
-  <si>
-    <t>ISSU_DATE</t>
-  </si>
-  <si>
-    <t>办理日期</t>
   </si>
   <si>
     <t>TX_DATE</t>
@@ -3395,7 +3407,7 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="54" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3709,6 +3721,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4945,261 +4963,261 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="19.1018518518519" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="5.44444444444444" style="148" customWidth="1"/>
-    <col min="2" max="2" width="10.6666666666667" style="148" customWidth="1"/>
-    <col min="3" max="3" width="8.23148148148148" style="148" customWidth="1"/>
-    <col min="4" max="4" width="6.88888888888889" style="148" customWidth="1"/>
-    <col min="5" max="5" width="8.36111111111111" style="148" customWidth="1"/>
-    <col min="6" max="6" width="54.3611111111111" style="148" customWidth="1"/>
-    <col min="7" max="7" width="6.88888888888889" style="148" customWidth="1"/>
-    <col min="8" max="8" width="6.76851851851852" style="148" customWidth="1"/>
-    <col min="9" max="9" width="8.76851851851852" style="148" customWidth="1"/>
-    <col min="10" max="26" width="19.1018518518519" style="148" customWidth="1"/>
+    <col min="1" max="1" width="5.44444444444444" style="150" customWidth="1"/>
+    <col min="2" max="2" width="10.6666666666667" style="150" customWidth="1"/>
+    <col min="3" max="3" width="8.23148148148148" style="150" customWidth="1"/>
+    <col min="4" max="4" width="6.88888888888889" style="150" customWidth="1"/>
+    <col min="5" max="5" width="8.36111111111111" style="150" customWidth="1"/>
+    <col min="6" max="6" width="54.3611111111111" style="150" customWidth="1"/>
+    <col min="7" max="7" width="6.88888888888889" style="150" customWidth="1"/>
+    <col min="8" max="8" width="6.76851851851852" style="150" customWidth="1"/>
+    <col min="9" max="9" width="8.76851851851852" style="150" customWidth="1"/>
+    <col min="10" max="26" width="19.1018518518519" style="150" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="145" customFormat="1" ht="29.25" customHeight="1" spans="1:9">
-      <c r="A1" s="149"/>
-    </row>
-    <row r="2" s="145" customFormat="1" ht="18.15" customHeight="1" spans="1:9">
-      <c r="A2" s="150" t="s">
+    <row r="1" s="147" customFormat="1" ht="29.25" customHeight="1" spans="1:9">
+      <c r="A1" s="151"/>
+    </row>
+    <row r="2" s="147" customFormat="1" ht="18.15" customHeight="1" spans="1:9">
+      <c r="A2" s="152" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="151"/>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="152"/>
-    </row>
-    <row r="3" s="145" customFormat="1" ht="12.75" customHeight="1" spans="1:9">
-      <c r="A3" s="153"/>
-      <c r="B3" s="154"/>
-      <c r="C3" s="154"/>
-      <c r="D3" s="154"/>
-      <c r="E3" s="154"/>
-      <c r="F3" s="154"/>
-      <c r="G3" s="154"/>
-      <c r="H3" s="154"/>
-      <c r="I3" s="154"/>
-    </row>
-    <row r="4" s="145" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A4" s="155" t="s">
+      <c r="B2" s="153"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
+      <c r="I2" s="154"/>
+    </row>
+    <row r="3" s="147" customFormat="1" ht="12.75" customHeight="1" spans="1:9">
+      <c r="A3" s="155"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+    </row>
+    <row r="4" s="147" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A4" s="157" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="157"/>
-      <c r="E4" s="158" t="s">
+      <c r="B4" s="158"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159"/>
-      <c r="H4" s="159"/>
-      <c r="I4" s="160"/>
-    </row>
-    <row r="5" s="145" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A5" s="161"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="162" t="s">
+      <c r="F4" s="160"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="162"/>
+    </row>
+    <row r="5" s="147" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A5" s="163"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="164" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="162"/>
+      <c r="F5" s="164"/>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="13"/>
     </row>
-    <row r="6" s="145" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A6" s="161"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="162" t="s">
+    <row r="6" s="147" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A6" s="163"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="164" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="162"/>
+      <c r="F6" s="164"/>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="13"/>
     </row>
-    <row r="7" s="145" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A7" s="163"/>
+    <row r="7" s="147" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A7" s="165"/>
       <c r="B7" s="72"/>
       <c r="C7" s="72"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="165" t="s">
+      <c r="D7" s="166"/>
+      <c r="E7" s="167" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="166"/>
-      <c r="G7" s="167"/>
-      <c r="H7" s="167"/>
-      <c r="I7" s="168"/>
-    </row>
-    <row r="8" s="145" customFormat="1" ht="21" customHeight="1" spans="1:9">
-      <c r="A8" s="169" t="s">
+      <c r="F7" s="168"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="170"/>
+    </row>
+    <row r="8" s="147" customFormat="1" ht="21" customHeight="1" spans="1:9">
+      <c r="A8" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="169" t="s">
+      <c r="B8" s="171" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="169" t="s">
+      <c r="C8" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="169" t="s">
+      <c r="D8" s="171" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="169" t="s">
+      <c r="E8" s="171" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="164"/>
-      <c r="G8" s="169" t="s">
+      <c r="F8" s="166"/>
+      <c r="G8" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="169" t="s">
+      <c r="H8" s="171" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="169" t="s">
+      <c r="I8" s="171" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" s="146" customFormat="1" ht="16.95" customHeight="1" spans="1:9">
-      <c r="A9" s="170"/>
-      <c r="B9" s="171"/>
-      <c r="C9" s="172"/>
-      <c r="D9" s="173"/>
-      <c r="E9" s="174"/>
+    <row r="9" s="148" customFormat="1" ht="16.95" customHeight="1" spans="1:9">
+      <c r="A9" s="172"/>
+      <c r="B9" s="173"/>
+      <c r="C9" s="174"/>
+      <c r="D9" s="175"/>
+      <c r="E9" s="176"/>
       <c r="F9" s="13"/>
-      <c r="G9" s="172"/>
-      <c r="H9" s="172"/>
-      <c r="I9" s="172"/>
-    </row>
-    <row r="10" s="146" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A10" s="170"/>
-      <c r="B10" s="171"/>
-      <c r="C10" s="172"/>
-      <c r="D10" s="173"/>
-      <c r="E10" s="174"/>
+      <c r="G9" s="174"/>
+      <c r="H9" s="174"/>
+      <c r="I9" s="174"/>
+    </row>
+    <row r="10" s="148" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A10" s="172"/>
+      <c r="B10" s="173"/>
+      <c r="C10" s="174"/>
+      <c r="D10" s="175"/>
+      <c r="E10" s="176"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="172"/>
-      <c r="H10" s="172"/>
-      <c r="I10" s="172"/>
-    </row>
-    <row r="11" s="146" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A11" s="170"/>
-      <c r="B11" s="171"/>
-      <c r="C11" s="172"/>
-      <c r="D11" s="173"/>
-      <c r="E11" s="174"/>
+      <c r="G10" s="174"/>
+      <c r="H10" s="174"/>
+      <c r="I10" s="174"/>
+    </row>
+    <row r="11" s="148" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A11" s="172"/>
+      <c r="B11" s="173"/>
+      <c r="C11" s="174"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="176"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="172"/>
-      <c r="H11" s="172"/>
-      <c r="I11" s="172"/>
-    </row>
-    <row r="12" s="146" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A12" s="170"/>
-      <c r="B12" s="171"/>
-      <c r="C12" s="172"/>
-      <c r="D12" s="173"/>
-      <c r="E12" s="174"/>
+      <c r="G11" s="174"/>
+      <c r="H11" s="174"/>
+      <c r="I11" s="174"/>
+    </row>
+    <row r="12" s="148" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A12" s="172"/>
+      <c r="B12" s="173"/>
+      <c r="C12" s="174"/>
+      <c r="D12" s="175"/>
+      <c r="E12" s="176"/>
       <c r="F12" s="13"/>
-      <c r="G12" s="172"/>
-      <c r="H12" s="172"/>
-      <c r="I12" s="172"/>
-    </row>
-    <row r="13" s="146" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A13" s="170"/>
-      <c r="B13" s="171"/>
-      <c r="C13" s="172"/>
-      <c r="D13" s="173"/>
-      <c r="E13" s="174"/>
+      <c r="G12" s="174"/>
+      <c r="H12" s="174"/>
+      <c r="I12" s="174"/>
+    </row>
+    <row r="13" s="148" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A13" s="172"/>
+      <c r="B13" s="173"/>
+      <c r="C13" s="174"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="176"/>
       <c r="F13" s="13"/>
-      <c r="G13" s="172"/>
-      <c r="H13" s="172"/>
-      <c r="I13" s="172"/>
-    </row>
-    <row r="14" s="146" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A14" s="170"/>
-      <c r="B14" s="171"/>
-      <c r="C14" s="172"/>
-      <c r="D14" s="173"/>
-      <c r="E14" s="174"/>
+      <c r="G13" s="174"/>
+      <c r="H13" s="174"/>
+      <c r="I13" s="174"/>
+    </row>
+    <row r="14" s="148" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A14" s="172"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="174"/>
+      <c r="D14" s="175"/>
+      <c r="E14" s="176"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="172"/>
-      <c r="H14" s="172"/>
-      <c r="I14" s="172"/>
-    </row>
-    <row r="15" s="146" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A15" s="170"/>
-      <c r="B15" s="171"/>
-      <c r="C15" s="172"/>
-      <c r="D15" s="173"/>
-      <c r="E15" s="174"/>
+      <c r="G14" s="174"/>
+      <c r="H14" s="174"/>
+      <c r="I14" s="174"/>
+    </row>
+    <row r="15" s="148" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A15" s="172"/>
+      <c r="B15" s="173"/>
+      <c r="C15" s="174"/>
+      <c r="D15" s="175"/>
+      <c r="E15" s="176"/>
       <c r="F15" s="13"/>
-      <c r="G15" s="172"/>
-      <c r="H15" s="172"/>
-      <c r="I15" s="172"/>
-    </row>
-    <row r="16" s="146" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A16" s="170"/>
-      <c r="B16" s="171"/>
-      <c r="C16" s="172"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="174"/>
+      <c r="G15" s="174"/>
+      <c r="H15" s="174"/>
+      <c r="I15" s="174"/>
+    </row>
+    <row r="16" s="148" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A16" s="172"/>
+      <c r="B16" s="173"/>
+      <c r="C16" s="174"/>
+      <c r="D16" s="175"/>
+      <c r="E16" s="176"/>
       <c r="F16" s="13"/>
-      <c r="G16" s="172"/>
-      <c r="H16" s="172"/>
-      <c r="I16" s="172"/>
-    </row>
-    <row r="17" s="146" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A17" s="170"/>
-      <c r="B17" s="171"/>
-      <c r="C17" s="172"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="174"/>
+      <c r="G16" s="174"/>
+      <c r="H16" s="174"/>
+      <c r="I16" s="174"/>
+    </row>
+    <row r="17" s="148" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A17" s="172"/>
+      <c r="B17" s="173"/>
+      <c r="C17" s="174"/>
+      <c r="D17" s="175"/>
+      <c r="E17" s="176"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="172"/>
-      <c r="H17" s="172"/>
-      <c r="I17" s="172"/>
-    </row>
-    <row r="18" s="146" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A18" s="170"/>
-      <c r="B18" s="171"/>
-      <c r="C18" s="172"/>
-      <c r="D18" s="173"/>
-      <c r="E18" s="174"/>
+      <c r="G17" s="174"/>
+      <c r="H17" s="174"/>
+      <c r="I17" s="174"/>
+    </row>
+    <row r="18" s="148" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A18" s="172"/>
+      <c r="B18" s="173"/>
+      <c r="C18" s="174"/>
+      <c r="D18" s="175"/>
+      <c r="E18" s="176"/>
       <c r="F18" s="13"/>
-      <c r="G18" s="172"/>
-      <c r="H18" s="172"/>
-      <c r="I18" s="172"/>
-    </row>
-    <row r="19" s="146" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A19" s="170"/>
-      <c r="B19" s="171"/>
-      <c r="C19" s="172"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="174"/>
+      <c r="G18" s="174"/>
+      <c r="H18" s="174"/>
+      <c r="I18" s="174"/>
+    </row>
+    <row r="19" s="148" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A19" s="172"/>
+      <c r="B19" s="173"/>
+      <c r="C19" s="174"/>
+      <c r="D19" s="175"/>
+      <c r="E19" s="176"/>
       <c r="F19" s="13"/>
-      <c r="G19" s="172"/>
-      <c r="H19" s="172"/>
-      <c r="I19" s="172"/>
-    </row>
-    <row r="20" s="146" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
-      <c r="A20" s="170"/>
-      <c r="B20" s="171"/>
-      <c r="C20" s="172"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="174"/>
+      <c r="G19" s="174"/>
+      <c r="H19" s="174"/>
+      <c r="I19" s="174"/>
+    </row>
+    <row r="20" s="148" customFormat="1" ht="10.8" customHeight="1" spans="1:9">
+      <c r="A20" s="172"/>
+      <c r="B20" s="173"/>
+      <c r="C20" s="174"/>
+      <c r="D20" s="175"/>
+      <c r="E20" s="176"/>
       <c r="F20" s="13"/>
-      <c r="G20" s="172"/>
-      <c r="H20" s="172"/>
-      <c r="I20" s="172"/>
-    </row>
-    <row r="21" s="147" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A21" s="175"/>
-    </row>
-    <row r="22" s="147" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A22" s="175"/>
-    </row>
-    <row r="23" s="147" customFormat="1" ht="12" customHeight="1"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="174"/>
+      <c r="I20" s="174"/>
+    </row>
+    <row r="21" s="149" customFormat="1" ht="12" customHeight="1" spans="1:9">
+      <c r="A21" s="177"/>
+    </row>
+    <row r="22" s="149" customFormat="1" ht="12" customHeight="1" spans="1:9">
+      <c r="A22" s="177"/>
+    </row>
+    <row r="23" s="149" customFormat="1" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="A1:I1"/>
@@ -5232,7 +5250,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:Q89"/>
   <sheetFormatPr defaultColWidth="8.23148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="70" customWidth="1"/>
@@ -5721,204 +5739,290 @@
       <c r="Q20" s="88"/>
     </row>
     <row r="21" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B21" s="110"/>
+      <c r="A21" s="80"/>
+      <c r="B21" s="81" t="s">
+        <v>236</v>
+      </c>
       <c r="C21" s="81"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="13"/>
+      <c r="D21" s="81" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="108" t="s">
+        <v>237</v>
+      </c>
+      <c r="F21" s="83"/>
+      <c r="G21" s="110"/>
       <c r="H21" s="84"/>
       <c r="I21" s="85"/>
       <c r="J21" s="86"/>
       <c r="L21" s="87"/>
       <c r="M21" s="81"/>
       <c r="N21" s="87"/>
-      <c r="O21" s="87"/>
-      <c r="P21" s="92"/>
-      <c r="Q21" s="93"/>
+      <c r="O21" s="90"/>
+      <c r="P21" s="88"/>
+      <c r="Q21" s="88"/>
     </row>
     <row r="22" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="B22" s="94"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="13"/>
+      <c r="A22" s="80"/>
+      <c r="B22" s="81" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" s="81"/>
+      <c r="D22" s="81" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="108" t="s">
+        <v>239</v>
+      </c>
+      <c r="F22" s="83"/>
+      <c r="G22" s="110"/>
       <c r="H22" s="84"/>
       <c r="I22" s="85"/>
       <c r="J22" s="86"/>
-      <c r="L22" s="96"/>
-      <c r="M22" s="97"/>
-      <c r="N22" s="97"/>
-      <c r="O22" s="97"/>
-      <c r="P22" s="92"/>
-      <c r="Q22" s="93"/>
-    </row>
-    <row r="23" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B23" s="73" t="s">
+      <c r="L22" s="87"/>
+      <c r="M22" s="81"/>
+      <c r="N22" s="87"/>
+      <c r="O22" s="90"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="88"/>
+    </row>
+    <row r="23" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A23" s="80"/>
+      <c r="B23" s="81" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" s="81"/>
+      <c r="D23" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="108" t="s">
+        <v>241</v>
+      </c>
+      <c r="F23" s="83"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="86"/>
+      <c r="L23" s="87"/>
+      <c r="M23" s="81"/>
+      <c r="N23" s="87"/>
+      <c r="O23" s="90"/>
+      <c r="P23" s="88"/>
+      <c r="Q23" s="88"/>
+    </row>
+    <row r="24" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A24" s="80"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="111"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="86"/>
+      <c r="L24" s="87"/>
+      <c r="M24" s="81"/>
+      <c r="N24" s="87"/>
+      <c r="O24" s="90"/>
+      <c r="P24" s="88"/>
+      <c r="Q24" s="88"/>
+    </row>
+    <row r="25" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="B25" s="112"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="112"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="85"/>
+      <c r="J25" s="86"/>
+      <c r="L25" s="87"/>
+      <c r="M25" s="81"/>
+      <c r="N25" s="87"/>
+      <c r="O25" s="87"/>
+      <c r="P25" s="92"/>
+      <c r="Q25" s="93"/>
+    </row>
+    <row r="26" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="B26" s="94"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="95"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="85"/>
+      <c r="J26" s="86"/>
+      <c r="L26" s="96"/>
+      <c r="M26" s="97"/>
+      <c r="N26" s="97"/>
+      <c r="O26" s="97"/>
+      <c r="P26" s="92"/>
+      <c r="Q26" s="93"/>
+    </row>
+    <row r="27" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
+      <c r="B27" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="13"/>
-      <c r="L23" s="38" t="s">
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="13"/>
+      <c r="L27" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="40"/>
-    </row>
-    <row r="24" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
-      <c r="B24" s="98" t="s">
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="40"/>
+    </row>
+    <row r="28" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
+      <c r="B28" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="98" t="s">
+      <c r="C28" s="98" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="98" t="s">
+      <c r="D28" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="13"/>
-      <c r="L24" s="99" t="s">
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="13"/>
+      <c r="L28" s="99" t="s">
         <v>102</v>
       </c>
-      <c r="M24" s="100" t="s">
+      <c r="M28" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="N24" s="23" t="s">
+      <c r="N28" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O24" s="23" t="s">
+      <c r="O28" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="P24" s="42" t="s">
+      <c r="P28" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="Q24" s="40"/>
-    </row>
-    <row r="25" s="4" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
-      <c r="B25" s="101"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="13"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="46"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="40"/>
-    </row>
-    <row r="26" s="4" customFormat="1" ht="10.8" customHeight="1" spans="1:17">
-      <c r="L26" s="35"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="46"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="40"/>
-    </row>
-    <row r="27" s="4" customFormat="1" ht="10.8" customHeight="1" spans="1:17">
-      <c r="L27" s="35"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="46"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="40"/>
-    </row>
-    <row r="28" ht="13.95" customHeight="1" spans="1:17">
-      <c r="L28" s="35"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="46"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="103"/>
       <c r="Q28" s="40"/>
     </row>
-    <row r="29" ht="13.95" customHeight="1" spans="1:17">
+    <row r="29" s="4" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
+      <c r="B29" s="101"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="13"/>
       <c r="L29" s="35"/>
       <c r="M29" s="36"/>
       <c r="N29" s="46"/>
       <c r="O29" s="46"/>
-      <c r="P29" s="103"/>
+      <c r="P29" s="45"/>
       <c r="Q29" s="40"/>
     </row>
-    <row r="30" ht="13.95" customHeight="1" spans="1:17">
-      <c r="L30" s="104"/>
-      <c r="M30" s="93"/>
-      <c r="N30" s="93"/>
-      <c r="O30" s="93"/>
-      <c r="P30" s="103"/>
+    <row r="30" s="4" customFormat="1" ht="10.8" customHeight="1" spans="1:17">
+      <c r="L30" s="35"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="45"/>
       <c r="Q30" s="40"/>
     </row>
-    <row r="31" ht="13.95" customHeight="1" spans="1:17">
-      <c r="L31" s="104"/>
-      <c r="M31" s="93"/>
-      <c r="N31" s="93"/>
-      <c r="O31" s="93"/>
-      <c r="P31" s="103"/>
+    <row r="31" s="4" customFormat="1" ht="10.8" customHeight="1" spans="1:17">
+      <c r="L31" s="35"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="45"/>
       <c r="Q31" s="40"/>
     </row>
     <row r="32" ht="13.95" customHeight="1" spans="1:17">
-      <c r="L32" s="104"/>
-      <c r="M32" s="93"/>
-      <c r="N32" s="93"/>
-      <c r="O32" s="93"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
       <c r="P32" s="103"/>
       <c r="Q32" s="40"/>
     </row>
     <row r="33" ht="13.95" customHeight="1" spans="12:17">
-      <c r="L33" s="104"/>
-      <c r="M33" s="93"/>
-      <c r="N33" s="93"/>
-      <c r="O33" s="93"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="36"/>
+      <c r="N33" s="46"/>
+      <c r="O33" s="46"/>
       <c r="P33" s="103"/>
       <c r="Q33" s="40"/>
     </row>
     <row r="34" ht="13.95" customHeight="1" spans="12:17">
-      <c r="L34" s="66"/>
-      <c r="M34" s="67"/>
-      <c r="N34" s="68"/>
+      <c r="L34" s="104"/>
+      <c r="M34" s="93"/>
+      <c r="N34" s="93"/>
       <c r="O34" s="93"/>
-      <c r="P34" s="69"/>
+      <c r="P34" s="103"/>
       <c r="Q34" s="40"/>
     </row>
     <row r="35" ht="13.95" customHeight="1" spans="12:17">
-      <c r="L35" s="105" t="s">
+      <c r="L35" s="104"/>
+      <c r="M35" s="93"/>
+      <c r="N35" s="93"/>
+      <c r="O35" s="93"/>
+      <c r="P35" s="103"/>
+      <c r="Q35" s="40"/>
+    </row>
+    <row r="36" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L36" s="104"/>
+      <c r="M36" s="93"/>
+      <c r="N36" s="93"/>
+      <c r="O36" s="93"/>
+      <c r="P36" s="103"/>
+      <c r="Q36" s="40"/>
+    </row>
+    <row r="37" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L37" s="104"/>
+      <c r="M37" s="93"/>
+      <c r="N37" s="93"/>
+      <c r="O37" s="93"/>
+      <c r="P37" s="103"/>
+      <c r="Q37" s="40"/>
+    </row>
+    <row r="38" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L38" s="66"/>
+      <c r="M38" s="67"/>
+      <c r="N38" s="68"/>
+      <c r="O38" s="93"/>
+      <c r="P38" s="69"/>
+      <c r="Q38" s="40"/>
+    </row>
+    <row r="39" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L39" s="105" t="s">
         <v>119</v>
       </c>
-      <c r="M35" s="39"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="39"/>
-      <c r="Q35" s="40"/>
-    </row>
-    <row r="36" ht="56" customHeight="1" spans="12:17">
-      <c r="L36" s="106"/>
-      <c r="M36" s="39"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="39"/>
-      <c r="Q36" s="40"/>
-    </row>
-    <row r="37" ht="13.95" customHeight="1"/>
-    <row r="38" ht="13.95" customHeight="1"/>
-    <row r="39" ht="13.95" customHeight="1"/>
-    <row r="40" ht="13.95" customHeight="1"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="40"/>
+    </row>
+    <row r="40" ht="56" customHeight="1" spans="12:17">
+      <c r="L40" s="106"/>
+      <c r="M40" s="39"/>
+      <c r="N40" s="39"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="39"/>
+      <c r="Q40" s="40"/>
+    </row>
     <row r="41" ht="13.95" customHeight="1"/>
     <row r="42" ht="13.95" customHeight="1"/>
     <row r="43" ht="13.95" customHeight="1"/>
@@ -5964,6 +6068,10 @@
     <row r="83" ht="13.95" customHeight="1"/>
     <row r="84" ht="13.95" customHeight="1"/>
     <row r="85" ht="13.95" customHeight="1"/>
+    <row r="86" ht="13.95" customHeight="1"/>
+    <row r="87" ht="13.95" customHeight="1"/>
+    <row r="88" ht="13.95" customHeight="1"/>
+    <row r="89" ht="13.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
     <mergeCell ref="B1:J1"/>
@@ -5973,28 +6081,28 @@
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="L4:Q4"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="L23:Q23"/>
-    <mergeCell ref="D24:J24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="D25:J25"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="L27:Q27"/>
+    <mergeCell ref="D28:J28"/>
     <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="D29:J29"/>
     <mergeCell ref="P29:Q29"/>
     <mergeCell ref="P30:Q30"/>
     <mergeCell ref="P31:Q31"/>
     <mergeCell ref="P32:Q32"/>
     <mergeCell ref="P33:Q33"/>
     <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="L35:Q35"/>
-    <mergeCell ref="L36:Q36"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="L39:Q39"/>
+    <mergeCell ref="L40:Q40"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C21 C22 C23 C7:C8">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -6046,12 +6154,12 @@
         <v>16</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
       <c r="F2" s="75" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
@@ -6210,14 +6318,14 @@
     <row r="9" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A9" s="80"/>
       <c r="B9" s="81" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C9" s="82"/>
       <c r="D9" s="81" t="s">
         <v>50</v>
       </c>
       <c r="E9" s="81" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F9" s="83"/>
       <c r="G9" s="83"/>
@@ -6234,14 +6342,14 @@
     <row r="10" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A10" s="80"/>
       <c r="B10" s="81" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C10" s="82"/>
       <c r="D10" s="81" t="s">
         <v>90</v>
       </c>
       <c r="E10" s="81" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F10" s="83"/>
       <c r="G10" s="83"/>
@@ -6258,14 +6366,14 @@
     <row r="11" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="80"/>
       <c r="B11" s="81" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C11" s="82"/>
       <c r="D11" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="81" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F11" s="83"/>
       <c r="G11" s="83"/>
@@ -6282,14 +6390,14 @@
     <row r="12" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A12" s="80"/>
       <c r="B12" s="81" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C12" s="82"/>
       <c r="D12" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="81" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F12" s="83"/>
       <c r="G12" s="83"/>
@@ -6306,14 +6414,14 @@
     <row r="13" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A13" s="80"/>
       <c r="B13" s="81" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C13" s="82"/>
       <c r="D13" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="81" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F13" s="83"/>
       <c r="G13" s="83"/>
@@ -6330,14 +6438,14 @@
     <row r="14" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A14" s="80"/>
       <c r="B14" s="81" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C14" s="82"/>
       <c r="D14" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="81" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F14" s="83"/>
       <c r="G14" s="83"/>
@@ -6354,14 +6462,14 @@
     <row r="15" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A15" s="80"/>
       <c r="B15" s="81" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C15" s="82"/>
       <c r="D15" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="81" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F15" s="83"/>
       <c r="G15" s="83"/>
@@ -6378,14 +6486,14 @@
     <row r="16" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A16" s="80"/>
       <c r="B16" s="81" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C16" s="82"/>
       <c r="D16" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E16" s="81" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="F16" s="83"/>
       <c r="G16" s="83"/>
@@ -6402,14 +6510,14 @@
     <row r="17" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A17" s="80"/>
       <c r="B17" s="81" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C17" s="82"/>
       <c r="D17" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E17" s="81" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="F17" s="83"/>
       <c r="G17" s="83"/>
@@ -6426,14 +6534,14 @@
     <row r="18" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A18" s="80"/>
       <c r="B18" s="91" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C18" s="82"/>
       <c r="D18" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E18" s="81" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F18" s="83"/>
       <c r="G18" s="83"/>
@@ -6444,14 +6552,14 @@
     <row r="19" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A19" s="80"/>
       <c r="B19" s="91" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C19" s="82"/>
       <c r="D19" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E19" s="81" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="F19" s="83"/>
       <c r="G19" s="83"/>
@@ -6462,14 +6570,14 @@
     <row r="20" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A20" s="80"/>
       <c r="B20" s="91" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C20" s="82"/>
       <c r="D20" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E20" s="81" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F20" s="83"/>
       <c r="G20" s="83"/>
@@ -6480,14 +6588,14 @@
     <row r="21" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
       <c r="A21" s="80"/>
       <c r="B21" s="91" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C21" s="82"/>
       <c r="D21" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E21" s="81" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F21" s="85"/>
       <c r="G21" s="85"/>
@@ -6498,14 +6606,14 @@
     <row r="22" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
       <c r="A22" s="80"/>
       <c r="B22" s="91" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C22" s="82"/>
       <c r="D22" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E22" s="81" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F22" s="85"/>
       <c r="G22" s="85"/>
@@ -6521,14 +6629,14 @@
     </row>
     <row r="23" s="4" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
       <c r="B23" s="91" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C23" s="82"/>
       <c r="D23" s="81" t="s">
         <v>70</v>
       </c>
       <c r="E23" s="81" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F23" s="85"/>
       <c r="G23" s="85"/>
@@ -6850,12 +6958,12 @@
         <v>16</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
       <c r="F2" s="75" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
@@ -7021,7 +7129,7 @@
         <v>80</v>
       </c>
       <c r="E9" s="81" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="F9" s="83"/>
       <c r="G9" s="83"/>
@@ -7062,14 +7170,14 @@
     <row r="11" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="80"/>
       <c r="B11" s="89" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C11" s="82"/>
       <c r="D11" s="81" t="s">
         <v>80</v>
       </c>
       <c r="E11" s="81" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F11" s="83"/>
       <c r="G11" s="83"/>
@@ -7537,22 +7645,22 @@
   <sheetData>
     <row r="1" ht="35" customHeight="1" spans="1:25">
       <c r="A1" s="7" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E1" s="10"/>
     </row>
     <row r="2" ht="56" customHeight="1" spans="1:25">
       <c r="A2" s="11" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -7561,7 +7669,7 @@
     </row>
     <row r="3" ht="23" customHeight="1" spans="1:25">
       <c r="A3" s="14" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B3" s="15">
         <v>1</v>
@@ -7592,66 +7700,66 @@
     </row>
     <row r="4" s="3" customFormat="1" ht="34" customHeight="1" spans="1:25">
       <c r="A4" s="17" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
       <c r="D4" s="13"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="19" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="18"/>
       <c r="M4" s="19" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="N4" s="19" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="O4" s="13"/>
       <c r="P4" s="19" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="R4" s="13"/>
       <c r="S4" s="18"/>
       <c r="T4" s="19" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="U4" s="19" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="V4" s="13"/>
       <c r="W4" s="19" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="X4" s="19" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="Y4" s="13"/>
     </row>
     <row r="5" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:25">
       <c r="A5" s="20" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>186</v>
@@ -7661,7 +7769,7 @@
         <v>40</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>42</v>
@@ -7680,7 +7788,7 @@
         <v>40</v>
       </c>
       <c r="N5" s="23" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="O5" s="23" t="s">
         <v>42</v>
@@ -7699,7 +7807,7 @@
         <v>40</v>
       </c>
       <c r="U5" s="23" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="V5" s="23" t="s">
         <v>42</v>
@@ -7716,7 +7824,7 @@
     </row>
     <row r="6" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:25">
       <c r="A6" s="25" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>84</v>
@@ -7727,7 +7835,7 @@
       <c r="D6" s="27"/>
       <c r="E6" s="21"/>
       <c r="F6" s="28" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>109</v>
@@ -7742,7 +7850,7 @@
       <c r="K6" s="28"/>
       <c r="L6" s="21"/>
       <c r="M6" s="28" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="N6" s="28" t="s">
         <v>109</v>
@@ -7757,7 +7865,7 @@
       <c r="R6" s="28"/>
       <c r="S6" s="21"/>
       <c r="T6" s="28" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="U6" s="28" t="s">
         <v>109</v>
@@ -7773,7 +7881,7 @@
     </row>
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A7" s="25" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>61</v>
@@ -7784,7 +7892,7 @@
       <c r="D7" s="27"/>
       <c r="E7" s="31"/>
       <c r="F7" s="28" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>109</v>
@@ -7799,7 +7907,7 @@
       <c r="K7" s="28"/>
       <c r="L7" s="31"/>
       <c r="M7" s="28" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="N7" s="28" t="s">
         <v>109</v>
@@ -7814,7 +7922,7 @@
       <c r="R7" s="28"/>
       <c r="S7" s="31"/>
       <c r="T7" s="28" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="U7" s="28" t="s">
         <v>109</v>
@@ -7830,7 +7938,7 @@
     </row>
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A8" s="25" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>65</v>
@@ -7841,7 +7949,7 @@
       <c r="D8" s="27"/>
       <c r="E8" s="31"/>
       <c r="F8" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>112</v>
@@ -7856,7 +7964,7 @@
       <c r="K8" s="28"/>
       <c r="L8" s="31"/>
       <c r="M8" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N8" s="28" t="s">
         <v>112</v>
@@ -7871,7 +7979,7 @@
       <c r="R8" s="28"/>
       <c r="S8" s="31"/>
       <c r="T8" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="U8" s="28" t="s">
         <v>112</v>
@@ -7887,18 +7995,18 @@
     </row>
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A9" s="25" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>172</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="31"/>
       <c r="F9" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>112</v>
@@ -7907,13 +8015,13 @@
         <v>172</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="J9" s="32"/>
       <c r="K9" s="28"/>
       <c r="L9" s="31"/>
       <c r="M9" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N9" s="28" t="s">
         <v>112</v>
@@ -7922,13 +8030,13 @@
         <v>172</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="Q9" s="32"/>
       <c r="R9" s="28"/>
       <c r="S9" s="31"/>
       <c r="T9" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="U9" s="28" t="s">
         <v>112</v>
@@ -7937,25 +8045,25 @@
         <v>172</v>
       </c>
       <c r="W9" s="30" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="X9" s="32"/>
       <c r="Y9" s="28"/>
     </row>
     <row r="10" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A10" s="25" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>92</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="33"/>
       <c r="F10" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>112</v>
@@ -7964,13 +8072,13 @@
         <v>92</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="J10" s="32"/>
       <c r="K10" s="28"/>
       <c r="L10" s="33"/>
       <c r="M10" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N10" s="28" t="s">
         <v>112</v>
@@ -7979,13 +8087,13 @@
         <v>92</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="Q10" s="32"/>
       <c r="R10" s="28"/>
       <c r="S10" s="33"/>
       <c r="T10" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="U10" s="28" t="s">
         <v>112</v>
@@ -7994,25 +8102,25 @@
         <v>92</v>
       </c>
       <c r="W10" s="30" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="X10" s="32"/>
       <c r="Y10" s="28"/>
     </row>
     <row r="11" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A11" s="25" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D11" s="34"/>
       <c r="E11" s="33"/>
       <c r="F11" s="28" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>109</v>
@@ -8027,7 +8135,7 @@
       <c r="K11" s="32"/>
       <c r="L11" s="33"/>
       <c r="M11" s="28" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="N11" s="28" t="s">
         <v>109</v>
@@ -8036,55 +8144,55 @@
         <v>215</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Q11" s="32"/>
       <c r="R11" s="32"/>
       <c r="S11" s="33"/>
       <c r="T11" s="28" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="U11" s="28" t="s">
         <v>109</v>
       </c>
       <c r="V11" s="29" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="W11" s="30" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="X11" s="32"/>
       <c r="Y11" s="32"/>
     </row>
     <row r="12" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A12" s="25" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="33"/>
       <c r="F12" s="28" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="I12" s="36" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="J12" s="28"/>
       <c r="K12" s="28"/>
       <c r="L12" s="33"/>
       <c r="M12" s="28" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="N12" s="28" t="s">
         <v>109</v>
@@ -8093,79 +8201,79 @@
         <v>211</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="Q12" s="28"/>
       <c r="R12" s="28"/>
       <c r="S12" s="33"/>
       <c r="T12" s="28" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="U12" s="28" t="s">
         <v>109</v>
       </c>
       <c r="V12" s="29" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="W12" s="30" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="X12" s="28"/>
       <c r="Y12" s="28"/>
     </row>
     <row r="13" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A13" s="25" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="33"/>
       <c r="F13" s="28" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G13" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="I13" s="36" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J13" s="28"/>
       <c r="K13" s="28"/>
       <c r="L13" s="33"/>
       <c r="M13" s="28" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="N13" s="28" t="s">
         <v>109</v>
       </c>
       <c r="O13" s="29" t="s">
-        <v>314</v>
+        <v>238</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
       <c r="Q13" s="28"/>
       <c r="R13" s="28"/>
       <c r="S13" s="33"/>
       <c r="T13" s="28" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="U13" s="28" t="s">
         <v>109</v>
       </c>
       <c r="V13" s="29" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="W13" s="30" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="X13" s="28"/>
       <c r="Y13" s="28"/>
@@ -8300,10 +8408,10 @@
       <c r="D17" s="13"/>
       <c r="E17" s="21"/>
       <c r="F17" s="28" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>109</v>
@@ -8313,10 +8421,10 @@
       <c r="K17" s="40"/>
       <c r="L17" s="21"/>
       <c r="M17" s="28" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="N17" s="28" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="O17" s="29" t="s">
         <v>109</v>
@@ -8326,10 +8434,10 @@
       <c r="R17" s="40"/>
       <c r="S17" s="21"/>
       <c r="T17" s="28" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="U17" s="28" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="V17" s="29" t="s">
         <v>109</v>
@@ -8345,53 +8453,53 @@
       <c r="D18" s="21"/>
       <c r="E18" s="21"/>
       <c r="F18" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="H18" s="29" t="s">
         <v>112</v>
       </c>
       <c r="I18" s="30" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="J18" s="45" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K18" s="40"/>
       <c r="L18" s="21"/>
       <c r="M18" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="O18" s="29" t="s">
         <v>112</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q18" s="45" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="R18" s="40"/>
       <c r="S18" s="21"/>
       <c r="T18" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="U18" s="28" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="V18" s="29" t="s">
         <v>112</v>
       </c>
       <c r="W18" s="30" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="X18" s="45" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Y18" s="40"/>
     </row>
@@ -8462,7 +8570,7 @@
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="47" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G21" s="39"/>
       <c r="H21" s="39"/>
@@ -8471,7 +8579,7 @@
       <c r="K21" s="40"/>
       <c r="L21" s="16"/>
       <c r="M21" s="47" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="N21" s="39"/>
       <c r="O21" s="39"/>
@@ -8480,7 +8588,7 @@
       <c r="R21" s="40"/>
       <c r="S21" s="16"/>
       <c r="T21" s="47" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="U21" s="39"/>
       <c r="V21" s="39"/>
@@ -8491,7 +8599,7 @@
     <row r="22" ht="13.95" customHeight="1"/>
     <row r="23" ht="13.95" customHeight="1" spans="1:25">
       <c r="A23" s="14" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B23" s="15">
         <v>2</v>
@@ -8508,24 +8616,24 @@
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:25">
       <c r="A24" s="17" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="13"/>
       <c r="E24" s="18"/>
       <c r="F24" s="19" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="19" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="K24" s="13"/>
       <c r="M24" s="48"/>
@@ -8535,13 +8643,13 @@
     </row>
     <row r="25" ht="29" customHeight="1" spans="1:25">
       <c r="A25" s="20" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>186</v>
@@ -8551,7 +8659,7 @@
         <v>40</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H25" s="23" t="s">
         <v>42</v>
@@ -8574,7 +8682,7 @@
     </row>
     <row r="26" ht="13.95" customHeight="1" spans="1:25">
       <c r="A26" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B26" s="52" t="s">
         <v>84</v>
@@ -8588,8 +8696,8 @@
       <c r="G26" s="28"/>
       <c r="H26" s="29"/>
       <c r="I26" s="30"/>
-      <c r="J26" s="176" t="s">
-        <v>329</v>
+      <c r="J26" s="178" t="s">
+        <v>333</v>
       </c>
       <c r="K26" s="28"/>
       <c r="M26" s="53"/>
@@ -8601,13 +8709,13 @@
     </row>
     <row r="27" ht="13.95" customHeight="1" spans="1:25">
       <c r="A27" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="21"/>
@@ -8615,10 +8723,10 @@
       <c r="G27" s="28"/>
       <c r="H27" s="29"/>
       <c r="I27" s="30" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="K27" s="28"/>
       <c r="M27" s="53"/>
@@ -8630,27 +8738,27 @@
     </row>
     <row r="28" ht="13.95" customHeight="1" spans="1:25">
       <c r="A28" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B28" s="52" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="31"/>
       <c r="F28" s="28" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G28" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="I28" s="30" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="J28" s="28"/>
       <c r="K28" s="28"/>
@@ -8663,24 +8771,24 @@
     </row>
     <row r="29" ht="13.95" customHeight="1" spans="1:25">
       <c r="A29" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B29" s="52" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E29" s="31"/>
       <c r="F29" s="28"/>
       <c r="G29" s="28"/>
       <c r="H29" s="29"/>
       <c r="I29" s="30"/>
-      <c r="J29" s="176" t="s">
-        <v>342</v>
+      <c r="J29" s="178" t="s">
+        <v>346</v>
       </c>
       <c r="K29" s="28"/>
       <c r="M29" s="53"/>
@@ -8692,27 +8800,27 @@
     </row>
     <row r="30" ht="13.95" customHeight="1" spans="1:25">
       <c r="A30" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B30" s="52" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D30" s="34"/>
       <c r="E30" s="33"/>
       <c r="F30" s="28" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G30" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="I30" s="30" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="J30" s="32"/>
       <c r="K30" s="28"/>
@@ -8725,27 +8833,27 @@
     </row>
     <row r="31" ht="13.95" customHeight="1" spans="1:25">
       <c r="A31" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B31" s="52" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D31" s="34"/>
       <c r="E31" s="33"/>
       <c r="F31" s="28" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G31" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I31" s="30" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J31" s="28"/>
       <c r="K31" s="28"/>
@@ -8758,18 +8866,18 @@
     </row>
     <row r="32" ht="13.95" customHeight="1" spans="1:25">
       <c r="A32" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B32" s="52" t="s">
         <v>172</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D32" s="34"/>
       <c r="E32" s="33"/>
       <c r="F32" s="28" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G32" s="28" t="s">
         <v>109</v>
@@ -8778,7 +8886,7 @@
         <v>172</v>
       </c>
       <c r="I32" s="30" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
@@ -8791,18 +8899,18 @@
     </row>
     <row r="33" ht="13.95" customHeight="1" spans="1:18">
       <c r="A33" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B33" s="52" t="s">
         <v>170</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D33" s="34"/>
       <c r="E33" s="33"/>
       <c r="F33" s="28" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G33" s="28" t="s">
         <v>109</v>
@@ -8811,7 +8919,7 @@
         <v>170</v>
       </c>
       <c r="I33" s="30" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J33" s="28"/>
       <c r="K33" s="28"/>
@@ -8824,18 +8932,18 @@
     </row>
     <row r="34" ht="13.95" customHeight="1" spans="1:18">
       <c r="A34" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B34" s="52" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D34" s="34"/>
       <c r="E34" s="33"/>
       <c r="F34" s="28" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G34" s="28" t="s">
         <v>109</v>
@@ -8857,13 +8965,13 @@
     </row>
     <row r="35" ht="13.95" customHeight="1" spans="1:18">
       <c r="A35" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B35" s="52" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D35" s="34"/>
       <c r="E35" s="33"/>
@@ -8871,11 +8979,11 @@
       <c r="G35" s="28"/>
       <c r="H35" s="29"/>
       <c r="I35" s="30"/>
-      <c r="J35" s="176" t="s">
-        <v>353</v>
+      <c r="J35" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K35" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M35" s="53"/>
       <c r="N35" s="53"/>
@@ -8886,13 +8994,13 @@
     </row>
     <row r="36" ht="13.95" customHeight="1" spans="1:18">
       <c r="A36" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B36" s="52" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D36" s="34"/>
       <c r="E36" s="33"/>
@@ -8900,11 +9008,11 @@
       <c r="G36" s="28"/>
       <c r="H36" s="29"/>
       <c r="I36" s="30"/>
-      <c r="J36" s="176" t="s">
-        <v>357</v>
+      <c r="J36" s="178" t="s">
+        <v>361</v>
       </c>
       <c r="K36" s="28" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="M36" s="53"/>
       <c r="N36" s="53"/>
@@ -8915,13 +9023,13 @@
     </row>
     <row r="37" ht="13.95" customHeight="1" spans="1:18">
       <c r="A37" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B37" s="52" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D37" s="34"/>
       <c r="E37" s="33"/>
@@ -8930,10 +9038,10 @@
       <c r="H37" s="29"/>
       <c r="I37" s="30"/>
       <c r="J37" s="28" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="K37" s="28" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="M37" s="53"/>
       <c r="N37" s="53"/>
@@ -8944,16 +9052,16 @@
     </row>
     <row r="38" ht="13.95" customHeight="1" spans="1:18">
       <c r="A38" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B38" s="52" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E38" s="33"/>
       <c r="F38" s="28"/>
@@ -8961,7 +9069,7 @@
       <c r="H38" s="29"/>
       <c r="I38" s="30"/>
       <c r="J38" s="28" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="K38" s="28"/>
       <c r="M38" s="53"/>
@@ -8973,16 +9081,16 @@
     </row>
     <row r="39" ht="13.95" customHeight="1" spans="1:18">
       <c r="A39" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B39" s="52" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E39" s="33"/>
       <c r="F39" s="28"/>
@@ -8990,7 +9098,7 @@
       <c r="H39" s="29"/>
       <c r="I39" s="30"/>
       <c r="J39" s="28" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="K39" s="28"/>
       <c r="M39" s="53"/>
@@ -9002,13 +9110,13 @@
     </row>
     <row r="40" ht="13.95" customHeight="1" spans="1:18">
       <c r="A40" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B40" s="52" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D40" s="34"/>
       <c r="E40" s="33"/>
@@ -9016,11 +9124,11 @@
       <c r="G40" s="28"/>
       <c r="H40" s="29"/>
       <c r="I40" s="30"/>
-      <c r="J40" s="176" t="s">
-        <v>353</v>
+      <c r="J40" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K40" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M40" s="53"/>
       <c r="N40" s="53"/>
@@ -9031,10 +9139,10 @@
     </row>
     <row r="41" ht="13.95" customHeight="1" spans="1:18">
       <c r="A41" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B41" s="52" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C41" s="27" t="s">
         <v>212</v>
@@ -9045,11 +9153,11 @@
       <c r="G41" s="28"/>
       <c r="H41" s="29"/>
       <c r="I41" s="30"/>
-      <c r="J41" s="176" t="s">
-        <v>374</v>
+      <c r="J41" s="178" t="s">
+        <v>378</v>
       </c>
       <c r="K41" s="28" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="M41" s="53"/>
       <c r="N41" s="53"/>
@@ -9060,13 +9168,13 @@
     </row>
     <row r="42" ht="13.95" customHeight="1" spans="1:18">
       <c r="A42" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B42" s="52" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D42" s="27"/>
       <c r="E42" s="33"/>
@@ -9074,11 +9182,11 @@
       <c r="G42" s="28"/>
       <c r="H42" s="29"/>
       <c r="I42" s="30"/>
-      <c r="J42" s="176" t="s">
-        <v>353</v>
+      <c r="J42" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K42" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M42" s="53"/>
       <c r="N42" s="53"/>
@@ -9089,13 +9197,13 @@
     </row>
     <row r="43" ht="13.95" customHeight="1" spans="1:18">
       <c r="A43" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B43" s="52" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="33"/>
@@ -9103,11 +9211,11 @@
       <c r="G43" s="28"/>
       <c r="H43" s="29"/>
       <c r="I43" s="30"/>
-      <c r="J43" s="176" t="s">
-        <v>353</v>
+      <c r="J43" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K43" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M43" s="53"/>
       <c r="N43" s="53"/>
@@ -9118,13 +9226,13 @@
     </row>
     <row r="44" ht="13.95" customHeight="1" spans="1:18">
       <c r="A44" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B44" s="52" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D44" s="27"/>
       <c r="E44" s="33"/>
@@ -9132,11 +9240,11 @@
       <c r="G44" s="28"/>
       <c r="H44" s="29"/>
       <c r="I44" s="30"/>
-      <c r="J44" s="176" t="s">
-        <v>353</v>
+      <c r="J44" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K44" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M44" s="53"/>
       <c r="N44" s="53"/>
@@ -9147,13 +9255,13 @@
     </row>
     <row r="45" ht="13.95" customHeight="1" spans="1:18">
       <c r="A45" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B45" s="52" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D45" s="27"/>
       <c r="E45" s="33"/>
@@ -9161,11 +9269,11 @@
       <c r="G45" s="28"/>
       <c r="H45" s="29"/>
       <c r="I45" s="30"/>
-      <c r="J45" s="176" t="s">
-        <v>353</v>
+      <c r="J45" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K45" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M45" s="53"/>
       <c r="N45" s="53"/>
@@ -9176,10 +9284,10 @@
     </row>
     <row r="46" ht="13.95" customHeight="1" spans="1:18">
       <c r="A46" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B46" s="52" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C46" s="27" t="s">
         <v>45</v>
@@ -9190,11 +9298,11 @@
       <c r="G46" s="28"/>
       <c r="H46" s="29"/>
       <c r="I46" s="30"/>
-      <c r="J46" s="176" t="s">
-        <v>353</v>
+      <c r="J46" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K46" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M46" s="53"/>
       <c r="N46" s="53"/>
@@ -9205,13 +9313,13 @@
     </row>
     <row r="47" ht="13.95" customHeight="1" spans="1:18">
       <c r="A47" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B47" s="52" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D47" s="27"/>
       <c r="E47" s="33"/>
@@ -9219,11 +9327,11 @@
       <c r="G47" s="28"/>
       <c r="H47" s="29"/>
       <c r="I47" s="30"/>
-      <c r="J47" s="176" t="s">
-        <v>353</v>
+      <c r="J47" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K47" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M47" s="53"/>
       <c r="N47" s="53"/>
@@ -9234,13 +9342,13 @@
     </row>
     <row r="48" ht="13.95" customHeight="1" spans="1:18">
       <c r="A48" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B48" s="52" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D48" s="27"/>
       <c r="E48" s="33"/>
@@ -9248,11 +9356,11 @@
       <c r="G48" s="28"/>
       <c r="H48" s="29"/>
       <c r="I48" s="30"/>
-      <c r="J48" s="176" t="s">
-        <v>353</v>
+      <c r="J48" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K48" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M48" s="53"/>
       <c r="N48" s="53"/>
@@ -9263,13 +9371,13 @@
     </row>
     <row r="49" ht="13.95" customHeight="1" spans="1:18">
       <c r="A49" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B49" s="52" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D49" s="27"/>
       <c r="E49" s="33"/>
@@ -9277,11 +9385,11 @@
       <c r="G49" s="28"/>
       <c r="H49" s="29"/>
       <c r="I49" s="30"/>
-      <c r="J49" s="176" t="s">
-        <v>353</v>
+      <c r="J49" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K49" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M49" s="53"/>
       <c r="N49" s="53"/>
@@ -9292,13 +9400,13 @@
     </row>
     <row r="50" ht="13.95" customHeight="1" spans="1:18">
       <c r="A50" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B50" s="52" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D50" s="27"/>
       <c r="E50" s="33"/>
@@ -9306,11 +9414,11 @@
       <c r="G50" s="28"/>
       <c r="H50" s="29"/>
       <c r="I50" s="30"/>
-      <c r="J50" s="176" t="s">
-        <v>353</v>
+      <c r="J50" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K50" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M50" s="53"/>
       <c r="N50" s="53"/>
@@ -9321,13 +9429,13 @@
     </row>
     <row r="51" ht="13.95" customHeight="1" spans="1:18">
       <c r="A51" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B51" s="52" t="s">
         <v>61</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D51" s="27"/>
       <c r="E51" s="33"/>
@@ -9335,11 +9443,11 @@
       <c r="G51" s="28"/>
       <c r="H51" s="29"/>
       <c r="I51" s="30"/>
-      <c r="J51" s="176" t="s">
-        <v>353</v>
+      <c r="J51" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K51" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M51" s="53"/>
       <c r="N51" s="53"/>
@@ -9350,13 +9458,13 @@
     </row>
     <row r="52" ht="13.95" customHeight="1" spans="1:18">
       <c r="A52" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B52" s="52" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D52" s="34"/>
       <c r="E52" s="33"/>
@@ -9364,11 +9472,11 @@
       <c r="G52" s="28"/>
       <c r="H52" s="29"/>
       <c r="I52" s="30"/>
-      <c r="J52" s="176" t="s">
-        <v>353</v>
+      <c r="J52" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K52" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M52" s="53"/>
       <c r="N52" s="53"/>
@@ -9379,13 +9487,13 @@
     </row>
     <row r="53" ht="13.95" customHeight="1" spans="1:18">
       <c r="A53" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B53" s="52" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D53" s="27"/>
       <c r="E53" s="33"/>
@@ -9393,11 +9501,11 @@
       <c r="G53" s="28"/>
       <c r="H53" s="29"/>
       <c r="I53" s="30"/>
-      <c r="J53" s="176" t="s">
-        <v>353</v>
+      <c r="J53" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K53" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M53" s="53"/>
       <c r="N53" s="53"/>
@@ -9408,13 +9516,13 @@
     </row>
     <row r="54" ht="13.95" customHeight="1" spans="1:18">
       <c r="A54" s="25" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B54" s="52" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D54" s="27"/>
       <c r="E54" s="33"/>
@@ -9422,11 +9530,11 @@
       <c r="G54" s="28"/>
       <c r="H54" s="29"/>
       <c r="I54" s="30"/>
-      <c r="J54" s="176" t="s">
-        <v>353</v>
+      <c r="J54" s="178" t="s">
+        <v>357</v>
       </c>
       <c r="K54" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M54" s="53"/>
       <c r="N54" s="53"/>
@@ -9437,13 +9545,13 @@
     </row>
     <row r="55" ht="13.95" customHeight="1" spans="1:18">
       <c r="A55" s="56" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B55" s="57" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C55" s="58" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D55" s="58"/>
       <c r="E55" s="59"/>
@@ -9451,11 +9559,11 @@
       <c r="G55" s="60"/>
       <c r="H55" s="61"/>
       <c r="I55" s="62"/>
-      <c r="J55" s="177" t="s">
-        <v>353</v>
+      <c r="J55" s="179" t="s">
+        <v>357</v>
       </c>
       <c r="K55" s="60" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M55" s="53"/>
       <c r="N55" s="53"/>
@@ -9466,13 +9574,13 @@
     </row>
     <row r="56" ht="13.95" customHeight="1" spans="1:18">
       <c r="A56" s="56" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B56" s="57" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C56" s="58" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D56" s="58"/>
       <c r="E56" s="59"/>
@@ -9484,7 +9592,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="60" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M56" s="53"/>
       <c r="N56" s="53"/>
@@ -9550,10 +9658,10 @@
       <c r="D59" s="13"/>
       <c r="E59" s="21"/>
       <c r="F59" s="28" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="H59" s="29" t="s">
         <v>109</v>
@@ -9608,7 +9716,7 @@
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
       <c r="F62" s="47" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G62" s="39"/>
       <c r="H62" s="39"/>
@@ -9620,7 +9728,7 @@
     <row r="63" ht="13.95" customHeight="1"/>
     <row r="64" ht="25" customHeight="1" spans="1:18">
       <c r="A64" s="14" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B64" s="15">
         <v>3</v>
@@ -9637,36 +9745,36 @@
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:11">
       <c r="A65" s="17" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
       <c r="D65" s="13"/>
       <c r="E65" s="18"/>
       <c r="F65" s="19" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="19" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="J65" s="19" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="K65" s="13"/>
     </row>
     <row r="66" ht="37" customHeight="1" spans="1:11">
       <c r="A66" s="20" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D66" s="20" t="s">
         <v>186</v>
@@ -9676,7 +9784,7 @@
         <v>40</v>
       </c>
       <c r="G66" s="23" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H66" s="23" t="s">
         <v>42</v>
@@ -9693,7 +9801,7 @@
     </row>
     <row r="67" ht="13.95" customHeight="1" spans="1:11">
       <c r="A67" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B67" s="52" t="s">
         <v>84</v>
@@ -9704,7 +9812,7 @@
       <c r="D67" s="34"/>
       <c r="E67" s="33"/>
       <c r="F67" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G67" s="28" t="s">
         <v>109</v>
@@ -9720,13 +9828,13 @@
     </row>
     <row r="68" ht="13.95" customHeight="1" spans="1:11">
       <c r="A68" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B68" s="52" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C68" s="27" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D68" s="27"/>
       <c r="E68" s="21"/>
@@ -9734,137 +9842,137 @@
       <c r="G68" s="28"/>
       <c r="H68" s="29"/>
       <c r="I68" s="30" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J68" s="28" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="K68" s="28"/>
     </row>
     <row r="69" ht="13.95" customHeight="1" spans="1:11">
       <c r="A69" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B69" s="52" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D69" s="27"/>
       <c r="E69" s="31"/>
       <c r="F69" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G69" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H69" s="52" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="I69" s="27" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J69" s="28"/>
       <c r="K69" s="28"/>
     </row>
     <row r="70" ht="13.95" customHeight="1" spans="1:11">
       <c r="A70" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B70" s="52" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D70" s="34" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E70" s="31"/>
       <c r="F70" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G70" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H70" s="52" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="I70" s="34" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J70" s="28"/>
       <c r="K70" s="28"/>
     </row>
     <row r="71" ht="13.95" customHeight="1" spans="1:11">
       <c r="A71" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B71" s="52" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D71" s="34"/>
       <c r="E71" s="33"/>
       <c r="F71" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G71" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H71" s="52" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="I71" s="34" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="J71" s="32"/>
       <c r="K71" s="28"/>
     </row>
     <row r="72" ht="13.95" customHeight="1" spans="1:11">
       <c r="A72" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B72" s="52" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D72" s="34"/>
       <c r="E72" s="33"/>
       <c r="F72" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G72" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H72" s="52" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I72" s="34" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J72" s="28"/>
       <c r="K72" s="28"/>
     </row>
     <row r="73" ht="13.95" customHeight="1" spans="1:11">
       <c r="A73" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B73" s="52" t="s">
         <v>172</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D73" s="34"/>
       <c r="E73" s="33"/>
       <c r="F73" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G73" s="28" t="s">
         <v>109</v>
@@ -9873,25 +9981,25 @@
         <v>172</v>
       </c>
       <c r="I73" s="34" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="J73" s="28"/>
       <c r="K73" s="28"/>
     </row>
     <row r="74" ht="13.95" customHeight="1" spans="1:11">
       <c r="A74" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B74" s="52" t="s">
         <v>170</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D74" s="34"/>
       <c r="E74" s="33"/>
       <c r="F74" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G74" s="28" t="s">
         <v>109</v>
@@ -9900,214 +10008,214 @@
         <v>170</v>
       </c>
       <c r="I74" s="34" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J74" s="28"/>
       <c r="K74" s="28"/>
     </row>
     <row r="75" ht="13.95" customHeight="1" spans="1:11">
       <c r="A75" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B75" s="52" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D75" s="34"/>
       <c r="E75" s="33"/>
       <c r="F75" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G75" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H75" s="52" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="I75" s="34" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="J75" s="28"/>
       <c r="K75" s="28"/>
     </row>
     <row r="76" ht="13.95" customHeight="1" spans="1:11">
       <c r="A76" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B76" s="52" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D76" s="34"/>
       <c r="E76" s="33"/>
       <c r="F76" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G76" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H76" s="52" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="I76" s="34" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="J76" s="28"/>
       <c r="K76" s="28"/>
     </row>
     <row r="77" ht="13.95" customHeight="1" spans="1:11">
       <c r="A77" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B77" s="52" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D77" s="34"/>
       <c r="E77" s="33"/>
       <c r="F77" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G77" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H77" s="52" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I77" s="34" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J77" s="28"/>
       <c r="K77" s="28"/>
     </row>
     <row r="78" ht="13.95" customHeight="1" spans="1:11">
       <c r="A78" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B78" s="52" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D78" s="34"/>
       <c r="E78" s="33"/>
       <c r="F78" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G78" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H78" s="52" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="I78" s="34" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="J78" s="28"/>
       <c r="K78" s="28"/>
     </row>
     <row r="79" ht="13.95" customHeight="1" spans="1:11">
       <c r="A79" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B79" s="52" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D79" s="34" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E79" s="33"/>
       <c r="F79" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G79" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H79" s="52" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="I79" s="34" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="J79" s="28"/>
       <c r="K79" s="28"/>
     </row>
     <row r="80" ht="13.95" customHeight="1" spans="1:11">
       <c r="A80" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B80" s="52" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C80" s="34" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D80" s="34" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E80" s="33"/>
       <c r="F80" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G80" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H80" s="52" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="I80" s="34" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="J80" s="28" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="K80" s="28" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="81" ht="13.95" customHeight="1" spans="1:11">
       <c r="A81" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B81" s="52" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D81" s="34"/>
       <c r="E81" s="33"/>
       <c r="F81" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G81" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H81" s="52" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="I81" s="34" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="J81" s="28"/>
       <c r="K81" s="28"/>
     </row>
     <row r="82" ht="13.95" customHeight="1" spans="1:11">
       <c r="A82" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B82" s="52" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C82" s="27" t="s">
         <v>212</v>
@@ -10115,13 +10223,13 @@
       <c r="D82" s="27"/>
       <c r="E82" s="33"/>
       <c r="F82" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G82" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H82" s="52" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="I82" s="27" t="s">
         <v>212</v>
@@ -10131,118 +10239,118 @@
     </row>
     <row r="83" ht="13.95" customHeight="1" spans="1:11">
       <c r="A83" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B83" s="52" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C83" s="27" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="33"/>
       <c r="F83" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G83" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H83" s="52" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I83" s="27" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="J83" s="28"/>
       <c r="K83" s="28"/>
     </row>
     <row r="84" ht="13.95" customHeight="1" spans="1:11">
       <c r="A84" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B84" s="52" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C84" s="27" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="33"/>
       <c r="F84" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G84" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H84" s="52" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="I84" s="27" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="J84" s="28"/>
       <c r="K84" s="28"/>
     </row>
     <row r="85" ht="13.95" customHeight="1" spans="1:11">
       <c r="A85" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B85" s="52" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C85" s="27" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D85" s="27"/>
       <c r="E85" s="33"/>
       <c r="F85" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G85" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H85" s="52" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="I85" s="27" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="J85" s="28"/>
       <c r="K85" s="28"/>
     </row>
     <row r="86" ht="13.95" customHeight="1" spans="1:11">
       <c r="A86" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B86" s="52" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C86" s="27" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D86" s="27"/>
       <c r="E86" s="33"/>
       <c r="F86" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G86" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H86" s="52" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="I86" s="27" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="J86" s="28"/>
       <c r="K86" s="28"/>
     </row>
     <row r="87" ht="13.95" customHeight="1" spans="1:11">
       <c r="A87" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B87" s="52" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C87" s="27" t="s">
         <v>45</v>
@@ -10250,13 +10358,13 @@
       <c r="D87" s="27"/>
       <c r="E87" s="33"/>
       <c r="F87" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G87" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H87" s="52" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="I87" s="27" t="s">
         <v>45</v>
@@ -10266,126 +10374,126 @@
     </row>
     <row r="88" ht="13.95" customHeight="1" spans="1:11">
       <c r="A88" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B88" s="52" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C88" s="27" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D88" s="27"/>
       <c r="E88" s="33"/>
       <c r="F88" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G88" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H88" s="52" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="I88" s="27" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="J88" s="28"/>
       <c r="K88" s="28"/>
     </row>
     <row r="89" ht="13.95" customHeight="1" spans="1:11">
       <c r="A89" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B89" s="52" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C89" s="27" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D89" s="27"/>
       <c r="E89" s="33"/>
       <c r="F89" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G89" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H89" s="52" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="I89" s="27" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="J89" s="28"/>
       <c r="K89" s="28"/>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B90" s="52" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C90" s="27" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D90" s="27"/>
       <c r="E90" s="33"/>
       <c r="F90" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G90" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H90" s="52" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="I90" s="27" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="J90" s="28"/>
       <c r="K90" s="28"/>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B91" s="52" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C91" s="27" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D91" s="27"/>
       <c r="E91" s="33"/>
       <c r="F91" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G91" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H91" s="52" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="I91" s="27" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="J91" s="28"/>
       <c r="K91" s="28"/>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B92" s="52" t="s">
         <v>61</v>
       </c>
       <c r="C92" s="27" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D92" s="27"/>
       <c r="E92" s="33"/>
       <c r="F92" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G92" s="28" t="s">
         <v>109</v>
@@ -10394,148 +10502,148 @@
         <v>61</v>
       </c>
       <c r="I92" s="27" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="J92" s="28"/>
       <c r="K92" s="28"/>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B93" s="52" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D93" s="34"/>
       <c r="E93" s="33"/>
       <c r="F93" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G93" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H93" s="52" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I93" s="34" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="J93" s="28"/>
       <c r="K93" s="28"/>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B94" s="52" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C94" s="27" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D94" s="27"/>
       <c r="E94" s="33"/>
       <c r="F94" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G94" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H94" s="52" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="I94" s="27" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="J94" s="28"/>
       <c r="K94" s="28"/>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B95" s="52" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C95" s="27" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D95" s="27"/>
       <c r="E95" s="33"/>
       <c r="F95" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G95" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H95" s="52" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="I95" s="27" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="J95" s="28"/>
       <c r="K95" s="28"/>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="56" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B96" s="57" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C96" s="58" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D96" s="58"/>
       <c r="E96" s="59"/>
       <c r="F96" s="60" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G96" s="60" t="s">
         <v>109</v>
       </c>
       <c r="H96" s="57" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="I96" s="58" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J96" s="60"/>
       <c r="K96" s="60" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="56" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B97" s="57" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C97" s="58" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D97" s="58"/>
       <c r="E97" s="59"/>
       <c r="F97" s="60" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G97" s="60" t="s">
         <v>109</v>
       </c>
       <c r="H97" s="57" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I97" s="58" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="J97" s="60"/>
       <c r="K97" s="60" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -10589,10 +10697,10 @@
       <c r="D100" s="13"/>
       <c r="E100" s="21"/>
       <c r="F100" s="28" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G100" s="28" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H100" s="29" t="s">
         <v>109</v>
@@ -10636,7 +10744,7 @@
       <c r="D103" s="16"/>
       <c r="E103" s="16"/>
       <c r="F103" s="47" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G103" s="39"/>
       <c r="H103" s="39"/>
@@ -10646,7 +10754,7 @@
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:11">
       <c r="A105" s="14" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B105" s="15">
         <v>4</v>
@@ -10663,36 +10771,36 @@
     </row>
     <row r="106" ht="27" customHeight="1" spans="1:11">
       <c r="A106" s="17" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
       <c r="D106" s="13"/>
       <c r="E106" s="18"/>
       <c r="F106" s="19" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="H106" s="13"/>
       <c r="I106" s="19" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="J106" s="19" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="K106" s="13"/>
     </row>
     <row r="107" ht="25" customHeight="1" spans="1:11">
       <c r="A107" s="20" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>186</v>
@@ -10702,7 +10810,7 @@
         <v>40</v>
       </c>
       <c r="G107" s="23" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H107" s="23" t="s">
         <v>42</v>
@@ -10719,68 +10827,68 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B108" s="26" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E108" s="33"/>
       <c r="F108" s="28"/>
       <c r="G108" s="28"/>
       <c r="H108" s="52"/>
       <c r="I108" s="34"/>
-      <c r="J108" s="176" t="s">
-        <v>409</v>
+      <c r="J108" s="178" t="s">
+        <v>413</v>
       </c>
       <c r="K108" s="28"/>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B109" s="26" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C109" s="27" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D109" s="27"/>
       <c r="E109" s="33"/>
       <c r="F109" s="28" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G109" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H109" s="52" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="I109" s="27" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="J109" s="28"/>
       <c r="K109" s="28"/>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B110" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C110" s="27" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D110" s="27"/>
       <c r="E110" s="33"/>
       <c r="F110" s="28" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G110" s="28" t="s">
         <v>112</v>
@@ -10796,54 +10904,54 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B111" s="26" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D111" s="34"/>
       <c r="E111" s="33"/>
       <c r="F111" s="28" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G111" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H111" s="52" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I111" s="34" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="J111" s="28"/>
       <c r="K111" s="28"/>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="25" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C112" s="27" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D112" s="27"/>
       <c r="E112" s="33"/>
       <c r="F112" s="28" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G112" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H112" s="52" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="I112" s="27" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="J112" s="28"/>
       <c r="K112" s="28"/>
@@ -10899,10 +11007,10 @@
       <c r="D115" s="13"/>
       <c r="E115" s="21"/>
       <c r="F115" s="28" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="G115" s="28" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="H115" s="29" t="s">
         <v>109</v>
@@ -10918,17 +11026,17 @@
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="28" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G116" s="28" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H116" s="29" t="s">
         <v>112</v>
       </c>
       <c r="I116" s="30"/>
       <c r="J116" s="45" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K116" s="40"/>
     </row>
@@ -10980,7 +11088,7 @@
       <c r="D120" s="16"/>
       <c r="E120" s="16"/>
       <c r="F120" s="47" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="G120" s="39"/>
       <c r="H120" s="39"/>
@@ -11092,102 +11200,102 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -11195,7 +11303,7 @@
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -11203,7 +11311,7 @@
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -11228,111 +11336,111 @@
   <sheetFormatPr defaultColWidth="6.66666666666667" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="2.66666666666667" style="70" customWidth="1"/>
-    <col min="2" max="2" width="4.33333333333333" style="130" customWidth="1"/>
-    <col min="3" max="3" width="6.44444444444444" style="131" customWidth="1"/>
-    <col min="4" max="4" width="12.1018518518519" style="131" customWidth="1"/>
-    <col min="5" max="5" width="19.4444444444444" style="132" customWidth="1"/>
-    <col min="6" max="6" width="29.4444444444444" style="133" customWidth="1"/>
-    <col min="7" max="7" width="52.6666666666667" style="132" customWidth="1"/>
+    <col min="2" max="2" width="4.33333333333333" style="132" customWidth="1"/>
+    <col min="3" max="3" width="6.44444444444444" style="133" customWidth="1"/>
+    <col min="4" max="4" width="12.1018518518519" style="133" customWidth="1"/>
+    <col min="5" max="5" width="19.4444444444444" style="134" customWidth="1"/>
+    <col min="6" max="6" width="29.4444444444444" style="135" customWidth="1"/>
+    <col min="7" max="7" width="52.6666666666667" style="134" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="129" customFormat="1" ht="21.6" customHeight="1" spans="1:7">
-      <c r="A1" s="134"/>
-      <c r="B1" s="135" t="s">
+    <row r="1" s="131" customFormat="1" ht="21.6" customHeight="1" spans="1:7">
+      <c r="A1" s="136"/>
+      <c r="B1" s="137" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="136" t="s">
+      <c r="C1" s="138" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="136" t="s">
+      <c r="D1" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="137" t="s">
+      <c r="E1" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="138" t="s">
+      <c r="F1" s="140" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="137" t="s">
+      <c r="G1" s="139" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="B2" s="139">
+      <c r="B2" s="141">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="140" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="142" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="141"/>
-      <c r="G2" s="142" t="s">
+      <c r="F2" s="143"/>
+      <c r="G2" s="144" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="B3" s="143"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="144" t="s">
+      <c r="B3" s="145"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="141"/>
-      <c r="G3" s="144"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="146"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="B4" s="143"/>
-      <c r="C4" s="139"/>
-      <c r="D4" s="139"/>
-      <c r="E4" s="144" t="s">
+      <c r="B4" s="145"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="141"/>
-      <c r="G4" s="144"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="146"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="B5" s="143"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="144" t="s">
+      <c r="B5" s="145"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
+      <c r="E5" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="141"/>
-      <c r="G5" s="144"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="146"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="B6" s="143"/>
-      <c r="C6" s="139"/>
-      <c r="D6" s="139"/>
-      <c r="E6" s="140" t="s">
+      <c r="B6" s="145"/>
+      <c r="C6" s="141"/>
+      <c r="D6" s="141"/>
+      <c r="E6" s="142" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="141"/>
-      <c r="G6" s="144" t="s">
+      <c r="F6" s="143"/>
+      <c r="G6" s="146" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="B7" s="143"/>
-      <c r="C7" s="139"/>
-      <c r="D7" s="139"/>
-      <c r="E7" s="144" t="s">
+      <c r="B7" s="145"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="141"/>
+      <c r="E7" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="141"/>
-      <c r="G7" s="144"/>
+      <c r="F7" s="143"/>
+      <c r="G7" s="146"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="B8" s="143"/>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="144" t="s">
+      <c r="B8" s="145"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="141"/>
+      <c r="E8" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="141"/>
-      <c r="G8" s="144"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="146"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:G8" etc:filterBottomFollowUsedRange="0">
@@ -11491,7 +11599,7 @@
       </c>
     </row>
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="112"/>
+      <c r="A6" s="114"/>
       <c r="B6" s="81" t="s">
         <v>46</v>
       </c>
@@ -11504,18 +11612,18 @@
       </c>
       <c r="F6" s="81"/>
       <c r="G6" s="81"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
       <c r="L6" s="81"/>
       <c r="M6" s="81"/>
       <c r="N6" s="87"/>
-      <c r="O6" s="115"/>
+      <c r="O6" s="117"/>
       <c r="P6" s="81"/>
       <c r="Q6" s="81"/>
     </row>
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="116"/>
+      <c r="A7" s="118"/>
       <c r="B7" s="81" t="s">
         <v>49</v>
       </c>
@@ -11528,18 +11636,18 @@
       </c>
       <c r="F7" s="81"/>
       <c r="G7" s="81"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="114"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="116"/>
       <c r="L7" s="81"/>
       <c r="M7" s="81"/>
       <c r="N7" s="87"/>
-      <c r="O7" s="115"/>
+      <c r="O7" s="117"/>
       <c r="P7" s="81"/>
       <c r="Q7" s="81"/>
     </row>
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="116"/>
+      <c r="A8" s="118"/>
       <c r="B8" s="81" t="s">
         <v>52</v>
       </c>
@@ -11552,18 +11660,18 @@
       </c>
       <c r="F8" s="81"/>
       <c r="G8" s="81"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
       <c r="L8" s="81"/>
       <c r="M8" s="81"/>
       <c r="N8" s="87"/>
-      <c r="O8" s="115"/>
+      <c r="O8" s="117"/>
       <c r="P8" s="81"/>
       <c r="Q8" s="81"/>
     </row>
     <row r="9" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="112"/>
+      <c r="A9" s="114"/>
       <c r="B9" s="81" t="s">
         <v>55</v>
       </c>
@@ -11578,16 +11686,16 @@
       <c r="G9" s="81"/>
       <c r="H9" s="86"/>
       <c r="I9" s="86"/>
-      <c r="J9" s="117"/>
+      <c r="J9" s="119"/>
       <c r="L9" s="81"/>
       <c r="M9" s="81"/>
       <c r="N9" s="87"/>
-      <c r="O9" s="115"/>
+      <c r="O9" s="117"/>
       <c r="P9" s="81"/>
       <c r="Q9" s="81"/>
     </row>
     <row r="10" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="116"/>
+      <c r="A10" s="118"/>
       <c r="B10" s="81" t="s">
         <v>58</v>
       </c>
@@ -11602,16 +11710,16 @@
       <c r="G10" s="81"/>
       <c r="H10" s="86"/>
       <c r="I10" s="86"/>
-      <c r="J10" s="117"/>
+      <c r="J10" s="119"/>
       <c r="L10" s="81"/>
       <c r="M10" s="81"/>
       <c r="N10" s="87"/>
-      <c r="O10" s="115"/>
+      <c r="O10" s="117"/>
       <c r="P10" s="81"/>
       <c r="Q10" s="81"/>
     </row>
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="116"/>
+      <c r="A11" s="118"/>
       <c r="B11" s="81" t="s">
         <v>61</v>
       </c>
@@ -11624,18 +11732,18 @@
       </c>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
       <c r="L11" s="81"/>
       <c r="M11" s="81"/>
       <c r="N11" s="87"/>
-      <c r="O11" s="115"/>
+      <c r="O11" s="117"/>
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
     </row>
     <row r="12" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="116"/>
+      <c r="A12" s="118"/>
       <c r="B12" s="81" t="s">
         <v>63</v>
       </c>
@@ -11654,12 +11762,12 @@
       <c r="L12" s="81"/>
       <c r="M12" s="81"/>
       <c r="N12" s="87"/>
-      <c r="O12" s="115"/>
+      <c r="O12" s="117"/>
       <c r="P12" s="81"/>
       <c r="Q12" s="81"/>
     </row>
     <row r="13" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="112"/>
+      <c r="A13" s="114"/>
       <c r="B13" s="81" t="s">
         <v>65</v>
       </c>
@@ -11678,12 +11786,12 @@
       <c r="L13" s="81"/>
       <c r="M13" s="81"/>
       <c r="N13" s="87"/>
-      <c r="O13" s="115"/>
+      <c r="O13" s="117"/>
       <c r="P13" s="81"/>
       <c r="Q13" s="81"/>
     </row>
     <row r="14" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="112"/>
+      <c r="A14" s="114"/>
       <c r="B14" s="81" t="s">
         <v>67</v>
       </c>
@@ -11698,16 +11806,16 @@
       <c r="G14" s="81"/>
       <c r="H14" s="84"/>
       <c r="I14" s="86"/>
-      <c r="J14" s="117"/>
+      <c r="J14" s="119"/>
       <c r="L14" s="81"/>
       <c r="M14" s="81"/>
       <c r="N14" s="87"/>
-      <c r="O14" s="115"/>
+      <c r="O14" s="117"/>
       <c r="P14" s="81"/>
       <c r="Q14" s="81"/>
     </row>
     <row r="15" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="116"/>
+      <c r="A15" s="118"/>
       <c r="B15" s="81" t="s">
         <v>69</v>
       </c>
@@ -11722,16 +11830,16 @@
       <c r="G15" s="81"/>
       <c r="H15" s="84"/>
       <c r="I15" s="86"/>
-      <c r="J15" s="117"/>
+      <c r="J15" s="119"/>
       <c r="L15" s="81"/>
       <c r="M15" s="81"/>
       <c r="N15" s="87"/>
-      <c r="O15" s="115"/>
+      <c r="O15" s="117"/>
       <c r="P15" s="81"/>
       <c r="Q15" s="81"/>
     </row>
     <row r="16" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="116"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="81" t="s">
         <v>72</v>
       </c>
@@ -11746,18 +11854,18 @@
       <c r="G16" s="81"/>
       <c r="H16" s="84"/>
       <c r="I16" s="86"/>
-      <c r="J16" s="117"/>
+      <c r="J16" s="119"/>
       <c r="L16" s="81"/>
       <c r="M16" s="81"/>
       <c r="N16" s="87"/>
-      <c r="O16" s="115"/>
+      <c r="O16" s="117"/>
       <c r="P16" s="81"/>
       <c r="Q16" s="81" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="116"/>
+      <c r="A17" s="118"/>
       <c r="B17" s="81" t="s">
         <v>76</v>
       </c>
@@ -11776,12 +11884,12 @@
       <c r="L17" s="81"/>
       <c r="M17" s="81"/>
       <c r="N17" s="87"/>
-      <c r="O17" s="115"/>
+      <c r="O17" s="117"/>
       <c r="P17" s="81"/>
       <c r="Q17" s="81"/>
     </row>
     <row r="18" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="116"/>
+      <c r="A18" s="118"/>
       <c r="B18" s="81" t="s">
         <v>79</v>
       </c>
@@ -11800,12 +11908,12 @@
       <c r="L18" s="81"/>
       <c r="M18" s="81"/>
       <c r="N18" s="87"/>
-      <c r="O18" s="115"/>
+      <c r="O18" s="117"/>
       <c r="P18" s="81"/>
       <c r="Q18" s="81"/>
     </row>
     <row r="19" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="116"/>
+      <c r="A19" s="118"/>
       <c r="B19" s="81" t="s">
         <v>82</v>
       </c>
@@ -11824,37 +11932,37 @@
       <c r="L19" s="81"/>
       <c r="M19" s="81"/>
       <c r="N19" s="87"/>
-      <c r="O19" s="115"/>
+      <c r="O19" s="117"/>
       <c r="P19" s="81"/>
       <c r="Q19" s="81"/>
     </row>
     <row r="20" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="116"/>
+      <c r="A20" s="118"/>
       <c r="B20" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="121"/>
+      <c r="C20" s="123"/>
       <c r="D20" s="81" t="s">
         <v>85</v>
       </c>
       <c r="E20" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="123"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="124"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="126"/>
       <c r="L20" s="81"/>
       <c r="M20" s="81"/>
       <c r="N20" s="87"/>
-      <c r="O20" s="115"/>
+      <c r="O20" s="117"/>
       <c r="P20" s="81"/>
       <c r="Q20" s="81"/>
     </row>
     <row r="21" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="116"/>
+      <c r="A21" s="118"/>
       <c r="B21" s="81" t="s">
         <v>87</v>
       </c>
@@ -11873,12 +11981,12 @@
       <c r="L21" s="81"/>
       <c r="M21" s="81"/>
       <c r="N21" s="87"/>
-      <c r="O21" s="115"/>
+      <c r="O21" s="117"/>
       <c r="P21" s="81"/>
       <c r="Q21" s="81"/>
     </row>
     <row r="22" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="112"/>
+      <c r="A22" s="114"/>
       <c r="B22" s="81" t="s">
         <v>89</v>
       </c>
@@ -11897,7 +12005,7 @@
       <c r="L22" s="81"/>
       <c r="M22" s="81"/>
       <c r="N22" s="87"/>
-      <c r="O22" s="115"/>
+      <c r="O22" s="117"/>
       <c r="P22" s="81"/>
       <c r="Q22" s="81"/>
     </row>
@@ -11918,10 +12026,10 @@
       <c r="H23" s="84"/>
       <c r="I23" s="86"/>
       <c r="J23" s="86"/>
-      <c r="L23" s="125"/>
+      <c r="L23" s="127"/>
       <c r="M23" s="88"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="127"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="129"/>
       <c r="P23" s="88"/>
       <c r="Q23" s="88"/>
     </row>
@@ -11942,10 +12050,10 @@
       <c r="H24" s="84"/>
       <c r="I24" s="86"/>
       <c r="J24" s="86"/>
-      <c r="L24" s="125"/>
+      <c r="L24" s="127"/>
       <c r="M24" s="88"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="127"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="129"/>
       <c r="P24" s="88"/>
       <c r="Q24" s="88"/>
     </row>
@@ -11966,10 +12074,10 @@
       <c r="H25" s="84"/>
       <c r="I25" s="86"/>
       <c r="J25" s="86"/>
-      <c r="L25" s="125"/>
+      <c r="L25" s="127"/>
       <c r="M25" s="88"/>
-      <c r="N25" s="126"/>
-      <c r="O25" s="127"/>
+      <c r="N25" s="128"/>
+      <c r="O25" s="129"/>
       <c r="P25" s="88"/>
       <c r="Q25" s="88"/>
     </row>
@@ -11978,16 +12086,16 @@
       <c r="B26" s="81"/>
       <c r="C26" s="81"/>
       <c r="D26" s="81"/>
-      <c r="E26" s="128"/>
+      <c r="E26" s="130"/>
       <c r="F26" s="83"/>
       <c r="G26" s="83"/>
       <c r="H26" s="84"/>
       <c r="I26" s="86"/>
       <c r="J26" s="86"/>
-      <c r="L26" s="125"/>
+      <c r="L26" s="127"/>
       <c r="M26" s="88"/>
-      <c r="N26" s="126"/>
-      <c r="O26" s="127"/>
+      <c r="N26" s="128"/>
+      <c r="O26" s="129"/>
       <c r="P26" s="88"/>
       <c r="Q26" s="88"/>
     </row>
@@ -11996,16 +12104,16 @@
       <c r="B27" s="81"/>
       <c r="C27" s="81"/>
       <c r="D27" s="81"/>
-      <c r="E27" s="128"/>
+      <c r="E27" s="130"/>
       <c r="F27" s="83"/>
       <c r="G27" s="83"/>
       <c r="H27" s="84"/>
       <c r="I27" s="86"/>
       <c r="J27" s="86"/>
-      <c r="L27" s="125"/>
+      <c r="L27" s="127"/>
       <c r="M27" s="88"/>
-      <c r="N27" s="126"/>
-      <c r="O27" s="127"/>
+      <c r="N27" s="128"/>
+      <c r="O27" s="129"/>
       <c r="P27" s="88"/>
       <c r="Q27" s="88"/>
     </row>
@@ -12014,16 +12122,16 @@
       <c r="B28" s="81"/>
       <c r="C28" s="81"/>
       <c r="D28" s="81"/>
-      <c r="E28" s="128"/>
+      <c r="E28" s="130"/>
       <c r="F28" s="83"/>
       <c r="G28" s="83"/>
       <c r="H28" s="84"/>
       <c r="I28" s="86"/>
       <c r="J28" s="86"/>
-      <c r="L28" s="125"/>
+      <c r="L28" s="127"/>
       <c r="M28" s="88"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="127"/>
+      <c r="N28" s="128"/>
+      <c r="O28" s="129"/>
       <c r="P28" s="88"/>
       <c r="Q28" s="88"/>
     </row>
@@ -12032,16 +12140,16 @@
       <c r="B29" s="81"/>
       <c r="C29" s="81"/>
       <c r="D29" s="81"/>
-      <c r="E29" s="128"/>
+      <c r="E29" s="130"/>
       <c r="F29" s="83"/>
       <c r="G29" s="83"/>
       <c r="H29" s="84"/>
       <c r="I29" s="86"/>
       <c r="J29" s="86"/>
-      <c r="L29" s="125"/>
+      <c r="L29" s="127"/>
       <c r="M29" s="88"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="127"/>
+      <c r="N29" s="128"/>
+      <c r="O29" s="129"/>
       <c r="P29" s="88"/>
       <c r="Q29" s="88"/>
     </row>
@@ -12050,16 +12158,16 @@
       <c r="B30" s="81"/>
       <c r="C30" s="81"/>
       <c r="D30" s="81"/>
-      <c r="E30" s="128"/>
+      <c r="E30" s="130"/>
       <c r="F30" s="83"/>
       <c r="G30" s="83"/>
       <c r="H30" s="84"/>
       <c r="I30" s="86"/>
       <c r="J30" s="86"/>
-      <c r="L30" s="125"/>
+      <c r="L30" s="127"/>
       <c r="M30" s="88"/>
-      <c r="N30" s="126"/>
-      <c r="O30" s="127"/>
+      <c r="N30" s="128"/>
+      <c r="O30" s="129"/>
       <c r="P30" s="88"/>
       <c r="Q30" s="88"/>
     </row>
@@ -12068,16 +12176,16 @@
       <c r="B31" s="81"/>
       <c r="C31" s="81"/>
       <c r="D31" s="81"/>
-      <c r="E31" s="128"/>
+      <c r="E31" s="130"/>
       <c r="F31" s="83"/>
       <c r="G31" s="83"/>
       <c r="H31" s="84"/>
       <c r="I31" s="86"/>
       <c r="J31" s="86"/>
-      <c r="L31" s="125"/>
+      <c r="L31" s="127"/>
       <c r="M31" s="88"/>
-      <c r="N31" s="126"/>
-      <c r="O31" s="127"/>
+      <c r="N31" s="128"/>
+      <c r="O31" s="129"/>
       <c r="P31" s="88"/>
       <c r="Q31" s="88"/>
     </row>
@@ -12086,16 +12194,16 @@
       <c r="B32" s="81"/>
       <c r="C32" s="81"/>
       <c r="D32" s="81"/>
-      <c r="E32" s="128"/>
+      <c r="E32" s="130"/>
       <c r="F32" s="83"/>
       <c r="G32" s="83"/>
       <c r="H32" s="84"/>
       <c r="I32" s="86"/>
       <c r="J32" s="86"/>
-      <c r="L32" s="125"/>
+      <c r="L32" s="127"/>
       <c r="M32" s="88"/>
-      <c r="N32" s="126"/>
-      <c r="O32" s="127"/>
+      <c r="N32" s="128"/>
+      <c r="O32" s="129"/>
       <c r="P32" s="88"/>
       <c r="Q32" s="88"/>
     </row>
@@ -12206,7 +12314,7 @@
       <c r="N37" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="O37" s="115"/>
+      <c r="O37" s="117"/>
       <c r="P37" s="45"/>
       <c r="Q37" s="40"/>
     </row>
@@ -12220,7 +12328,7 @@
       <c r="N38" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="O38" s="115"/>
+      <c r="O38" s="117"/>
       <c r="P38" s="45" t="s">
         <v>113</v>
       </c>
@@ -12236,7 +12344,7 @@
       <c r="N39" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="O39" s="115"/>
+      <c r="O39" s="117"/>
       <c r="P39" s="45" t="s">
         <v>117</v>
       </c>
@@ -12248,7 +12356,7 @@
       <c r="N40" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="O40" s="115"/>
+      <c r="O40" s="117"/>
       <c r="P40" s="103"/>
       <c r="Q40" s="40"/>
     </row>
@@ -12546,7 +12654,7 @@
       </c>
     </row>
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="112"/>
+      <c r="A6" s="114"/>
       <c r="B6" s="81" t="s">
         <v>123</v>
       </c>
@@ -12559,18 +12667,18 @@
       </c>
       <c r="F6" s="81"/>
       <c r="G6" s="81"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
       <c r="L6" s="81"/>
       <c r="M6" s="81"/>
       <c r="N6" s="87"/>
-      <c r="O6" s="115"/>
+      <c r="O6" s="117"/>
       <c r="P6" s="81"/>
       <c r="Q6" s="81"/>
     </row>
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="116"/>
+      <c r="A7" s="118"/>
       <c r="B7" s="81" t="s">
         <v>125</v>
       </c>
@@ -12583,18 +12691,18 @@
       </c>
       <c r="F7" s="81"/>
       <c r="G7" s="81"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="114"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="116"/>
       <c r="L7" s="81"/>
       <c r="M7" s="81"/>
       <c r="N7" s="87"/>
-      <c r="O7" s="115"/>
+      <c r="O7" s="117"/>
       <c r="P7" s="81"/>
       <c r="Q7" s="81"/>
     </row>
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="116"/>
+      <c r="A8" s="118"/>
       <c r="B8" s="81" t="s">
         <v>55</v>
       </c>
@@ -12607,18 +12715,18 @@
       </c>
       <c r="F8" s="81"/>
       <c r="G8" s="81"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
       <c r="L8" s="81"/>
       <c r="M8" s="81"/>
       <c r="N8" s="87"/>
-      <c r="O8" s="115"/>
+      <c r="O8" s="117"/>
       <c r="P8" s="81"/>
       <c r="Q8" s="81"/>
     </row>
     <row r="9" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="112"/>
+      <c r="A9" s="114"/>
       <c r="B9" s="81" t="s">
         <v>58</v>
       </c>
@@ -12633,16 +12741,16 @@
       <c r="G9" s="81"/>
       <c r="H9" s="86"/>
       <c r="I9" s="86"/>
-      <c r="J9" s="117"/>
+      <c r="J9" s="119"/>
       <c r="L9" s="81"/>
       <c r="M9" s="81"/>
       <c r="N9" s="87"/>
-      <c r="O9" s="115"/>
+      <c r="O9" s="117"/>
       <c r="P9" s="81"/>
       <c r="Q9" s="81"/>
     </row>
     <row r="10" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="116"/>
+      <c r="A10" s="118"/>
       <c r="B10" s="81" t="s">
         <v>61</v>
       </c>
@@ -12657,16 +12765,16 @@
       <c r="G10" s="81"/>
       <c r="H10" s="86"/>
       <c r="I10" s="86"/>
-      <c r="J10" s="117"/>
+      <c r="J10" s="119"/>
       <c r="L10" s="81"/>
       <c r="M10" s="81"/>
       <c r="N10" s="87"/>
-      <c r="O10" s="115"/>
+      <c r="O10" s="117"/>
       <c r="P10" s="81"/>
       <c r="Q10" s="81"/>
     </row>
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="116"/>
+      <c r="A11" s="118"/>
       <c r="B11" s="81" t="s">
         <v>65</v>
       </c>
@@ -12679,18 +12787,18 @@
       </c>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
       <c r="L11" s="81"/>
       <c r="M11" s="81"/>
       <c r="N11" s="87"/>
-      <c r="O11" s="115"/>
+      <c r="O11" s="117"/>
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
     </row>
     <row r="12" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="116"/>
+      <c r="A12" s="118"/>
       <c r="B12" s="81" t="s">
         <v>92</v>
       </c>
@@ -12709,12 +12817,12 @@
       <c r="L12" s="81"/>
       <c r="M12" s="81"/>
       <c r="N12" s="87"/>
-      <c r="O12" s="115"/>
+      <c r="O12" s="117"/>
       <c r="P12" s="81"/>
       <c r="Q12" s="81"/>
     </row>
     <row r="13" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="112"/>
+      <c r="A13" s="114"/>
       <c r="B13" s="81" t="s">
         <v>63</v>
       </c>
@@ -12733,12 +12841,12 @@
       <c r="L13" s="81"/>
       <c r="M13" s="81"/>
       <c r="N13" s="87"/>
-      <c r="O13" s="115"/>
+      <c r="O13" s="117"/>
       <c r="P13" s="81"/>
       <c r="Q13" s="81"/>
     </row>
     <row r="14" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="112"/>
+      <c r="A14" s="114"/>
       <c r="B14" s="81" t="s">
         <v>76</v>
       </c>
@@ -12753,16 +12861,16 @@
       <c r="G14" s="81"/>
       <c r="H14" s="84"/>
       <c r="I14" s="86"/>
-      <c r="J14" s="117"/>
+      <c r="J14" s="119"/>
       <c r="L14" s="81"/>
       <c r="M14" s="81"/>
       <c r="N14" s="87"/>
-      <c r="O14" s="115"/>
+      <c r="O14" s="117"/>
       <c r="P14" s="81"/>
       <c r="Q14" s="81"/>
     </row>
     <row r="15" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="116"/>
+      <c r="A15" s="118"/>
       <c r="B15" s="81" t="s">
         <v>79</v>
       </c>
@@ -12777,16 +12885,16 @@
       <c r="G15" s="81"/>
       <c r="H15" s="84"/>
       <c r="I15" s="86"/>
-      <c r="J15" s="117"/>
+      <c r="J15" s="119"/>
       <c r="L15" s="81"/>
       <c r="M15" s="81"/>
       <c r="N15" s="87"/>
-      <c r="O15" s="115"/>
+      <c r="O15" s="117"/>
       <c r="P15" s="81"/>
       <c r="Q15" s="81"/>
     </row>
     <row r="16" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="116"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="81" t="s">
         <v>130</v>
       </c>
@@ -12801,18 +12909,18 @@
       <c r="G16" s="81"/>
       <c r="H16" s="84"/>
       <c r="I16" s="86"/>
-      <c r="J16" s="117"/>
+      <c r="J16" s="119"/>
       <c r="L16" s="81"/>
       <c r="M16" s="81"/>
       <c r="N16" s="87"/>
-      <c r="O16" s="115"/>
+      <c r="O16" s="117"/>
       <c r="P16" s="81"/>
       <c r="Q16" s="81" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="116"/>
+      <c r="A17" s="118"/>
       <c r="B17" s="81" t="s">
         <v>84</v>
       </c>
@@ -12831,12 +12939,12 @@
       <c r="L17" s="81"/>
       <c r="M17" s="81"/>
       <c r="N17" s="87"/>
-      <c r="O17" s="115"/>
+      <c r="O17" s="117"/>
       <c r="P17" s="81"/>
       <c r="Q17" s="81"/>
     </row>
     <row r="18" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="116"/>
+      <c r="A18" s="118"/>
       <c r="B18" s="81" t="s">
         <v>87</v>
       </c>
@@ -12855,12 +12963,12 @@
       <c r="L18" s="81"/>
       <c r="M18" s="81"/>
       <c r="N18" s="87"/>
-      <c r="O18" s="115"/>
+      <c r="O18" s="117"/>
       <c r="P18" s="81"/>
       <c r="Q18" s="81"/>
     </row>
     <row r="19" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="116"/>
+      <c r="A19" s="118"/>
       <c r="B19" s="81" t="s">
         <v>132</v>
       </c>
@@ -12879,37 +12987,37 @@
       <c r="L19" s="81"/>
       <c r="M19" s="81"/>
       <c r="N19" s="87"/>
-      <c r="O19" s="115"/>
+      <c r="O19" s="117"/>
       <c r="P19" s="81"/>
       <c r="Q19" s="81"/>
     </row>
     <row r="20" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="116"/>
+      <c r="A20" s="118"/>
       <c r="B20" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="121"/>
+      <c r="C20" s="123"/>
       <c r="D20" s="81" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="108" t="s">
         <v>136</v>
       </c>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="123"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="124"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="126"/>
       <c r="L20" s="81"/>
       <c r="M20" s="81"/>
       <c r="N20" s="87"/>
-      <c r="O20" s="115"/>
+      <c r="O20" s="117"/>
       <c r="P20" s="81"/>
       <c r="Q20" s="81"/>
     </row>
     <row r="21" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="116"/>
+      <c r="A21" s="118"/>
       <c r="B21" s="81" t="s">
         <v>137</v>
       </c>
@@ -12928,12 +13036,12 @@
       <c r="L21" s="81"/>
       <c r="M21" s="81"/>
       <c r="N21" s="87"/>
-      <c r="O21" s="115"/>
+      <c r="O21" s="117"/>
       <c r="P21" s="81"/>
       <c r="Q21" s="81"/>
     </row>
     <row r="22" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="112"/>
+      <c r="A22" s="114"/>
       <c r="B22" s="81" t="s">
         <v>140</v>
       </c>
@@ -12952,7 +13060,7 @@
       <c r="L22" s="81"/>
       <c r="M22" s="81"/>
       <c r="N22" s="87"/>
-      <c r="O22" s="115"/>
+      <c r="O22" s="117"/>
       <c r="P22" s="81"/>
       <c r="Q22" s="81"/>
     </row>
@@ -12967,10 +13075,10 @@
       <c r="H23" s="84"/>
       <c r="I23" s="86"/>
       <c r="J23" s="86"/>
-      <c r="L23" s="125"/>
+      <c r="L23" s="127"/>
       <c r="M23" s="88"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="127"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="129"/>
       <c r="P23" s="88"/>
       <c r="Q23" s="88"/>
     </row>
@@ -12985,10 +13093,10 @@
       <c r="H24" s="84"/>
       <c r="I24" s="86"/>
       <c r="J24" s="86"/>
-      <c r="L24" s="125"/>
+      <c r="L24" s="127"/>
       <c r="M24" s="88"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="127"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="129"/>
       <c r="P24" s="88"/>
       <c r="Q24" s="88"/>
     </row>
@@ -13003,10 +13111,10 @@
       <c r="H25" s="84"/>
       <c r="I25" s="86"/>
       <c r="J25" s="86"/>
-      <c r="L25" s="125"/>
+      <c r="L25" s="127"/>
       <c r="M25" s="88"/>
-      <c r="N25" s="126"/>
-      <c r="O25" s="127"/>
+      <c r="N25" s="128"/>
+      <c r="O25" s="129"/>
       <c r="P25" s="88"/>
       <c r="Q25" s="88"/>
     </row>
@@ -13015,16 +13123,16 @@
       <c r="B26" s="81"/>
       <c r="C26" s="81"/>
       <c r="D26" s="81"/>
-      <c r="E26" s="128"/>
+      <c r="E26" s="130"/>
       <c r="F26" s="83"/>
       <c r="G26" s="83"/>
       <c r="H26" s="84"/>
       <c r="I26" s="86"/>
       <c r="J26" s="86"/>
-      <c r="L26" s="125"/>
+      <c r="L26" s="127"/>
       <c r="M26" s="88"/>
-      <c r="N26" s="126"/>
-      <c r="O26" s="127"/>
+      <c r="N26" s="128"/>
+      <c r="O26" s="129"/>
       <c r="P26" s="88"/>
       <c r="Q26" s="88"/>
     </row>
@@ -13033,16 +13141,16 @@
       <c r="B27" s="81"/>
       <c r="C27" s="81"/>
       <c r="D27" s="81"/>
-      <c r="E27" s="128"/>
+      <c r="E27" s="130"/>
       <c r="F27" s="83"/>
       <c r="G27" s="83"/>
       <c r="H27" s="84"/>
       <c r="I27" s="86"/>
       <c r="J27" s="86"/>
-      <c r="L27" s="125"/>
+      <c r="L27" s="127"/>
       <c r="M27" s="88"/>
-      <c r="N27" s="126"/>
-      <c r="O27" s="127"/>
+      <c r="N27" s="128"/>
+      <c r="O27" s="129"/>
       <c r="P27" s="88"/>
       <c r="Q27" s="88"/>
     </row>
@@ -13051,16 +13159,16 @@
       <c r="B28" s="81"/>
       <c r="C28" s="81"/>
       <c r="D28" s="81"/>
-      <c r="E28" s="128"/>
+      <c r="E28" s="130"/>
       <c r="F28" s="83"/>
       <c r="G28" s="83"/>
       <c r="H28" s="84"/>
       <c r="I28" s="86"/>
       <c r="J28" s="86"/>
-      <c r="L28" s="125"/>
+      <c r="L28" s="127"/>
       <c r="M28" s="88"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="127"/>
+      <c r="N28" s="128"/>
+      <c r="O28" s="129"/>
       <c r="P28" s="88"/>
       <c r="Q28" s="88"/>
     </row>
@@ -13069,16 +13177,16 @@
       <c r="B29" s="81"/>
       <c r="C29" s="81"/>
       <c r="D29" s="81"/>
-      <c r="E29" s="128"/>
+      <c r="E29" s="130"/>
       <c r="F29" s="83"/>
       <c r="G29" s="83"/>
       <c r="H29" s="84"/>
       <c r="I29" s="86"/>
       <c r="J29" s="86"/>
-      <c r="L29" s="125"/>
+      <c r="L29" s="127"/>
       <c r="M29" s="88"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="127"/>
+      <c r="N29" s="128"/>
+      <c r="O29" s="129"/>
       <c r="P29" s="88"/>
       <c r="Q29" s="88"/>
     </row>
@@ -13087,16 +13195,16 @@
       <c r="B30" s="81"/>
       <c r="C30" s="81"/>
       <c r="D30" s="81"/>
-      <c r="E30" s="128"/>
+      <c r="E30" s="130"/>
       <c r="F30" s="83"/>
       <c r="G30" s="83"/>
       <c r="H30" s="84"/>
       <c r="I30" s="86"/>
       <c r="J30" s="86"/>
-      <c r="L30" s="125"/>
+      <c r="L30" s="127"/>
       <c r="M30" s="88"/>
-      <c r="N30" s="126"/>
-      <c r="O30" s="127"/>
+      <c r="N30" s="128"/>
+      <c r="O30" s="129"/>
       <c r="P30" s="88"/>
       <c r="Q30" s="88"/>
     </row>
@@ -13105,16 +13213,16 @@
       <c r="B31" s="81"/>
       <c r="C31" s="81"/>
       <c r="D31" s="81"/>
-      <c r="E31" s="128"/>
+      <c r="E31" s="130"/>
       <c r="F31" s="83"/>
       <c r="G31" s="83"/>
       <c r="H31" s="84"/>
       <c r="I31" s="86"/>
       <c r="J31" s="86"/>
-      <c r="L31" s="125"/>
+      <c r="L31" s="127"/>
       <c r="M31" s="88"/>
-      <c r="N31" s="126"/>
-      <c r="O31" s="127"/>
+      <c r="N31" s="128"/>
+      <c r="O31" s="129"/>
       <c r="P31" s="88"/>
       <c r="Q31" s="88"/>
     </row>
@@ -13123,16 +13231,16 @@
       <c r="B32" s="81"/>
       <c r="C32" s="81"/>
       <c r="D32" s="81"/>
-      <c r="E32" s="128"/>
+      <c r="E32" s="130"/>
       <c r="F32" s="83"/>
       <c r="G32" s="83"/>
       <c r="H32" s="84"/>
       <c r="I32" s="86"/>
       <c r="J32" s="86"/>
-      <c r="L32" s="125"/>
+      <c r="L32" s="127"/>
       <c r="M32" s="88"/>
-      <c r="N32" s="126"/>
-      <c r="O32" s="127"/>
+      <c r="N32" s="128"/>
+      <c r="O32" s="129"/>
       <c r="P32" s="88"/>
       <c r="Q32" s="88"/>
     </row>
@@ -13243,7 +13351,7 @@
       <c r="N37" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="O37" s="115"/>
+      <c r="O37" s="117"/>
       <c r="P37" s="45"/>
       <c r="Q37" s="40"/>
     </row>
@@ -13257,7 +13365,7 @@
       <c r="N38" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="O38" s="115"/>
+      <c r="O38" s="117"/>
       <c r="P38" s="45" t="s">
         <v>113</v>
       </c>
@@ -13273,7 +13381,7 @@
       <c r="N39" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="O39" s="115"/>
+      <c r="O39" s="117"/>
       <c r="P39" s="45" t="s">
         <v>117</v>
       </c>
@@ -13285,7 +13393,7 @@
       <c r="N40" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="O40" s="115"/>
+      <c r="O40" s="117"/>
       <c r="P40" s="103"/>
       <c r="Q40" s="40"/>
     </row>
@@ -13583,7 +13691,7 @@
       </c>
     </row>
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="112"/>
+      <c r="A6" s="114"/>
       <c r="B6" s="81" t="s">
         <v>46</v>
       </c>
@@ -13596,18 +13704,18 @@
       </c>
       <c r="F6" s="81"/>
       <c r="G6" s="81"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
       <c r="L6" s="81"/>
       <c r="M6" s="81"/>
       <c r="N6" s="87"/>
-      <c r="O6" s="115"/>
+      <c r="O6" s="117"/>
       <c r="P6" s="81"/>
       <c r="Q6" s="81"/>
     </row>
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="116"/>
+      <c r="A7" s="118"/>
       <c r="B7" s="81" t="s">
         <v>55</v>
       </c>
@@ -13620,18 +13728,18 @@
       </c>
       <c r="F7" s="81"/>
       <c r="G7" s="81"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="114"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="116"/>
       <c r="L7" s="81"/>
       <c r="M7" s="81"/>
       <c r="N7" s="87"/>
-      <c r="O7" s="115"/>
+      <c r="O7" s="117"/>
       <c r="P7" s="81"/>
       <c r="Q7" s="81"/>
     </row>
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="116"/>
+      <c r="A8" s="118"/>
       <c r="B8" s="81" t="s">
         <v>58</v>
       </c>
@@ -13644,18 +13752,18 @@
       </c>
       <c r="F8" s="81"/>
       <c r="G8" s="81"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
       <c r="L8" s="81"/>
       <c r="M8" s="81"/>
       <c r="N8" s="87"/>
-      <c r="O8" s="115"/>
+      <c r="O8" s="117"/>
       <c r="P8" s="81"/>
       <c r="Q8" s="81"/>
     </row>
     <row r="9" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="112"/>
+      <c r="A9" s="114"/>
       <c r="B9" s="81" t="s">
         <v>61</v>
       </c>
@@ -13670,16 +13778,16 @@
       <c r="G9" s="81"/>
       <c r="H9" s="86"/>
       <c r="I9" s="86"/>
-      <c r="J9" s="117"/>
+      <c r="J9" s="119"/>
       <c r="L9" s="81"/>
       <c r="M9" s="81"/>
       <c r="N9" s="87"/>
-      <c r="O9" s="115"/>
+      <c r="O9" s="117"/>
       <c r="P9" s="81"/>
       <c r="Q9" s="81"/>
     </row>
     <row r="10" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="116"/>
+      <c r="A10" s="118"/>
       <c r="B10" s="81" t="s">
         <v>63</v>
       </c>
@@ -13694,16 +13802,16 @@
       <c r="G10" s="81"/>
       <c r="H10" s="86"/>
       <c r="I10" s="86"/>
-      <c r="J10" s="117"/>
+      <c r="J10" s="119"/>
       <c r="L10" s="81"/>
       <c r="M10" s="81"/>
       <c r="N10" s="87"/>
-      <c r="O10" s="115"/>
+      <c r="O10" s="117"/>
       <c r="P10" s="81"/>
       <c r="Q10" s="81"/>
     </row>
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="116"/>
+      <c r="A11" s="118"/>
       <c r="B11" s="81" t="s">
         <v>65</v>
       </c>
@@ -13716,18 +13824,18 @@
       </c>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
       <c r="L11" s="81"/>
       <c r="M11" s="81"/>
       <c r="N11" s="87"/>
-      <c r="O11" s="115"/>
+      <c r="O11" s="117"/>
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
     </row>
     <row r="12" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="116"/>
+      <c r="A12" s="118"/>
       <c r="B12" s="81" t="s">
         <v>146</v>
       </c>
@@ -13746,12 +13854,12 @@
       <c r="L12" s="81"/>
       <c r="M12" s="81"/>
       <c r="N12" s="87"/>
-      <c r="O12" s="115"/>
+      <c r="O12" s="117"/>
       <c r="P12" s="81"/>
       <c r="Q12" s="81"/>
     </row>
     <row r="13" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="112"/>
+      <c r="A13" s="114"/>
       <c r="B13" s="81" t="s">
         <v>148</v>
       </c>
@@ -13770,12 +13878,12 @@
       <c r="L13" s="81"/>
       <c r="M13" s="81"/>
       <c r="N13" s="87"/>
-      <c r="O13" s="115"/>
+      <c r="O13" s="117"/>
       <c r="P13" s="81"/>
       <c r="Q13" s="81"/>
     </row>
     <row r="14" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="112"/>
+      <c r="A14" s="114"/>
       <c r="B14" s="81" t="s">
         <v>76</v>
       </c>
@@ -13790,16 +13898,16 @@
       <c r="G14" s="81"/>
       <c r="H14" s="84"/>
       <c r="I14" s="86"/>
-      <c r="J14" s="117"/>
+      <c r="J14" s="119"/>
       <c r="L14" s="81"/>
       <c r="M14" s="81"/>
       <c r="N14" s="87"/>
-      <c r="O14" s="115"/>
+      <c r="O14" s="117"/>
       <c r="P14" s="81"/>
       <c r="Q14" s="81"/>
     </row>
     <row r="15" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="116"/>
+      <c r="A15" s="118"/>
       <c r="B15" s="81" t="s">
         <v>92</v>
       </c>
@@ -13814,16 +13922,16 @@
       <c r="G15" s="81"/>
       <c r="H15" s="84"/>
       <c r="I15" s="86"/>
-      <c r="J15" s="117"/>
+      <c r="J15" s="119"/>
       <c r="L15" s="81"/>
       <c r="M15" s="81"/>
       <c r="N15" s="87"/>
-      <c r="O15" s="115"/>
+      <c r="O15" s="117"/>
       <c r="P15" s="81"/>
       <c r="Q15" s="81"/>
     </row>
     <row r="16" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="116"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="81" t="s">
         <v>79</v>
       </c>
@@ -13838,18 +13946,18 @@
       <c r="G16" s="81"/>
       <c r="H16" s="84"/>
       <c r="I16" s="86"/>
-      <c r="J16" s="117"/>
+      <c r="J16" s="119"/>
       <c r="L16" s="81"/>
       <c r="M16" s="81"/>
       <c r="N16" s="87"/>
-      <c r="O16" s="115"/>
+      <c r="O16" s="117"/>
       <c r="P16" s="81"/>
       <c r="Q16" s="81" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="116"/>
+      <c r="A17" s="118"/>
       <c r="B17" s="81" t="s">
         <v>152</v>
       </c>
@@ -13868,12 +13976,12 @@
       <c r="L17" s="81"/>
       <c r="M17" s="81"/>
       <c r="N17" s="87"/>
-      <c r="O17" s="115"/>
+      <c r="O17" s="117"/>
       <c r="P17" s="81"/>
       <c r="Q17" s="81"/>
     </row>
     <row r="18" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="116"/>
+      <c r="A18" s="118"/>
       <c r="B18" s="81" t="s">
         <v>154</v>
       </c>
@@ -13892,12 +14000,12 @@
       <c r="L18" s="81"/>
       <c r="M18" s="81"/>
       <c r="N18" s="87"/>
-      <c r="O18" s="115"/>
+      <c r="O18" s="117"/>
       <c r="P18" s="81"/>
       <c r="Q18" s="81"/>
     </row>
     <row r="19" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="116"/>
+      <c r="A19" s="118"/>
       <c r="B19" s="81" t="s">
         <v>156</v>
       </c>
@@ -13916,37 +14024,37 @@
       <c r="L19" s="81"/>
       <c r="M19" s="81"/>
       <c r="N19" s="87"/>
-      <c r="O19" s="115"/>
+      <c r="O19" s="117"/>
       <c r="P19" s="81"/>
       <c r="Q19" s="81"/>
     </row>
     <row r="20" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="116"/>
+      <c r="A20" s="118"/>
       <c r="B20" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="121"/>
+      <c r="C20" s="123"/>
       <c r="D20" s="81" t="s">
         <v>95</v>
       </c>
       <c r="E20" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="123"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="124"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="126"/>
       <c r="L20" s="81"/>
       <c r="M20" s="81"/>
       <c r="N20" s="87"/>
-      <c r="O20" s="115"/>
+      <c r="O20" s="117"/>
       <c r="P20" s="81"/>
       <c r="Q20" s="81"/>
     </row>
     <row r="21" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="116"/>
+      <c r="A21" s="118"/>
       <c r="B21" s="81" t="s">
         <v>160</v>
       </c>
@@ -13965,12 +14073,12 @@
       <c r="L21" s="81"/>
       <c r="M21" s="81"/>
       <c r="N21" s="87"/>
-      <c r="O21" s="115"/>
+      <c r="O21" s="117"/>
       <c r="P21" s="81"/>
       <c r="Q21" s="81"/>
     </row>
     <row r="22" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="112"/>
+      <c r="A22" s="114"/>
       <c r="B22" s="81" t="s">
         <v>84</v>
       </c>
@@ -13989,7 +14097,7 @@
       <c r="L22" s="81"/>
       <c r="M22" s="81"/>
       <c r="N22" s="87"/>
-      <c r="O22" s="115"/>
+      <c r="O22" s="117"/>
       <c r="P22" s="81"/>
       <c r="Q22" s="81"/>
     </row>
@@ -14010,10 +14118,10 @@
       <c r="H23" s="84"/>
       <c r="I23" s="86"/>
       <c r="J23" s="86"/>
-      <c r="L23" s="125"/>
+      <c r="L23" s="127"/>
       <c r="M23" s="88"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="127"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="129"/>
       <c r="P23" s="88"/>
       <c r="Q23" s="88"/>
     </row>
@@ -14034,10 +14142,10 @@
       <c r="H24" s="84"/>
       <c r="I24" s="86"/>
       <c r="J24" s="86"/>
-      <c r="L24" s="125"/>
+      <c r="L24" s="127"/>
       <c r="M24" s="88"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="127"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="129"/>
       <c r="P24" s="88"/>
       <c r="Q24" s="88"/>
     </row>
@@ -14058,10 +14166,10 @@
       <c r="H25" s="84"/>
       <c r="I25" s="86"/>
       <c r="J25" s="86"/>
-      <c r="L25" s="125"/>
+      <c r="L25" s="127"/>
       <c r="M25" s="88"/>
-      <c r="N25" s="126"/>
-      <c r="O25" s="127"/>
+      <c r="N25" s="128"/>
+      <c r="O25" s="129"/>
       <c r="P25" s="88"/>
       <c r="Q25" s="88"/>
     </row>
@@ -14082,10 +14190,10 @@
       <c r="H26" s="84"/>
       <c r="I26" s="86"/>
       <c r="J26" s="86"/>
-      <c r="L26" s="125"/>
+      <c r="L26" s="127"/>
       <c r="M26" s="88"/>
-      <c r="N26" s="126"/>
-      <c r="O26" s="127"/>
+      <c r="N26" s="128"/>
+      <c r="O26" s="129"/>
       <c r="P26" s="88"/>
       <c r="Q26" s="88"/>
     </row>
@@ -14094,16 +14202,16 @@
       <c r="B27" s="81"/>
       <c r="C27" s="81"/>
       <c r="D27" s="81"/>
-      <c r="E27" s="128"/>
+      <c r="E27" s="130"/>
       <c r="F27" s="83"/>
       <c r="G27" s="83"/>
       <c r="H27" s="84"/>
       <c r="I27" s="86"/>
       <c r="J27" s="86"/>
-      <c r="L27" s="125"/>
+      <c r="L27" s="127"/>
       <c r="M27" s="88"/>
-      <c r="N27" s="126"/>
-      <c r="O27" s="127"/>
+      <c r="N27" s="128"/>
+      <c r="O27" s="129"/>
       <c r="P27" s="88"/>
       <c r="Q27" s="88"/>
     </row>
@@ -14112,16 +14220,16 @@
       <c r="B28" s="81"/>
       <c r="C28" s="81"/>
       <c r="D28" s="81"/>
-      <c r="E28" s="128"/>
+      <c r="E28" s="130"/>
       <c r="F28" s="83"/>
       <c r="G28" s="83"/>
       <c r="H28" s="84"/>
       <c r="I28" s="86"/>
       <c r="J28" s="86"/>
-      <c r="L28" s="125"/>
+      <c r="L28" s="127"/>
       <c r="M28" s="88"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="127"/>
+      <c r="N28" s="128"/>
+      <c r="O28" s="129"/>
       <c r="P28" s="88"/>
       <c r="Q28" s="88"/>
     </row>
@@ -14130,16 +14238,16 @@
       <c r="B29" s="81"/>
       <c r="C29" s="81"/>
       <c r="D29" s="81"/>
-      <c r="E29" s="128"/>
+      <c r="E29" s="130"/>
       <c r="F29" s="83"/>
       <c r="G29" s="83"/>
       <c r="H29" s="84"/>
       <c r="I29" s="86"/>
       <c r="J29" s="86"/>
-      <c r="L29" s="125"/>
+      <c r="L29" s="127"/>
       <c r="M29" s="88"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="127"/>
+      <c r="N29" s="128"/>
+      <c r="O29" s="129"/>
       <c r="P29" s="88"/>
       <c r="Q29" s="88"/>
     </row>
@@ -14148,16 +14256,16 @@
       <c r="B30" s="81"/>
       <c r="C30" s="81"/>
       <c r="D30" s="81"/>
-      <c r="E30" s="128"/>
+      <c r="E30" s="130"/>
       <c r="F30" s="83"/>
       <c r="G30" s="83"/>
       <c r="H30" s="84"/>
       <c r="I30" s="86"/>
       <c r="J30" s="86"/>
-      <c r="L30" s="125"/>
+      <c r="L30" s="127"/>
       <c r="M30" s="88"/>
-      <c r="N30" s="126"/>
-      <c r="O30" s="127"/>
+      <c r="N30" s="128"/>
+      <c r="O30" s="129"/>
       <c r="P30" s="88"/>
       <c r="Q30" s="88"/>
     </row>
@@ -14166,16 +14274,16 @@
       <c r="B31" s="81"/>
       <c r="C31" s="81"/>
       <c r="D31" s="81"/>
-      <c r="E31" s="128"/>
+      <c r="E31" s="130"/>
       <c r="F31" s="83"/>
       <c r="G31" s="83"/>
       <c r="H31" s="84"/>
       <c r="I31" s="86"/>
       <c r="J31" s="86"/>
-      <c r="L31" s="125"/>
+      <c r="L31" s="127"/>
       <c r="M31" s="88"/>
-      <c r="N31" s="126"/>
-      <c r="O31" s="127"/>
+      <c r="N31" s="128"/>
+      <c r="O31" s="129"/>
       <c r="P31" s="88"/>
       <c r="Q31" s="88"/>
     </row>
@@ -14184,16 +14292,16 @@
       <c r="B32" s="81"/>
       <c r="C32" s="81"/>
       <c r="D32" s="81"/>
-      <c r="E32" s="128"/>
+      <c r="E32" s="130"/>
       <c r="F32" s="83"/>
       <c r="G32" s="83"/>
       <c r="H32" s="84"/>
       <c r="I32" s="86"/>
       <c r="J32" s="86"/>
-      <c r="L32" s="125"/>
+      <c r="L32" s="127"/>
       <c r="M32" s="88"/>
-      <c r="N32" s="126"/>
-      <c r="O32" s="127"/>
+      <c r="N32" s="128"/>
+      <c r="O32" s="129"/>
       <c r="P32" s="88"/>
       <c r="Q32" s="88"/>
     </row>
@@ -14304,7 +14412,7 @@
       <c r="N37" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="O37" s="115"/>
+      <c r="O37" s="117"/>
       <c r="P37" s="45"/>
       <c r="Q37" s="40"/>
     </row>
@@ -14318,7 +14426,7 @@
       <c r="N38" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="O38" s="115"/>
+      <c r="O38" s="117"/>
       <c r="P38" s="45" t="s">
         <v>113</v>
       </c>
@@ -14334,7 +14442,7 @@
       <c r="N39" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="O39" s="115"/>
+      <c r="O39" s="117"/>
       <c r="P39" s="45" t="s">
         <v>117</v>
       </c>
@@ -14346,7 +14454,7 @@
       <c r="N40" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="O40" s="115"/>
+      <c r="O40" s="117"/>
       <c r="P40" s="103"/>
       <c r="Q40" s="40"/>
     </row>
@@ -14604,61 +14712,61 @@
       <c r="Q5" s="24"/>
     </row>
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="112"/>
+      <c r="A6" s="114"/>
       <c r="B6" s="81"/>
       <c r="C6" s="81"/>
       <c r="D6" s="81"/>
       <c r="E6" s="108"/>
       <c r="F6" s="81"/>
       <c r="G6" s="81"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
       <c r="L6" s="81"/>
       <c r="M6" s="81"/>
       <c r="N6" s="87"/>
-      <c r="O6" s="115"/>
+      <c r="O6" s="117"/>
       <c r="P6" s="81"/>
       <c r="Q6" s="81"/>
     </row>
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="116"/>
+      <c r="A7" s="118"/>
       <c r="B7" s="81"/>
       <c r="C7" s="81"/>
       <c r="D7" s="81"/>
       <c r="E7" s="108"/>
       <c r="F7" s="81"/>
       <c r="G7" s="81"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="114"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="116"/>
       <c r="L7" s="81"/>
       <c r="M7" s="81"/>
       <c r="N7" s="87"/>
-      <c r="O7" s="115"/>
+      <c r="O7" s="117"/>
       <c r="P7" s="81"/>
       <c r="Q7" s="81"/>
     </row>
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="116"/>
+      <c r="A8" s="118"/>
       <c r="B8" s="81"/>
       <c r="C8" s="81"/>
       <c r="D8" s="81"/>
       <c r="E8" s="108"/>
       <c r="F8" s="81"/>
       <c r="G8" s="81"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
       <c r="L8" s="81"/>
       <c r="M8" s="81"/>
       <c r="N8" s="87"/>
-      <c r="O8" s="115"/>
+      <c r="O8" s="117"/>
       <c r="P8" s="81"/>
       <c r="Q8" s="81"/>
     </row>
     <row r="9" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="112"/>
+      <c r="A9" s="114"/>
       <c r="B9" s="81"/>
       <c r="C9" s="81"/>
       <c r="D9" s="81"/>
@@ -14667,16 +14775,16 @@
       <c r="G9" s="81"/>
       <c r="H9" s="86"/>
       <c r="I9" s="86"/>
-      <c r="J9" s="117"/>
+      <c r="J9" s="119"/>
       <c r="L9" s="81"/>
       <c r="M9" s="81"/>
       <c r="N9" s="87"/>
-      <c r="O9" s="115"/>
+      <c r="O9" s="117"/>
       <c r="P9" s="81"/>
       <c r="Q9" s="81"/>
     </row>
     <row r="10" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="116"/>
+      <c r="A10" s="118"/>
       <c r="B10" s="81"/>
       <c r="C10" s="81"/>
       <c r="D10" s="81"/>
@@ -14685,34 +14793,34 @@
       <c r="G10" s="81"/>
       <c r="H10" s="86"/>
       <c r="I10" s="86"/>
-      <c r="J10" s="117"/>
+      <c r="J10" s="119"/>
       <c r="L10" s="81"/>
       <c r="M10" s="81"/>
       <c r="N10" s="87"/>
-      <c r="O10" s="115"/>
+      <c r="O10" s="117"/>
       <c r="P10" s="81"/>
       <c r="Q10" s="81"/>
     </row>
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="116"/>
+      <c r="A11" s="118"/>
       <c r="B11" s="81"/>
       <c r="C11" s="81"/>
       <c r="D11" s="81"/>
       <c r="E11" s="108"/>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
       <c r="L11" s="81"/>
       <c r="M11" s="81"/>
       <c r="N11" s="87"/>
-      <c r="O11" s="115"/>
+      <c r="O11" s="117"/>
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
     </row>
     <row r="12" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="116"/>
+      <c r="A12" s="118"/>
       <c r="B12" s="81"/>
       <c r="C12" s="81"/>
       <c r="D12" s="81"/>
@@ -14725,12 +14833,12 @@
       <c r="L12" s="81"/>
       <c r="M12" s="81"/>
       <c r="N12" s="87"/>
-      <c r="O12" s="115"/>
+      <c r="O12" s="117"/>
       <c r="P12" s="81"/>
       <c r="Q12" s="81"/>
     </row>
     <row r="13" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="112"/>
+      <c r="A13" s="114"/>
       <c r="B13" s="81"/>
       <c r="C13" s="81"/>
       <c r="D13" s="81"/>
@@ -14743,12 +14851,12 @@
       <c r="L13" s="81"/>
       <c r="M13" s="81"/>
       <c r="N13" s="87"/>
-      <c r="O13" s="115"/>
+      <c r="O13" s="117"/>
       <c r="P13" s="81"/>
       <c r="Q13" s="81"/>
     </row>
     <row r="14" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="112"/>
+      <c r="A14" s="114"/>
       <c r="B14" s="81"/>
       <c r="C14" s="81"/>
       <c r="D14" s="81"/>
@@ -14757,16 +14865,16 @@
       <c r="G14" s="81"/>
       <c r="H14" s="84"/>
       <c r="I14" s="86"/>
-      <c r="J14" s="117"/>
+      <c r="J14" s="119"/>
       <c r="L14" s="81"/>
       <c r="M14" s="81"/>
       <c r="N14" s="87"/>
-      <c r="O14" s="115"/>
+      <c r="O14" s="117"/>
       <c r="P14" s="81"/>
       <c r="Q14" s="81"/>
     </row>
     <row r="15" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="116"/>
+      <c r="A15" s="118"/>
       <c r="B15" s="81"/>
       <c r="C15" s="81"/>
       <c r="D15" s="81"/>
@@ -14775,16 +14883,16 @@
       <c r="G15" s="81"/>
       <c r="H15" s="84"/>
       <c r="I15" s="86"/>
-      <c r="J15" s="117"/>
+      <c r="J15" s="119"/>
       <c r="L15" s="81"/>
       <c r="M15" s="81"/>
       <c r="N15" s="87"/>
-      <c r="O15" s="115"/>
+      <c r="O15" s="117"/>
       <c r="P15" s="81"/>
       <c r="Q15" s="81"/>
     </row>
     <row r="16" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="116"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="81"/>
       <c r="C16" s="81"/>
       <c r="D16" s="81"/>
@@ -14793,16 +14901,16 @@
       <c r="G16" s="81"/>
       <c r="H16" s="84"/>
       <c r="I16" s="86"/>
-      <c r="J16" s="117"/>
+      <c r="J16" s="119"/>
       <c r="L16" s="81"/>
       <c r="M16" s="81"/>
       <c r="N16" s="87"/>
-      <c r="O16" s="115"/>
+      <c r="O16" s="117"/>
       <c r="P16" s="81"/>
       <c r="Q16" s="81"/>
     </row>
     <row r="17" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="116"/>
+      <c r="A17" s="118"/>
       <c r="B17" s="81"/>
       <c r="C17" s="81"/>
       <c r="D17" s="81"/>
@@ -14815,12 +14923,12 @@
       <c r="L17" s="81"/>
       <c r="M17" s="81"/>
       <c r="N17" s="87"/>
-      <c r="O17" s="115"/>
+      <c r="O17" s="117"/>
       <c r="P17" s="81"/>
       <c r="Q17" s="81"/>
     </row>
     <row r="18" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="116"/>
+      <c r="A18" s="118"/>
       <c r="B18" s="81"/>
       <c r="C18" s="81"/>
       <c r="D18" s="81"/>
@@ -14833,12 +14941,12 @@
       <c r="L18" s="81"/>
       <c r="M18" s="81"/>
       <c r="N18" s="87"/>
-      <c r="O18" s="115"/>
+      <c r="O18" s="117"/>
       <c r="P18" s="81"/>
       <c r="Q18" s="81"/>
     </row>
     <row r="19" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="116"/>
+      <c r="A19" s="118"/>
       <c r="B19" s="81"/>
       <c r="C19" s="81"/>
       <c r="D19" s="81"/>
@@ -14851,31 +14959,31 @@
       <c r="L19" s="81"/>
       <c r="M19" s="81"/>
       <c r="N19" s="87"/>
-      <c r="O19" s="115"/>
+      <c r="O19" s="117"/>
       <c r="P19" s="81"/>
       <c r="Q19" s="81"/>
     </row>
     <row r="20" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="116"/>
+      <c r="A20" s="118"/>
       <c r="B20" s="81"/>
-      <c r="C20" s="121"/>
+      <c r="C20" s="123"/>
       <c r="D20" s="81"/>
       <c r="E20" s="108"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="123"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="124"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="126"/>
       <c r="L20" s="81"/>
       <c r="M20" s="81"/>
       <c r="N20" s="87"/>
-      <c r="O20" s="115"/>
+      <c r="O20" s="117"/>
       <c r="P20" s="81"/>
       <c r="Q20" s="81"/>
     </row>
     <row r="21" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="116"/>
+      <c r="A21" s="118"/>
       <c r="B21" s="81"/>
       <c r="C21" s="81"/>
       <c r="D21" s="81"/>
@@ -14888,12 +14996,12 @@
       <c r="L21" s="81"/>
       <c r="M21" s="81"/>
       <c r="N21" s="87"/>
-      <c r="O21" s="115"/>
+      <c r="O21" s="117"/>
       <c r="P21" s="81"/>
       <c r="Q21" s="81"/>
     </row>
     <row r="22" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="112"/>
+      <c r="A22" s="114"/>
       <c r="B22" s="81"/>
       <c r="C22" s="81"/>
       <c r="D22" s="81"/>
@@ -14906,7 +15014,7 @@
       <c r="L22" s="81"/>
       <c r="M22" s="81"/>
       <c r="N22" s="87"/>
-      <c r="O22" s="115"/>
+      <c r="O22" s="117"/>
       <c r="P22" s="81"/>
       <c r="Q22" s="81"/>
     </row>
@@ -14921,10 +15029,10 @@
       <c r="H23" s="84"/>
       <c r="I23" s="86"/>
       <c r="J23" s="86"/>
-      <c r="L23" s="125"/>
+      <c r="L23" s="127"/>
       <c r="M23" s="88"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="127"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="129"/>
       <c r="P23" s="88"/>
       <c r="Q23" s="88"/>
     </row>
@@ -14939,10 +15047,10 @@
       <c r="H24" s="84"/>
       <c r="I24" s="86"/>
       <c r="J24" s="86"/>
-      <c r="L24" s="125"/>
+      <c r="L24" s="127"/>
       <c r="M24" s="88"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="127"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="129"/>
       <c r="P24" s="88"/>
       <c r="Q24" s="88"/>
     </row>
@@ -14957,10 +15065,10 @@
       <c r="H25" s="84"/>
       <c r="I25" s="86"/>
       <c r="J25" s="86"/>
-      <c r="L25" s="125"/>
+      <c r="L25" s="127"/>
       <c r="M25" s="88"/>
-      <c r="N25" s="126"/>
-      <c r="O25" s="127"/>
+      <c r="N25" s="128"/>
+      <c r="O25" s="129"/>
       <c r="P25" s="88"/>
       <c r="Q25" s="88"/>
     </row>
@@ -14975,10 +15083,10 @@
       <c r="H26" s="84"/>
       <c r="I26" s="86"/>
       <c r="J26" s="86"/>
-      <c r="L26" s="125"/>
+      <c r="L26" s="127"/>
       <c r="M26" s="88"/>
-      <c r="N26" s="126"/>
-      <c r="O26" s="127"/>
+      <c r="N26" s="128"/>
+      <c r="O26" s="129"/>
       <c r="P26" s="88"/>
       <c r="Q26" s="88"/>
     </row>
@@ -14987,16 +15095,16 @@
       <c r="B27" s="81"/>
       <c r="C27" s="81"/>
       <c r="D27" s="81"/>
-      <c r="E27" s="128"/>
+      <c r="E27" s="130"/>
       <c r="F27" s="83"/>
       <c r="G27" s="83"/>
       <c r="H27" s="84"/>
       <c r="I27" s="86"/>
       <c r="J27" s="86"/>
-      <c r="L27" s="125"/>
+      <c r="L27" s="127"/>
       <c r="M27" s="88"/>
-      <c r="N27" s="126"/>
-      <c r="O27" s="127"/>
+      <c r="N27" s="128"/>
+      <c r="O27" s="129"/>
       <c r="P27" s="88"/>
       <c r="Q27" s="88"/>
     </row>
@@ -15005,16 +15113,16 @@
       <c r="B28" s="81"/>
       <c r="C28" s="81"/>
       <c r="D28" s="81"/>
-      <c r="E28" s="128"/>
+      <c r="E28" s="130"/>
       <c r="F28" s="83"/>
       <c r="G28" s="83"/>
       <c r="H28" s="84"/>
       <c r="I28" s="86"/>
       <c r="J28" s="86"/>
-      <c r="L28" s="125"/>
+      <c r="L28" s="127"/>
       <c r="M28" s="88"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="127"/>
+      <c r="N28" s="128"/>
+      <c r="O28" s="129"/>
       <c r="P28" s="88"/>
       <c r="Q28" s="88"/>
     </row>
@@ -15023,16 +15131,16 @@
       <c r="B29" s="81"/>
       <c r="C29" s="81"/>
       <c r="D29" s="81"/>
-      <c r="E29" s="128"/>
+      <c r="E29" s="130"/>
       <c r="F29" s="83"/>
       <c r="G29" s="83"/>
       <c r="H29" s="84"/>
       <c r="I29" s="86"/>
       <c r="J29" s="86"/>
-      <c r="L29" s="125"/>
+      <c r="L29" s="127"/>
       <c r="M29" s="88"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="127"/>
+      <c r="N29" s="128"/>
+      <c r="O29" s="129"/>
       <c r="P29" s="88"/>
       <c r="Q29" s="88"/>
     </row>
@@ -15041,16 +15149,16 @@
       <c r="B30" s="81"/>
       <c r="C30" s="81"/>
       <c r="D30" s="81"/>
-      <c r="E30" s="128"/>
+      <c r="E30" s="130"/>
       <c r="F30" s="83"/>
       <c r="G30" s="83"/>
       <c r="H30" s="84"/>
       <c r="I30" s="86"/>
       <c r="J30" s="86"/>
-      <c r="L30" s="125"/>
+      <c r="L30" s="127"/>
       <c r="M30" s="88"/>
-      <c r="N30" s="126"/>
-      <c r="O30" s="127"/>
+      <c r="N30" s="128"/>
+      <c r="O30" s="129"/>
       <c r="P30" s="88"/>
       <c r="Q30" s="88"/>
     </row>
@@ -15059,16 +15167,16 @@
       <c r="B31" s="81"/>
       <c r="C31" s="81"/>
       <c r="D31" s="81"/>
-      <c r="E31" s="128"/>
+      <c r="E31" s="130"/>
       <c r="F31" s="83"/>
       <c r="G31" s="83"/>
       <c r="H31" s="84"/>
       <c r="I31" s="86"/>
       <c r="J31" s="86"/>
-      <c r="L31" s="125"/>
+      <c r="L31" s="127"/>
       <c r="M31" s="88"/>
-      <c r="N31" s="126"/>
-      <c r="O31" s="127"/>
+      <c r="N31" s="128"/>
+      <c r="O31" s="129"/>
       <c r="P31" s="88"/>
       <c r="Q31" s="88"/>
     </row>
@@ -15077,16 +15185,16 @@
       <c r="B32" s="81"/>
       <c r="C32" s="81"/>
       <c r="D32" s="81"/>
-      <c r="E32" s="128"/>
+      <c r="E32" s="130"/>
       <c r="F32" s="83"/>
       <c r="G32" s="83"/>
       <c r="H32" s="84"/>
       <c r="I32" s="86"/>
       <c r="J32" s="86"/>
-      <c r="L32" s="125"/>
+      <c r="L32" s="127"/>
       <c r="M32" s="88"/>
-      <c r="N32" s="126"/>
-      <c r="O32" s="127"/>
+      <c r="N32" s="128"/>
+      <c r="O32" s="129"/>
       <c r="P32" s="88"/>
       <c r="Q32" s="88"/>
     </row>
@@ -15171,7 +15279,7 @@
       <c r="L37" s="81"/>
       <c r="M37" s="81"/>
       <c r="N37" s="87"/>
-      <c r="O37" s="115"/>
+      <c r="O37" s="117"/>
       <c r="P37" s="45"/>
       <c r="Q37" s="40"/>
     </row>
@@ -15179,7 +15287,7 @@
       <c r="L38" s="81"/>
       <c r="M38" s="81"/>
       <c r="N38" s="87"/>
-      <c r="O38" s="115"/>
+      <c r="O38" s="117"/>
       <c r="P38" s="45"/>
       <c r="Q38" s="40"/>
     </row>
@@ -15187,7 +15295,7 @@
       <c r="L39" s="81"/>
       <c r="M39" s="81"/>
       <c r="N39" s="87"/>
-      <c r="O39" s="115"/>
+      <c r="O39" s="117"/>
       <c r="P39" s="45"/>
       <c r="Q39" s="40"/>
     </row>
@@ -15195,7 +15303,7 @@
       <c r="L40" s="81"/>
       <c r="M40" s="81"/>
       <c r="N40" s="87"/>
-      <c r="O40" s="115"/>
+      <c r="O40" s="117"/>
       <c r="P40" s="103"/>
       <c r="Q40" s="40"/>
     </row>
@@ -15489,7 +15597,7 @@
       </c>
     </row>
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="112"/>
+      <c r="A6" s="114"/>
       <c r="B6" s="81" t="s">
         <v>165</v>
       </c>
@@ -15502,18 +15610,18 @@
       </c>
       <c r="F6" s="81"/>
       <c r="G6" s="81"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
       <c r="L6" s="81"/>
       <c r="M6" s="81"/>
       <c r="N6" s="87"/>
-      <c r="O6" s="115"/>
+      <c r="O6" s="117"/>
       <c r="P6" s="81"/>
       <c r="Q6" s="81"/>
     </row>
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="116"/>
+      <c r="A7" s="118"/>
       <c r="B7" s="81" t="s">
         <v>61</v>
       </c>
@@ -15526,18 +15634,18 @@
       </c>
       <c r="F7" s="81"/>
       <c r="G7" s="81"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="114"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="116"/>
       <c r="L7" s="81"/>
       <c r="M7" s="81"/>
       <c r="N7" s="87"/>
-      <c r="O7" s="115"/>
+      <c r="O7" s="117"/>
       <c r="P7" s="81"/>
       <c r="Q7" s="81"/>
     </row>
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="116"/>
+      <c r="A8" s="118"/>
       <c r="B8" s="81" t="s">
         <v>65</v>
       </c>
@@ -15550,18 +15658,18 @@
       </c>
       <c r="F8" s="81"/>
       <c r="G8" s="81"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
       <c r="L8" s="81"/>
       <c r="M8" s="81"/>
       <c r="N8" s="87"/>
-      <c r="O8" s="115"/>
+      <c r="O8" s="117"/>
       <c r="P8" s="81"/>
       <c r="Q8" s="81"/>
     </row>
     <row r="9" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="112"/>
+      <c r="A9" s="114"/>
       <c r="B9" s="81" t="s">
         <v>63</v>
       </c>
@@ -15576,16 +15684,16 @@
       <c r="G9" s="81"/>
       <c r="H9" s="86"/>
       <c r="I9" s="86"/>
-      <c r="J9" s="117"/>
+      <c r="J9" s="119"/>
       <c r="L9" s="81"/>
       <c r="M9" s="81"/>
       <c r="N9" s="87"/>
-      <c r="O9" s="115"/>
+      <c r="O9" s="117"/>
       <c r="P9" s="81"/>
       <c r="Q9" s="81"/>
     </row>
     <row r="10" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="116"/>
+      <c r="A10" s="118"/>
       <c r="B10" s="81" t="s">
         <v>170</v>
       </c>
@@ -15600,16 +15708,16 @@
       <c r="G10" s="81"/>
       <c r="H10" s="86"/>
       <c r="I10" s="86"/>
-      <c r="J10" s="117"/>
+      <c r="J10" s="119"/>
       <c r="L10" s="81"/>
       <c r="M10" s="81"/>
       <c r="N10" s="87"/>
-      <c r="O10" s="115"/>
+      <c r="O10" s="117"/>
       <c r="P10" s="81"/>
       <c r="Q10" s="81"/>
     </row>
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="116"/>
+      <c r="A11" s="118"/>
       <c r="B11" s="81" t="s">
         <v>172</v>
       </c>
@@ -15622,18 +15730,18 @@
       </c>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
       <c r="L11" s="81"/>
       <c r="M11" s="81"/>
       <c r="N11" s="87"/>
-      <c r="O11" s="115"/>
+      <c r="O11" s="117"/>
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
     </row>
     <row r="12" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="116"/>
+      <c r="A12" s="118"/>
       <c r="B12" s="81" t="s">
         <v>174</v>
       </c>
@@ -15652,12 +15760,12 @@
       <c r="L12" s="81"/>
       <c r="M12" s="81"/>
       <c r="N12" s="87"/>
-      <c r="O12" s="115"/>
+      <c r="O12" s="117"/>
       <c r="P12" s="81"/>
       <c r="Q12" s="81"/>
     </row>
     <row r="13" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="112"/>
+      <c r="A13" s="114"/>
       <c r="B13" s="81" t="s">
         <v>176</v>
       </c>
@@ -15676,12 +15784,12 @@
       <c r="L13" s="81"/>
       <c r="M13" s="81"/>
       <c r="N13" s="87"/>
-      <c r="O13" s="115"/>
+      <c r="O13" s="117"/>
       <c r="P13" s="81"/>
       <c r="Q13" s="81"/>
     </row>
     <row r="14" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="112"/>
+      <c r="A14" s="114"/>
       <c r="B14" s="81" t="s">
         <v>178</v>
       </c>
@@ -15696,16 +15804,16 @@
       <c r="G14" s="81"/>
       <c r="H14" s="84"/>
       <c r="I14" s="86"/>
-      <c r="J14" s="117"/>
+      <c r="J14" s="119"/>
       <c r="L14" s="81"/>
       <c r="M14" s="81"/>
       <c r="N14" s="87"/>
-      <c r="O14" s="115"/>
+      <c r="O14" s="117"/>
       <c r="P14" s="81"/>
       <c r="Q14" s="81"/>
     </row>
     <row r="15" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="116"/>
+      <c r="A15" s="118"/>
       <c r="B15" s="81" t="s">
         <v>180</v>
       </c>
@@ -15720,16 +15828,16 @@
       <c r="G15" s="81"/>
       <c r="H15" s="84"/>
       <c r="I15" s="86"/>
-      <c r="J15" s="117"/>
+      <c r="J15" s="119"/>
       <c r="L15" s="81"/>
       <c r="M15" s="81"/>
       <c r="N15" s="87"/>
-      <c r="O15" s="115"/>
+      <c r="O15" s="117"/>
       <c r="P15" s="81"/>
       <c r="Q15" s="81"/>
     </row>
     <row r="16" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="116"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="81" t="s">
         <v>182</v>
       </c>
@@ -15744,19 +15852,19 @@
       <c r="G16" s="81"/>
       <c r="H16" s="84"/>
       <c r="I16" s="86"/>
-      <c r="J16" s="117"/>
+      <c r="J16" s="119"/>
       <c r="L16" s="81"/>
       <c r="M16" s="81"/>
       <c r="N16" s="87"/>
-      <c r="O16" s="115"/>
+      <c r="O16" s="117"/>
       <c r="P16" s="81"/>
       <c r="Q16" s="81" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="116"/>
-      <c r="B17" s="118" t="s">
+      <c r="A17" s="118"/>
+      <c r="B17" s="120" t="s">
         <v>184</v>
       </c>
       <c r="C17" s="81"/>
@@ -15774,20 +15882,20 @@
       <c r="L17" s="81"/>
       <c r="M17" s="81"/>
       <c r="N17" s="87"/>
-      <c r="O17" s="115"/>
+      <c r="O17" s="117"/>
       <c r="P17" s="81"/>
       <c r="Q17" s="81"/>
     </row>
     <row r="18" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="116"/>
-      <c r="B18" s="119" t="s">
+      <c r="A18" s="118"/>
+      <c r="B18" s="121" t="s">
         <v>187</v>
       </c>
       <c r="C18" s="81"/>
-      <c r="D18" s="120" t="s">
+      <c r="D18" s="122" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="119" t="s">
+      <c r="E18" s="121" t="s">
         <v>188</v>
       </c>
       <c r="F18" s="81"/>
@@ -15798,17 +15906,17 @@
       <c r="L18" s="81"/>
       <c r="M18" s="81"/>
       <c r="N18" s="87"/>
-      <c r="O18" s="115"/>
+      <c r="O18" s="117"/>
       <c r="P18" s="81"/>
       <c r="Q18" s="81"/>
     </row>
     <row r="19" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="116"/>
+      <c r="A19" s="118"/>
       <c r="B19" s="81" t="s">
         <v>189</v>
       </c>
       <c r="C19" s="81"/>
-      <c r="D19" s="120" t="s">
+      <c r="D19" s="122" t="s">
         <v>70</v>
       </c>
       <c r="E19" s="81" t="s">
@@ -15822,31 +15930,31 @@
       <c r="L19" s="81"/>
       <c r="M19" s="81"/>
       <c r="N19" s="87"/>
-      <c r="O19" s="115"/>
+      <c r="O19" s="117"/>
       <c r="P19" s="81"/>
       <c r="Q19" s="81"/>
     </row>
     <row r="20" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="116"/>
+      <c r="A20" s="118"/>
       <c r="B20" s="81"/>
-      <c r="C20" s="121"/>
+      <c r="C20" s="123"/>
       <c r="D20" s="81"/>
       <c r="E20" s="108"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="123"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="124"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="126"/>
       <c r="L20" s="81"/>
       <c r="M20" s="81"/>
       <c r="N20" s="87"/>
-      <c r="O20" s="115"/>
+      <c r="O20" s="117"/>
       <c r="P20" s="81"/>
       <c r="Q20" s="81"/>
     </row>
     <row r="21" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="116"/>
+      <c r="A21" s="118"/>
       <c r="B21" s="81"/>
       <c r="C21" s="81"/>
       <c r="D21" s="81"/>
@@ -15859,12 +15967,12 @@
       <c r="L21" s="81"/>
       <c r="M21" s="81"/>
       <c r="N21" s="87"/>
-      <c r="O21" s="115"/>
+      <c r="O21" s="117"/>
       <c r="P21" s="81"/>
       <c r="Q21" s="81"/>
     </row>
     <row r="22" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="112"/>
+      <c r="A22" s="114"/>
       <c r="B22" s="81"/>
       <c r="C22" s="81"/>
       <c r="D22" s="81"/>
@@ -15877,7 +15985,7 @@
       <c r="L22" s="81"/>
       <c r="M22" s="81"/>
       <c r="N22" s="87"/>
-      <c r="O22" s="115"/>
+      <c r="O22" s="117"/>
       <c r="P22" s="81"/>
       <c r="Q22" s="81"/>
     </row>
@@ -15892,10 +16000,10 @@
       <c r="H23" s="84"/>
       <c r="I23" s="86"/>
       <c r="J23" s="86"/>
-      <c r="L23" s="125"/>
+      <c r="L23" s="127"/>
       <c r="M23" s="88"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="127"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="129"/>
       <c r="P23" s="88"/>
       <c r="Q23" s="88"/>
     </row>
@@ -15910,10 +16018,10 @@
       <c r="H24" s="84"/>
       <c r="I24" s="86"/>
       <c r="J24" s="86"/>
-      <c r="L24" s="125"/>
+      <c r="L24" s="127"/>
       <c r="M24" s="88"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="127"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="129"/>
       <c r="P24" s="88"/>
       <c r="Q24" s="88"/>
     </row>
@@ -15928,10 +16036,10 @@
       <c r="H25" s="84"/>
       <c r="I25" s="86"/>
       <c r="J25" s="86"/>
-      <c r="L25" s="125"/>
+      <c r="L25" s="127"/>
       <c r="M25" s="88"/>
-      <c r="N25" s="126"/>
-      <c r="O25" s="127"/>
+      <c r="N25" s="128"/>
+      <c r="O25" s="129"/>
       <c r="P25" s="88"/>
       <c r="Q25" s="88"/>
     </row>
@@ -15946,10 +16054,10 @@
       <c r="H26" s="84"/>
       <c r="I26" s="86"/>
       <c r="J26" s="86"/>
-      <c r="L26" s="125"/>
+      <c r="L26" s="127"/>
       <c r="M26" s="88"/>
-      <c r="N26" s="126"/>
-      <c r="O26" s="127"/>
+      <c r="N26" s="128"/>
+      <c r="O26" s="129"/>
       <c r="P26" s="88"/>
       <c r="Q26" s="88"/>
     </row>
@@ -15958,16 +16066,16 @@
       <c r="B27" s="81"/>
       <c r="C27" s="81"/>
       <c r="D27" s="81"/>
-      <c r="E27" s="128"/>
+      <c r="E27" s="130"/>
       <c r="F27" s="83"/>
       <c r="G27" s="83"/>
       <c r="H27" s="84"/>
       <c r="I27" s="86"/>
       <c r="J27" s="86"/>
-      <c r="L27" s="125"/>
+      <c r="L27" s="127"/>
       <c r="M27" s="88"/>
-      <c r="N27" s="126"/>
-      <c r="O27" s="127"/>
+      <c r="N27" s="128"/>
+      <c r="O27" s="129"/>
       <c r="P27" s="88"/>
       <c r="Q27" s="88"/>
     </row>
@@ -15976,16 +16084,16 @@
       <c r="B28" s="81"/>
       <c r="C28" s="81"/>
       <c r="D28" s="81"/>
-      <c r="E28" s="128"/>
+      <c r="E28" s="130"/>
       <c r="F28" s="83"/>
       <c r="G28" s="83"/>
       <c r="H28" s="84"/>
       <c r="I28" s="86"/>
       <c r="J28" s="86"/>
-      <c r="L28" s="125"/>
+      <c r="L28" s="127"/>
       <c r="M28" s="88"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="127"/>
+      <c r="N28" s="128"/>
+      <c r="O28" s="129"/>
       <c r="P28" s="88"/>
       <c r="Q28" s="88"/>
     </row>
@@ -15994,16 +16102,16 @@
       <c r="B29" s="81"/>
       <c r="C29" s="81"/>
       <c r="D29" s="81"/>
-      <c r="E29" s="128"/>
+      <c r="E29" s="130"/>
       <c r="F29" s="83"/>
       <c r="G29" s="83"/>
       <c r="H29" s="84"/>
       <c r="I29" s="86"/>
       <c r="J29" s="86"/>
-      <c r="L29" s="125"/>
+      <c r="L29" s="127"/>
       <c r="M29" s="88"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="127"/>
+      <c r="N29" s="128"/>
+      <c r="O29" s="129"/>
       <c r="P29" s="88"/>
       <c r="Q29" s="88"/>
     </row>
@@ -16012,16 +16120,16 @@
       <c r="B30" s="81"/>
       <c r="C30" s="81"/>
       <c r="D30" s="81"/>
-      <c r="E30" s="128"/>
+      <c r="E30" s="130"/>
       <c r="F30" s="83"/>
       <c r="G30" s="83"/>
       <c r="H30" s="84"/>
       <c r="I30" s="86"/>
       <c r="J30" s="86"/>
-      <c r="L30" s="125"/>
+      <c r="L30" s="127"/>
       <c r="M30" s="88"/>
-      <c r="N30" s="126"/>
-      <c r="O30" s="127"/>
+      <c r="N30" s="128"/>
+      <c r="O30" s="129"/>
       <c r="P30" s="88"/>
       <c r="Q30" s="88"/>
     </row>
@@ -16030,16 +16138,16 @@
       <c r="B31" s="81"/>
       <c r="C31" s="81"/>
       <c r="D31" s="81"/>
-      <c r="E31" s="128"/>
+      <c r="E31" s="130"/>
       <c r="F31" s="83"/>
       <c r="G31" s="83"/>
       <c r="H31" s="84"/>
       <c r="I31" s="86"/>
       <c r="J31" s="86"/>
-      <c r="L31" s="125"/>
+      <c r="L31" s="127"/>
       <c r="M31" s="88"/>
-      <c r="N31" s="126"/>
-      <c r="O31" s="127"/>
+      <c r="N31" s="128"/>
+      <c r="O31" s="129"/>
       <c r="P31" s="88"/>
       <c r="Q31" s="88"/>
     </row>
@@ -16048,16 +16156,16 @@
       <c r="B32" s="81"/>
       <c r="C32" s="81"/>
       <c r="D32" s="81"/>
-      <c r="E32" s="128"/>
+      <c r="E32" s="130"/>
       <c r="F32" s="83"/>
       <c r="G32" s="83"/>
       <c r="H32" s="84"/>
       <c r="I32" s="86"/>
       <c r="J32" s="86"/>
-      <c r="L32" s="125"/>
+      <c r="L32" s="127"/>
       <c r="M32" s="88"/>
-      <c r="N32" s="126"/>
-      <c r="O32" s="127"/>
+      <c r="N32" s="128"/>
+      <c r="O32" s="129"/>
       <c r="P32" s="88"/>
       <c r="Q32" s="88"/>
     </row>
@@ -16168,7 +16276,7 @@
       <c r="N37" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="O37" s="115"/>
+      <c r="O37" s="117"/>
       <c r="P37" s="45"/>
       <c r="Q37" s="40"/>
     </row>
@@ -16182,7 +16290,7 @@
       <c r="N38" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="O38" s="115"/>
+      <c r="O38" s="117"/>
       <c r="P38" s="45" t="s">
         <v>113</v>
       </c>
@@ -16198,7 +16306,7 @@
       <c r="N39" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="O39" s="115"/>
+      <c r="O39" s="117"/>
       <c r="P39" s="45" t="s">
         <v>117</v>
       </c>
@@ -16210,7 +16318,7 @@
       <c r="N40" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="O40" s="115"/>
+      <c r="O40" s="117"/>
       <c r="P40" s="103"/>
       <c r="Q40" s="40"/>
     </row>
@@ -16508,7 +16616,7 @@
       </c>
     </row>
     <row r="6" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A6" s="112"/>
+      <c r="A6" s="114"/>
       <c r="B6" s="81" t="s">
         <v>193</v>
       </c>
@@ -16521,18 +16629,18 @@
       </c>
       <c r="F6" s="81"/>
       <c r="G6" s="81"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
       <c r="L6" s="81"/>
       <c r="M6" s="81"/>
       <c r="N6" s="87"/>
-      <c r="O6" s="115"/>
+      <c r="O6" s="117"/>
       <c r="P6" s="81"/>
       <c r="Q6" s="81"/>
     </row>
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A7" s="116"/>
+      <c r="A7" s="118"/>
       <c r="B7" s="81" t="s">
         <v>194</v>
       </c>
@@ -16545,18 +16653,18 @@
       </c>
       <c r="F7" s="81"/>
       <c r="G7" s="81"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="114"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="116"/>
       <c r="L7" s="81"/>
       <c r="M7" s="81"/>
       <c r="N7" s="87"/>
-      <c r="O7" s="115"/>
+      <c r="O7" s="117"/>
       <c r="P7" s="81"/>
       <c r="Q7" s="81"/>
     </row>
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A8" s="116"/>
+      <c r="A8" s="118"/>
       <c r="B8" s="81" t="s">
         <v>195</v>
       </c>
@@ -16569,18 +16677,18 @@
       </c>
       <c r="F8" s="81"/>
       <c r="G8" s="81"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
       <c r="L8" s="81"/>
       <c r="M8" s="81"/>
       <c r="N8" s="87"/>
-      <c r="O8" s="115"/>
+      <c r="O8" s="117"/>
       <c r="P8" s="81"/>
       <c r="Q8" s="81"/>
     </row>
     <row r="9" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A9" s="112"/>
+      <c r="A9" s="114"/>
       <c r="B9" s="81" t="s">
         <v>197</v>
       </c>
@@ -16595,16 +16703,16 @@
       <c r="G9" s="81"/>
       <c r="H9" s="86"/>
       <c r="I9" s="86"/>
-      <c r="J9" s="117"/>
+      <c r="J9" s="119"/>
       <c r="L9" s="81"/>
       <c r="M9" s="81"/>
       <c r="N9" s="87"/>
-      <c r="O9" s="115"/>
+      <c r="O9" s="117"/>
       <c r="P9" s="81"/>
       <c r="Q9" s="81"/>
     </row>
     <row r="10" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A10" s="116"/>
+      <c r="A10" s="118"/>
       <c r="B10" s="81" t="s">
         <v>199</v>
       </c>
@@ -16619,16 +16727,16 @@
       <c r="G10" s="81"/>
       <c r="H10" s="86"/>
       <c r="I10" s="86"/>
-      <c r="J10" s="117"/>
+      <c r="J10" s="119"/>
       <c r="L10" s="81"/>
       <c r="M10" s="81"/>
       <c r="N10" s="87"/>
-      <c r="O10" s="115"/>
+      <c r="O10" s="117"/>
       <c r="P10" s="81"/>
       <c r="Q10" s="81"/>
     </row>
     <row r="11" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A11" s="116"/>
+      <c r="A11" s="118"/>
       <c r="B11" s="81" t="s">
         <v>201</v>
       </c>
@@ -16641,18 +16749,18 @@
       </c>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
       <c r="L11" s="81"/>
       <c r="M11" s="81"/>
       <c r="N11" s="87"/>
-      <c r="O11" s="115"/>
+      <c r="O11" s="117"/>
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
     </row>
     <row r="12" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A12" s="116"/>
+      <c r="A12" s="118"/>
       <c r="B12" s="81" t="s">
         <v>203</v>
       </c>
@@ -16671,12 +16779,12 @@
       <c r="L12" s="81"/>
       <c r="M12" s="81"/>
       <c r="N12" s="87"/>
-      <c r="O12" s="115"/>
+      <c r="O12" s="117"/>
       <c r="P12" s="81"/>
       <c r="Q12" s="81"/>
     </row>
     <row r="13" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A13" s="112"/>
+      <c r="A13" s="114"/>
       <c r="B13" s="81" t="s">
         <v>205</v>
       </c>
@@ -16695,12 +16803,12 @@
       <c r="L13" s="81"/>
       <c r="M13" s="81"/>
       <c r="N13" s="87"/>
-      <c r="O13" s="115"/>
+      <c r="O13" s="117"/>
       <c r="P13" s="81"/>
       <c r="Q13" s="81"/>
     </row>
     <row r="14" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A14" s="112"/>
+      <c r="A14" s="114"/>
       <c r="B14" s="81" t="s">
         <v>206</v>
       </c>
@@ -16715,16 +16823,16 @@
       <c r="G14" s="81"/>
       <c r="H14" s="84"/>
       <c r="I14" s="86"/>
-      <c r="J14" s="117"/>
+      <c r="J14" s="119"/>
       <c r="L14" s="81"/>
       <c r="M14" s="81"/>
       <c r="N14" s="87"/>
-      <c r="O14" s="115"/>
+      <c r="O14" s="117"/>
       <c r="P14" s="81"/>
       <c r="Q14" s="81"/>
     </row>
     <row r="15" s="6" customFormat="1" ht="13.8" customHeight="1" spans="1:17">
-      <c r="A15" s="116"/>
+      <c r="A15" s="118"/>
       <c r="B15" s="81" t="s">
         <v>208</v>
       </c>
@@ -16739,16 +16847,16 @@
       <c r="G15" s="81"/>
       <c r="H15" s="84"/>
       <c r="I15" s="86"/>
-      <c r="J15" s="117"/>
+      <c r="J15" s="119"/>
       <c r="L15" s="81"/>
       <c r="M15" s="81"/>
       <c r="N15" s="87"/>
-      <c r="O15" s="115"/>
+      <c r="O15" s="117"/>
       <c r="P15" s="81"/>
       <c r="Q15" s="81"/>
     </row>
     <row r="16" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A16" s="116"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="81"/>
       <c r="C16" s="81"/>
       <c r="D16" s="81"/>
@@ -16757,19 +16865,19 @@
       <c r="G16" s="81"/>
       <c r="H16" s="84"/>
       <c r="I16" s="86"/>
-      <c r="J16" s="117"/>
+      <c r="J16" s="119"/>
       <c r="L16" s="81"/>
       <c r="M16" s="81"/>
       <c r="N16" s="87"/>
-      <c r="O16" s="115"/>
+      <c r="O16" s="117"/>
       <c r="P16" s="81"/>
       <c r="Q16" s="81" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A17" s="116"/>
-      <c r="B17" s="118"/>
+      <c r="A17" s="118"/>
+      <c r="B17" s="120"/>
       <c r="C17" s="81"/>
       <c r="D17" s="81"/>
       <c r="E17" s="81"/>
@@ -16781,16 +16889,16 @@
       <c r="L17" s="81"/>
       <c r="M17" s="81"/>
       <c r="N17" s="87"/>
-      <c r="O17" s="115"/>
+      <c r="O17" s="117"/>
       <c r="P17" s="81"/>
       <c r="Q17" s="81"/>
     </row>
     <row r="18" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A18" s="116"/>
-      <c r="B18" s="119"/>
+      <c r="A18" s="118"/>
+      <c r="B18" s="121"/>
       <c r="C18" s="81"/>
-      <c r="D18" s="120"/>
-      <c r="E18" s="119"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="121"/>
       <c r="F18" s="81"/>
       <c r="G18" s="81"/>
       <c r="H18" s="84"/>
@@ -16799,15 +16907,15 @@
       <c r="L18" s="81"/>
       <c r="M18" s="81"/>
       <c r="N18" s="87"/>
-      <c r="O18" s="115"/>
+      <c r="O18" s="117"/>
       <c r="P18" s="81"/>
       <c r="Q18" s="81"/>
     </row>
     <row r="19" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A19" s="116"/>
+      <c r="A19" s="118"/>
       <c r="B19" s="81"/>
       <c r="C19" s="81"/>
-      <c r="D19" s="120"/>
+      <c r="D19" s="122"/>
       <c r="E19" s="81"/>
       <c r="F19" s="81"/>
       <c r="G19" s="81"/>
@@ -16817,31 +16925,31 @@
       <c r="L19" s="81"/>
       <c r="M19" s="81"/>
       <c r="N19" s="87"/>
-      <c r="O19" s="115"/>
+      <c r="O19" s="117"/>
       <c r="P19" s="81"/>
       <c r="Q19" s="81"/>
     </row>
     <row r="20" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A20" s="116"/>
+      <c r="A20" s="118"/>
       <c r="B20" s="81"/>
-      <c r="C20" s="121"/>
+      <c r="C20" s="123"/>
       <c r="D20" s="81"/>
       <c r="E20" s="108"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="123"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="124"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="126"/>
       <c r="L20" s="81"/>
       <c r="M20" s="81"/>
       <c r="N20" s="87"/>
-      <c r="O20" s="115"/>
+      <c r="O20" s="117"/>
       <c r="P20" s="81"/>
       <c r="Q20" s="81"/>
     </row>
     <row r="21" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A21" s="116"/>
+      <c r="A21" s="118"/>
       <c r="B21" s="81"/>
       <c r="C21" s="81"/>
       <c r="D21" s="81"/>
@@ -16854,12 +16962,12 @@
       <c r="L21" s="81"/>
       <c r="M21" s="81"/>
       <c r="N21" s="87"/>
-      <c r="O21" s="115"/>
+      <c r="O21" s="117"/>
       <c r="P21" s="81"/>
       <c r="Q21" s="81"/>
     </row>
     <row r="22" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
-      <c r="A22" s="112"/>
+      <c r="A22" s="114"/>
       <c r="B22" s="81"/>
       <c r="C22" s="81"/>
       <c r="D22" s="81"/>
@@ -16872,7 +16980,7 @@
       <c r="L22" s="81"/>
       <c r="M22" s="81"/>
       <c r="N22" s="87"/>
-      <c r="O22" s="115"/>
+      <c r="O22" s="117"/>
       <c r="P22" s="81"/>
       <c r="Q22" s="81"/>
     </row>
@@ -16887,10 +16995,10 @@
       <c r="H23" s="84"/>
       <c r="I23" s="86"/>
       <c r="J23" s="86"/>
-      <c r="L23" s="125"/>
+      <c r="L23" s="127"/>
       <c r="M23" s="88"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="127"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="129"/>
       <c r="P23" s="88"/>
       <c r="Q23" s="88"/>
     </row>
@@ -16905,10 +17013,10 @@
       <c r="H24" s="84"/>
       <c r="I24" s="86"/>
       <c r="J24" s="86"/>
-      <c r="L24" s="125"/>
+      <c r="L24" s="127"/>
       <c r="M24" s="88"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="127"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="129"/>
       <c r="P24" s="88"/>
       <c r="Q24" s="88"/>
     </row>
@@ -16923,10 +17031,10 @@
       <c r="H25" s="84"/>
       <c r="I25" s="86"/>
       <c r="J25" s="86"/>
-      <c r="L25" s="125"/>
+      <c r="L25" s="127"/>
       <c r="M25" s="88"/>
-      <c r="N25" s="126"/>
-      <c r="O25" s="127"/>
+      <c r="N25" s="128"/>
+      <c r="O25" s="129"/>
       <c r="P25" s="88"/>
       <c r="Q25" s="88"/>
     </row>
@@ -16941,10 +17049,10 @@
       <c r="H26" s="84"/>
       <c r="I26" s="86"/>
       <c r="J26" s="86"/>
-      <c r="L26" s="125"/>
+      <c r="L26" s="127"/>
       <c r="M26" s="88"/>
-      <c r="N26" s="126"/>
-      <c r="O26" s="127"/>
+      <c r="N26" s="128"/>
+      <c r="O26" s="129"/>
       <c r="P26" s="88"/>
       <c r="Q26" s="88"/>
     </row>
@@ -16953,16 +17061,16 @@
       <c r="B27" s="81"/>
       <c r="C27" s="81"/>
       <c r="D27" s="81"/>
-      <c r="E27" s="128"/>
+      <c r="E27" s="130"/>
       <c r="F27" s="83"/>
       <c r="G27" s="83"/>
       <c r="H27" s="84"/>
       <c r="I27" s="86"/>
       <c r="J27" s="86"/>
-      <c r="L27" s="125"/>
+      <c r="L27" s="127"/>
       <c r="M27" s="88"/>
-      <c r="N27" s="126"/>
-      <c r="O27" s="127"/>
+      <c r="N27" s="128"/>
+      <c r="O27" s="129"/>
       <c r="P27" s="88"/>
       <c r="Q27" s="88"/>
     </row>
@@ -16971,16 +17079,16 @@
       <c r="B28" s="81"/>
       <c r="C28" s="81"/>
       <c r="D28" s="81"/>
-      <c r="E28" s="128"/>
+      <c r="E28" s="130"/>
       <c r="F28" s="83"/>
       <c r="G28" s="83"/>
       <c r="H28" s="84"/>
       <c r="I28" s="86"/>
       <c r="J28" s="86"/>
-      <c r="L28" s="125"/>
+      <c r="L28" s="127"/>
       <c r="M28" s="88"/>
-      <c r="N28" s="126"/>
-      <c r="O28" s="127"/>
+      <c r="N28" s="128"/>
+      <c r="O28" s="129"/>
       <c r="P28" s="88"/>
       <c r="Q28" s="88"/>
     </row>
@@ -16989,16 +17097,16 @@
       <c r="B29" s="81"/>
       <c r="C29" s="81"/>
       <c r="D29" s="81"/>
-      <c r="E29" s="128"/>
+      <c r="E29" s="130"/>
       <c r="F29" s="83"/>
       <c r="G29" s="83"/>
       <c r="H29" s="84"/>
       <c r="I29" s="86"/>
       <c r="J29" s="86"/>
-      <c r="L29" s="125"/>
+      <c r="L29" s="127"/>
       <c r="M29" s="88"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="127"/>
+      <c r="N29" s="128"/>
+      <c r="O29" s="129"/>
       <c r="P29" s="88"/>
       <c r="Q29" s="88"/>
     </row>
@@ -17007,16 +17115,16 @@
       <c r="B30" s="81"/>
       <c r="C30" s="81"/>
       <c r="D30" s="81"/>
-      <c r="E30" s="128"/>
+      <c r="E30" s="130"/>
       <c r="F30" s="83"/>
       <c r="G30" s="83"/>
       <c r="H30" s="84"/>
       <c r="I30" s="86"/>
       <c r="J30" s="86"/>
-      <c r="L30" s="125"/>
+      <c r="L30" s="127"/>
       <c r="M30" s="88"/>
-      <c r="N30" s="126"/>
-      <c r="O30" s="127"/>
+      <c r="N30" s="128"/>
+      <c r="O30" s="129"/>
       <c r="P30" s="88"/>
       <c r="Q30" s="88"/>
     </row>
@@ -17025,16 +17133,16 @@
       <c r="B31" s="81"/>
       <c r="C31" s="81"/>
       <c r="D31" s="81"/>
-      <c r="E31" s="128"/>
+      <c r="E31" s="130"/>
       <c r="F31" s="83"/>
       <c r="G31" s="83"/>
       <c r="H31" s="84"/>
       <c r="I31" s="86"/>
       <c r="J31" s="86"/>
-      <c r="L31" s="125"/>
+      <c r="L31" s="127"/>
       <c r="M31" s="88"/>
-      <c r="N31" s="126"/>
-      <c r="O31" s="127"/>
+      <c r="N31" s="128"/>
+      <c r="O31" s="129"/>
       <c r="P31" s="88"/>
       <c r="Q31" s="88"/>
     </row>
@@ -17043,16 +17151,16 @@
       <c r="B32" s="81"/>
       <c r="C32" s="81"/>
       <c r="D32" s="81"/>
-      <c r="E32" s="128"/>
+      <c r="E32" s="130"/>
       <c r="F32" s="83"/>
       <c r="G32" s="83"/>
       <c r="H32" s="84"/>
       <c r="I32" s="86"/>
       <c r="J32" s="86"/>
-      <c r="L32" s="125"/>
+      <c r="L32" s="127"/>
       <c r="M32" s="88"/>
-      <c r="N32" s="126"/>
-      <c r="O32" s="127"/>
+      <c r="N32" s="128"/>
+      <c r="O32" s="129"/>
       <c r="P32" s="88"/>
       <c r="Q32" s="88"/>
     </row>
@@ -17163,7 +17271,7 @@
       <c r="N37" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="O37" s="115"/>
+      <c r="O37" s="117"/>
       <c r="P37" s="45"/>
       <c r="Q37" s="40"/>
     </row>
@@ -17177,7 +17285,7 @@
       <c r="N38" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="O38" s="115"/>
+      <c r="O38" s="117"/>
       <c r="P38" s="45" t="s">
         <v>113</v>
       </c>
@@ -17193,7 +17301,7 @@
       <c r="N39" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="O39" s="115"/>
+      <c r="O39" s="117"/>
       <c r="P39" s="45" t="s">
         <v>117</v>
       </c>
@@ -17205,7 +17313,7 @@
       <c r="N40" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="O40" s="115"/>
+      <c r="O40" s="117"/>
       <c r="P40" s="103"/>
       <c r="Q40" s="40"/>
     </row>

--- a/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
+++ b/data_assets/mapping/dwd_to_dws/DWS汇总层数据模型_CRM_ V1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="5" activeTab="9"/>
+    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="753" firstSheet="5" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="修订记录" sheetId="1" r:id="rId1"/>
@@ -17,17 +17,18 @@
     <sheet name="客户转介绍" sheetId="8" r:id="rId8"/>
     <sheet name="转介绍提醒表" sheetId="9" r:id="rId9"/>
     <sheet name="客户资产负债基数表" sheetId="10" r:id="rId10"/>
-    <sheet name="客户资产负债表" sheetId="11" r:id="rId11"/>
-    <sheet name="客户等级信息表" sheetId="12" r:id="rId12"/>
-    <sheet name="零售潜在客户信息表" sheetId="13" r:id="rId13"/>
-    <sheet name="逻辑模型维度描述" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet name="客户资产负债表历史表" sheetId="15" r:id="rId11"/>
+    <sheet name="客户资产负债表" sheetId="11" r:id="rId12"/>
+    <sheet name="客户等级信息表" sheetId="12" r:id="rId13"/>
+    <sheet name="零售潜在客户信息表" sheetId="13" r:id="rId14"/>
+    <sheet name="逻辑模型维度描述" sheetId="14" state="hidden" r:id="rId15"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
     <externalReference r:id="rId18"/>
     <externalReference r:id="rId19"/>
+    <externalReference r:id="rId20"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">实体清单!$B$1:$G$8</definedName>
@@ -53,17 +54,6 @@
     <definedName name="_Toc205004289" localSheetId="9">#REF!</definedName>
     <definedName name="_Toc275247984" localSheetId="9">#REF!</definedName>
     <definedName name="Basel" localSheetId="9">[2]Parameters!$C$32:$C$33</definedName>
-    <definedName name="Database" localSheetId="10" hidden="1">#REF!</definedName>
-    <definedName name="_Toc205004290" localSheetId="10">#REF!</definedName>
-    <definedName name="常用数据标准" localSheetId="10">#REF!</definedName>
-    <definedName name="_Toc205004288" localSheetId="10">#REF!</definedName>
-    <definedName name="_Toc256075879" localSheetId="10">#REF!</definedName>
-    <definedName name="YesNoBasel2" localSheetId="10">[3]Parameters!#REF!</definedName>
-    <definedName name="area" localSheetId="10">[1]建议意见清单!$A$1:$F$21</definedName>
-    <definedName name="_Toc205004291" localSheetId="10">#REF!</definedName>
-    <definedName name="_Toc205004289" localSheetId="10">#REF!</definedName>
-    <definedName name="_Toc275247984" localSheetId="10">#REF!</definedName>
-    <definedName name="Basel" localSheetId="10">[2]Parameters!$C$32:$C$33</definedName>
     <definedName name="Database" localSheetId="11" hidden="1">#REF!</definedName>
     <definedName name="_Toc205004290" localSheetId="11">#REF!</definedName>
     <definedName name="常用数据标准" localSheetId="11">#REF!</definedName>
@@ -80,12 +70,34 @@
     <definedName name="常用数据标准" localSheetId="12">#REF!</definedName>
     <definedName name="_Toc205004288" localSheetId="12">#REF!</definedName>
     <definedName name="_Toc256075879" localSheetId="12">#REF!</definedName>
-    <definedName name="YesNoBasel2" localSheetId="12">[5]Parameters!#REF!</definedName>
+    <definedName name="YesNoBasel2" localSheetId="12">[3]Parameters!#REF!</definedName>
     <definedName name="area" localSheetId="12">[1]建议意见清单!$A$1:$F$21</definedName>
     <definedName name="_Toc205004291" localSheetId="12">#REF!</definedName>
     <definedName name="_Toc205004289" localSheetId="12">#REF!</definedName>
     <definedName name="_Toc275247984" localSheetId="12">#REF!</definedName>
-    <definedName name="Basel" localSheetId="12">[4]Parameters!$C$32:$C$33</definedName>
+    <definedName name="Basel" localSheetId="12">[2]Parameters!$C$32:$C$33</definedName>
+    <definedName name="Database" localSheetId="13" hidden="1">#REF!</definedName>
+    <definedName name="_Toc205004290" localSheetId="13">#REF!</definedName>
+    <definedName name="常用数据标准" localSheetId="13">#REF!</definedName>
+    <definedName name="_Toc205004288" localSheetId="13">#REF!</definedName>
+    <definedName name="_Toc256075879" localSheetId="13">#REF!</definedName>
+    <definedName name="YesNoBasel2" localSheetId="13">[5]Parameters!#REF!</definedName>
+    <definedName name="area" localSheetId="13">[1]建议意见清单!$A$1:$F$21</definedName>
+    <definedName name="_Toc205004291" localSheetId="13">#REF!</definedName>
+    <definedName name="_Toc205004289" localSheetId="13">#REF!</definedName>
+    <definedName name="_Toc275247984" localSheetId="13">#REF!</definedName>
+    <definedName name="Basel" localSheetId="13">[4]Parameters!$C$32:$C$33</definedName>
+    <definedName name="Database" localSheetId="10" hidden="1">#REF!</definedName>
+    <definedName name="_Toc205004290" localSheetId="10">#REF!</definedName>
+    <definedName name="常用数据标准" localSheetId="10">#REF!</definedName>
+    <definedName name="_Toc205004288" localSheetId="10">#REF!</definedName>
+    <definedName name="_Toc256075879" localSheetId="10">#REF!</definedName>
+    <definedName name="YesNoBasel2" localSheetId="10">[3]Parameters!#REF!</definedName>
+    <definedName name="area" localSheetId="10">[1]建议意见清单!$A$1:$F$21</definedName>
+    <definedName name="_Toc205004291" localSheetId="10">#REF!</definedName>
+    <definedName name="_Toc205004289" localSheetId="10">#REF!</definedName>
+    <definedName name="_Toc275247984" localSheetId="10">#REF!</definedName>
+    <definedName name="Basel" localSheetId="10">[2]Parameters!$C$32:$C$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -105,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="444">
   <si>
     <t>文档修订记录</t>
   </si>
@@ -840,100 +852,106 @@
     <t>投保单号或者借据号</t>
   </si>
   <si>
+    <t>客户资产负债表历史表</t>
+  </si>
+  <si>
+    <t>DWS_CUST_ASSE_LIAB_HIS</t>
+  </si>
+  <si>
+    <t>ORG_ID_LOAN</t>
+  </si>
+  <si>
+    <t>信贷归属机构</t>
+  </si>
+  <si>
+    <t>BAL_TYPE</t>
+  </si>
+  <si>
+    <t>类型1-余额2-月日均3-季日均4-年日均</t>
+  </si>
+  <si>
+    <t>AUM_BAL</t>
+  </si>
+  <si>
+    <t>AUM余额</t>
+  </si>
+  <si>
+    <t>DEPO_BAL</t>
+  </si>
+  <si>
+    <t>存款余额</t>
+  </si>
+  <si>
+    <t>DEPO_CURNT_DEPO_BAL</t>
+  </si>
+  <si>
+    <t>活期余额</t>
+  </si>
+  <si>
+    <t>FIXD_DEPO_BAL</t>
+  </si>
+  <si>
+    <t>普通定期余额</t>
+  </si>
+  <si>
+    <t>LEHUI_BAL</t>
+  </si>
+  <si>
+    <t>乐惠存产品余额</t>
+  </si>
+  <si>
+    <t>LARGEDP_BAL</t>
+  </si>
+  <si>
+    <t>大额存单余额</t>
+  </si>
+  <si>
+    <t>FIN_BAL</t>
+  </si>
+  <si>
+    <t>理财余额</t>
+  </si>
+  <si>
+    <t>CLOSE_AGEN_FIN_BAL</t>
+  </si>
+  <si>
+    <t>代销封闭式理财余额</t>
+  </si>
+  <si>
+    <t>OPEN_AGEN_FIN_BAL</t>
+  </si>
+  <si>
+    <t>代销开放式理财余额</t>
+  </si>
+  <si>
+    <t>CLOSE_SELF_FIN_BAL</t>
+  </si>
+  <si>
+    <t>自营封闭式理财余额</t>
+  </si>
+  <si>
+    <t>OPEN_SELF_FIN_BAL</t>
+  </si>
+  <si>
+    <t>自营开放式理财余额</t>
+  </si>
+  <si>
+    <t>INSUR_BAL</t>
+  </si>
+  <si>
+    <t>保险余额</t>
+  </si>
+  <si>
+    <t>LOAN_BAL</t>
+  </si>
+  <si>
+    <t>贷款余额</t>
+  </si>
+  <si>
     <t>客户资产负债表</t>
   </si>
   <si>
     <t>DWS_CUST_ASSE_LIAB</t>
-  </si>
-  <si>
-    <t>ORG_ID_LOAN</t>
-  </si>
-  <si>
-    <t>信贷归属机构</t>
-  </si>
-  <si>
-    <t>BAL_TYPE</t>
-  </si>
-  <si>
-    <t>类型1-余额2-月日均3-季日均4-年日均</t>
-  </si>
-  <si>
-    <t>AUM_BAL</t>
-  </si>
-  <si>
-    <t>AUM余额</t>
-  </si>
-  <si>
-    <t>DEPO_BAL</t>
-  </si>
-  <si>
-    <t>定期余额</t>
-  </si>
-  <si>
-    <t>DEPO_CURNT_DEPO_BAL</t>
-  </si>
-  <si>
-    <t>活期余额</t>
-  </si>
-  <si>
-    <t>FIXD_DEPO_BAL</t>
-  </si>
-  <si>
-    <t>普通定期余额</t>
-  </si>
-  <si>
-    <t>LEHUI_BAL</t>
-  </si>
-  <si>
-    <t>乐惠存产品余额</t>
-  </si>
-  <si>
-    <t>LARGEDP_BAL</t>
-  </si>
-  <si>
-    <t>大额存单余额</t>
-  </si>
-  <si>
-    <t>FIN_BAL</t>
-  </si>
-  <si>
-    <t>理财余额</t>
-  </si>
-  <si>
-    <t>CLOSE_AGEN_FIN_BAL</t>
-  </si>
-  <si>
-    <t>代销封闭式理财余额</t>
-  </si>
-  <si>
-    <t>OPEN_AGEN_FIN_BAL</t>
-  </si>
-  <si>
-    <t>代销开放式理财余额</t>
-  </si>
-  <si>
-    <t>CLOSE_SELF_FIN_BAL</t>
-  </si>
-  <si>
-    <t>自营封闭式理财余额</t>
-  </si>
-  <si>
-    <t>OPEN_SELF_FIN_BAL</t>
-  </si>
-  <si>
-    <t>自营开放式理财余额</t>
-  </si>
-  <si>
-    <t>INSUR_BAL</t>
-  </si>
-  <si>
-    <t>保险余额</t>
-  </si>
-  <si>
-    <t>LOAN_BAL</t>
-  </si>
-  <si>
-    <t>贷款余额</t>
   </si>
   <si>
     <t>客户等级信息表</t>
@@ -6102,7 +6120,7 @@
     <mergeCell ref="L40:Q40"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C21 C22 C23 C7:C8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:C8 C21:C23">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -6918,6 +6936,810 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:Q83"/>
+  <sheetFormatPr defaultColWidth="8.23148148148148" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.66666666666667" style="70" customWidth="1"/>
+    <col min="2" max="2" width="27.5462962962963" style="70" customWidth="1"/>
+    <col min="3" max="3" width="8.88888888888889" style="70" customWidth="1"/>
+    <col min="4" max="4" width="15.1851851851852" style="70" customWidth="1"/>
+    <col min="5" max="5" width="38.8888888888889" style="70" customWidth="1"/>
+    <col min="6" max="6" width="10.7685185185185" style="70" customWidth="1"/>
+    <col min="7" max="7" width="12.1018518518519" style="70" customWidth="1"/>
+    <col min="8" max="8" width="8.76851851851852" style="70" customWidth="1"/>
+    <col min="9" max="9" width="8.23148148148148" style="70" customWidth="1"/>
+    <col min="10" max="10" width="8.76851851851852" style="70" customWidth="1"/>
+    <col min="11" max="11" width="8.23148148148148" style="70" customWidth="1"/>
+    <col min="12" max="12" width="24.1851851851852" style="70" customWidth="1"/>
+    <col min="13" max="13" width="23" style="70" customWidth="1"/>
+    <col min="14" max="14" width="17.3611111111111" style="70" customWidth="1"/>
+    <col min="15" max="15" width="16.8796296296296" style="70" customWidth="1"/>
+    <col min="16" max="16" width="10.2685185185185" style="70" customWidth="1"/>
+    <col min="17" max="17" width="16.8148148148148" style="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
+      <c r="B1" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+    </row>
+    <row r="2" s="3" customFormat="1" ht="21" customHeight="1" spans="1:17">
+      <c r="B2" s="73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="74" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="75" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="30.6" customHeight="1" spans="1:17">
+      <c r="B3" s="11"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" s="3" customFormat="1" ht="17.55" customHeight="1" spans="1:17">
+      <c r="B4" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13"/>
+      <c r="L4" s="77" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="40"/>
+    </row>
+    <row r="5" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:17">
+      <c r="B5" s="78" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="78" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="78" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="78" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="79" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="P5" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A6" s="80"/>
+      <c r="B6" s="81" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="82"/>
+      <c r="D6" s="81" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="81" t="s">
+        <v>139</v>
+      </c>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="86"/>
+      <c r="L6" s="87"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="87"/>
+      <c r="P6" s="88"/>
+      <c r="Q6" s="88"/>
+    </row>
+    <row r="7" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A7" s="80"/>
+      <c r="B7" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="82"/>
+      <c r="D7" s="81" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="81" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="86"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="87"/>
+      <c r="P7" s="88"/>
+      <c r="Q7" s="88"/>
+    </row>
+    <row r="8" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A8" s="80"/>
+      <c r="B8" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="82"/>
+      <c r="D8" s="81" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="81" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="86"/>
+      <c r="L8" s="87"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="87"/>
+      <c r="O8" s="90"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="88"/>
+    </row>
+    <row r="9" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A9" s="80"/>
+      <c r="B9" s="81" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="82"/>
+      <c r="D9" s="81" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="81" t="s">
+        <v>245</v>
+      </c>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="84"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="86"/>
+      <c r="L9" s="87"/>
+      <c r="M9" s="81"/>
+      <c r="N9" s="87"/>
+      <c r="O9" s="87"/>
+      <c r="P9" s="88"/>
+      <c r="Q9" s="88"/>
+    </row>
+    <row r="10" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A10" s="80"/>
+      <c r="B10" s="81" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="82"/>
+      <c r="D10" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="81" t="s">
+        <v>247</v>
+      </c>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="86"/>
+      <c r="L10" s="87"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="87"/>
+      <c r="O10" s="87"/>
+      <c r="P10" s="88"/>
+      <c r="Q10" s="88"/>
+    </row>
+    <row r="11" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A11" s="80"/>
+      <c r="B11" s="81" t="s">
+        <v>248</v>
+      </c>
+      <c r="C11" s="82"/>
+      <c r="D11" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="81" t="s">
+        <v>249</v>
+      </c>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="86"/>
+      <c r="L11" s="87"/>
+      <c r="M11" s="81"/>
+      <c r="N11" s="87"/>
+      <c r="O11" s="87"/>
+      <c r="P11" s="88"/>
+      <c r="Q11" s="88"/>
+    </row>
+    <row r="12" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A12" s="80"/>
+      <c r="B12" s="81" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="82"/>
+      <c r="D12" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="81" t="s">
+        <v>251</v>
+      </c>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="86"/>
+      <c r="L12" s="87"/>
+      <c r="M12" s="81"/>
+      <c r="N12" s="87"/>
+      <c r="O12" s="90"/>
+      <c r="P12" s="88"/>
+      <c r="Q12" s="88"/>
+    </row>
+    <row r="13" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A13" s="80"/>
+      <c r="B13" s="81" t="s">
+        <v>252</v>
+      </c>
+      <c r="C13" s="82"/>
+      <c r="D13" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="81" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="86"/>
+      <c r="L13" s="87"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="87"/>
+      <c r="O13" s="90"/>
+      <c r="P13" s="88"/>
+      <c r="Q13" s="88"/>
+    </row>
+    <row r="14" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A14" s="80"/>
+      <c r="B14" s="81" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="82"/>
+      <c r="D14" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="81" t="s">
+        <v>255</v>
+      </c>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="86"/>
+      <c r="L14" s="87"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="87"/>
+      <c r="O14" s="90"/>
+      <c r="P14" s="88"/>
+      <c r="Q14" s="88"/>
+    </row>
+    <row r="15" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A15" s="80"/>
+      <c r="B15" s="81" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="82"/>
+      <c r="D15" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="81" t="s">
+        <v>257</v>
+      </c>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="85"/>
+      <c r="J15" s="86"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="87"/>
+      <c r="O15" s="87"/>
+      <c r="P15" s="88"/>
+      <c r="Q15" s="88"/>
+    </row>
+    <row r="16" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A16" s="80"/>
+      <c r="B16" s="81" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" s="82"/>
+      <c r="D16" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="81" t="s">
+        <v>259</v>
+      </c>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="85"/>
+      <c r="J16" s="86"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="87"/>
+      <c r="O16" s="90"/>
+      <c r="P16" s="88"/>
+      <c r="Q16" s="88"/>
+    </row>
+    <row r="17" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A17" s="80"/>
+      <c r="B17" s="81" t="s">
+        <v>260</v>
+      </c>
+      <c r="C17" s="82"/>
+      <c r="D17" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="81" t="s">
+        <v>261</v>
+      </c>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="86"/>
+      <c r="L17" s="87"/>
+      <c r="M17" s="81"/>
+      <c r="N17" s="87"/>
+      <c r="O17" s="87"/>
+      <c r="P17" s="88"/>
+      <c r="Q17" s="88"/>
+    </row>
+    <row r="18" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A18" s="80"/>
+      <c r="B18" s="91" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" s="82"/>
+      <c r="D18" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="81" t="s">
+        <v>263</v>
+      </c>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="86"/>
+    </row>
+    <row r="19" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A19" s="80"/>
+      <c r="B19" s="91" t="s">
+        <v>264</v>
+      </c>
+      <c r="C19" s="82"/>
+      <c r="D19" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="81" t="s">
+        <v>265</v>
+      </c>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="86"/>
+    </row>
+    <row r="20" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
+      <c r="A20" s="80"/>
+      <c r="B20" s="91" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" s="82"/>
+      <c r="D20" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="81" t="s">
+        <v>267</v>
+      </c>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="86"/>
+    </row>
+    <row r="21" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
+      <c r="A21" s="80"/>
+      <c r="B21" s="91" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="82"/>
+      <c r="D21" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="81" t="s">
+        <v>269</v>
+      </c>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="85"/>
+    </row>
+    <row r="22" s="3" customFormat="1" ht="17.4" customHeight="1" spans="1:17">
+      <c r="A22" s="80"/>
+      <c r="B22" s="91" t="s">
+        <v>270</v>
+      </c>
+      <c r="C22" s="82"/>
+      <c r="D22" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="81" t="s">
+        <v>271</v>
+      </c>
+      <c r="F22" s="85"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="85"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="85"/>
+      <c r="L22" s="87"/>
+      <c r="M22" s="81"/>
+      <c r="N22" s="87"/>
+      <c r="O22" s="90"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="88"/>
+    </row>
+    <row r="23" s="4" customFormat="1" ht="11.4" customHeight="1" spans="1:17">
+      <c r="B23" s="91" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" s="82"/>
+      <c r="D23" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="81" t="s">
+        <v>273</v>
+      </c>
+      <c r="F23" s="85"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="85"/>
+      <c r="L23" s="87"/>
+      <c r="M23" s="81"/>
+      <c r="N23" s="87"/>
+      <c r="O23" s="87"/>
+      <c r="P23" s="92"/>
+      <c r="Q23" s="93"/>
+    </row>
+    <row r="24" s="4" customFormat="1" ht="10.8" customHeight="1" spans="1:17">
+      <c r="B24" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="82"/>
+      <c r="D24" s="81" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="81" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="85"/>
+      <c r="G24" s="85"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="85"/>
+      <c r="L24" s="96"/>
+      <c r="M24" s="97"/>
+      <c r="N24" s="97"/>
+      <c r="O24" s="97"/>
+      <c r="P24" s="92"/>
+      <c r="Q24" s="93"/>
+    </row>
+    <row r="25" s="4" customFormat="1" ht="10.8" customHeight="1" spans="1:17">
+      <c r="B25" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="13"/>
+      <c r="L25" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="40"/>
+    </row>
+    <row r="26" ht="13.95" customHeight="1" spans="1:17">
+      <c r="B26" s="98" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="98" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="98" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="13"/>
+      <c r="L26" s="99" t="s">
+        <v>102</v>
+      </c>
+      <c r="M26" s="100" t="s">
+        <v>103</v>
+      </c>
+      <c r="N26" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O26" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="P26" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q26" s="40"/>
+    </row>
+    <row r="27" ht="13.95" customHeight="1" spans="1:17">
+      <c r="B27" s="101"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="13"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="40"/>
+    </row>
+    <row r="28" ht="13.95" customHeight="1" spans="1:17">
+      <c r="L28" s="35"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="40"/>
+    </row>
+    <row r="29" ht="13.95" customHeight="1" spans="1:17">
+      <c r="L29" s="35"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="40"/>
+    </row>
+    <row r="30" ht="13.95" customHeight="1" spans="1:17">
+      <c r="L30" s="35"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="103"/>
+      <c r="Q30" s="40"/>
+    </row>
+    <row r="31" ht="13.95" customHeight="1" spans="1:17">
+      <c r="L31" s="35"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="103"/>
+      <c r="Q31" s="40"/>
+    </row>
+    <row r="32" ht="13.95" customHeight="1" spans="1:17">
+      <c r="L32" s="104"/>
+      <c r="M32" s="93"/>
+      <c r="N32" s="93"/>
+      <c r="O32" s="93"/>
+      <c r="P32" s="103"/>
+      <c r="Q32" s="40"/>
+    </row>
+    <row r="33" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L33" s="104"/>
+      <c r="M33" s="93"/>
+      <c r="N33" s="93"/>
+      <c r="O33" s="93"/>
+      <c r="P33" s="103"/>
+      <c r="Q33" s="40"/>
+    </row>
+    <row r="34" ht="56" customHeight="1" spans="12:17">
+      <c r="L34" s="104"/>
+      <c r="M34" s="93"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="93"/>
+      <c r="P34" s="103"/>
+      <c r="Q34" s="40"/>
+    </row>
+    <row r="35" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L35" s="104"/>
+      <c r="M35" s="93"/>
+      <c r="N35" s="93"/>
+      <c r="O35" s="93"/>
+      <c r="P35" s="103"/>
+      <c r="Q35" s="40"/>
+    </row>
+    <row r="36" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L36" s="66"/>
+      <c r="M36" s="67"/>
+      <c r="N36" s="68"/>
+      <c r="O36" s="93"/>
+      <c r="P36" s="69"/>
+      <c r="Q36" s="40"/>
+    </row>
+    <row r="37" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L37" s="105" t="s">
+        <v>119</v>
+      </c>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="39"/>
+      <c r="Q37" s="40"/>
+    </row>
+    <row r="38" ht="13.95" customHeight="1" spans="12:17">
+      <c r="L38" s="106"/>
+      <c r="M38" s="39"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="39"/>
+      <c r="Q38" s="40"/>
+    </row>
+    <row r="39" ht="13.95" customHeight="1"/>
+    <row r="40" ht="13.95" customHeight="1"/>
+    <row r="41" ht="13.95" customHeight="1"/>
+    <row r="42" ht="13.95" customHeight="1"/>
+    <row r="43" ht="13.95" customHeight="1"/>
+    <row r="44" ht="13.95" customHeight="1"/>
+    <row r="45" ht="13.95" customHeight="1"/>
+    <row r="46" ht="13.95" customHeight="1"/>
+    <row r="47" ht="13.95" customHeight="1"/>
+    <row r="48" ht="13.95" customHeight="1"/>
+    <row r="49" ht="13.95" customHeight="1"/>
+    <row r="50" ht="13.95" customHeight="1"/>
+    <row r="51" ht="13.95" customHeight="1"/>
+    <row r="52" ht="13.95" customHeight="1"/>
+    <row r="53" ht="13.95" customHeight="1"/>
+    <row r="54" ht="13.95" customHeight="1"/>
+    <row r="55" ht="13.95" customHeight="1"/>
+    <row r="56" ht="13.95" customHeight="1"/>
+    <row r="57" ht="13.95" customHeight="1"/>
+    <row r="58" ht="13.95" customHeight="1"/>
+    <row r="59" ht="13.95" customHeight="1"/>
+    <row r="60" ht="13.95" customHeight="1"/>
+    <row r="61" ht="13.95" customHeight="1"/>
+    <row r="62" ht="13.95" customHeight="1"/>
+    <row r="63" ht="13.95" customHeight="1"/>
+    <row r="64" ht="13.95" customHeight="1"/>
+    <row r="65" ht="13.95" customHeight="1"/>
+    <row r="66" ht="13.95" customHeight="1"/>
+    <row r="67" ht="13.95" customHeight="1"/>
+    <row r="68" ht="13.95" customHeight="1"/>
+    <row r="69" ht="13.95" customHeight="1"/>
+    <row r="70" ht="13.95" customHeight="1"/>
+    <row r="71" ht="13.95" customHeight="1"/>
+    <row r="72" ht="13.95" customHeight="1"/>
+    <row r="73" ht="13.95" customHeight="1"/>
+    <row r="74" ht="13.95" customHeight="1"/>
+    <row r="75" ht="13.95" customHeight="1"/>
+    <row r="76" ht="13.95" customHeight="1"/>
+    <row r="77" ht="13.95" customHeight="1"/>
+    <row r="78" ht="13.95" customHeight="1"/>
+    <row r="79" ht="13.95" customHeight="1"/>
+    <row r="80" ht="13.95" customHeight="1"/>
+    <row r="81" ht="13.95" customHeight="1"/>
+    <row r="82" ht="13.95" customHeight="1"/>
+    <row r="83" ht="13.95" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="L4:Q4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="L21:Q21"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="L33:Q33"/>
+    <mergeCell ref="L34:Q34"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C20">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultColWidth="8.23148148148148" defaultRowHeight="14.4"/>
   <cols>
@@ -6958,12 +7780,12 @@
         <v>16</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
       <c r="F2" s="75" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
@@ -7129,7 +7951,7 @@
         <v>80</v>
       </c>
       <c r="E9" s="81" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F9" s="83"/>
       <c r="G9" s="83"/>
@@ -7170,14 +7992,14 @@
     <row r="11" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:17">
       <c r="A11" s="80"/>
       <c r="B11" s="89" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C11" s="82"/>
       <c r="D11" s="81" t="s">
         <v>80</v>
       </c>
       <c r="E11" s="81" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F11" s="83"/>
       <c r="G11" s="83"/>
@@ -7618,7 +8440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Y120"/>
@@ -7645,22 +8467,22 @@
   <sheetData>
     <row r="1" ht="35" customHeight="1" spans="1:25">
       <c r="A1" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E1" s="10"/>
     </row>
     <row r="2" ht="56" customHeight="1" spans="1:25">
       <c r="A2" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -7669,7 +8491,7 @@
     </row>
     <row r="3" ht="23" customHeight="1" spans="1:25">
       <c r="A3" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B3" s="15">
         <v>1</v>
@@ -7700,66 +8522,66 @@
     </row>
     <row r="4" s="3" customFormat="1" ht="34" customHeight="1" spans="1:25">
       <c r="A4" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
       <c r="D4" s="13"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="18"/>
       <c r="M4" s="19" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N4" s="19" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O4" s="13"/>
       <c r="P4" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="R4" s="13"/>
       <c r="S4" s="18"/>
       <c r="T4" s="19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="U4" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="V4" s="13"/>
       <c r="W4" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="X4" s="19" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Y4" s="13"/>
     </row>
     <row r="5" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:25">
       <c r="A5" s="20" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>186</v>
@@ -7769,7 +8591,7 @@
         <v>40</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>42</v>
@@ -7788,7 +8610,7 @@
         <v>40</v>
       </c>
       <c r="N5" s="23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O5" s="23" t="s">
         <v>42</v>
@@ -7807,7 +8629,7 @@
         <v>40</v>
       </c>
       <c r="U5" s="23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="V5" s="23" t="s">
         <v>42</v>
@@ -7824,7 +8646,7 @@
     </row>
     <row r="6" s="4" customFormat="1" ht="16.95" customHeight="1" spans="1:25">
       <c r="A6" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>84</v>
@@ -7835,7 +8657,7 @@
       <c r="D6" s="27"/>
       <c r="E6" s="21"/>
       <c r="F6" s="28" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>109</v>
@@ -7850,7 +8672,7 @@
       <c r="K6" s="28"/>
       <c r="L6" s="21"/>
       <c r="M6" s="28" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N6" s="28" t="s">
         <v>109</v>
@@ -7865,7 +8687,7 @@
       <c r="R6" s="28"/>
       <c r="S6" s="21"/>
       <c r="T6" s="28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="U6" s="28" t="s">
         <v>109</v>
@@ -7881,7 +8703,7 @@
     </row>
     <row r="7" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A7" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>61</v>
@@ -7892,7 +8714,7 @@
       <c r="D7" s="27"/>
       <c r="E7" s="31"/>
       <c r="F7" s="28" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>109</v>
@@ -7907,7 +8729,7 @@
       <c r="K7" s="28"/>
       <c r="L7" s="31"/>
       <c r="M7" s="28" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N7" s="28" t="s">
         <v>109</v>
@@ -7922,7 +8744,7 @@
       <c r="R7" s="28"/>
       <c r="S7" s="31"/>
       <c r="T7" s="28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="U7" s="28" t="s">
         <v>109</v>
@@ -7938,7 +8760,7 @@
     </row>
     <row r="8" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A8" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>65</v>
@@ -7949,7 +8771,7 @@
       <c r="D8" s="27"/>
       <c r="E8" s="31"/>
       <c r="F8" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>112</v>
@@ -7964,7 +8786,7 @@
       <c r="K8" s="28"/>
       <c r="L8" s="31"/>
       <c r="M8" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N8" s="28" t="s">
         <v>112</v>
@@ -7979,7 +8801,7 @@
       <c r="R8" s="28"/>
       <c r="S8" s="31"/>
       <c r="T8" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="U8" s="28" t="s">
         <v>112</v>
@@ -7995,18 +8817,18 @@
     </row>
     <row r="9" s="5" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A9" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>172</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="31"/>
       <c r="F9" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>112</v>
@@ -8015,13 +8837,13 @@
         <v>172</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J9" s="32"/>
       <c r="K9" s="28"/>
       <c r="L9" s="31"/>
       <c r="M9" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N9" s="28" t="s">
         <v>112</v>
@@ -8030,13 +8852,13 @@
         <v>172</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q9" s="32"/>
       <c r="R9" s="28"/>
       <c r="S9" s="31"/>
       <c r="T9" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="U9" s="28" t="s">
         <v>112</v>
@@ -8045,25 +8867,25 @@
         <v>172</v>
       </c>
       <c r="W9" s="30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="X9" s="32"/>
       <c r="Y9" s="28"/>
     </row>
     <row r="10" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A10" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>92</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="33"/>
       <c r="F10" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>112</v>
@@ -8072,13 +8894,13 @@
         <v>92</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J10" s="32"/>
       <c r="K10" s="28"/>
       <c r="L10" s="33"/>
       <c r="M10" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N10" s="28" t="s">
         <v>112</v>
@@ -8087,13 +8909,13 @@
         <v>92</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q10" s="32"/>
       <c r="R10" s="28"/>
       <c r="S10" s="33"/>
       <c r="T10" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="U10" s="28" t="s">
         <v>112</v>
@@ -8102,25 +8924,25 @@
         <v>92</v>
       </c>
       <c r="W10" s="30" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="X10" s="32"/>
       <c r="Y10" s="28"/>
     </row>
     <row r="11" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A11" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D11" s="34"/>
       <c r="E11" s="33"/>
       <c r="F11" s="28" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>109</v>
@@ -8135,7 +8957,7 @@
       <c r="K11" s="32"/>
       <c r="L11" s="33"/>
       <c r="M11" s="28" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N11" s="28" t="s">
         <v>109</v>
@@ -8144,55 +8966,55 @@
         <v>215</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q11" s="32"/>
       <c r="R11" s="32"/>
       <c r="S11" s="33"/>
       <c r="T11" s="28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="U11" s="28" t="s">
         <v>109</v>
       </c>
       <c r="V11" s="29" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="W11" s="30" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="X11" s="32"/>
       <c r="Y11" s="32"/>
     </row>
     <row r="12" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A12" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="33"/>
       <c r="F12" s="28" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I12" s="36" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J12" s="28"/>
       <c r="K12" s="28"/>
       <c r="L12" s="33"/>
       <c r="M12" s="28" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N12" s="28" t="s">
         <v>109</v>
@@ -8201,55 +9023,55 @@
         <v>211</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q12" s="28"/>
       <c r="R12" s="28"/>
       <c r="S12" s="33"/>
       <c r="T12" s="28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="U12" s="28" t="s">
         <v>109</v>
       </c>
       <c r="V12" s="29" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="W12" s="30" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="X12" s="28"/>
       <c r="Y12" s="28"/>
     </row>
     <row r="13" s="6" customFormat="1" ht="13.95" customHeight="1" spans="1:25">
       <c r="A13" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="33"/>
       <c r="F13" s="28" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G13" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I13" s="36" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J13" s="28"/>
       <c r="K13" s="28"/>
       <c r="L13" s="33"/>
       <c r="M13" s="28" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N13" s="28" t="s">
         <v>109</v>
@@ -8264,16 +9086,16 @@
       <c r="R13" s="28"/>
       <c r="S13" s="33"/>
       <c r="T13" s="28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="U13" s="28" t="s">
         <v>109</v>
       </c>
       <c r="V13" s="29" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="W13" s="30" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="X13" s="28"/>
       <c r="Y13" s="28"/>
@@ -8408,10 +9230,10 @@
       <c r="D17" s="13"/>
       <c r="E17" s="21"/>
       <c r="F17" s="28" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>109</v>
@@ -8421,10 +9243,10 @@
       <c r="K17" s="40"/>
       <c r="L17" s="21"/>
       <c r="M17" s="28" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N17" s="28" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O17" s="29" t="s">
         <v>109</v>
@@ -8434,10 +9256,10 @@
       <c r="R17" s="40"/>
       <c r="S17" s="21"/>
       <c r="T17" s="28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="U17" s="28" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="V17" s="29" t="s">
         <v>109</v>
@@ -8453,53 +9275,53 @@
       <c r="D18" s="21"/>
       <c r="E18" s="21"/>
       <c r="F18" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H18" s="29" t="s">
         <v>112</v>
       </c>
       <c r="I18" s="30" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J18" s="45" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K18" s="40"/>
       <c r="L18" s="21"/>
       <c r="M18" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O18" s="29" t="s">
         <v>112</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q18" s="45" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="R18" s="40"/>
       <c r="S18" s="21"/>
       <c r="T18" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="U18" s="28" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="V18" s="29" t="s">
         <v>112</v>
       </c>
       <c r="W18" s="30" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="X18" s="45" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Y18" s="40"/>
     </row>
@@ -8570,7 +9392,7 @@
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="47" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G21" s="39"/>
       <c r="H21" s="39"/>
@@ -8579,7 +9401,7 @@
       <c r="K21" s="40"/>
       <c r="L21" s="16"/>
       <c r="M21" s="47" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N21" s="39"/>
       <c r="O21" s="39"/>
@@ -8588,7 +9410,7 @@
       <c r="R21" s="40"/>
       <c r="S21" s="16"/>
       <c r="T21" s="47" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="U21" s="39"/>
       <c r="V21" s="39"/>
@@ -8599,7 +9421,7 @@
     <row r="22" ht="13.95" customHeight="1"/>
     <row r="23" ht="13.95" customHeight="1" spans="1:25">
       <c r="A23" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B23" s="15">
         <v>2</v>
@@ -8616,24 +9438,24 @@
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:25">
       <c r="A24" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="13"/>
       <c r="E24" s="18"/>
       <c r="F24" s="19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K24" s="13"/>
       <c r="M24" s="48"/>
@@ -8643,13 +9465,13 @@
     </row>
     <row r="25" ht="29" customHeight="1" spans="1:25">
       <c r="A25" s="20" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>186</v>
@@ -8659,7 +9481,7 @@
         <v>40</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H25" s="23" t="s">
         <v>42</v>
@@ -8682,7 +9504,7 @@
     </row>
     <row r="26" ht="13.95" customHeight="1" spans="1:25">
       <c r="A26" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B26" s="52" t="s">
         <v>84</v>
@@ -8697,7 +9519,7 @@
       <c r="H26" s="29"/>
       <c r="I26" s="30"/>
       <c r="J26" s="178" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K26" s="28"/>
       <c r="M26" s="53"/>
@@ -8709,13 +9531,13 @@
     </row>
     <row r="27" ht="13.95" customHeight="1" spans="1:25">
       <c r="A27" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="21"/>
@@ -8723,10 +9545,10 @@
       <c r="G27" s="28"/>
       <c r="H27" s="29"/>
       <c r="I27" s="30" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K27" s="28"/>
       <c r="M27" s="53"/>
@@ -8738,27 +9560,27 @@
     </row>
     <row r="28" ht="13.95" customHeight="1" spans="1:25">
       <c r="A28" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B28" s="52" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="31"/>
       <c r="F28" s="28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G28" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I28" s="30" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J28" s="28"/>
       <c r="K28" s="28"/>
@@ -8771,16 +9593,16 @@
     </row>
     <row r="29" ht="13.95" customHeight="1" spans="1:25">
       <c r="A29" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B29" s="52" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E29" s="31"/>
       <c r="F29" s="28"/>
@@ -8788,7 +9610,7 @@
       <c r="H29" s="29"/>
       <c r="I29" s="30"/>
       <c r="J29" s="178" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K29" s="28"/>
       <c r="M29" s="53"/>
@@ -8800,27 +9622,27 @@
     </row>
     <row r="30" ht="13.95" customHeight="1" spans="1:25">
       <c r="A30" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B30" s="52" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D30" s="34"/>
       <c r="E30" s="33"/>
       <c r="F30" s="28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G30" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I30" s="30" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J30" s="32"/>
       <c r="K30" s="28"/>
@@ -8833,27 +9655,27 @@
     </row>
     <row r="31" ht="13.95" customHeight="1" spans="1:25">
       <c r="A31" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B31" s="52" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D31" s="34"/>
       <c r="E31" s="33"/>
       <c r="F31" s="28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G31" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I31" s="30" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J31" s="28"/>
       <c r="K31" s="28"/>
@@ -8866,18 +9688,18 @@
     </row>
     <row r="32" ht="13.95" customHeight="1" spans="1:25">
       <c r="A32" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B32" s="52" t="s">
         <v>172</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D32" s="34"/>
       <c r="E32" s="33"/>
       <c r="F32" s="28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G32" s="28" t="s">
         <v>109</v>
@@ -8886,7 +9708,7 @@
         <v>172</v>
       </c>
       <c r="I32" s="30" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
@@ -8899,18 +9721,18 @@
     </row>
     <row r="33" ht="13.95" customHeight="1" spans="1:18">
       <c r="A33" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B33" s="52" t="s">
         <v>170</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D33" s="34"/>
       <c r="E33" s="33"/>
       <c r="F33" s="28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G33" s="28" t="s">
         <v>109</v>
@@ -8919,7 +9741,7 @@
         <v>170</v>
       </c>
       <c r="I33" s="30" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J33" s="28"/>
       <c r="K33" s="28"/>
@@ -8932,18 +9754,18 @@
     </row>
     <row r="34" ht="13.95" customHeight="1" spans="1:18">
       <c r="A34" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B34" s="52" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D34" s="34"/>
       <c r="E34" s="33"/>
       <c r="F34" s="28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G34" s="28" t="s">
         <v>109</v>
@@ -8965,13 +9787,13 @@
     </row>
     <row r="35" ht="13.95" customHeight="1" spans="1:18">
       <c r="A35" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B35" s="52" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D35" s="34"/>
       <c r="E35" s="33"/>
@@ -8980,10 +9802,10 @@
       <c r="H35" s="29"/>
       <c r="I35" s="30"/>
       <c r="J35" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K35" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M35" s="53"/>
       <c r="N35" s="53"/>
@@ -8994,13 +9816,13 @@
     </row>
     <row r="36" ht="13.95" customHeight="1" spans="1:18">
       <c r="A36" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B36" s="52" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D36" s="34"/>
       <c r="E36" s="33"/>
@@ -9009,10 +9831,10 @@
       <c r="H36" s="29"/>
       <c r="I36" s="30"/>
       <c r="J36" s="178" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K36" s="28" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M36" s="53"/>
       <c r="N36" s="53"/>
@@ -9023,13 +9845,13 @@
     </row>
     <row r="37" ht="13.95" customHeight="1" spans="1:18">
       <c r="A37" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B37" s="52" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D37" s="34"/>
       <c r="E37" s="33"/>
@@ -9038,10 +9860,10 @@
       <c r="H37" s="29"/>
       <c r="I37" s="30"/>
       <c r="J37" s="28" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K37" s="28" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M37" s="53"/>
       <c r="N37" s="53"/>
@@ -9052,16 +9874,16 @@
     </row>
     <row r="38" ht="13.95" customHeight="1" spans="1:18">
       <c r="A38" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B38" s="52" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E38" s="33"/>
       <c r="F38" s="28"/>
@@ -9069,7 +9891,7 @@
       <c r="H38" s="29"/>
       <c r="I38" s="30"/>
       <c r="J38" s="28" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K38" s="28"/>
       <c r="M38" s="53"/>
@@ -9081,16 +9903,16 @@
     </row>
     <row r="39" ht="13.95" customHeight="1" spans="1:18">
       <c r="A39" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B39" s="52" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E39" s="33"/>
       <c r="F39" s="28"/>
@@ -9098,7 +9920,7 @@
       <c r="H39" s="29"/>
       <c r="I39" s="30"/>
       <c r="J39" s="28" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K39" s="28"/>
       <c r="M39" s="53"/>
@@ -9110,13 +9932,13 @@
     </row>
     <row r="40" ht="13.95" customHeight="1" spans="1:18">
       <c r="A40" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B40" s="52" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D40" s="34"/>
       <c r="E40" s="33"/>
@@ -9125,10 +9947,10 @@
       <c r="H40" s="29"/>
       <c r="I40" s="30"/>
       <c r="J40" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K40" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M40" s="53"/>
       <c r="N40" s="53"/>
@@ -9139,10 +9961,10 @@
     </row>
     <row r="41" ht="13.95" customHeight="1" spans="1:18">
       <c r="A41" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B41" s="52" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C41" s="27" t="s">
         <v>212</v>
@@ -9154,10 +9976,10 @@
       <c r="H41" s="29"/>
       <c r="I41" s="30"/>
       <c r="J41" s="178" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K41" s="28" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M41" s="53"/>
       <c r="N41" s="53"/>
@@ -9168,13 +9990,13 @@
     </row>
     <row r="42" ht="13.95" customHeight="1" spans="1:18">
       <c r="A42" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B42" s="52" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D42" s="27"/>
       <c r="E42" s="33"/>
@@ -9183,10 +10005,10 @@
       <c r="H42" s="29"/>
       <c r="I42" s="30"/>
       <c r="J42" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K42" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M42" s="53"/>
       <c r="N42" s="53"/>
@@ -9197,13 +10019,13 @@
     </row>
     <row r="43" ht="13.95" customHeight="1" spans="1:18">
       <c r="A43" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B43" s="52" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="33"/>
@@ -9212,10 +10034,10 @@
       <c r="H43" s="29"/>
       <c r="I43" s="30"/>
       <c r="J43" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K43" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M43" s="53"/>
       <c r="N43" s="53"/>
@@ -9226,13 +10048,13 @@
     </row>
     <row r="44" ht="13.95" customHeight="1" spans="1:18">
       <c r="A44" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B44" s="52" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D44" s="27"/>
       <c r="E44" s="33"/>
@@ -9241,10 +10063,10 @@
       <c r="H44" s="29"/>
       <c r="I44" s="30"/>
       <c r="J44" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K44" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M44" s="53"/>
       <c r="N44" s="53"/>
@@ -9255,13 +10077,13 @@
     </row>
     <row r="45" ht="13.95" customHeight="1" spans="1:18">
       <c r="A45" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B45" s="52" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D45" s="27"/>
       <c r="E45" s="33"/>
@@ -9270,10 +10092,10 @@
       <c r="H45" s="29"/>
       <c r="I45" s="30"/>
       <c r="J45" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K45" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M45" s="53"/>
       <c r="N45" s="53"/>
@@ -9284,10 +10106,10 @@
     </row>
     <row r="46" ht="13.95" customHeight="1" spans="1:18">
       <c r="A46" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B46" s="52" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C46" s="27" t="s">
         <v>45</v>
@@ -9299,10 +10121,10 @@
       <c r="H46" s="29"/>
       <c r="I46" s="30"/>
       <c r="J46" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K46" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M46" s="53"/>
       <c r="N46" s="53"/>
@@ -9313,13 +10135,13 @@
     </row>
     <row r="47" ht="13.95" customHeight="1" spans="1:18">
       <c r="A47" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B47" s="52" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D47" s="27"/>
       <c r="E47" s="33"/>
@@ -9328,10 +10150,10 @@
       <c r="H47" s="29"/>
       <c r="I47" s="30"/>
       <c r="J47" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K47" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M47" s="53"/>
       <c r="N47" s="53"/>
@@ -9342,13 +10164,13 @@
     </row>
     <row r="48" ht="13.95" customHeight="1" spans="1:18">
       <c r="A48" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B48" s="52" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D48" s="27"/>
       <c r="E48" s="33"/>
@@ -9357,10 +10179,10 @@
       <c r="H48" s="29"/>
       <c r="I48" s="30"/>
       <c r="J48" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K48" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M48" s="53"/>
       <c r="N48" s="53"/>
@@ -9371,13 +10193,13 @@
     </row>
     <row r="49" ht="13.95" customHeight="1" spans="1:18">
       <c r="A49" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B49" s="52" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D49" s="27"/>
       <c r="E49" s="33"/>
@@ -9386,10 +10208,10 @@
       <c r="H49" s="29"/>
       <c r="I49" s="30"/>
       <c r="J49" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K49" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M49" s="53"/>
       <c r="N49" s="53"/>
@@ -9400,13 +10222,13 @@
     </row>
     <row r="50" ht="13.95" customHeight="1" spans="1:18">
       <c r="A50" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B50" s="52" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D50" s="27"/>
       <c r="E50" s="33"/>
@@ -9415,10 +10237,10 @@
       <c r="H50" s="29"/>
       <c r="I50" s="30"/>
       <c r="J50" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K50" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M50" s="53"/>
       <c r="N50" s="53"/>
@@ -9429,13 +10251,13 @@
     </row>
     <row r="51" ht="13.95" customHeight="1" spans="1:18">
       <c r="A51" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B51" s="52" t="s">
         <v>61</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D51" s="27"/>
       <c r="E51" s="33"/>
@@ -9444,10 +10266,10 @@
       <c r="H51" s="29"/>
       <c r="I51" s="30"/>
       <c r="J51" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K51" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M51" s="53"/>
       <c r="N51" s="53"/>
@@ -9458,13 +10280,13 @@
     </row>
     <row r="52" ht="13.95" customHeight="1" spans="1:18">
       <c r="A52" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B52" s="52" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D52" s="34"/>
       <c r="E52" s="33"/>
@@ -9473,10 +10295,10 @@
       <c r="H52" s="29"/>
       <c r="I52" s="30"/>
       <c r="J52" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K52" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M52" s="53"/>
       <c r="N52" s="53"/>
@@ -9487,13 +10309,13 @@
     </row>
     <row r="53" ht="13.95" customHeight="1" spans="1:18">
       <c r="A53" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B53" s="52" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D53" s="27"/>
       <c r="E53" s="33"/>
@@ -9502,10 +10324,10 @@
       <c r="H53" s="29"/>
       <c r="I53" s="30"/>
       <c r="J53" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K53" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M53" s="53"/>
       <c r="N53" s="53"/>
@@ -9516,13 +10338,13 @@
     </row>
     <row r="54" ht="13.95" customHeight="1" spans="1:18">
       <c r="A54" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B54" s="52" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D54" s="27"/>
       <c r="E54" s="33"/>
@@ -9531,10 +10353,10 @@
       <c r="H54" s="29"/>
       <c r="I54" s="30"/>
       <c r="J54" s="178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K54" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M54" s="53"/>
       <c r="N54" s="53"/>
@@ -9545,13 +10367,13 @@
     </row>
     <row r="55" ht="13.95" customHeight="1" spans="1:18">
       <c r="A55" s="56" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B55" s="57" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C55" s="58" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D55" s="58"/>
       <c r="E55" s="59"/>
@@ -9560,10 +10382,10 @@
       <c r="H55" s="61"/>
       <c r="I55" s="62"/>
       <c r="J55" s="179" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K55" s="60" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M55" s="53"/>
       <c r="N55" s="53"/>
@@ -9574,13 +10396,13 @@
     </row>
     <row r="56" ht="13.95" customHeight="1" spans="1:18">
       <c r="A56" s="56" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B56" s="57" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C56" s="58" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D56" s="58"/>
       <c r="E56" s="59"/>
@@ -9592,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="60" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M56" s="53"/>
       <c r="N56" s="53"/>
@@ -9658,10 +10480,10 @@
       <c r="D59" s="13"/>
       <c r="E59" s="21"/>
       <c r="F59" s="28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H59" s="29" t="s">
         <v>109</v>
@@ -9716,7 +10538,7 @@
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
       <c r="F62" s="47" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G62" s="39"/>
       <c r="H62" s="39"/>
@@ -9728,7 +10550,7 @@
     <row r="63" ht="13.95" customHeight="1"/>
     <row r="64" ht="25" customHeight="1" spans="1:18">
       <c r="A64" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B64" s="15">
         <v>3</v>
@@ -9745,36 +10567,36 @@
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:11">
       <c r="A65" s="17" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
       <c r="D65" s="13"/>
       <c r="E65" s="18"/>
       <c r="F65" s="19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J65" s="19" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K65" s="13"/>
     </row>
     <row r="66" ht="37" customHeight="1" spans="1:11">
       <c r="A66" s="20" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D66" s="20" t="s">
         <v>186</v>
@@ -9784,7 +10606,7 @@
         <v>40</v>
       </c>
       <c r="G66" s="23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H66" s="23" t="s">
         <v>42</v>
@@ -9801,7 +10623,7 @@
     </row>
     <row r="67" ht="13.95" customHeight="1" spans="1:11">
       <c r="A67" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B67" s="52" t="s">
         <v>84</v>
@@ -9812,7 +10634,7 @@
       <c r="D67" s="34"/>
       <c r="E67" s="33"/>
       <c r="F67" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G67" s="28" t="s">
         <v>109</v>
@@ -9828,13 +10650,13 @@
     </row>
     <row r="68" ht="13.95" customHeight="1" spans="1:11">
       <c r="A68" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B68" s="52" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C68" s="27" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D68" s="27"/>
       <c r="E68" s="21"/>
@@ -9842,137 +10664,137 @@
       <c r="G68" s="28"/>
       <c r="H68" s="29"/>
       <c r="I68" s="30" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J68" s="28" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K68" s="28"/>
     </row>
     <row r="69" ht="13.95" customHeight="1" spans="1:11">
       <c r="A69" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B69" s="52" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D69" s="27"/>
       <c r="E69" s="31"/>
       <c r="F69" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G69" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H69" s="52" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I69" s="27" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J69" s="28"/>
       <c r="K69" s="28"/>
     </row>
     <row r="70" ht="13.95" customHeight="1" spans="1:11">
       <c r="A70" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B70" s="52" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D70" s="34" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E70" s="31"/>
       <c r="F70" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G70" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H70" s="52" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I70" s="34" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J70" s="28"/>
       <c r="K70" s="28"/>
     </row>
     <row r="71" ht="13.95" customHeight="1" spans="1:11">
       <c r="A71" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B71" s="52" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D71" s="34"/>
       <c r="E71" s="33"/>
       <c r="F71" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G71" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H71" s="52" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I71" s="34" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J71" s="32"/>
       <c r="K71" s="28"/>
     </row>
     <row r="72" ht="13.95" customHeight="1" spans="1:11">
       <c r="A72" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B72" s="52" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D72" s="34"/>
       <c r="E72" s="33"/>
       <c r="F72" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G72" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H72" s="52" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I72" s="34" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J72" s="28"/>
       <c r="K72" s="28"/>
     </row>
     <row r="73" ht="13.95" customHeight="1" spans="1:11">
       <c r="A73" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B73" s="52" t="s">
         <v>172</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D73" s="34"/>
       <c r="E73" s="33"/>
       <c r="F73" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G73" s="28" t="s">
         <v>109</v>
@@ -9981,25 +10803,25 @@
         <v>172</v>
       </c>
       <c r="I73" s="34" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J73" s="28"/>
       <c r="K73" s="28"/>
     </row>
     <row r="74" ht="13.95" customHeight="1" spans="1:11">
       <c r="A74" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B74" s="52" t="s">
         <v>170</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D74" s="34"/>
       <c r="E74" s="33"/>
       <c r="F74" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G74" s="28" t="s">
         <v>109</v>
@@ -10008,214 +10830,214 @@
         <v>170</v>
       </c>
       <c r="I74" s="34" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J74" s="28"/>
       <c r="K74" s="28"/>
     </row>
     <row r="75" ht="13.95" customHeight="1" spans="1:11">
       <c r="A75" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B75" s="52" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D75" s="34"/>
       <c r="E75" s="33"/>
       <c r="F75" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G75" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H75" s="52" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I75" s="34" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J75" s="28"/>
       <c r="K75" s="28"/>
     </row>
     <row r="76" ht="13.95" customHeight="1" spans="1:11">
       <c r="A76" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B76" s="52" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D76" s="34"/>
       <c r="E76" s="33"/>
       <c r="F76" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G76" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H76" s="52" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I76" s="34" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J76" s="28"/>
       <c r="K76" s="28"/>
     </row>
     <row r="77" ht="13.95" customHeight="1" spans="1:11">
       <c r="A77" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B77" s="52" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D77" s="34"/>
       <c r="E77" s="33"/>
       <c r="F77" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G77" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H77" s="52" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I77" s="34" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J77" s="28"/>
       <c r="K77" s="28"/>
     </row>
     <row r="78" ht="13.95" customHeight="1" spans="1:11">
       <c r="A78" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B78" s="52" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D78" s="34"/>
       <c r="E78" s="33"/>
       <c r="F78" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G78" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H78" s="52" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I78" s="34" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J78" s="28"/>
       <c r="K78" s="28"/>
     </row>
     <row r="79" ht="13.95" customHeight="1" spans="1:11">
       <c r="A79" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B79" s="52" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D79" s="34" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E79" s="33"/>
       <c r="F79" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G79" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H79" s="52" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I79" s="34" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J79" s="28"/>
       <c r="K79" s="28"/>
     </row>
     <row r="80" ht="13.95" customHeight="1" spans="1:11">
       <c r="A80" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B80" s="52" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C80" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D80" s="34" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E80" s="33"/>
       <c r="F80" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G80" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H80" s="52" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I80" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J80" s="28" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K80" s="28" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="81" ht="13.95" customHeight="1" spans="1:11">
       <c r="A81" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B81" s="52" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D81" s="34"/>
       <c r="E81" s="33"/>
       <c r="F81" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G81" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H81" s="52" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I81" s="34" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J81" s="28"/>
       <c r="K81" s="28"/>
     </row>
     <row r="82" ht="13.95" customHeight="1" spans="1:11">
       <c r="A82" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B82" s="52" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C82" s="27" t="s">
         <v>212</v>
@@ -10223,13 +11045,13 @@
       <c r="D82" s="27"/>
       <c r="E82" s="33"/>
       <c r="F82" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G82" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H82" s="52" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I82" s="27" t="s">
         <v>212</v>
@@ -10239,118 +11061,118 @@
     </row>
     <row r="83" ht="13.95" customHeight="1" spans="1:11">
       <c r="A83" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B83" s="52" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C83" s="27" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="33"/>
       <c r="F83" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G83" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H83" s="52" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I83" s="27" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J83" s="28"/>
       <c r="K83" s="28"/>
     </row>
     <row r="84" ht="13.95" customHeight="1" spans="1:11">
       <c r="A84" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B84" s="52" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C84" s="27" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="33"/>
       <c r="F84" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G84" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H84" s="52" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I84" s="27" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J84" s="28"/>
       <c r="K84" s="28"/>
     </row>
     <row r="85" ht="13.95" customHeight="1" spans="1:11">
       <c r="A85" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B85" s="52" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C85" s="27" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D85" s="27"/>
       <c r="E85" s="33"/>
       <c r="F85" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G85" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H85" s="52" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I85" s="27" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J85" s="28"/>
       <c r="K85" s="28"/>
     </row>
     <row r="86" ht="13.95" customHeight="1" spans="1:11">
       <c r="A86" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B86" s="52" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C86" s="27" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D86" s="27"/>
       <c r="E86" s="33"/>
       <c r="F86" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G86" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H86" s="52" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="I86" s="27" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J86" s="28"/>
       <c r="K86" s="28"/>
     </row>
     <row r="87" ht="13.95" customHeight="1" spans="1:11">
       <c r="A87" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B87" s="52" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C87" s="27" t="s">
         <v>45</v>
@@ -10358,13 +11180,13 @@
       <c r="D87" s="27"/>
       <c r="E87" s="33"/>
       <c r="F87" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G87" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H87" s="52" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I87" s="27" t="s">
         <v>45</v>
@@ -10374,126 +11196,126 @@
     </row>
     <row r="88" ht="13.95" customHeight="1" spans="1:11">
       <c r="A88" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B88" s="52" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C88" s="27" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D88" s="27"/>
       <c r="E88" s="33"/>
       <c r="F88" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G88" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H88" s="52" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I88" s="27" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J88" s="28"/>
       <c r="K88" s="28"/>
     </row>
     <row r="89" ht="13.95" customHeight="1" spans="1:11">
       <c r="A89" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B89" s="52" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C89" s="27" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D89" s="27"/>
       <c r="E89" s="33"/>
       <c r="F89" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G89" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H89" s="52" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I89" s="27" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J89" s="28"/>
       <c r="K89" s="28"/>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B90" s="52" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C90" s="27" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D90" s="27"/>
       <c r="E90" s="33"/>
       <c r="F90" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G90" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H90" s="52" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I90" s="27" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J90" s="28"/>
       <c r="K90" s="28"/>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B91" s="52" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C91" s="27" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D91" s="27"/>
       <c r="E91" s="33"/>
       <c r="F91" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G91" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H91" s="52" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I91" s="27" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J91" s="28"/>
       <c r="K91" s="28"/>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B92" s="52" t="s">
         <v>61</v>
       </c>
       <c r="C92" s="27" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D92" s="27"/>
       <c r="E92" s="33"/>
       <c r="F92" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G92" s="28" t="s">
         <v>109</v>
@@ -10502,148 +11324,148 @@
         <v>61</v>
       </c>
       <c r="I92" s="27" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J92" s="28"/>
       <c r="K92" s="28"/>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B93" s="52" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D93" s="34"/>
       <c r="E93" s="33"/>
       <c r="F93" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G93" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H93" s="52" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I93" s="34" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J93" s="28"/>
       <c r="K93" s="28"/>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B94" s="52" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C94" s="27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D94" s="27"/>
       <c r="E94" s="33"/>
       <c r="F94" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G94" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H94" s="52" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I94" s="27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J94" s="28"/>
       <c r="K94" s="28"/>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B95" s="52" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C95" s="27" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D95" s="27"/>
       <c r="E95" s="33"/>
       <c r="F95" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G95" s="28" t="s">
         <v>109</v>
       </c>
       <c r="H95" s="52" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="I95" s="27" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J95" s="28"/>
       <c r="K95" s="28"/>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="56" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B96" s="57" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C96" s="58" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D96" s="58"/>
       <c r="E96" s="59"/>
       <c r="F96" s="60" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G96" s="60" t="s">
         <v>109</v>
       </c>
       <c r="H96" s="57" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="I96" s="58" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J96" s="60"/>
       <c r="K96" s="60" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="56" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B97" s="57" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C97" s="58" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D97" s="58"/>
       <c r="E97" s="59"/>
       <c r="F97" s="60" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G97" s="60" t="s">
         <v>109</v>
       </c>
       <c r="H97" s="57" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I97" s="58" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J97" s="60"/>
       <c r="K97" s="60" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -10697,10 +11519,10 @@
       <c r="D100" s="13"/>
       <c r="E100" s="21"/>
       <c r="F100" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G100" s="28" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H100" s="29" t="s">
         <v>109</v>
@@ -10744,7 +11566,7 @@
       <c r="D103" s="16"/>
       <c r="E103" s="16"/>
       <c r="F103" s="47" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G103" s="39"/>
       <c r="H103" s="39"/>
@@ -10754,7 +11576,7 @@
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:11">
       <c r="A105" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B105" s="15">
         <v>4</v>
@@ -10771,36 +11593,36 @@
     </row>
     <row r="106" ht="27" customHeight="1" spans="1:11">
       <c r="A106" s="17" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
       <c r="D106" s="13"/>
       <c r="E106" s="18"/>
       <c r="F106" s="19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H106" s="13"/>
       <c r="I106" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J106" s="19" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K106" s="13"/>
     </row>
     <row r="107" ht="25" customHeight="1" spans="1:11">
       <c r="A107" s="20" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>186</v>
@@ -10810,7 +11632,7 @@
         <v>40</v>
       </c>
       <c r="G107" s="23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H107" s="23" t="s">
         <v>42</v>
@@ -10827,16 +11649,16 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B108" s="26" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E108" s="33"/>
       <c r="F108" s="28"/>
@@ -10844,51 +11666,51 @@
       <c r="H108" s="52"/>
       <c r="I108" s="34"/>
       <c r="J108" s="178" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K108" s="28"/>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B109" s="26" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C109" s="27" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D109" s="27"/>
       <c r="E109" s="33"/>
       <c r="F109" s="28" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G109" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H109" s="52" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I109" s="27" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J109" s="28"/>
       <c r="K109" s="28"/>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B110" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C110" s="27" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D110" s="27"/>
       <c r="E110" s="33"/>
       <c r="F110" s="28" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G110" s="28" t="s">
         <v>112</v>
@@ -10904,54 +11726,54 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B111" s="26" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D111" s="34"/>
       <c r="E111" s="33"/>
       <c r="F111" s="28" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G111" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H111" s="52" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I111" s="34" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J111" s="28"/>
       <c r="K111" s="28"/>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C112" s="27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D112" s="27"/>
       <c r="E112" s="33"/>
       <c r="F112" s="28" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G112" s="28" t="s">
         <v>112</v>
       </c>
       <c r="H112" s="52" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I112" s="27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J112" s="28"/>
       <c r="K112" s="28"/>
@@ -11007,10 +11829,10 @@
       <c r="D115" s="13"/>
       <c r="E115" s="21"/>
       <c r="F115" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="G115" s="28" t="s">
         <v>282</v>
-      </c>
-      <c r="G115" s="28" t="s">
-        <v>280</v>
       </c>
       <c r="H115" s="29" t="s">
         <v>109</v>
@@ -11026,17 +11848,17 @@
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="28" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G116" s="28" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H116" s="29" t="s">
         <v>112</v>
       </c>
       <c r="I116" s="30"/>
       <c r="J116" s="45" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K116" s="40"/>
     </row>
@@ -11088,7 +11910,7 @@
       <c r="D120" s="16"/>
       <c r="E120" s="16"/>
       <c r="F120" s="47" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G120" s="39"/>
       <c r="H120" s="39"/>
@@ -11186,7 +12008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet690"/>
   <dimension ref="A1:D12"/>
@@ -11200,102 +12022,102 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -11303,7 +12125,7 @@
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -11311,7 +12133,7 @@
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
